--- a/Översikt MELLERUD.xlsx
+++ b/Översikt MELLERUD.xlsx
@@ -601,7 +601,7 @@
         <v>46184</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>46112</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>45614</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>44840</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>45614</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>45734</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>45670</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>46020</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>45253</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>44963</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>45006</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 28216-2026</t>
+          <t>A 25764-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46196</v>
+        <v>45804</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1880,27 +1880,22 @@
       <c r="G13" t="inlineStr">
         <is>
           <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I13" t="n">
         <v>2.5</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>1</v>
@@ -1912,21 +1907,134 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
       </c>
       <c r="T13" t="n">
+        <v>5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Guldlockmossa
+Lönnlav
+Rostfläck</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 25764-2025 artfynd.xlsx", "A 25764-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 25764-2025 karta.png", "A 25764-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 25764-2025 georefererad karta.tif", "A 25764-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 25764-2025 FSC-klagomål.docx", "A 25764-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 25764-2025 FSC-klagomål mail.docx", "A 25764-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 25764-2025 tillsynsbegäran.docx", "A 25764-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 25764-2025 tillsynsbegäran mail.docx", "A 25764-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 28216-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>46196</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2</v>
+      </c>
+      <c r="S14" t="n">
         <v>4</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Gulvit blekspik
@@ -1934,112 +2042,112 @@
 Gröngöling</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 28216-2026 artfynd.xlsx", "A 28216-2026")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 28216-2026 karta.png", "A 28216-2026")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 28216-2026 georefererad karta.tif", "A 28216-2026")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 28216-2026 FSC-klagomål.docx", "A 28216-2026")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 28216-2026 FSC-klagomål mail.docx", "A 28216-2026")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 28216-2026 tillsynsbegäran.docx", "A 28216-2026")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 28216-2026 tillsynsbegäran mail.docx", "A 28216-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>A 33141-2026</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
         <v>46244</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
+      <c r="E15" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t>Övriga Aktiebolag</t>
         </is>
       </c>
-      <c r="I14" t="n">
+      <c r="I15" t="n">
         <v>5.9</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J15" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K15" t="n">
         <v>3</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
         <v>1</v>
       </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>4</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T15" t="n">
         <v>7</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U15" t="n">
         <v>7</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Kattfotslav
 Grön sköldmossa
@@ -2047,143 +2155,35 @@
 Mandelriska</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 33141-2026 artfynd.xlsx", "A 33141-2026")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 33141-2026 karta.png", "A 33141-2026")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 33141-2026 georefererad karta.tif", "A 33141-2026")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 33141-2026 FSC-klagomål.docx", "A 33141-2026")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 33141-2026 FSC-klagomål mail.docx", "A 33141-2026")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 33141-2026 tillsynsbegäran.docx", "A 33141-2026")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 33141-2026 tillsynsbegäran mail.docx", "A 33141-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 25764-2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45804</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" t="n">
-        <v>4</v>
-      </c>
-      <c r="T15" t="n">
-        <v>5</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Guldlockmossa
-Lönnlav
-Rostfläck</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 25764-2025 artfynd.xlsx", "A 25764-2025")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 25764-2025 karta.png", "A 25764-2025")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 25764-2025 georefererad karta.tif", "A 25764-2025")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 25764-2025 FSC-klagomål.docx", "A 25764-2025")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 25764-2025 FSC-klagomål mail.docx", "A 25764-2025")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 25764-2025 tillsynsbegäran.docx", "A 25764-2025")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 25764-2025 tillsynsbegäran mail.docx", "A 25764-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>46020</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>45390</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>44896</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>44804</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>44750</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 43349-2024</t>
+          <t>A 10814-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2740,10 +2740,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45568</v>
+        <v>45369</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2755,8 +2755,13 @@
           <t>MELLERUD</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>4.1</v>
+        <v>6.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2765,10 +2770,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2783,7 +2788,7 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2792,687 +2797,682 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Brunfläckig pärlemorfjäril</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 10814-2024 artfynd.xlsx", "A 10814-2024")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 10814-2024 karta.png", "A 10814-2024")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 10814-2024 georefererad karta.tif", "A 10814-2024")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 10814-2024 FSC-klagomål.docx", "A 10814-2024")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 10814-2024 FSC-klagomål mail.docx", "A 10814-2024")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 10814-2024 tillsynsbegäran.docx", "A 10814-2024")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 10814-2024 tillsynsbegäran mail.docx", "A 10814-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 23546-2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
         <v>1</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 23546-2026 artfynd.xlsx", "A 23546-2026")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 23546-2026 karta.png", "A 23546-2026")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 23546-2026 georefererad karta.tif", "A 23546-2026")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 23546-2026 FSC-klagomål.docx", "A 23546-2026")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 23546-2026 FSC-klagomål mail.docx", "A 23546-2026")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 23546-2026 tillsynsbegäran.docx", "A 23546-2026")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 23546-2026 tillsynsbegäran mail.docx", "A 23546-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 43531-2025</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>45911</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>8</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 43531-2025 artfynd.xlsx", "A 43531-2025")</f>
+        <v/>
+      </c>
+      <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 43531-2025 karta.png", "A 43531-2025")</f>
+        <v/>
+      </c>
+      <c r="Y23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 43531-2025 georefererad karta.tif", "A 43531-2025")</f>
+        <v/>
+      </c>
+      <c r="AA23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 43531-2025 FSC-klagomål.docx", "A 43531-2025")</f>
+        <v/>
+      </c>
+      <c r="AB23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 43531-2025 FSC-klagomål mail.docx", "A 43531-2025")</f>
+        <v/>
+      </c>
+      <c r="AC23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 43531-2025 tillsynsbegäran.docx", "A 43531-2025")</f>
+        <v/>
+      </c>
+      <c r="AD23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 43531-2025 tillsynsbegäran mail.docx", "A 43531-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 26518-2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Rotfingersvamp</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 26518-2026 artfynd.xlsx", "A 26518-2026")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 26518-2026 karta.png", "A 26518-2026")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 26518-2026 georefererad karta.tif", "A 26518-2026")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 26518-2026 FSC-klagomål.docx", "A 26518-2026")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 26518-2026 FSC-klagomål mail.docx", "A 26518-2026")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 26518-2026 tillsynsbegäran.docx", "A 26518-2026")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 26518-2026 tillsynsbegäran mail.docx", "A 26518-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 8169-2023</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>44974</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Älg</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 8169-2023 artfynd.xlsx", "A 8169-2023")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 8169-2023 karta.png", "A 8169-2023")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 8169-2023 georefererad karta.tif", "A 8169-2023")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 8169-2023 FSC-klagomål.docx", "A 8169-2023")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 8169-2023 FSC-klagomål mail.docx", "A 8169-2023")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 8169-2023 tillsynsbegäran.docx", "A 8169-2023")</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 8169-2023 tillsynsbegäran mail.docx", "A 8169-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A 43349-2024</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>45568</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 43349-2024 artfynd.xlsx", "A 43349-2024")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 43349-2024 karta.png", "A 43349-2024")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 43349-2024 georefererad karta.tif", "A 43349-2024")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 43349-2024 FSC-klagomål.docx", "A 43349-2024")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 43349-2024 FSC-klagomål mail.docx", "A 43349-2024")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 43349-2024 tillsynsbegäran.docx", "A 43349-2024")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 43349-2024 tillsynsbegäran mail.docx", "A 43349-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 8169-2023</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>44974</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 3992-2023</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>44952</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J27" t="n">
         <v>1</v>
       </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
         <v>1</v>
       </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
+      <c r="T27" t="n">
         <v>1</v>
       </c>
-      <c r="T22" t="n">
-        <v>1</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Älg</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 8169-2023 artfynd.xlsx", "A 8169-2023")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 8169-2023 karta.png", "A 8169-2023")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 8169-2023 georefererad karta.tif", "A 8169-2023")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 8169-2023 FSC-klagomål.docx", "A 8169-2023")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 8169-2023 FSC-klagomål mail.docx", "A 8169-2023")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 8169-2023 tillsynsbegäran.docx", "A 8169-2023")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 8169-2023 tillsynsbegäran mail.docx", "A 8169-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 10814-2024</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>45369</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1</v>
-      </c>
-      <c r="S23" t="n">
-        <v>1</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Brunfläckig pärlemorfjäril</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 10814-2024 artfynd.xlsx", "A 10814-2024")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 10814-2024 karta.png", "A 10814-2024")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 10814-2024 georefererad karta.tif", "A 10814-2024")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 10814-2024 FSC-klagomål.docx", "A 10814-2024")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 10814-2024 FSC-klagomål mail.docx", "A 10814-2024")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 10814-2024 tillsynsbegäran.docx", "A 10814-2024")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 10814-2024 tillsynsbegäran mail.docx", "A 10814-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 3992-2023</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>44952</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Fläcknycklar</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 3992-2023 artfynd.xlsx", "A 3992-2023")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 3992-2023 karta.png", "A 3992-2023")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 3992-2023 georefererad karta.tif", "A 3992-2023")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 3992-2023 FSC-klagomål.docx", "A 3992-2023")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 3992-2023 FSC-klagomål mail.docx", "A 3992-2023")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 3992-2023 tillsynsbegäran.docx", "A 3992-2023")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 3992-2023 tillsynsbegäran mail.docx", "A 3992-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 23546-2026</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>46163</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 23546-2026 artfynd.xlsx", "A 23546-2026")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 23546-2026 karta.png", "A 23546-2026")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 23546-2026 georefererad karta.tif", "A 23546-2026")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 23546-2026 FSC-klagomål.docx", "A 23546-2026")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 23546-2026 FSC-klagomål mail.docx", "A 23546-2026")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 23546-2026 tillsynsbegäran.docx", "A 23546-2026")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 23546-2026 tillsynsbegäran mail.docx", "A 23546-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 43531-2025</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>45911</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>8</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>1</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 43531-2025 artfynd.xlsx", "A 43531-2025")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 43531-2025 karta.png", "A 43531-2025")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 43531-2025 georefererad karta.tif", "A 43531-2025")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 43531-2025 FSC-klagomål.docx", "A 43531-2025")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 43531-2025 FSC-klagomål mail.docx", "A 43531-2025")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 43531-2025 tillsynsbegäran.docx", "A 43531-2025")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 43531-2025 tillsynsbegäran mail.docx", "A 43531-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 26518-2026</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>46183</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1</v>
-      </c>
-      <c r="S27" t="n">
-        <v>1</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Rotfingersvamp</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 26518-2026 artfynd.xlsx", "A 26518-2026")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 26518-2026 karta.png", "A 26518-2026")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 26518-2026 georefererad karta.tif", "A 26518-2026")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 26518-2026 FSC-klagomål.docx", "A 26518-2026")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 26518-2026 FSC-klagomål mail.docx", "A 26518-2026")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 26518-2026 tillsynsbegäran.docx", "A 26518-2026")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 26518-2026 tillsynsbegäran mail.docx", "A 26518-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>44754</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>44732</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>44615</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>44783</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>44754</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         <v>44461</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>44546</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>44752</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>44484</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>44873</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>44456</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         <v>44469</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>44752</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>44564</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>44460</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>44578</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>44657</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 44530-2022</t>
+          <t>A 9796-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44840</v>
+        <v>44620</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4790,7 +4790,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 9796-2022</t>
+          <t>A 44530-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44620</v>
+        <v>44840</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4880,7 +4880,7 @@
         <v>44677</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>44720</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>44676</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         <v>44817</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>44539</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>44704</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>44484</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>44508</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 32642-2022</t>
+          <t>A 52269-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5461,10 +5461,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44783</v>
+        <v>44873</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5520,7 +5520,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 10401-2024</t>
+          <t>A 32642-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5534,10 +5534,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45365</v>
+        <v>44783</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>7.6</v>
+        <v>4.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5593,7 +5593,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 26530-2023</t>
+          <t>A 61060-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5607,10 +5607,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45092</v>
+        <v>44915</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.5</v>
+        <v>8.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5666,7 +5666,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 12334-2024</t>
+          <t>A 61061-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5680,10 +5680,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45378</v>
+        <v>44915</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5739,7 +5739,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 32299-2024</t>
+          <t>A 3989-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5753,10 +5753,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45512</v>
+        <v>44952</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5812,7 +5812,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 37267-2024</t>
+          <t>A 4054-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5826,10 +5826,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45540</v>
+        <v>45684</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.2</v>
+        <v>1.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5885,7 +5885,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 10398-2024</t>
+          <t>A 9374-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5899,10 +5899,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45365</v>
+        <v>44981</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5958,7 +5958,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 17685-2024</t>
+          <t>A 56025-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5972,10 +5972,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45418</v>
+        <v>45624</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6031,7 +6031,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 1921-2025</t>
+          <t>A 19872-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6045,10 +6045,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45671</v>
+        <v>45054</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.4</v>
+        <v>8.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6104,7 +6104,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 33666-2023</t>
+          <t>A 9152-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6118,10 +6118,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45132</v>
+        <v>45357</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6177,7 +6177,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 28319-2025</t>
+          <t>A 32549-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6191,10 +6191,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45818</v>
+        <v>45513</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6207,7 +6207,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6250,7 +6250,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 6283-2023</t>
+          <t>A 9456-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6264,10 +6264,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44965</v>
+        <v>45359</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6323,7 +6323,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 1883-2023</t>
+          <t>A 51173-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6337,10 +6337,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44939</v>
+        <v>45212</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6396,7 +6396,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 28870-2025</t>
+          <t>A 24533-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45820</v>
+        <v>45798</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>7.9</v>
+        <v>5.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6469,7 +6469,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 8160-2026</t>
+          <t>A 24527-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6483,10 +6483,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46064</v>
+        <v>45798</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6542,7 +6542,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 53317-2024</t>
+          <t>A 43017-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6556,10 +6556,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45614</v>
+        <v>45567</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6572,7 +6572,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6615,7 +6615,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 52471-2023</t>
+          <t>A 25623-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6629,10 +6629,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45225</v>
+        <v>45803</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6688,7 +6688,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 43353-2024</t>
+          <t>A 25652-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6702,10 +6702,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45568</v>
+        <v>45803</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6761,7 +6761,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 10356-2025</t>
+          <t>A 7154-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6771,14 +6771,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45720</v>
+        <v>45344</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6834,7 +6834,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 38888-2025</t>
+          <t>A 4416-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6848,10 +6848,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45887</v>
+        <v>45686</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6864,7 +6864,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6907,7 +6907,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 32842-2025</t>
+          <t>A 25635-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6921,10 +6921,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45839</v>
+        <v>45803</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>6.1</v>
+        <v>0.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6980,7 +6980,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 9573-2026</t>
+          <t>A 63249-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6994,10 +6994,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46071</v>
+        <v>46010</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7010,7 +7010,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>5.2</v>
+        <v>0.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7053,7 +7053,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 23450-2025</t>
+          <t>A 38653-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7067,10 +7067,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45792</v>
+        <v>45884</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7083,7 +7083,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.6</v>
+        <v>5.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 27908-2025</t>
+          <t>A 33388-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7140,10 +7140,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45817</v>
+        <v>44788</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7199,7 +7199,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 11442-2024</t>
+          <t>A 24978-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7213,10 +7213,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45372</v>
+        <v>44728</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 42723-2025</t>
+          <t>A 60395-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7282,14 +7282,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45908</v>
+        <v>45643</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7302,7 +7302,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7345,7 +7345,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 43398-2025</t>
+          <t>A 38888-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7359,10 +7359,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45911</v>
+        <v>45887</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7418,7 +7418,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 36141-2025</t>
+          <t>A 46917-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45866</v>
+        <v>44851</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7448,7 +7448,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7491,7 +7491,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 26639-2025</t>
+          <t>A 17693-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7505,10 +7505,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45810</v>
+        <v>45037</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>5.4</v>
+        <v>11.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7564,7 +7564,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 15227-2025</t>
+          <t>A 12501-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7578,10 +7578,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45744</v>
+        <v>45730</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7637,7 +7637,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 36048-2025</t>
+          <t>A 11848-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7651,10 +7651,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45866</v>
+        <v>45728</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7667,7 +7667,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7710,7 +7710,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 334-2023</t>
+          <t>A 8165-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7724,10 +7724,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44929</v>
+        <v>44974</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7783,7 +7783,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 53307-2024</t>
+          <t>A 37267-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7797,10 +7797,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45614</v>
+        <v>45540</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7813,7 +7813,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7856,7 +7856,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 44020-2025</t>
+          <t>A 17528-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7870,10 +7870,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45915</v>
+        <v>45415</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7886,7 +7886,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7929,7 +7929,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 36963-2025</t>
+          <t>A 52922-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7943,10 +7943,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45874</v>
+        <v>45610</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8002,7 +8002,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 44600-2025</t>
+          <t>A 7228-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8016,10 +8016,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45917</v>
+        <v>45702</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8032,7 +8032,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>7.2</v>
+        <v>1.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8075,7 +8075,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 44573-2025</t>
+          <t>A 14596-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8089,10 +8089,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45917</v>
+        <v>44655</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>5.5</v>
+        <v>0.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8148,7 +8148,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 44608-2025</t>
+          <t>A 13800-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8162,10 +8162,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45917</v>
+        <v>45007</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8178,7 +8178,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8221,7 +8221,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 45991-2025</t>
+          <t>A 8155-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8235,10 +8235,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45924</v>
+        <v>44974</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8251,7 +8251,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>4.4</v>
+        <v>2.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8294,7 +8294,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 45935-2025</t>
+          <t>A 1830-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8308,10 +8308,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45923</v>
+        <v>46035</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8367,7 +8367,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 45861-2025</t>
+          <t>A 1827-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8381,10 +8381,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45923</v>
+        <v>46035</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>10.2</v>
+        <v>2.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8440,7 +8440,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 38040-2025</t>
+          <t>A 12157-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8450,14 +8450,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45882</v>
+        <v>44636</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8470,7 +8470,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8513,7 +8513,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 46668-2025</t>
+          <t>A 28319-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8527,10 +8527,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45926</v>
+        <v>45818</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8586,7 +8586,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 46872-2025</t>
+          <t>A 28870-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8600,10 +8600,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45929</v>
+        <v>45820</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.4</v>
+        <v>7.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8659,7 +8659,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 38653-2025</t>
+          <t>A 3178-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8673,10 +8673,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45884</v>
+        <v>46041</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8689,7 +8689,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>5.3</v>
+        <v>0.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8732,7 +8732,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 38663-2025</t>
+          <t>A 27908-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8746,10 +8746,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45884</v>
+        <v>45817</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8805,7 +8805,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 11121-2026</t>
+          <t>A 3250-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8815,14 +8815,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46079</v>
+        <v>46041</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8835,7 +8835,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8878,7 +8878,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 11323-2026</t>
+          <t>A 51783-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8888,14 +8888,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46080</v>
+        <v>45222</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>7.3</v>
+        <v>1.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 11249-2026</t>
+          <t>A 42723-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8965,10 +8965,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46080</v>
+        <v>45908</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8981,7 +8981,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9024,7 +9024,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 40064-2023</t>
+          <t>A 3201-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9038,10 +9038,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45168</v>
+        <v>46041</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9054,7 +9054,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9097,7 +9097,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 26428-2022</t>
+          <t>A 43398-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9111,10 +9111,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44736</v>
+        <v>45911</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9127,7 +9127,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9170,7 +9170,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 49718-2025</t>
+          <t>A 39535-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9184,10 +9184,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45939</v>
+        <v>45551</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.1</v>
+        <v>4.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9243,7 +9243,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 8923-2024</t>
+          <t>A 7443-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9257,10 +9257,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45356</v>
+        <v>44971</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>3.2</v>
+        <v>0.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9316,7 +9316,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 25109-2022</t>
+          <t>A 44020-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9330,10 +9330,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44729</v>
+        <v>45915</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9346,7 +9346,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9389,7 +9389,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 13594-2026</t>
+          <t>A 5324-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9399,14 +9399,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46096</v>
+        <v>46050</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9419,7 +9419,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9462,7 +9462,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 43406-2025</t>
+          <t>A 44600-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9476,10 +9476,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45911</v>
+        <v>45917</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9492,7 +9492,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.5</v>
+        <v>7.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9535,7 +9535,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 25399-2023</t>
+          <t>A 32842-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9545,14 +9545,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45089</v>
+        <v>45839</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.9</v>
+        <v>6.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9608,7 +9608,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 53232-2025</t>
+          <t>A 44608-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9622,10 +9622,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45958</v>
+        <v>45917</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9681,7 +9681,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 50478-2025</t>
+          <t>A 44573-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9695,10 +9695,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45945</v>
+        <v>45917</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1</v>
+        <v>5.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9754,7 +9754,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 50482-2025</t>
+          <t>A 10356-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9768,10 +9768,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45945</v>
+        <v>45720</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>8.800000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9827,7 +9827,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 50441-2023</t>
+          <t>A 45861-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9841,10 +9841,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45216</v>
+        <v>45923</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.7</v>
+        <v>10.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9900,7 +9900,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 32304-2024</t>
+          <t>A 17685-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9914,10 +9914,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45512</v>
+        <v>45418</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9973,7 +9973,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 56349-2025</t>
+          <t>A 45935-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9987,10 +9987,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45974</v>
+        <v>45923</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10003,7 +10003,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10046,7 +10046,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 56026-2025</t>
+          <t>A 45991-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10060,10 +10060,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45973</v>
+        <v>45924</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.2</v>
+        <v>4.4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10119,7 +10119,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 4416-2025</t>
+          <t>A 7047-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10133,10 +10133,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45686</v>
+        <v>46057</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10149,7 +10149,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10192,7 +10192,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 15971-2023</t>
+          <t>A 7125-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10206,10 +10206,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45022</v>
+        <v>46058</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10222,7 +10222,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10265,7 +10265,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 53254-2022</t>
+          <t>A 23450-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10279,10 +10279,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44876</v>
+        <v>45792</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10295,7 +10295,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10338,7 +10338,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 18055-2026</t>
+          <t>A 7120-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10352,10 +10352,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46125</v>
+        <v>46058</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10368,7 +10368,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>5.2</v>
+        <v>0.8</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10411,7 +10411,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 59808-2025</t>
+          <t>A 46872-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10425,10 +10425,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45992</v>
+        <v>45929</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10441,7 +10441,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 59806-2025</t>
+          <t>A 7117-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10498,10 +10498,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45992</v>
+        <v>46058</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10514,7 +10514,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10557,7 +10557,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 59804-2025</t>
+          <t>A 46668-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10571,10 +10571,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45992</v>
+        <v>45926</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10587,7 +10587,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10630,7 +10630,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 73351-2021</t>
+          <t>A 8160-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10644,10 +10644,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44551</v>
+        <v>46064</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>6.1</v>
+        <v>2.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10703,7 +10703,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 59802-2025</t>
+          <t>A 11442-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10717,10 +10717,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45992</v>
+        <v>45372</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10733,7 +10733,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10776,7 +10776,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 51916-2022</t>
+          <t>A 15227-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10786,14 +10786,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44868</v>
+        <v>45744</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10849,7 +10849,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 60203-2025</t>
+          <t>A 26639-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10863,10 +10863,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45994</v>
+        <v>45810</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10879,7 +10879,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.4</v>
+        <v>5.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10922,7 +10922,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 61177-2025</t>
+          <t>A 36141-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10932,14 +10932,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46000</v>
+        <v>45866</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10995,7 +10995,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 61180-2025</t>
+          <t>A 36048-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11009,10 +11009,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46000</v>
+        <v>45866</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11025,7 +11025,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11085,7 +11085,7 @@
         <v>45531</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 61811-2023</t>
+          <t>A 9573-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11155,10 +11155,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45264</v>
+        <v>46071</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11170,13 +11170,8 @@
           <t>MELLERUD</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>7.9</v>
+        <v>5.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11219,7 +11214,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 34415-2024</t>
+          <t>A 16656-2022</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11233,10 +11228,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45525</v>
+        <v>44672</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11249,7 +11244,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>4.3</v>
+        <v>1.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11292,7 +11287,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 63249-2025</t>
+          <t>A 49718-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11306,10 +11301,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46010</v>
+        <v>45939</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11322,7 +11317,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11365,7 +11360,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 33092-2023</t>
+          <t>A 11249-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11379,10 +11374,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45126</v>
+        <v>46080</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11395,7 +11390,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2.9</v>
+        <v>4.8</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11438,7 +11433,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 40065-2023</t>
+          <t>A 11121-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11448,14 +11443,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45168</v>
+        <v>46079</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11468,7 +11463,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11511,7 +11506,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 493-2025</t>
+          <t>A 36963-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11525,10 +11520,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45664</v>
+        <v>45874</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11541,7 +11536,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11584,7 +11579,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 3989-2023</t>
+          <t>A 11323-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11594,14 +11589,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44952</v>
+        <v>46080</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11614,7 +11609,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.5</v>
+        <v>7.3</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11657,7 +11652,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 51783-2023</t>
+          <t>A 52471-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11671,10 +11666,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45222</v>
+        <v>45225</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11687,7 +11682,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11730,7 +11725,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 49449-2025</t>
+          <t>A 38040-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11744,10 +11739,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45938</v>
+        <v>45882</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11803,7 +11798,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 20573-2026</t>
+          <t>A 38663-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11817,10 +11812,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46140</v>
+        <v>45884</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11832,13 +11827,8 @@
           <t>MELLERUD</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>1.9</v>
+        <v>4.2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11881,7 +11871,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 1830-2026</t>
+          <t>A 43406-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11895,10 +11885,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46035</v>
+        <v>45911</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11911,7 +11901,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11954,7 +11944,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 24312-2025</t>
+          <t>A 25109-2022</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11968,10 +11958,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45797</v>
+        <v>44729</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11984,7 +11974,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12027,7 +12017,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 1827-2026</t>
+          <t>A 53307-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12041,10 +12031,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46035</v>
+        <v>45614</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12057,7 +12047,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12100,7 +12090,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 3250-2026</t>
+          <t>A 39728-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12114,10 +12104,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46041</v>
+        <v>45167</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12130,7 +12120,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12173,7 +12163,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 3178-2026</t>
+          <t>A 17543-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12187,10 +12177,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46041</v>
+        <v>45036</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12203,7 +12193,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12246,7 +12236,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 53565-2022</t>
+          <t>A 53254-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12260,10 +12250,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44879</v>
+        <v>44876</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12276,7 +12266,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12319,7 +12309,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 3201-2026</t>
+          <t>A 13594-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12329,14 +12319,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46041</v>
+        <v>46096</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12349,7 +12339,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12392,7 +12382,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 32498-2024</t>
+          <t>A 1921-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12406,10 +12396,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45513</v>
+        <v>45671</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12422,7 +12412,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12465,7 +12455,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 5324-2026</t>
+          <t>A 50478-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12479,10 +12469,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46050</v>
+        <v>45945</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12495,7 +12485,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12538,7 +12528,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 27510-2023</t>
+          <t>A 50482-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12552,10 +12542,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45097</v>
+        <v>45945</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12568,7 +12558,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12611,7 +12601,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 28865-2025</t>
+          <t>A 53232-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12625,10 +12615,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45820</v>
+        <v>45958</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12641,7 +12631,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12684,7 +12674,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 36146-2025</t>
+          <t>A 60996-2022</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12698,10 +12688,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45866</v>
+        <v>44914</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12714,7 +12704,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12757,7 +12747,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 59723-2025</t>
+          <t>A 18055-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12771,10 +12761,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45992</v>
+        <v>46125</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12787,7 +12777,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>12.3</v>
+        <v>5.2</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12830,7 +12820,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 7117-2026</t>
+          <t>A 15323-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12844,10 +12834,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46058</v>
+        <v>45400</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12860,7 +12850,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.8</v>
+        <v>10.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12903,7 +12893,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 7125-2026</t>
+          <t>A 10398-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12917,10 +12907,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46058</v>
+        <v>45365</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12933,7 +12923,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12976,7 +12966,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 7047-2026</t>
+          <t>A 56026-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12990,10 +12980,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46057</v>
+        <v>45973</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13006,7 +12996,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13049,7 +13039,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 7120-2026</t>
+          <t>A 56349-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13063,10 +13053,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46058</v>
+        <v>45974</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13079,7 +13069,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13122,7 +13112,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 22313-2023</t>
+          <t>A 24312-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13136,10 +13126,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45070</v>
+        <v>45797</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13152,7 +13142,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13195,7 +13185,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 35603-2024</t>
+          <t>A 493-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13209,10 +13199,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45531</v>
+        <v>45664</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13225,7 +13215,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.7</v>
+        <v>3.9</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13268,7 +13258,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 14568-2022</t>
+          <t>A 35603-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13282,10 +13272,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44655</v>
+        <v>45531</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13298,7 +13288,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13341,7 +13331,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 32384-2023</t>
+          <t>A 58861-2022</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13355,10 +13345,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45120</v>
+        <v>44903</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13371,7 +13361,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13414,7 +13404,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 21432-2026</t>
+          <t>A 11256-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13428,10 +13418,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46148</v>
+        <v>45726</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13444,7 +13434,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>4.3</v>
+        <v>0.5</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13487,7 +13477,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 39942-2023</t>
+          <t>A 36146-2025</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13501,10 +13491,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45167</v>
+        <v>45866</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13517,7 +13507,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13560,7 +13550,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 22364-2026</t>
+          <t>A 8923-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13574,10 +13564,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46154</v>
+        <v>45356</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13590,7 +13580,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13633,7 +13623,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 12713-2022</t>
+          <t>A 49449-2025</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13647,10 +13637,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44641</v>
+        <v>45938</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13663,7 +13653,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13706,7 +13696,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 21977-2026</t>
+          <t>A 39942-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13720,10 +13710,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46153</v>
+        <v>45167</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13779,7 +13769,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 22337-2026</t>
+          <t>A 59804-2025</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13793,10 +13783,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46154</v>
+        <v>45992</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13809,7 +13799,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13852,7 +13842,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 18854-2023</t>
+          <t>A 59802-2025</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13866,10 +13856,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45042</v>
+        <v>45992</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13882,7 +13872,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13925,7 +13915,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 1369-2025</t>
+          <t>A 59808-2025</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13939,10 +13929,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45667</v>
+        <v>45992</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13955,7 +13945,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13998,7 +13988,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 51785-2023</t>
+          <t>A 3998-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14012,10 +14002,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45222</v>
+        <v>45684</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14028,7 +14018,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>3.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14071,7 +14061,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 3998-2025</t>
+          <t>A 59806-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14085,10 +14075,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45684</v>
+        <v>45992</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14101,7 +14091,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>8.199999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14144,7 +14134,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 16746-2023</t>
+          <t>A 60203-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14158,10 +14148,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45030</v>
+        <v>45994</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14174,7 +14164,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14217,7 +14207,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 19872-2023</t>
+          <t>A 61177-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14227,14 +14217,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45054</v>
+        <v>46000</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14247,7 +14237,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>8.4</v>
+        <v>0.9</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14290,7 +14280,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 51436-2025</t>
+          <t>A 61180-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14304,10 +14294,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45950</v>
+        <v>46000</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14320,7 +14310,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14363,7 +14353,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 59865-2024</t>
+          <t>A 32384-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14377,10 +14367,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45639</v>
+        <v>45120</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14393,7 +14383,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>5.9</v>
+        <v>1.1</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14436,7 +14426,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 32832-2024</t>
+          <t>A 53565-2022</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14450,10 +14440,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45516</v>
+        <v>44879</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14466,7 +14456,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14509,7 +14499,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 8492-2022</t>
+          <t>A 59723-2025</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14523,10 +14513,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44613</v>
+        <v>45992</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14539,7 +14529,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.6</v>
+        <v>12.3</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14582,7 +14572,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 28863-2025</t>
+          <t>A 20573-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14596,10 +14586,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45820</v>
+        <v>46140</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14609,6 +14599,11 @@
       <c r="G180" t="inlineStr">
         <is>
           <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I180" t="n">
@@ -14655,7 +14650,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 10428-2022</t>
+          <t>A 6283-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14669,10 +14664,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44623</v>
+        <v>44965</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14685,7 +14680,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14728,7 +14723,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 21618-2024</t>
+          <t>A 40064-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14742,10 +14737,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45442</v>
+        <v>45168</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14758,7 +14753,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14801,7 +14796,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 21620-2024</t>
+          <t>A 28865-2025</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14815,10 +14810,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45442</v>
+        <v>45820</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14831,7 +14826,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14874,7 +14869,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 33388-2022</t>
+          <t>A 34415-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14888,10 +14883,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44788</v>
+        <v>45525</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14904,7 +14899,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>8.699999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14947,7 +14942,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 46761-2023</t>
+          <t>A 32304-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14961,10 +14956,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45198</v>
+        <v>45512</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14977,7 +14972,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15020,7 +15015,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 59269-2025</t>
+          <t>A 46761-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15034,10 +15029,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45988</v>
+        <v>45198</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15050,7 +15045,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15093,7 +15088,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 16656-2022</t>
+          <t>A 21077-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15107,10 +15102,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44672</v>
+        <v>45057</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15123,7 +15118,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15166,7 +15161,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 51463-2023</t>
+          <t>A 22313-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15180,10 +15175,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45221</v>
+        <v>45070</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15196,7 +15191,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15239,7 +15234,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 25036-2026</t>
+          <t>A 52128-2021</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15253,10 +15248,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46174</v>
+        <v>44463</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15269,7 +15264,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>5.9</v>
+        <v>1.9</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15312,7 +15307,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 36138-2025</t>
+          <t>A 17160-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15326,10 +15321,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45866</v>
+        <v>45412</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15342,7 +15337,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15385,7 +15380,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 25458-2026</t>
+          <t>A 48256-2022</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15399,10 +15394,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46177</v>
+        <v>44858</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15415,7 +15410,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15458,7 +15453,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 34116-2023</t>
+          <t>A 21432-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15468,14 +15463,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45126</v>
+        <v>46148</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15531,7 +15526,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 25954-2026</t>
+          <t>A 21977-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15545,10 +15540,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46181</v>
+        <v>46153</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15604,7 +15599,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 56025-2024</t>
+          <t>A 22364-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15618,10 +15613,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45624</v>
+        <v>46154</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15634,7 +15629,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15677,7 +15672,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 11256-2025</t>
+          <t>A 22337-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15691,10 +15686,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45726</v>
+        <v>46154</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15707,7 +15702,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15750,7 +15745,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 26527-2026</t>
+          <t>A 8152-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15764,10 +15759,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46183</v>
+        <v>44974</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15779,13 +15774,8 @@
           <t>MELLERUD</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I196" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15828,7 +15818,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 26536-2026</t>
+          <t>A 16746-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15842,10 +15832,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46183</v>
+        <v>45030</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15857,13 +15847,8 @@
           <t>MELLERUD</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I197" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15906,7 +15891,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 8155-2023</t>
+          <t>A 1369-2025</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15920,10 +15905,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>44974</v>
+        <v>45667</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15936,7 +15921,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15979,7 +15964,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 53573-2023</t>
+          <t>A 32832-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15993,10 +15978,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45230</v>
+        <v>45516</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16009,7 +15994,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16052,7 +16037,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 61060-2022</t>
+          <t>A 59865-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16066,10 +16051,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44915</v>
+        <v>45639</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16082,7 +16067,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>8.4</v>
+        <v>5.9</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16125,7 +16110,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 61061-2022</t>
+          <t>A 51436-2025</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16139,10 +16124,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>44915</v>
+        <v>45950</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16155,7 +16140,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16198,7 +16183,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 55391-2023</t>
+          <t>A 28863-2025</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16212,10 +16197,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45238</v>
+        <v>45820</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16228,7 +16213,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16271,7 +16256,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 54796-2022</t>
+          <t>A 40065-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16285,10 +16270,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>44883</v>
+        <v>45168</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16301,7 +16286,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16344,7 +16329,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 13800-2023</t>
+          <t>A 59269-2025</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16358,10 +16343,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45007</v>
+        <v>45988</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16374,7 +16359,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16417,7 +16402,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 48879-2024</t>
+          <t>A 25036-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16431,10 +16416,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45594</v>
+        <v>46174</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16447,7 +16432,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.1</v>
+        <v>5.9</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16490,7 +16475,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 45834-2023</t>
+          <t>A 36138-2025</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16504,10 +16489,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45195</v>
+        <v>45866</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16520,7 +16505,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16563,7 +16548,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 32520-2026</t>
+          <t>A 25458-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16577,10 +16562,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46239</v>
+        <v>46177</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16593,7 +16578,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16636,7 +16621,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 32691-2026</t>
+          <t>A 25954-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16650,10 +16635,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46240</v>
+        <v>46181</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16666,7 +16651,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16709,7 +16694,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 52269-2022</t>
+          <t>A 26536-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16723,10 +16708,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>44873</v>
+        <v>46183</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16738,8 +16723,13 @@
           <t>MELLERUD</t>
         </is>
       </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I209" t="n">
-        <v>4.6</v>
+        <v>0.6</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16782,7 +16772,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 15323-2024</t>
+          <t>A 26527-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16796,10 +16786,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45400</v>
+        <v>46183</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16811,8 +16801,13 @@
           <t>MELLERUD</t>
         </is>
       </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I210" t="n">
-        <v>10.6</v>
+        <v>1.3</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16855,7 +16850,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 17160-2024</t>
+          <t>A 32520-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16869,10 +16864,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45412</v>
+        <v>46239</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16885,7 +16880,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16928,7 +16923,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 19545-2024</t>
+          <t>A 45834-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16942,10 +16937,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45429</v>
+        <v>45195</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16958,7 +16953,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17001,7 +16996,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 52128-2021</t>
+          <t>A 51463-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17015,10 +17010,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>44463</v>
+        <v>45221</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17031,7 +17026,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17074,7 +17069,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 46917-2022</t>
+          <t>A 32691-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17088,10 +17083,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>44851</v>
+        <v>46240</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17104,7 +17099,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17147,7 +17142,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 60996-2022</t>
+          <t>A 8492-2022</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17161,10 +17156,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>44914</v>
+        <v>44613</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17177,7 +17172,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17220,7 +17215,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 12157-2022</t>
+          <t>A 33450-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17230,14 +17225,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>44636</v>
+        <v>46246</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17250,7 +17245,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17293,7 +17288,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 9456-2024</t>
+          <t>A 20578-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17307,10 +17302,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45359</v>
+        <v>46140</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17322,8 +17317,13 @@
           <t>MELLERUD</t>
         </is>
       </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I217" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17383,7 +17383,7 @@
         <v>46205</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 33450-2026</t>
+          <t>A 29939-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17453,10 +17453,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46246</v>
+        <v>46205</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17469,7 +17469,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17512,7 +17512,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 29939-2026</t>
+          <t>A 48879-2024</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17526,10 +17526,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46205</v>
+        <v>45594</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17585,7 +17585,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 53270-2024</t>
+          <t>A 5647-2023</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17599,10 +17599,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45614</v>
+        <v>44960</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17658,7 +17658,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 5647-2023</t>
+          <t>A 34065-2026</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17672,10 +17672,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>44960</v>
+        <v>46252</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17731,7 +17731,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 7443-2023</t>
+          <t>A 12334-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17745,10 +17745,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>44971</v>
+        <v>45378</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17761,7 +17761,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17804,7 +17804,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 20578-2026</t>
+          <t>A 12713-2022</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17818,10 +17818,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46140</v>
+        <v>44641</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17833,13 +17833,8 @@
           <t>MELLERUD</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I224" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17882,7 +17877,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 1886-2023</t>
+          <t>A 11219-2024</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17896,10 +17891,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>44939</v>
+        <v>45371</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17912,7 +17907,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17955,7 +17950,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 34065-2026</t>
+          <t>A 18205-2024</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17969,10 +17964,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>46252</v>
+        <v>45420</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17985,7 +17980,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18028,7 +18023,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 9374-2023</t>
+          <t>A 31836-2026</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18042,10 +18037,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>44981</v>
+        <v>46230</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18058,7 +18053,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18101,7 +18096,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 48256-2022</t>
+          <t>A 36960-2026</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18115,10 +18110,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>44858</v>
+        <v>46273</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18131,7 +18126,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>1.9</v>
+        <v>8.1</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18174,7 +18169,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 23238-2024</t>
+          <t>A 10428-2022</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18188,10 +18183,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45453</v>
+        <v>44623</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18204,7 +18199,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18247,7 +18242,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 7154-2024</t>
+          <t>A 31889-2026</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18257,14 +18252,14 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45344</v>
+        <v>46231</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18277,7 +18272,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18320,7 +18315,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 24978-2022</t>
+          <t>A 54796-2022</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18334,10 +18329,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>44728</v>
+        <v>44883</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18350,7 +18345,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18393,7 +18388,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 18205-2024</t>
+          <t>A 53573-2023</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18407,10 +18402,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45420</v>
+        <v>45230</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18423,7 +18418,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18466,7 +18461,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 17543-2023</t>
+          <t>A 34116-2023</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18476,14 +18471,14 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45036</v>
+        <v>45126</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18496,7 +18491,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>1.8</v>
+        <v>4.3</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18539,7 +18534,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 17538-2023</t>
+          <t>A 1883-2023</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18553,10 +18548,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45036</v>
+        <v>44939</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18569,7 +18564,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18612,7 +18607,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 11219-2024</t>
+          <t>A 1886-2023</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18626,10 +18621,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45371</v>
+        <v>44939</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18642,7 +18637,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18685,7 +18680,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 31836-2026</t>
+          <t>A 27510-2023</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18699,10 +18694,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>46230</v>
+        <v>45097</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18715,7 +18710,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18758,7 +18753,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 58861-2022</t>
+          <t>A 334-2023</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18772,10 +18767,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>44903</v>
+        <v>44929</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18788,7 +18783,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18831,7 +18826,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 39728-2023</t>
+          <t>A 32299-2024</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18845,10 +18840,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45167</v>
+        <v>45512</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18861,7 +18856,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18904,7 +18899,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 51173-2023</t>
+          <t>A 32498-2024</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18918,10 +18913,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45212</v>
+        <v>45513</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18934,7 +18929,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18977,7 +18972,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 4054-2025</t>
+          <t>A 43353-2024</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18991,10 +18986,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45684</v>
+        <v>45568</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19007,7 +19002,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -19050,7 +19045,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 14596-2022</t>
+          <t>A 51916-2022</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -19060,14 +19055,14 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>44655</v>
+        <v>44868</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19080,7 +19075,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>0.9</v>
+        <v>4.5</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -19123,7 +19118,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 36960-2026</t>
+          <t>A 33666-2023</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19137,10 +19132,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>46273</v>
+        <v>45132</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19153,7 +19148,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>8.1</v>
+        <v>0.4</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19196,7 +19191,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 39535-2024</t>
+          <t>A 51785-2023</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19210,10 +19205,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45551</v>
+        <v>45222</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19226,7 +19221,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19269,7 +19264,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 32549-2024</t>
+          <t>A 33092-2023</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19283,10 +19278,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45513</v>
+        <v>45126</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19299,7 +19294,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19342,7 +19337,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 21077-2023</t>
+          <t>A 55391-2023</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19356,10 +19351,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45057</v>
+        <v>45238</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19372,7 +19367,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19415,7 +19410,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 31889-2026</t>
+          <t>A 15971-2023</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19429,10 +19424,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>46231</v>
+        <v>45022</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19445,7 +19440,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19488,7 +19483,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 9152-2024</t>
+          <t>A 53317-2024</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19502,10 +19497,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45357</v>
+        <v>45614</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19518,7 +19513,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19561,7 +19556,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 8152-2023</t>
+          <t>A 73351-2021</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19575,10 +19570,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>44974</v>
+        <v>44551</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19591,7 +19586,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>1.4</v>
+        <v>6.1</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19634,7 +19629,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 21698-2025</t>
+          <t>A 26428-2022</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19648,10 +19643,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45783</v>
+        <v>44736</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19664,7 +19659,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19707,7 +19702,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 21678-2025</t>
+          <t>A 21618-2024</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19721,10 +19716,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45783</v>
+        <v>45442</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19737,7 +19732,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19780,7 +19775,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 21689-2025</t>
+          <t>A 21620-2024</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19794,10 +19789,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>45783</v>
+        <v>45442</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19810,7 +19805,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -19853,7 +19848,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 27342-2024</t>
+          <t>A 26530-2023</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19867,10 +19862,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45473</v>
+        <v>45092</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19883,7 +19878,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19926,7 +19921,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 13313-2024</t>
+          <t>A 18854-2023</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19940,10 +19935,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45386</v>
+        <v>45042</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19956,7 +19951,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -19999,7 +19994,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 8667-2025</t>
+          <t>A 14568-2022</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -20013,10 +20008,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45712</v>
+        <v>44655</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20029,7 +20024,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -20072,7 +20067,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 60993-2022</t>
+          <t>A 61811-2023</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20086,10 +20081,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>44914</v>
+        <v>45264</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20101,8 +20096,13 @@
           <t>MELLERUD</t>
         </is>
       </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I255" t="n">
-        <v>0.6</v>
+        <v>7.9</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20145,7 +20145,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 10100-2025</t>
+          <t>A 25399-2023</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20155,14 +20155,14 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45719</v>
+        <v>45089</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20175,7 +20175,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20218,7 +20218,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 10097-2025</t>
+          <t>A 23238-2024</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -20232,10 +20232,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>45719</v>
+        <v>45453</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20248,7 +20248,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20291,7 +20291,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 10357-2025</t>
+          <t>A 53270-2024</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20305,10 +20305,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45720</v>
+        <v>45614</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20364,7 +20364,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 10358-2025</t>
+          <t>A 17538-2023</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20378,10 +20378,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>45720</v>
+        <v>45036</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20437,7 +20437,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 11213-2025</t>
+          <t>A 19545-2024</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -20451,10 +20451,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45726</v>
+        <v>45429</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20467,7 +20467,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>4.8</v>
+        <v>0.7</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -20510,7 +20510,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 24527-2025</t>
+          <t>A 50441-2023</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -20524,10 +20524,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>45798</v>
+        <v>45216</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -20583,7 +20583,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 24533-2025</t>
+          <t>A 10401-2024</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -20597,10 +20597,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>45798</v>
+        <v>45365</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20613,7 +20613,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -20656,7 +20656,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 43017-2024</t>
+          <t>A 21689-2025</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -20670,10 +20670,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>45567</v>
+        <v>45783</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20686,7 +20686,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -20729,7 +20729,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 25652-2025</t>
+          <t>A 21678-2025</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -20743,10 +20743,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>45803</v>
+        <v>45783</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20759,7 +20759,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -20802,7 +20802,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 25635-2025</t>
+          <t>A 21698-2025</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>45803</v>
+        <v>45783</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20832,7 +20832,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -20875,7 +20875,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>A 25623-2025</t>
+          <t>A 13313-2024</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -20889,10 +20889,10 @@
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>45803</v>
+        <v>45386</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20905,7 +20905,7 @@
         </is>
       </c>
       <c r="I266" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -20948,7 +20948,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>A 60395-2024</t>
+          <t>A 27342-2024</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -20958,14 +20958,14 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>45643</v>
+        <v>45473</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20978,7 +20978,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -21021,7 +21021,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>A 8165-2023</t>
+          <t>A 10100-2025</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -21035,10 +21035,10 @@
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>44974</v>
+        <v>45719</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21051,7 +21051,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -21094,7 +21094,7 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>A 17528-2024</t>
+          <t>A 8667-2025</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -21108,10 +21108,10 @@
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>45415</v>
+        <v>45712</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21124,7 +21124,7 @@
         </is>
       </c>
       <c r="I269" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -21167,7 +21167,7 @@
     <row r="270" ht="15" customHeight="1">
       <c r="A270" t="inlineStr">
         <is>
-          <t>A 52922-2024</t>
+          <t>A 10357-2025</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -21181,10 +21181,10 @@
         </is>
       </c>
       <c r="D270" s="1" t="n">
-        <v>45610</v>
+        <v>45720</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21197,7 +21197,7 @@
         </is>
       </c>
       <c r="I270" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -21240,7 +21240,7 @@
     <row r="271" ht="15" customHeight="1">
       <c r="A271" t="inlineStr">
         <is>
-          <t>A 11848-2025</t>
+          <t>A 10358-2025</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -21254,10 +21254,10 @@
         </is>
       </c>
       <c r="D271" s="1" t="n">
-        <v>45728</v>
+        <v>45720</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21270,7 +21270,7 @@
         </is>
       </c>
       <c r="I271" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J271" t="n">
         <v>0</v>
@@ -21313,7 +21313,7 @@
     <row r="272" ht="15" customHeight="1">
       <c r="A272" t="inlineStr">
         <is>
-          <t>A 12501-2025</t>
+          <t>A 60993-2022</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -21327,10 +21327,10 @@
         </is>
       </c>
       <c r="D272" s="1" t="n">
-        <v>45730</v>
+        <v>44914</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21343,7 +21343,7 @@
         </is>
       </c>
       <c r="I272" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J272" t="n">
         <v>0</v>
@@ -21386,7 +21386,7 @@
     <row r="273" ht="15" customHeight="1">
       <c r="A273" t="inlineStr">
         <is>
-          <t>A 17693-2023</t>
+          <t>A 10097-2025</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -21400,10 +21400,10 @@
         </is>
       </c>
       <c r="D273" s="1" t="n">
-        <v>45037</v>
+        <v>45719</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21416,7 +21416,7 @@
         </is>
       </c>
       <c r="I273" t="n">
-        <v>11.3</v>
+        <v>2.6</v>
       </c>
       <c r="J273" t="n">
         <v>0</v>
@@ -21459,7 +21459,7 @@
     <row r="274" ht="15" customHeight="1">
       <c r="A274" t="inlineStr">
         <is>
-          <t>A 7228-2025</t>
+          <t>A 11213-2025</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -21473,10 +21473,10 @@
         </is>
       </c>
       <c r="D274" s="1" t="n">
-        <v>45702</v>
+        <v>45726</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21489,7 +21489,7 @@
         </is>
       </c>
       <c r="I274" t="n">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="J274" t="n">
         <v>0</v>
@@ -21549,7 +21549,7 @@
         <v>44551</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21622,7 +21622,7 @@
         <v>45351</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21695,7 +21695,7 @@
         <v>46184</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21768,7 +21768,7 @@
         <v>46188</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>

--- a/Översikt MELLERUD.xlsx
+++ b/Översikt MELLERUD.xlsx
@@ -601,7 +601,7 @@
         <v>46184</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>46112</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>45614</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 44523-2022</t>
+          <t>A 53463-2024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -975,10 +975,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44840</v>
+        <v>45614</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -991,19 +991,19 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L5" t="n">
         <v>3</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -1015,21 +1015,135 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
       </c>
       <c r="T5" t="n">
+        <v>19</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Grålila vaxing
+Uddbräken
+Lädervaxing
+Scharlakansvaxing
+Sårläka
+Blodvaxing
+Honungsvaxing
+Igelkottsröksvamp
+Luktvaxing
+Ängsvaxing agg.</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 53463-2024 artfynd.xlsx", "A 53463-2024")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 53463-2024 karta.png", "A 53463-2024")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 53463-2024 georefererad karta.tif", "A 53463-2024")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 53463-2024 FSC-klagomål.docx", "A 53463-2024")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 53463-2024 FSC-klagomål mail.docx", "A 53463-2024")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 53463-2024 tillsynsbegäran.docx", "A 53463-2024")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 53463-2024 tillsynsbegäran mail.docx", "A 53463-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 44523-2022</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>44840</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>6</v>
+      </c>
+      <c r="R6" t="n">
+        <v>3</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="n">
         <v>15</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>4</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Aspfjädermossa
 Skirmossa
@@ -1043,149 +1157,35 @@
 Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 44523-2022 artfynd.xlsx", "A 44523-2022")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 44523-2022 karta.png", "A 44523-2022")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 44523-2022 georefererad karta.tif", "A 44523-2022")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 44523-2022 FSC-klagomål.docx", "A 44523-2022")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 44523-2022 FSC-klagomål mail.docx", "A 44523-2022")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 44523-2022 tillsynsbegäran.docx", "A 44523-2022")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 44523-2022 tillsynsbegäran mail.docx", "A 44523-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 53463-2024</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45614</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>5</v>
-      </c>
-      <c r="L6" t="n">
-        <v>3</v>
-      </c>
-      <c r="M6" t="n">
-        <v>2</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>5</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="n">
-        <v>19</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Grålila vaxing
-Uddbräken
-Lädervaxing
-Scharlakansvaxing
-Sårläka
-Blodvaxing
-Honungsvaxing
-Igelkottsröksvamp
-Luktvaxing
-Ängsvaxing agg.</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 53463-2024 artfynd.xlsx", "A 53463-2024")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 53463-2024 karta.png", "A 53463-2024")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 53463-2024 georefererad karta.tif", "A 53463-2024")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 53463-2024 FSC-klagomål.docx", "A 53463-2024")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 53463-2024 FSC-klagomål mail.docx", "A 53463-2024")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 53463-2024 tillsynsbegäran.docx", "A 53463-2024")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 53463-2024 tillsynsbegäran mail.docx", "A 53463-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>45734</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>45670</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>46020</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>45253</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>44963</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>45006</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 25764-2025</t>
+          <t>A 28216-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45804</v>
+        <v>46196</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1880,22 +1880,27 @@
       <c r="G13" t="inlineStr">
         <is>
           <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I13" t="n">
         <v>2.5</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
         <v>1</v>
@@ -1907,21 +1912,242 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
       </c>
       <c r="T13" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Gulvit blekspik
+Guldlockmossa
+Gröngöling</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 28216-2026 artfynd.xlsx", "A 28216-2026")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 28216-2026 karta.png", "A 28216-2026")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 28216-2026 georefererad karta.tif", "A 28216-2026")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 28216-2026 FSC-klagomål.docx", "A 28216-2026")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 28216-2026 FSC-klagomål mail.docx", "A 28216-2026")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 28216-2026 tillsynsbegäran.docx", "A 28216-2026")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 28216-2026 tillsynsbegäran mail.docx", "A 28216-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 33141-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
+      <c r="T14" t="n">
+        <v>7</v>
+      </c>
+      <c r="U14" t="n">
+        <v>7</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Kattfotslav
+Grön sköldmossa
+Kornknutmossa
+Mandelriska</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 33141-2026 artfynd.xlsx", "A 33141-2026")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 33141-2026 karta.png", "A 33141-2026")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 33141-2026 georefererad karta.tif", "A 33141-2026")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 33141-2026 FSC-klagomål.docx", "A 33141-2026")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 33141-2026 FSC-klagomål mail.docx", "A 33141-2026")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 33141-2026 tillsynsbegäran.docx", "A 33141-2026")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 33141-2026 tillsynsbegäran mail.docx", "A 33141-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 25764-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45804</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4</v>
+      </c>
+      <c r="T15" t="n">
         <v>5</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Ask
 Guldlockmossa
@@ -1929,261 +2155,35 @@
 Rostfläck</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 25764-2025 artfynd.xlsx", "A 25764-2025")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 25764-2025 karta.png", "A 25764-2025")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 25764-2025 georefererad karta.tif", "A 25764-2025")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 25764-2025 FSC-klagomål.docx", "A 25764-2025")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 25764-2025 FSC-klagomål mail.docx", "A 25764-2025")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 25764-2025 tillsynsbegäran.docx", "A 25764-2025")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 25764-2025 tillsynsbegäran mail.docx", "A 25764-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 28216-2026</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>46196</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2</v>
-      </c>
-      <c r="S14" t="n">
-        <v>4</v>
-      </c>
-      <c r="T14" t="n">
-        <v>4</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Gulvit blekspik
-Guldlockmossa
-Gröngöling</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 28216-2026 artfynd.xlsx", "A 28216-2026")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 28216-2026 karta.png", "A 28216-2026")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 28216-2026 georefererad karta.tif", "A 28216-2026")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 28216-2026 FSC-klagomål.docx", "A 28216-2026")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 28216-2026 FSC-klagomål mail.docx", "A 28216-2026")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 28216-2026 tillsynsbegäran.docx", "A 28216-2026")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 28216-2026 tillsynsbegäran mail.docx", "A 28216-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 33141-2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46244</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>4</v>
-      </c>
-      <c r="T15" t="n">
-        <v>7</v>
-      </c>
-      <c r="U15" t="n">
-        <v>7</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Kattfotslav
-Grön sköldmossa
-Kornknutmossa
-Mandelriska</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 33141-2026 artfynd.xlsx", "A 33141-2026")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 33141-2026 karta.png", "A 33141-2026")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 33141-2026 georefererad karta.tif", "A 33141-2026")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 33141-2026 FSC-klagomål.docx", "A 33141-2026")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 33141-2026 FSC-klagomål mail.docx", "A 33141-2026")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 33141-2026 tillsynsbegäran.docx", "A 33141-2026")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 33141-2026 tillsynsbegäran mail.docx", "A 33141-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>46020</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>45390</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>44896</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>44804</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>44750</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 10814-2024</t>
+          <t>A 43349-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2740,10 +2740,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45369</v>
+        <v>45568</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2755,13 +2755,8 @@
           <t>MELLERUD</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>6.6</v>
+        <v>4.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2770,10 +2765,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2788,7 +2783,7 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2797,682 +2792,687 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 43349-2024 artfynd.xlsx", "A 43349-2024")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 43349-2024 karta.png", "A 43349-2024")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 43349-2024 georefererad karta.tif", "A 43349-2024")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 43349-2024 FSC-klagomål.docx", "A 43349-2024")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 43349-2024 FSC-klagomål mail.docx", "A 43349-2024")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 43349-2024 tillsynsbegäran.docx", "A 43349-2024")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 43349-2024 tillsynsbegäran mail.docx", "A 43349-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 8169-2023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>44974</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 8169-2023 artfynd.xlsx", "A 8169-2023")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 8169-2023 karta.png", "A 8169-2023")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 8169-2023 georefererad karta.tif", "A 8169-2023")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 8169-2023 FSC-klagomål.docx", "A 8169-2023")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 8169-2023 FSC-klagomål mail.docx", "A 8169-2023")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 8169-2023 tillsynsbegäran.docx", "A 8169-2023")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 8169-2023 tillsynsbegäran mail.docx", "A 8169-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 10814-2024</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>45369</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 10814-2024 artfynd.xlsx", "A 10814-2024")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 10814-2024 karta.png", "A 10814-2024")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 10814-2024 georefererad karta.tif", "A 10814-2024")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 10814-2024 FSC-klagomål.docx", "A 10814-2024")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 10814-2024 FSC-klagomål mail.docx", "A 10814-2024")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 10814-2024 tillsynsbegäran.docx", "A 10814-2024")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 10814-2024 tillsynsbegäran mail.docx", "A 10814-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 3992-2023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>44952</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 3992-2023 artfynd.xlsx", "A 3992-2023")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 3992-2023 karta.png", "A 3992-2023")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 3992-2023 georefererad karta.tif", "A 3992-2023")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 3992-2023 FSC-klagomål.docx", "A 3992-2023")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 3992-2023 FSC-klagomål mail.docx", "A 3992-2023")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 3992-2023 tillsynsbegäran.docx", "A 3992-2023")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 3992-2023 tillsynsbegäran mail.docx", "A 3992-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>A 23546-2026</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
         <v>46163</v>
       </c>
-      <c r="E22" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
+      <c r="E25" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
         <v>3.6</v>
       </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
         <v>1</v>
       </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
         <v>1</v>
       </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
         <v>1</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T25" t="n">
         <v>3</v>
       </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Lunglav</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 23546-2026 artfynd.xlsx", "A 23546-2026")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 23546-2026 karta.png", "A 23546-2026")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 23546-2026 georefererad karta.tif", "A 23546-2026")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 23546-2026 FSC-klagomål.docx", "A 23546-2026")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 23546-2026 FSC-klagomål mail.docx", "A 23546-2026")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 23546-2026 tillsynsbegäran.docx", "A 23546-2026")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 23546-2026 tillsynsbegäran mail.docx", "A 23546-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>A 43531-2025</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
         <v>45911</v>
       </c>
-      <c r="E23" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
+      <c r="E26" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
         <is>
           <t>Övriga Aktiebolag</t>
         </is>
       </c>
-      <c r="I23" t="n">
+      <c r="I26" t="n">
         <v>8</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J26" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
         <v>1</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T26" t="n">
         <v>1</v>
       </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Kungsfågel</t>
         </is>
       </c>
-      <c r="W23">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 43531-2025 artfynd.xlsx", "A 43531-2025")</f>
         <v/>
       </c>
-      <c r="X23">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 43531-2025 karta.png", "A 43531-2025")</f>
         <v/>
       </c>
-      <c r="Y23">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 43531-2025 georefererad karta.tif", "A 43531-2025")</f>
         <v/>
       </c>
-      <c r="AA23">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 43531-2025 FSC-klagomål.docx", "A 43531-2025")</f>
         <v/>
       </c>
-      <c r="AB23">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 43531-2025 FSC-klagomål mail.docx", "A 43531-2025")</f>
         <v/>
       </c>
-      <c r="AC23">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 43531-2025 tillsynsbegäran.docx", "A 43531-2025")</f>
         <v/>
       </c>
-      <c r="AD23">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 43531-2025 tillsynsbegäran mail.docx", "A 43531-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>A 26518-2026</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
         <v>46183</v>
       </c>
-      <c r="E24" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
+      <c r="E27" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
         <is>
           <t>Kommuner</t>
         </is>
       </c>
-      <c r="I24" t="n">
+      <c r="I27" t="n">
         <v>0.4</v>
       </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
         <v>1</v>
       </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
         <v>1</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R27" t="n">
         <v>1</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S27" t="n">
         <v>1</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T27" t="n">
         <v>1</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U27" t="n">
         <v>1</v>
       </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Rotfingersvamp</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 26518-2026 artfynd.xlsx", "A 26518-2026")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 26518-2026 karta.png", "A 26518-2026")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 26518-2026 georefererad karta.tif", "A 26518-2026")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 26518-2026 FSC-klagomål.docx", "A 26518-2026")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 26518-2026 FSC-klagomål mail.docx", "A 26518-2026")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 26518-2026 tillsynsbegäran.docx", "A 26518-2026")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 26518-2026 tillsynsbegäran mail.docx", "A 26518-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 8169-2023</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>44974</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Älg</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 8169-2023 artfynd.xlsx", "A 8169-2023")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 8169-2023 karta.png", "A 8169-2023")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 8169-2023 georefererad karta.tif", "A 8169-2023")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 8169-2023 FSC-klagomål.docx", "A 8169-2023")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 8169-2023 FSC-klagomål mail.docx", "A 8169-2023")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 8169-2023 tillsynsbegäran.docx", "A 8169-2023")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 8169-2023 tillsynsbegäran mail.docx", "A 8169-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 43349-2024</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>45568</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>1</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Älg</t>
-        </is>
-      </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 43349-2024 artfynd.xlsx", "A 43349-2024")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 43349-2024 karta.png", "A 43349-2024")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 43349-2024 georefererad karta.tif", "A 43349-2024")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 43349-2024 FSC-klagomål.docx", "A 43349-2024")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 43349-2024 FSC-klagomål mail.docx", "A 43349-2024")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 43349-2024 tillsynsbegäran.docx", "A 43349-2024")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 43349-2024 tillsynsbegäran mail.docx", "A 43349-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 3992-2023</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>44952</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>1</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 3992-2023 artfynd.xlsx", "A 3992-2023")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 3992-2023 karta.png", "A 3992-2023")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 3992-2023 georefererad karta.tif", "A 3992-2023")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 3992-2023 FSC-klagomål.docx", "A 3992-2023")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 3992-2023 FSC-klagomål mail.docx", "A 3992-2023")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 3992-2023 tillsynsbegäran.docx", "A 3992-2023")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 3992-2023 tillsynsbegäran mail.docx", "A 3992-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>44754</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>44732</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>44615</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>44783</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>44754</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         <v>44461</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>44546</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>44752</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>44484</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>44873</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>44456</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         <v>44469</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>44752</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>44564</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>44460</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>44578</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>44657</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 9796-2022</t>
+          <t>A 44530-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44620</v>
+        <v>44840</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4790,7 +4790,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 44530-2022</t>
+          <t>A 9796-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44840</v>
+        <v>44620</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4880,7 +4880,7 @@
         <v>44677</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 23350-2022</t>
+          <t>A 32642-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4950,10 +4950,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44720</v>
+        <v>44783</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.4</v>
+        <v>4.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 17019-2022</t>
+          <t>A 23350-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5023,10 +5023,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44676</v>
+        <v>44720</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5082,7 +5082,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 39171-2022</t>
+          <t>A 10401-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5096,10 +5096,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44817</v>
+        <v>45365</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.5</v>
+        <v>7.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5155,7 +5155,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 71252-2021</t>
+          <t>A 17019-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5169,10 +5169,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44539</v>
+        <v>44676</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5228,7 +5228,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 21097-2022</t>
+          <t>A 26530-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5242,10 +5242,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44704</v>
+        <v>45092</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5301,7 +5301,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 57801-2021</t>
+          <t>A 16656-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5315,10 +5315,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44484</v>
+        <v>44672</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5374,7 +5374,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 63539-2021</t>
+          <t>A 39171-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5388,10 +5388,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44508</v>
+        <v>44817</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5447,7 +5447,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 52269-2022</t>
+          <t>A 51463-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5461,10 +5461,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44873</v>
+        <v>45221</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.6</v>
+        <v>2.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5520,7 +5520,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 32642-2022</t>
+          <t>A 71252-2021</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5534,10 +5534,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44783</v>
+        <v>44539</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5593,7 +5593,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 61060-2022</t>
+          <t>A 21097-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5607,10 +5607,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44915</v>
+        <v>44704</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>8.4</v>
+        <v>0.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5666,7 +5666,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 61061-2022</t>
+          <t>A 63539-2021</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5680,10 +5680,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44915</v>
+        <v>44508</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>8.5</v>
+        <v>1.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5739,7 +5739,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 3989-2023</t>
+          <t>A 57801-2021</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5753,10 +5753,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44952</v>
+        <v>44484</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5812,7 +5812,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 4054-2025</t>
+          <t>A 38040-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5826,10 +5826,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45684</v>
+        <v>45882</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5885,7 +5885,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 9374-2023</t>
+          <t>A 12334-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5899,10 +5899,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44981</v>
+        <v>45378</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5958,7 +5958,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 56025-2024</t>
+          <t>A 34116-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5968,14 +5968,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45624</v>
+        <v>45126</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.1</v>
+        <v>4.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6031,7 +6031,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 19872-2023</t>
+          <t>A 56025-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6045,10 +6045,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45054</v>
+        <v>45624</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>8.4</v>
+        <v>2.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6104,7 +6104,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 9152-2024</t>
+          <t>A 11256-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6118,10 +6118,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45357</v>
+        <v>45726</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6177,7 +6177,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 32549-2024</t>
+          <t>A 38653-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6191,10 +6191,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45513</v>
+        <v>45884</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6207,7 +6207,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>5.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6250,7 +6250,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 9456-2024</t>
+          <t>A 38663-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6264,10 +6264,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45359</v>
+        <v>45884</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6323,7 +6323,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 51173-2023</t>
+          <t>A 8155-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6337,10 +6337,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45212</v>
+        <v>44974</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6396,7 +6396,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 24533-2025</t>
+          <t>A 53573-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45798</v>
+        <v>45230</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6469,7 +6469,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 24527-2025</t>
+          <t>A 61060-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6483,10 +6483,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45798</v>
+        <v>44915</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.6</v>
+        <v>8.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6542,7 +6542,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 43017-2024</t>
+          <t>A 61061-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6556,10 +6556,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45567</v>
+        <v>44915</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6572,7 +6572,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.4</v>
+        <v>8.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6615,7 +6615,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 25623-2025</t>
+          <t>A 55391-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6629,10 +6629,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45803</v>
+        <v>45238</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6688,7 +6688,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 25652-2025</t>
+          <t>A 54796-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6702,10 +6702,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45803</v>
+        <v>44883</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6761,7 +6761,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 7154-2024</t>
+          <t>A 11121-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6775,10 +6775,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45344</v>
+        <v>46079</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6834,7 +6834,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 4416-2025</t>
+          <t>A 52471-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6848,10 +6848,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45686</v>
+        <v>45225</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6864,7 +6864,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6907,7 +6907,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 25635-2025</t>
+          <t>A 11323-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6917,14 +6917,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45803</v>
+        <v>46080</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.4</v>
+        <v>7.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6980,7 +6980,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 63249-2025</t>
+          <t>A 11249-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6994,10 +6994,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46010</v>
+        <v>46080</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7010,7 +7010,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.6</v>
+        <v>4.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7053,7 +7053,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 38653-2025</t>
+          <t>A 38888-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7067,10 +7067,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45884</v>
+        <v>45887</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7083,7 +7083,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>5.3</v>
+        <v>1.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 33388-2022</t>
+          <t>A 32299-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7140,10 +7140,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44788</v>
+        <v>45512</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>8.699999999999999</v>
+        <v>3.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7199,7 +7199,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 24978-2022</t>
+          <t>A 13800-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7213,10 +7213,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44728</v>
+        <v>45007</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7272,7 +7272,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 60395-2024</t>
+          <t>A 48879-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7282,14 +7282,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45643</v>
+        <v>45594</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7302,7 +7302,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7345,7 +7345,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 38888-2025</t>
+          <t>A 13594-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7355,14 +7355,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45887</v>
+        <v>46096</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7418,7 +7418,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 46917-2022</t>
+          <t>A 27908-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44851</v>
+        <v>45817</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7448,7 +7448,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7491,7 +7491,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 17693-2023</t>
+          <t>A 45834-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7505,10 +7505,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45037</v>
+        <v>45195</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>11.3</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7564,7 +7564,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 12501-2025</t>
+          <t>A 42723-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7578,10 +7578,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45730</v>
+        <v>45908</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7637,7 +7637,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 11848-2025</t>
+          <t>A 37267-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7651,10 +7651,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45728</v>
+        <v>45540</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7667,7 +7667,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7710,7 +7710,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 8165-2023</t>
+          <t>A 43398-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7724,10 +7724,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44974</v>
+        <v>45911</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7783,7 +7783,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 37267-2024</t>
+          <t>A 10398-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7797,10 +7797,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45540</v>
+        <v>45365</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7813,7 +7813,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7856,7 +7856,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 17528-2024</t>
+          <t>A 44020-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7870,10 +7870,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45415</v>
+        <v>45915</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7886,7 +7886,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7929,7 +7929,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 52922-2024</t>
+          <t>A 44600-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7943,10 +7943,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45610</v>
+        <v>45917</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.2</v>
+        <v>7.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8002,7 +8002,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 7228-2025</t>
+          <t>A 44573-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8016,10 +8016,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45702</v>
+        <v>45917</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8032,7 +8032,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.4</v>
+        <v>5.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8075,7 +8075,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 14596-2022</t>
+          <t>A 17685-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8089,10 +8089,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44655</v>
+        <v>45418</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 13800-2023</t>
+          <t>A 44608-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8162,10 +8162,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45007</v>
+        <v>45917</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8178,7 +8178,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8221,7 +8221,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 8155-2023</t>
+          <t>A 33666-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8235,10 +8235,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44974</v>
+        <v>45132</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8251,7 +8251,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.7</v>
+        <v>0.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8294,7 +8294,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 1830-2026</t>
+          <t>A 1921-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8308,10 +8308,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46035</v>
+        <v>45671</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8367,7 +8367,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 1827-2026</t>
+          <t>A 6283-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8381,10 +8381,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46035</v>
+        <v>44965</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8440,7 +8440,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 12157-2022</t>
+          <t>A 1883-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8450,14 +8450,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44636</v>
+        <v>44939</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8470,7 +8470,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8513,7 +8513,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 28319-2025</t>
+          <t>A 45991-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8527,10 +8527,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45818</v>
+        <v>45924</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.9</v>
+        <v>4.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8586,7 +8586,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 28870-2025</t>
+          <t>A 45935-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8600,10 +8600,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45820</v>
+        <v>45923</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>7.9</v>
+        <v>1.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8659,7 +8659,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 3178-2026</t>
+          <t>A 45861-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8673,10 +8673,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46041</v>
+        <v>45923</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8689,7 +8689,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.8</v>
+        <v>10.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8732,7 +8732,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 27908-2025</t>
+          <t>A 18055-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8746,10 +8746,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45817</v>
+        <v>46125</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.1</v>
+        <v>5.2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8805,7 +8805,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 3250-2026</t>
+          <t>A 46668-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8819,10 +8819,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46041</v>
+        <v>45926</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8835,7 +8835,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8878,7 +8878,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 51783-2023</t>
+          <t>A 46872-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8892,10 +8892,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45222</v>
+        <v>45929</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 42723-2025</t>
+          <t>A 52269-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8965,10 +8965,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45908</v>
+        <v>44873</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8981,7 +8981,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.4</v>
+        <v>4.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9024,7 +9024,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 3201-2026</t>
+          <t>A 53317-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9038,10 +9038,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46041</v>
+        <v>45614</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9054,7 +9054,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>3.2</v>
+        <v>0.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9097,7 +9097,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 43398-2025</t>
+          <t>A 49718-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9111,10 +9111,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45911</v>
+        <v>45939</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9127,7 +9127,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9170,7 +9170,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 39535-2024</t>
+          <t>A 43353-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9184,10 +9184,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45551</v>
+        <v>45568</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>4.7</v>
+        <v>1.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9243,7 +9243,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 7443-2023</t>
+          <t>A 10356-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9257,10 +9257,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44971</v>
+        <v>45720</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9316,7 +9316,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 44020-2025</t>
+          <t>A 15323-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9330,10 +9330,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45915</v>
+        <v>45400</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9346,7 +9346,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3.1</v>
+        <v>10.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9389,7 +9389,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 5324-2026</t>
+          <t>A 43406-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9403,10 +9403,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46050</v>
+        <v>45911</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9419,7 +9419,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9462,7 +9462,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 44600-2025</t>
+          <t>A 53232-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9476,10 +9476,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45917</v>
+        <v>45958</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9492,7 +9492,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>7.2</v>
+        <v>0.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9535,7 +9535,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 32842-2025</t>
+          <t>A 493-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9549,10 +9549,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45839</v>
+        <v>45664</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>6.1</v>
+        <v>3.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9608,7 +9608,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 44608-2025</t>
+          <t>A 50478-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9622,10 +9622,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45917</v>
+        <v>45945</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9681,7 +9681,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 44573-2025</t>
+          <t>A 50482-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9695,10 +9695,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45917</v>
+        <v>45945</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>5.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9754,7 +9754,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 10356-2025</t>
+          <t>A 49449-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9768,10 +9768,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45720</v>
+        <v>45938</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9827,7 +9827,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 45861-2025</t>
+          <t>A 20573-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9841,10 +9841,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45923</v>
+        <v>46140</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9856,8 +9856,13 @@
           <t>MELLERUD</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>10.2</v>
+        <v>1.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9900,7 +9905,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 17685-2024</t>
+          <t>A 334-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9914,10 +9919,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45418</v>
+        <v>44929</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9930,7 +9935,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9973,7 +9978,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 45935-2025</t>
+          <t>A 24312-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9987,10 +9992,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45923</v>
+        <v>45797</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10003,7 +10008,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10046,7 +10051,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 45991-2025</t>
+          <t>A 53307-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10060,10 +10065,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45924</v>
+        <v>45614</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10076,7 +10081,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10119,7 +10124,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 7047-2026</t>
+          <t>A 53565-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10133,10 +10138,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46057</v>
+        <v>44879</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10149,7 +10154,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10192,7 +10197,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 7125-2026</t>
+          <t>A 56349-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10206,10 +10211,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46058</v>
+        <v>45974</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10222,7 +10227,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10265,7 +10270,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 23450-2025</t>
+          <t>A 56026-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10279,10 +10284,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45792</v>
+        <v>45973</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10295,7 +10300,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10338,7 +10343,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 7120-2026</t>
+          <t>A 28865-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10352,10 +10357,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46058</v>
+        <v>45820</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10368,7 +10373,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10411,7 +10416,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 46872-2025</t>
+          <t>A 36146-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10425,10 +10430,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45929</v>
+        <v>45866</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10441,7 +10446,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10484,7 +10489,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 7117-2026</t>
+          <t>A 17160-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10498,10 +10503,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46058</v>
+        <v>45412</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10514,7 +10519,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.8</v>
+        <v>3.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10557,7 +10562,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 46668-2025</t>
+          <t>A 19545-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10571,10 +10576,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45926</v>
+        <v>45429</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10587,7 +10592,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10630,7 +10635,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 8160-2026</t>
+          <t>A 59723-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10644,10 +10649,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46064</v>
+        <v>45992</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10660,7 +10665,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.7</v>
+        <v>12.3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10703,7 +10708,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 11442-2024</t>
+          <t>A 52128-2021</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10717,10 +10722,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45372</v>
+        <v>44463</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10733,7 +10738,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10776,7 +10781,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 15227-2025</t>
+          <t>A 46917-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10790,10 +10795,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45744</v>
+        <v>44851</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10806,7 +10811,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10849,7 +10854,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 26639-2025</t>
+          <t>A 35603-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10863,10 +10868,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45810</v>
+        <v>45531</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10879,7 +10884,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>5.4</v>
+        <v>1.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10922,7 +10927,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 36141-2025</t>
+          <t>A 40064-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10936,10 +10941,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45866</v>
+        <v>45168</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10952,7 +10957,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10995,7 +11000,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 36048-2025</t>
+          <t>A 26428-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11009,10 +11014,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45866</v>
+        <v>44736</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11025,7 +11030,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11068,7 +11073,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 35605-2024</t>
+          <t>A 60996-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11082,10 +11087,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45531</v>
+        <v>44914</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11098,7 +11103,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11141,7 +11146,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 9573-2026</t>
+          <t>A 8923-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11155,10 +11160,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46071</v>
+        <v>45356</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11171,7 +11176,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11214,7 +11219,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 16656-2022</t>
+          <t>A 59808-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11228,10 +11233,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44672</v>
+        <v>45992</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11244,7 +11249,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11287,7 +11292,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 49718-2025</t>
+          <t>A 59806-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11301,10 +11306,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45939</v>
+        <v>45992</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11317,7 +11322,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11360,7 +11365,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 11249-2026</t>
+          <t>A 59804-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11374,10 +11379,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46080</v>
+        <v>45992</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11390,7 +11395,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11433,7 +11438,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 11121-2026</t>
+          <t>A 25109-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11443,14 +11448,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46079</v>
+        <v>44729</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11463,7 +11468,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11506,7 +11511,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 36963-2025</t>
+          <t>A 59802-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11520,10 +11525,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45874</v>
+        <v>45992</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11536,7 +11541,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11579,7 +11584,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 11323-2026</t>
+          <t>A 12157-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11593,10 +11598,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46080</v>
+        <v>44636</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11609,7 +11614,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>7.3</v>
+        <v>2.7</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11652,7 +11657,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 52471-2023</t>
+          <t>A 60203-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11666,10 +11671,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45225</v>
+        <v>45994</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11682,7 +11687,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11725,7 +11730,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 38040-2025</t>
+          <t>A 21432-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11739,10 +11744,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45882</v>
+        <v>46148</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11755,7 +11760,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2</v>
+        <v>4.3</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11798,7 +11803,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 38663-2025</t>
+          <t>A 61177-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11808,14 +11813,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45884</v>
+        <v>46000</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11828,7 +11833,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>4.2</v>
+        <v>0.9</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11871,7 +11876,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 43406-2025</t>
+          <t>A 61180-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11885,10 +11890,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45911</v>
+        <v>46000</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11901,7 +11906,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11944,7 +11949,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 25109-2022</t>
+          <t>A 22364-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11958,10 +11963,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44729</v>
+        <v>46154</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11974,7 +11979,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12017,7 +12022,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 53307-2024</t>
+          <t>A 25399-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12027,14 +12032,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45614</v>
+        <v>45089</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12047,7 +12052,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12090,7 +12095,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 39728-2023</t>
+          <t>A 50441-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12104,10 +12109,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45167</v>
+        <v>45216</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12120,7 +12125,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12163,7 +12168,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 17543-2023</t>
+          <t>A 9456-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12177,10 +12182,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45036</v>
+        <v>45359</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12236,7 +12241,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 53254-2022</t>
+          <t>A 21977-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12250,10 +12255,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44876</v>
+        <v>46153</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12266,7 +12271,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12309,7 +12314,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 13594-2026</t>
+          <t>A 22337-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12319,14 +12324,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46096</v>
+        <v>46154</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12339,7 +12344,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12382,7 +12387,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 1921-2025</t>
+          <t>A 32304-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12396,10 +12401,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45671</v>
+        <v>45512</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12412,7 +12417,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12455,7 +12460,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 50478-2025</t>
+          <t>A 63249-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12469,10 +12474,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45945</v>
+        <v>46010</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12485,7 +12490,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12528,7 +12533,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 50482-2025</t>
+          <t>A 1369-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12542,10 +12547,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45945</v>
+        <v>45667</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12558,7 +12563,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>8.800000000000001</v>
+        <v>1.9</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12601,7 +12606,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 53232-2025</t>
+          <t>A 16746-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12615,10 +12620,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45958</v>
+        <v>45030</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12631,7 +12636,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12674,7 +12679,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 60996-2022</t>
+          <t>A 51436-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12688,10 +12693,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44914</v>
+        <v>45950</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12704,7 +12709,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12747,7 +12752,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 18055-2026</t>
+          <t>A 59865-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12761,10 +12766,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46125</v>
+        <v>45639</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12777,7 +12782,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12820,7 +12825,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 15323-2024</t>
+          <t>A 4416-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12834,10 +12839,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45400</v>
+        <v>45686</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12850,7 +12855,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>10.6</v>
+        <v>0.5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12893,7 +12898,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 10398-2024</t>
+          <t>A 15971-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12907,10 +12912,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45365</v>
+        <v>45022</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12923,7 +12928,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12966,7 +12971,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 56026-2025</t>
+          <t>A 32832-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12980,10 +12985,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45973</v>
+        <v>45516</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12996,7 +13001,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13039,7 +13044,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 56349-2025</t>
+          <t>A 53254-2022</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13053,10 +13058,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45974</v>
+        <v>44876</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13069,7 +13074,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13112,7 +13117,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 24312-2025</t>
+          <t>A 28863-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13126,10 +13131,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45797</v>
+        <v>45820</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13142,7 +13147,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13185,7 +13190,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 493-2025</t>
+          <t>A 1830-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13199,10 +13204,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45664</v>
+        <v>46035</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13215,7 +13220,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13258,7 +13263,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 35603-2024</t>
+          <t>A 1827-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13272,10 +13277,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45531</v>
+        <v>46035</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13288,7 +13293,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13331,7 +13336,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 58861-2022</t>
+          <t>A 73351-2021</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13345,10 +13350,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44903</v>
+        <v>44551</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13361,7 +13366,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>4.8</v>
+        <v>6.1</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13404,7 +13409,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 11256-2025</t>
+          <t>A 53270-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13418,10 +13423,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45726</v>
+        <v>45614</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13434,7 +13439,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13477,7 +13482,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 36146-2025</t>
+          <t>A 3250-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13491,10 +13496,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45866</v>
+        <v>46041</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13507,7 +13512,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13550,7 +13555,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 8923-2024</t>
+          <t>A 51916-2022</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13560,14 +13565,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45356</v>
+        <v>44868</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13580,7 +13585,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13623,7 +13628,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 49449-2025</t>
+          <t>A 5647-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13637,10 +13642,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45938</v>
+        <v>44960</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13653,7 +13658,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13696,7 +13701,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 39942-2023</t>
+          <t>A 3178-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13710,10 +13715,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45167</v>
+        <v>46041</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13726,7 +13731,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13769,7 +13774,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 59804-2025</t>
+          <t>A 7443-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13783,10 +13788,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45992</v>
+        <v>44971</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13799,7 +13804,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13842,7 +13847,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 59802-2025</t>
+          <t>A 59269-2025</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13856,10 +13861,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45992</v>
+        <v>45988</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13872,7 +13877,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.8</v>
+        <v>3.5</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13915,7 +13920,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 59808-2025</t>
+          <t>A 3201-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13929,10 +13934,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45992</v>
+        <v>46041</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13945,7 +13950,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13988,7 +13993,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 3998-2025</t>
+          <t>A 35605-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14002,10 +14007,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45684</v>
+        <v>45531</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14018,7 +14023,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>8.199999999999999</v>
+        <v>1.4</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14061,7 +14066,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 59806-2025</t>
+          <t>A 61811-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14075,10 +14080,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45992</v>
+        <v>45264</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14090,8 +14095,13 @@
           <t>MELLERUD</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I173" t="n">
-        <v>0.5</v>
+        <v>7.9</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14134,7 +14144,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 60203-2025</t>
+          <t>A 1886-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14148,10 +14158,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45994</v>
+        <v>44939</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14164,7 +14174,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14207,7 +14217,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 61177-2025</t>
+          <t>A 25036-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14217,14 +14227,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46000</v>
+        <v>46174</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14237,7 +14247,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.9</v>
+        <v>5.9</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14280,7 +14290,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 61180-2025</t>
+          <t>A 5324-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14294,10 +14304,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46000</v>
+        <v>46050</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14310,7 +14320,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14353,7 +14363,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 32384-2023</t>
+          <t>A 36138-2025</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14367,10 +14377,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45120</v>
+        <v>45866</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14383,7 +14393,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14426,7 +14436,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 53565-2022</t>
+          <t>A 25458-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14440,10 +14450,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44879</v>
+        <v>46177</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14456,7 +14466,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14499,7 +14509,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 59723-2025</t>
+          <t>A 34415-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14513,10 +14523,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45992</v>
+        <v>45525</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14529,7 +14539,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>12.3</v>
+        <v>4.3</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14572,7 +14582,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 20573-2026</t>
+          <t>A 25954-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14586,10 +14596,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46140</v>
+        <v>46181</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14601,13 +14611,8 @@
           <t>MELLERUD</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I180" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14650,7 +14655,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 6283-2023</t>
+          <t>A 7117-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14664,10 +14669,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44965</v>
+        <v>46058</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14680,7 +14685,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14723,7 +14728,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 40064-2023</t>
+          <t>A 7125-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14737,10 +14742,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45168</v>
+        <v>46058</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14753,7 +14758,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14796,7 +14801,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 28865-2025</t>
+          <t>A 7047-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14810,10 +14815,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45820</v>
+        <v>46057</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14826,7 +14831,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14869,7 +14874,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 34415-2024</t>
+          <t>A 7120-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14883,10 +14888,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45525</v>
+        <v>46058</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14899,7 +14904,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>4.3</v>
+        <v>0.8</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14942,7 +14947,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 32304-2024</t>
+          <t>A 33092-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14956,10 +14961,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45512</v>
+        <v>45126</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14972,7 +14977,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15015,7 +15020,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 46761-2023</t>
+          <t>A 26527-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15029,10 +15034,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45198</v>
+        <v>46183</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15042,6 +15047,11 @@
       <c r="G186" t="inlineStr">
         <is>
           <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I186" t="n">
@@ -15088,7 +15098,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 21077-2023</t>
+          <t>A 40065-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15102,10 +15112,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45057</v>
+        <v>45168</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15118,7 +15128,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15161,7 +15171,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 22313-2023</t>
+          <t>A 8160-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15175,10 +15185,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45070</v>
+        <v>46064</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15191,7 +15201,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15234,7 +15244,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 52128-2021</t>
+          <t>A 26536-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15248,10 +15258,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>44463</v>
+        <v>46183</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15263,8 +15273,13 @@
           <t>MELLERUD</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I189" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15307,7 +15322,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 17160-2024</t>
+          <t>A 3989-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15321,10 +15336,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45412</v>
+        <v>44952</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15337,7 +15352,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15380,7 +15395,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 48256-2022</t>
+          <t>A 51783-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15394,10 +15409,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44858</v>
+        <v>45222</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15410,7 +15425,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15453,7 +15468,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 21432-2026</t>
+          <t>A 9573-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15467,10 +15482,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46148</v>
+        <v>46071</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15483,7 +15498,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15526,7 +15541,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 21977-2026</t>
+          <t>A 32498-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15540,10 +15555,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46153</v>
+        <v>45513</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15556,7 +15571,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15599,7 +15614,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 22364-2026</t>
+          <t>A 9374-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15613,10 +15628,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46154</v>
+        <v>44981</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15629,7 +15644,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15672,7 +15687,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 22337-2026</t>
+          <t>A 48256-2022</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15686,10 +15701,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46154</v>
+        <v>44858</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15702,7 +15717,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15745,7 +15760,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 8152-2023</t>
+          <t>A 23238-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15759,10 +15774,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44974</v>
+        <v>45453</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15775,7 +15790,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15818,7 +15833,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 16746-2023</t>
+          <t>A 27510-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15832,10 +15847,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45030</v>
+        <v>45097</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15848,7 +15863,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15891,7 +15906,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 1369-2025</t>
+          <t>A 7154-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15901,14 +15916,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45667</v>
+        <v>45344</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15921,7 +15936,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15964,7 +15979,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 32832-2024</t>
+          <t>A 24978-2022</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15978,10 +15993,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45516</v>
+        <v>44728</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15994,7 +16009,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16037,7 +16052,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 59865-2024</t>
+          <t>A 18205-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16051,10 +16066,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45639</v>
+        <v>45420</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16067,7 +16082,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>5.9</v>
+        <v>0.9</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16110,7 +16125,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 51436-2025</t>
+          <t>A 32520-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16124,10 +16139,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45950</v>
+        <v>46239</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16140,7 +16155,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16183,7 +16198,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 28863-2025</t>
+          <t>A 17543-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16197,10 +16212,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45820</v>
+        <v>45036</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16213,7 +16228,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16256,7 +16271,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 40065-2023</t>
+          <t>A 32691-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16270,10 +16285,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45168</v>
+        <v>46240</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16286,7 +16301,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16329,7 +16344,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 59269-2025</t>
+          <t>A 17538-2023</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16343,10 +16358,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45988</v>
+        <v>45036</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16359,7 +16374,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16402,7 +16417,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 25036-2026</t>
+          <t>A 11219-2024</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16416,10 +16431,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46174</v>
+        <v>45371</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16432,7 +16447,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16475,7 +16490,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 36138-2025</t>
+          <t>A 22313-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16489,10 +16504,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45866</v>
+        <v>45070</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16505,7 +16520,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16548,7 +16563,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 25458-2026</t>
+          <t>A 14568-2022</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16562,10 +16577,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46177</v>
+        <v>44655</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16578,7 +16593,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16621,7 +16636,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 25954-2026</t>
+          <t>A 32384-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16635,10 +16650,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46181</v>
+        <v>45120</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16651,7 +16666,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16694,7 +16709,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 26536-2026</t>
+          <t>A 29936-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16708,10 +16723,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46183</v>
+        <v>46205</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16723,13 +16738,8 @@
           <t>MELLERUD</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I209" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16772,7 +16782,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 26527-2026</t>
+          <t>A 33450-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16786,10 +16796,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46183</v>
+        <v>46246</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16801,13 +16811,8 @@
           <t>MELLERUD</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I210" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16850,7 +16855,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 32520-2026</t>
+          <t>A 29939-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16864,10 +16869,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46239</v>
+        <v>46205</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16880,7 +16885,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16923,7 +16928,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 45834-2023</t>
+          <t>A 39942-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16937,10 +16942,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45195</v>
+        <v>45167</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16953,7 +16958,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16996,7 +17001,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 51463-2023</t>
+          <t>A 20578-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17010,10 +17015,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45221</v>
+        <v>46140</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17025,8 +17030,13 @@
           <t>MELLERUD</t>
         </is>
       </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I213" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17069,7 +17079,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 32691-2026</t>
+          <t>A 12713-2022</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17083,10 +17093,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46240</v>
+        <v>44641</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17099,7 +17109,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17142,7 +17152,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 8492-2022</t>
+          <t>A 18854-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17156,10 +17166,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>44613</v>
+        <v>45042</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17172,7 +17182,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17215,7 +17225,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 33450-2026</t>
+          <t>A 34065-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17229,10 +17239,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46246</v>
+        <v>46252</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17245,7 +17255,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17288,7 +17298,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 20578-2026</t>
+          <t>A 51785-2023</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17302,10 +17312,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46140</v>
+        <v>45222</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17317,13 +17327,8 @@
           <t>MELLERUD</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I217" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17366,7 +17371,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 29936-2026</t>
+          <t>A 3998-2025</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17380,10 +17385,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46205</v>
+        <v>45684</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17396,7 +17401,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17439,7 +17444,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 29939-2026</t>
+          <t>A 19872-2023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17453,10 +17458,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46205</v>
+        <v>45054</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17469,7 +17474,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>3</v>
+        <v>8.4</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17512,7 +17517,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 48879-2024</t>
+          <t>A 8492-2022</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17526,10 +17531,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45594</v>
+        <v>44613</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17542,7 +17547,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17585,7 +17590,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 5647-2023</t>
+          <t>A 10428-2022</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17599,10 +17604,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>44960</v>
+        <v>44623</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17615,7 +17620,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17658,7 +17663,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 34065-2026</t>
+          <t>A 21618-2024</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17672,10 +17677,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>46252</v>
+        <v>45442</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17688,7 +17693,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17731,7 +17736,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 12334-2024</t>
+          <t>A 21620-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17745,10 +17750,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45378</v>
+        <v>45442</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17761,7 +17766,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17804,7 +17809,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 12713-2022</t>
+          <t>A 33388-2022</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17818,10 +17823,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>44641</v>
+        <v>44788</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17834,7 +17839,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>2.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17877,7 +17882,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 11219-2024</t>
+          <t>A 46761-2023</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17891,10 +17896,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45371</v>
+        <v>45198</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17907,7 +17912,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>6</v>
+        <v>1.3</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17950,7 +17955,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 18205-2024</t>
+          <t>A 58861-2022</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17964,10 +17969,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45420</v>
+        <v>44903</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17980,7 +17985,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>0.9</v>
+        <v>4.8</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18023,7 +18028,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 31836-2026</t>
+          <t>A 39728-2023</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18037,10 +18042,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>46230</v>
+        <v>45167</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18053,7 +18058,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18096,7 +18101,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 36960-2026</t>
+          <t>A 51173-2023</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18110,10 +18115,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>46273</v>
+        <v>45212</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18126,7 +18131,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>8.1</v>
+        <v>2</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18169,7 +18174,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 10428-2022</t>
+          <t>A 31836-2026</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18183,10 +18188,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>44623</v>
+        <v>46230</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18199,7 +18204,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18242,7 +18247,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 31889-2026</t>
+          <t>A 4054-2025</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18256,10 +18261,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>46231</v>
+        <v>45684</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18272,7 +18277,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18315,7 +18320,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 54796-2022</t>
+          <t>A 14596-2022</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18329,10 +18334,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>44883</v>
+        <v>44655</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18345,7 +18350,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18388,7 +18393,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 53573-2023</t>
+          <t>A 39535-2024</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18402,10 +18407,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45230</v>
+        <v>45551</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18418,7 +18423,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18461,7 +18466,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 34116-2023</t>
+          <t>A 32549-2024</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18471,14 +18476,14 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45126</v>
+        <v>45513</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18491,7 +18496,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>4.3</v>
+        <v>1</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18534,7 +18539,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 1883-2023</t>
+          <t>A 21077-2023</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18548,10 +18553,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>44939</v>
+        <v>45057</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18564,7 +18569,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18607,7 +18612,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 1886-2023</t>
+          <t>A 36960-2026</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18621,10 +18626,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>44939</v>
+        <v>46273</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18637,7 +18642,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>1</v>
+        <v>8.1</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18680,7 +18685,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 27510-2023</t>
+          <t>A 9152-2024</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18694,10 +18699,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45097</v>
+        <v>45357</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18710,7 +18715,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18753,7 +18758,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 334-2023</t>
+          <t>A 31889-2026</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18767,10 +18772,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>44929</v>
+        <v>46231</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18783,7 +18788,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18826,7 +18831,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 32299-2024</t>
+          <t>A 8152-2023</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18840,10 +18845,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45512</v>
+        <v>44974</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18856,7 +18861,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18899,7 +18904,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 32498-2024</t>
+          <t>A 21698-2025</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18913,10 +18918,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45513</v>
+        <v>45783</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18929,7 +18934,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18972,7 +18977,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 43353-2024</t>
+          <t>A 21678-2025</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18986,10 +18991,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45568</v>
+        <v>45783</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19002,7 +19007,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -19045,7 +19050,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 51916-2022</t>
+          <t>A 21689-2025</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -19055,14 +19060,14 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>44868</v>
+        <v>45783</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19075,7 +19080,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -19118,7 +19123,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 33666-2023</t>
+          <t>A 27342-2024</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19132,10 +19137,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45132</v>
+        <v>45473</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19148,7 +19153,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19191,7 +19196,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 51785-2023</t>
+          <t>A 13313-2024</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19205,10 +19210,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45222</v>
+        <v>45386</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19221,7 +19226,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19264,7 +19269,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 33092-2023</t>
+          <t>A 8667-2025</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19278,10 +19283,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45126</v>
+        <v>45712</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19294,7 +19299,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19337,7 +19342,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 55391-2023</t>
+          <t>A 60993-2022</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19351,10 +19356,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45238</v>
+        <v>44914</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19367,7 +19372,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19410,7 +19415,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 15971-2023</t>
+          <t>A 10100-2025</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19424,10 +19429,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45022</v>
+        <v>45719</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19440,7 +19445,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19483,7 +19488,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 53317-2024</t>
+          <t>A 10097-2025</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19497,10 +19502,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45614</v>
+        <v>45719</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19513,7 +19518,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>0.3</v>
+        <v>2.6</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19556,7 +19561,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 73351-2021</t>
+          <t>A 10357-2025</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19570,10 +19575,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>44551</v>
+        <v>45720</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19586,7 +19591,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>6.1</v>
+        <v>0.9</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19629,7 +19634,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 26428-2022</t>
+          <t>A 10358-2025</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19643,10 +19648,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>44736</v>
+        <v>45720</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19659,7 +19664,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19702,7 +19707,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 21618-2024</t>
+          <t>A 11213-2025</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19716,10 +19721,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45442</v>
+        <v>45726</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19732,7 +19737,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>1</v>
+        <v>4.8</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19775,7 +19780,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 21620-2024</t>
+          <t>A 24527-2025</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19789,10 +19794,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>45442</v>
+        <v>45798</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19805,7 +19810,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -19848,7 +19853,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 26530-2023</t>
+          <t>A 24533-2025</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19862,10 +19867,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45092</v>
+        <v>45798</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19878,7 +19883,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>2.5</v>
+        <v>5.8</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19921,7 +19926,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 18854-2023</t>
+          <t>A 43017-2024</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19935,10 +19940,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45042</v>
+        <v>45567</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19951,7 +19956,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -19994,7 +19999,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 14568-2022</t>
+          <t>A 25652-2025</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -20008,10 +20013,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>44655</v>
+        <v>45803</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20024,7 +20029,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -20067,7 +20072,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 61811-2023</t>
+          <t>A 25635-2025</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20081,10 +20086,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45264</v>
+        <v>45803</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20096,13 +20101,8 @@
           <t>MELLERUD</t>
         </is>
       </c>
-      <c r="H255" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I255" t="n">
-        <v>7.9</v>
+        <v>0.4</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20145,7 +20145,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 25399-2023</t>
+          <t>A 25623-2025</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20155,14 +20155,14 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45089</v>
+        <v>45803</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20175,7 +20175,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20218,7 +20218,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 23238-2024</t>
+          <t>A 60395-2024</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -20228,14 +20228,14 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>45453</v>
+        <v>45643</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20248,7 +20248,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20291,7 +20291,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 53270-2024</t>
+          <t>A 8165-2023</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20305,10 +20305,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45614</v>
+        <v>44974</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20321,7 +20321,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20364,7 +20364,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 17538-2023</t>
+          <t>A 17528-2024</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20378,10 +20378,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>45036</v>
+        <v>45415</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20437,7 +20437,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 19545-2024</t>
+          <t>A 52922-2024</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -20451,10 +20451,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45429</v>
+        <v>45610</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20467,7 +20467,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -20510,7 +20510,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 50441-2023</t>
+          <t>A 11848-2025</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -20524,10 +20524,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>45216</v>
+        <v>45728</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -20583,7 +20583,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 10401-2024</t>
+          <t>A 12501-2025</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -20597,10 +20597,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>45365</v>
+        <v>45730</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20613,7 +20613,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>7.6</v>
+        <v>2.1</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -20656,7 +20656,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 21689-2025</t>
+          <t>A 17693-2023</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -20670,10 +20670,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>45783</v>
+        <v>45037</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20686,7 +20686,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>1.5</v>
+        <v>11.3</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -20729,7 +20729,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 21678-2025</t>
+          <t>A 7228-2025</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -20743,10 +20743,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>45783</v>
+        <v>45702</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20759,7 +20759,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -20802,7 +20802,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 21698-2025</t>
+          <t>A 28319-2025</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>45783</v>
+        <v>45818</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20832,7 +20832,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -20875,7 +20875,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>A 13313-2024</t>
+          <t>A 28870-2025</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -20889,10 +20889,10 @@
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>45386</v>
+        <v>45820</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20905,7 +20905,7 @@
         </is>
       </c>
       <c r="I266" t="n">
-        <v>2.1</v>
+        <v>7.9</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -20948,7 +20948,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>A 27342-2024</t>
+          <t>A 32842-2025</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -20962,10 +20962,10 @@
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>45473</v>
+        <v>45839</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20978,7 +20978,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>2.4</v>
+        <v>6.1</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -21021,7 +21021,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>A 10100-2025</t>
+          <t>A 23450-2025</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -21035,10 +21035,10 @@
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>45719</v>
+        <v>45792</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21051,7 +21051,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -21094,7 +21094,7 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>A 8667-2025</t>
+          <t>A 11442-2024</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -21108,10 +21108,10 @@
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>45712</v>
+        <v>45372</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21124,7 +21124,7 @@
         </is>
       </c>
       <c r="I269" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -21167,7 +21167,7 @@
     <row r="270" ht="15" customHeight="1">
       <c r="A270" t="inlineStr">
         <is>
-          <t>A 10357-2025</t>
+          <t>A 36141-2025</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -21181,10 +21181,10 @@
         </is>
       </c>
       <c r="D270" s="1" t="n">
-        <v>45720</v>
+        <v>45866</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21240,7 +21240,7 @@
     <row r="271" ht="15" customHeight="1">
       <c r="A271" t="inlineStr">
         <is>
-          <t>A 10358-2025</t>
+          <t>A 26639-2025</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -21254,10 +21254,10 @@
         </is>
       </c>
       <c r="D271" s="1" t="n">
-        <v>45720</v>
+        <v>45810</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21270,7 +21270,7 @@
         </is>
       </c>
       <c r="I271" t="n">
-        <v>0.7</v>
+        <v>5.4</v>
       </c>
       <c r="J271" t="n">
         <v>0</v>
@@ -21313,7 +21313,7 @@
     <row r="272" ht="15" customHeight="1">
       <c r="A272" t="inlineStr">
         <is>
-          <t>A 60993-2022</t>
+          <t>A 15227-2025</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -21327,10 +21327,10 @@
         </is>
       </c>
       <c r="D272" s="1" t="n">
-        <v>44914</v>
+        <v>45744</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21343,7 +21343,7 @@
         </is>
       </c>
       <c r="I272" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J272" t="n">
         <v>0</v>
@@ -21386,7 +21386,7 @@
     <row r="273" ht="15" customHeight="1">
       <c r="A273" t="inlineStr">
         <is>
-          <t>A 10097-2025</t>
+          <t>A 36048-2025</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -21400,10 +21400,10 @@
         </is>
       </c>
       <c r="D273" s="1" t="n">
-        <v>45719</v>
+        <v>45866</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21416,7 +21416,7 @@
         </is>
       </c>
       <c r="I273" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J273" t="n">
         <v>0</v>
@@ -21459,7 +21459,7 @@
     <row r="274" ht="15" customHeight="1">
       <c r="A274" t="inlineStr">
         <is>
-          <t>A 11213-2025</t>
+          <t>A 36963-2025</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -21473,10 +21473,10 @@
         </is>
       </c>
       <c r="D274" s="1" t="n">
-        <v>45726</v>
+        <v>45874</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21489,7 +21489,7 @@
         </is>
       </c>
       <c r="I274" t="n">
-        <v>4.8</v>
+        <v>0.7</v>
       </c>
       <c r="J274" t="n">
         <v>0</v>
@@ -21549,7 +21549,7 @@
         <v>44551</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21622,7 +21622,7 @@
         <v>45351</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21695,7 +21695,7 @@
         <v>46184</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21768,7 +21768,7 @@
         <v>46188</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>

--- a/Översikt MELLERUD.xlsx
+++ b/Översikt MELLERUD.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE280"/>
+  <dimension ref="A1:AE279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>46184</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>46112</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>45614</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>44840</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>45614</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>45734</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>46020</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>45670</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>45253</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>44963</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>45006</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 25764-2025</t>
+          <t>A 28216-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1868,10 +1868,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45804</v>
+        <v>46196</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1881,22 +1881,27 @@
       <c r="G13" t="inlineStr">
         <is>
           <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I13" t="n">
         <v>2.5</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
         <v>1</v>
@@ -1908,21 +1913,242 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
       </c>
       <c r="T13" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Gulvit blekspik
+Guldlockmossa
+Gröngöling</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 28216-2026 artfynd.xlsx", "A 28216-2026")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 28216-2026 karta.png", "A 28216-2026")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 28216-2026 georefererad karta.tif", "A 28216-2026")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 28216-2026 FSC-klagomål.docx", "A 28216-2026")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 28216-2026 FSC-klagomål mail.docx", "A 28216-2026")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 28216-2026 tillsynsbegäran.docx", "A 28216-2026")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 28216-2026 tillsynsbegäran mail.docx", "A 28216-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 33141-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
+      <c r="T14" t="n">
+        <v>7</v>
+      </c>
+      <c r="U14" t="n">
+        <v>7</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Kattfotslav
+Grön sköldmossa
+Kornknutmossa
+Mandelriska</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 33141-2026 artfynd.xlsx", "A 33141-2026")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 33141-2026 karta.png", "A 33141-2026")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 33141-2026 georefererad karta.tif", "A 33141-2026")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 33141-2026 FSC-klagomål.docx", "A 33141-2026")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 33141-2026 FSC-klagomål mail.docx", "A 33141-2026")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 33141-2026 tillsynsbegäran.docx", "A 33141-2026")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 33141-2026 tillsynsbegäran mail.docx", "A 33141-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 25764-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45804</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4</v>
+      </c>
+      <c r="T15" t="n">
         <v>5</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Ask
 Guldlockmossa
@@ -1930,261 +2156,35 @@
 Rostfläck</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 25764-2025 artfynd.xlsx", "A 25764-2025")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 25764-2025 karta.png", "A 25764-2025")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 25764-2025 georefererad karta.tif", "A 25764-2025")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 25764-2025 FSC-klagomål.docx", "A 25764-2025")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 25764-2025 FSC-klagomål mail.docx", "A 25764-2025")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 25764-2025 tillsynsbegäran.docx", "A 25764-2025")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 25764-2025 tillsynsbegäran mail.docx", "A 25764-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 28216-2026</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>46196</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2</v>
-      </c>
-      <c r="S14" t="n">
-        <v>4</v>
-      </c>
-      <c r="T14" t="n">
-        <v>4</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Gulvit blekspik
-Guldlockmossa
-Gröngöling</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 28216-2026 artfynd.xlsx", "A 28216-2026")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 28216-2026 karta.png", "A 28216-2026")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 28216-2026 georefererad karta.tif", "A 28216-2026")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 28216-2026 FSC-klagomål.docx", "A 28216-2026")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 28216-2026 FSC-klagomål mail.docx", "A 28216-2026")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 28216-2026 tillsynsbegäran.docx", "A 28216-2026")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 28216-2026 tillsynsbegäran mail.docx", "A 28216-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 33141-2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46244</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>4</v>
-      </c>
-      <c r="T15" t="n">
-        <v>7</v>
-      </c>
-      <c r="U15" t="n">
-        <v>7</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Kattfotslav
-Grön sköldmossa
-Kornknutmossa
-Mandelriska</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 33141-2026 artfynd.xlsx", "A 33141-2026")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 33141-2026 karta.png", "A 33141-2026")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 33141-2026 georefererad karta.tif", "A 33141-2026")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 33141-2026 FSC-klagomål.docx", "A 33141-2026")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 33141-2026 FSC-klagomål mail.docx", "A 33141-2026")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 33141-2026 tillsynsbegäran.docx", "A 33141-2026")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 33141-2026 tillsynsbegäran mail.docx", "A 33141-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>46020</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>45390</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>44896</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>44804</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>44750</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 10814-2024</t>
+          <t>A 43349-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45369</v>
+        <v>45568</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2756,13 +2756,8 @@
           <t>MELLERUD</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>6.6</v>
+        <v>4.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2771,10 +2766,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2789,7 +2784,7 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2798,682 +2793,687 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 43349-2024 artfynd.xlsx", "A 43349-2024")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 43349-2024 karta.png", "A 43349-2024")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 43349-2024 georefererad karta.tif", "A 43349-2024")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 43349-2024 FSC-klagomål.docx", "A 43349-2024")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 43349-2024 FSC-klagomål mail.docx", "A 43349-2024")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 43349-2024 tillsynsbegäran.docx", "A 43349-2024")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 43349-2024 tillsynsbegäran mail.docx", "A 43349-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 8169-2023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>44974</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 8169-2023 artfynd.xlsx", "A 8169-2023")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 8169-2023 karta.png", "A 8169-2023")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 8169-2023 georefererad karta.tif", "A 8169-2023")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 8169-2023 FSC-klagomål.docx", "A 8169-2023")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 8169-2023 FSC-klagomål mail.docx", "A 8169-2023")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 8169-2023 tillsynsbegäran.docx", "A 8169-2023")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 8169-2023 tillsynsbegäran mail.docx", "A 8169-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 10814-2024</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>45369</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 10814-2024 artfynd.xlsx", "A 10814-2024")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 10814-2024 karta.png", "A 10814-2024")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 10814-2024 georefererad karta.tif", "A 10814-2024")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 10814-2024 FSC-klagomål.docx", "A 10814-2024")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 10814-2024 FSC-klagomål mail.docx", "A 10814-2024")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 10814-2024 tillsynsbegäran.docx", "A 10814-2024")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 10814-2024 tillsynsbegäran mail.docx", "A 10814-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 3992-2023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>44952</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 3992-2023 artfynd.xlsx", "A 3992-2023")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 3992-2023 karta.png", "A 3992-2023")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 3992-2023 georefererad karta.tif", "A 3992-2023")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 3992-2023 FSC-klagomål.docx", "A 3992-2023")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 3992-2023 FSC-klagomål mail.docx", "A 3992-2023")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 3992-2023 tillsynsbegäran.docx", "A 3992-2023")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 3992-2023 tillsynsbegäran mail.docx", "A 3992-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>A 23546-2026</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
         <v>46163</v>
       </c>
-      <c r="E22" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
+      <c r="E25" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
         <v>3.6</v>
       </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
         <v>1</v>
       </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
         <v>1</v>
       </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
         <v>1</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T25" t="n">
         <v>3</v>
       </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Lunglav</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 23546-2026 artfynd.xlsx", "A 23546-2026")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 23546-2026 karta.png", "A 23546-2026")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 23546-2026 georefererad karta.tif", "A 23546-2026")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 23546-2026 FSC-klagomål.docx", "A 23546-2026")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 23546-2026 FSC-klagomål mail.docx", "A 23546-2026")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 23546-2026 tillsynsbegäran.docx", "A 23546-2026")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 23546-2026 tillsynsbegäran mail.docx", "A 23546-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 8169-2023</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>44974</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A 43531-2025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>45911</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>8</v>
+      </c>
+      <c r="J26" t="n">
         <v>1</v>
       </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
         <v>1</v>
       </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
+      <c r="T26" t="n">
         <v>1</v>
       </c>
-      <c r="T23" t="n">
-        <v>1</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Älg</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 8169-2023 artfynd.xlsx", "A 8169-2023")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 8169-2023 karta.png", "A 8169-2023")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 8169-2023 georefererad karta.tif", "A 8169-2023")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 8169-2023 FSC-klagomål.docx", "A 8169-2023")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 8169-2023 FSC-klagomål mail.docx", "A 8169-2023")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 8169-2023 tillsynsbegäran.docx", "A 8169-2023")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 8169-2023 tillsynsbegäran mail.docx", "A 8169-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 43531-2025</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>45911</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>8</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Kungsfågel</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 43531-2025 artfynd.xlsx", "A 43531-2025")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 43531-2025 karta.png", "A 43531-2025")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 43531-2025 georefererad karta.tif", "A 43531-2025")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 43531-2025 FSC-klagomål.docx", "A 43531-2025")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 43531-2025 FSC-klagomål mail.docx", "A 43531-2025")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 43531-2025 tillsynsbegäran.docx", "A 43531-2025")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 43531-2025 tillsynsbegäran mail.docx", "A 43531-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 43349-2024</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>45568</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 26518-2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
         <v>1</v>
       </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
         <v>1</v>
       </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
+      <c r="R27" t="n">
         <v>1</v>
       </c>
-      <c r="T25" t="n">
+      <c r="S27" t="n">
         <v>1</v>
       </c>
-      <c r="U25" t="n">
+      <c r="T27" t="n">
         <v>1</v>
       </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Älg</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 43349-2024 artfynd.xlsx", "A 43349-2024")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 43349-2024 karta.png", "A 43349-2024")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 43349-2024 georefererad karta.tif", "A 43349-2024")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 43349-2024 FSC-klagomål.docx", "A 43349-2024")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 43349-2024 FSC-klagomål mail.docx", "A 43349-2024")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 43349-2024 tillsynsbegäran.docx", "A 43349-2024")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 43349-2024 tillsynsbegäran mail.docx", "A 43349-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 26518-2026</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>46183</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
+      <c r="U27" t="n">
         <v>1</v>
       </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1</v>
-      </c>
-      <c r="S26" t="n">
-        <v>1</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Rotfingersvamp</t>
         </is>
       </c>
-      <c r="W26">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 26518-2026 artfynd.xlsx", "A 26518-2026")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 26518-2026 karta.png", "A 26518-2026")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 26518-2026 georefererad karta.tif", "A 26518-2026")</f>
         <v/>
       </c>
-      <c r="AA26">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 26518-2026 FSC-klagomål.docx", "A 26518-2026")</f>
         <v/>
       </c>
-      <c r="AB26">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 26518-2026 FSC-klagomål mail.docx", "A 26518-2026")</f>
         <v/>
       </c>
-      <c r="AC26">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 26518-2026 tillsynsbegäran.docx", "A 26518-2026")</f>
         <v/>
       </c>
-      <c r="AD26">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 26518-2026 tillsynsbegäran mail.docx", "A 26518-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 3992-2023</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>44952</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>1</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 3992-2023 artfynd.xlsx", "A 3992-2023")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 3992-2023 karta.png", "A 3992-2023")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 3992-2023 georefererad karta.tif", "A 3992-2023")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 3992-2023 FSC-klagomål.docx", "A 3992-2023")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 3992-2023 FSC-klagomål mail.docx", "A 3992-2023")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 3992-2023 tillsynsbegäran.docx", "A 3992-2023")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 3992-2023 tillsynsbegäran mail.docx", "A 3992-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         <v>46281</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>44754</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>44732</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 9008-2022</t>
+          <t>A 32627-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3742,10 +3742,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44615</v>
+        <v>44783</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.1</v>
+        <v>1.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3801,7 +3801,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 32627-2022</t>
+          <t>A 9008-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3815,10 +3815,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44783</v>
+        <v>44615</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3891,7 +3891,7 @@
         <v>44754</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>44461</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>44546</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4110,7 +4110,7 @@
         <v>44752</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>44484</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>44873</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 50370-2021</t>
+          <t>A 53672-2021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4326,10 +4326,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44456</v>
+        <v>44469</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4385,7 +4385,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 53672-2021</t>
+          <t>A 29341-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4399,10 +4399,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44469</v>
+        <v>44752</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.7</v>
+        <v>3.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4458,7 +4458,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 29341-2022</t>
+          <t>A 73-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4472,10 +4472,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44752</v>
+        <v>44564</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4531,7 +4531,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 73-2022</t>
+          <t>A 50694-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4541,14 +4541,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44564</v>
+        <v>44460</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4604,7 +4604,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 50694-2021</t>
+          <t>A 2355-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4614,14 +4614,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44460</v>
+        <v>44578</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4634,7 +4634,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4677,7 +4677,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 2355-2022</t>
+          <t>A 15025-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4691,10 +4691,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44578</v>
+        <v>44657</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4750,7 +4750,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 15025-2022</t>
+          <t>A 44530-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4764,10 +4764,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44657</v>
+        <v>44840</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4840,7 +4840,7 @@
         <v>44620</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4896,7 +4896,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 44530-2022</t>
+          <t>A 17109-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4906,14 +4906,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44840</v>
+        <v>44677</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 17109-2022</t>
+          <t>A 23350-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4979,14 +4979,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44677</v>
+        <v>44720</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5042,7 +5042,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 23350-2022</t>
+          <t>A 17019-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5056,10 +5056,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44720</v>
+        <v>44676</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5115,7 +5115,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 17019-2022</t>
+          <t>A 39171-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44676</v>
+        <v>44817</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5188,7 +5188,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 39171-2022</t>
+          <t>A 71252-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5202,10 +5202,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44817</v>
+        <v>44539</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5261,7 +5261,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 71252-2021</t>
+          <t>A 21097-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5275,10 +5275,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44539</v>
+        <v>44704</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.7</v>
+        <v>0.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5334,7 +5334,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 21097-2022</t>
+          <t>A 63539-2021</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5348,10 +5348,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44704</v>
+        <v>44508</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5407,7 +5407,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 63539-2021</t>
+          <t>A 57801-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5421,10 +5421,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44508</v>
+        <v>44484</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5480,7 +5480,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 57801-2021</t>
+          <t>A 32642-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5494,10 +5494,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44484</v>
+        <v>44783</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5553,7 +5553,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 32642-2022</t>
+          <t>A 26530-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5567,10 +5567,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44783</v>
+        <v>45092</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5626,7 +5626,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 61060-2022</t>
+          <t>A 12334-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5640,10 +5640,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44915</v>
+        <v>45378</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5656,7 +5656,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>8.4</v>
+        <v>2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5699,7 +5699,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 61061-2022</t>
+          <t>A 10401-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5713,10 +5713,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44915</v>
+        <v>45365</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5772,7 +5772,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 3989-2023</t>
+          <t>A 32299-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5786,10 +5786,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44952</v>
+        <v>45512</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5845,7 +5845,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 4054-2025</t>
+          <t>A 37267-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5859,10 +5859,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45684</v>
+        <v>45540</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.9</v>
+        <v>4.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5918,7 +5918,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 9374-2023</t>
+          <t>A 10398-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5932,10 +5932,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44981</v>
+        <v>45365</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5991,7 +5991,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 9152-2024</t>
+          <t>A 17685-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6005,10 +6005,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45357</v>
+        <v>45418</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6064,7 +6064,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 52269-2022</t>
+          <t>A 1921-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6078,10 +6078,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44873</v>
+        <v>45671</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.6</v>
+        <v>0.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6137,7 +6137,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 56025-2024</t>
+          <t>A 33666-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6151,10 +6151,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45624</v>
+        <v>45132</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6210,7 +6210,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 19872-2023</t>
+          <t>A 6283-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6224,10 +6224,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45054</v>
+        <v>44965</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>8.4</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6283,7 +6283,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 9456-2024</t>
+          <t>A 28319-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6297,10 +6297,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45359</v>
+        <v>45818</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6356,7 +6356,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 51173-2023</t>
+          <t>A 1883-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6370,10 +6370,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45212</v>
+        <v>44939</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6429,7 +6429,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 32549-2024</t>
+          <t>A 8160-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6443,10 +6443,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45513</v>
+        <v>46064</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6502,7 +6502,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 7154-2024</t>
+          <t>A 28870-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6512,14 +6512,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45344</v>
+        <v>45820</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.9</v>
+        <v>7.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 4416-2025</t>
+          <t>A 52471-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6589,10 +6589,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45686</v>
+        <v>45225</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6648,7 +6648,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 46917-2022</t>
+          <t>A 9573-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6662,10 +6662,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44851</v>
+        <v>46071</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.8</v>
+        <v>5.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6721,7 +6721,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 37267-2024</t>
+          <t>A 38888-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6735,10 +6735,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45540</v>
+        <v>45887</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4.2</v>
+        <v>1.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6794,7 +6794,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 24533-2025</t>
+          <t>A 53317-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6808,10 +6808,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45798</v>
+        <v>45614</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>5.8</v>
+        <v>0.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6867,7 +6867,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 33388-2022</t>
+          <t>A 43353-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6881,10 +6881,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44788</v>
+        <v>45568</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>8.699999999999999</v>
+        <v>1.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6940,7 +6940,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 14596-2022</t>
+          <t>A 10356-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6954,10 +6954,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44655</v>
+        <v>45720</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7013,7 +7013,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 13800-2023</t>
+          <t>A 11121-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7023,14 +7023,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45007</v>
+        <v>46079</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7086,7 +7086,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 8155-2023</t>
+          <t>A 11323-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7096,14 +7096,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44974</v>
+        <v>46080</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.7</v>
+        <v>7.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7159,7 +7159,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 24978-2022</t>
+          <t>A 11249-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7173,10 +7173,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44728</v>
+        <v>46080</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7232,7 +7232,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 24527-2025</t>
+          <t>A 32842-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7246,10 +7246,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45798</v>
+        <v>45839</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.6</v>
+        <v>6.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7305,7 +7305,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 43017-2024</t>
+          <t>A 13594-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7315,14 +7315,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45567</v>
+        <v>46096</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7378,7 +7378,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 25623-2025</t>
+          <t>A 23450-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7392,10 +7392,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45803</v>
+        <v>45792</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 12157-2022</t>
+          <t>A 334-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7461,14 +7461,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44636</v>
+        <v>44929</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7524,7 +7524,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 25652-2025</t>
+          <t>A 11442-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7538,10 +7538,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45803</v>
+        <v>45372</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7597,7 +7597,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 25635-2025</t>
+          <t>A 53307-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7611,10 +7611,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45803</v>
+        <v>45614</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7670,7 +7670,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 38653-2025</t>
+          <t>A 36141-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7684,10 +7684,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45884</v>
+        <v>45866</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>5.3</v>
+        <v>0.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7743,7 +7743,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 51783-2023</t>
+          <t>A 26639-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7757,10 +7757,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45222</v>
+        <v>45810</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.8</v>
+        <v>5.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7816,7 +7816,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 60395-2024</t>
+          <t>A 15227-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7826,14 +7826,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45643</v>
+        <v>45744</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7889,7 +7889,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 38888-2025</t>
+          <t>A 36048-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7903,10 +7903,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45887</v>
+        <v>45866</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 1830-2026</t>
+          <t>A 36963-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7976,10 +7976,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46035</v>
+        <v>45874</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8035,7 +8035,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 17693-2023</t>
+          <t>A 18055-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8049,10 +8049,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45037</v>
+        <v>46125</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>11.3</v>
+        <v>5.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8108,7 +8108,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 12501-2025</t>
+          <t>A 40064-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8122,10 +8122,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45730</v>
+        <v>45168</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8181,7 +8181,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 11848-2025</t>
+          <t>A 38040-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8195,10 +8195,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45728</v>
+        <v>45882</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 8165-2023</t>
+          <t>A 26428-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8268,10 +8268,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44974</v>
+        <v>44736</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8327,7 +8327,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 17528-2024</t>
+          <t>A 8923-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8341,10 +8341,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45415</v>
+        <v>45356</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8400,7 +8400,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 52922-2024</t>
+          <t>A 38653-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8414,10 +8414,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45610</v>
+        <v>45884</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.2</v>
+        <v>5.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8473,7 +8473,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 1827-2026</t>
+          <t>A 38663-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8487,10 +8487,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46035</v>
+        <v>45884</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.3</v>
+        <v>4.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8546,7 +8546,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 7228-2025</t>
+          <t>A 27908-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8560,10 +8560,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45702</v>
+        <v>45817</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8619,7 +8619,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 39535-2024</t>
+          <t>A 25109-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8633,10 +8633,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45551</v>
+        <v>44729</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8649,7 +8649,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4.7</v>
+        <v>0.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8692,7 +8692,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 7443-2023</t>
+          <t>A 42723-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8706,10 +8706,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44971</v>
+        <v>45908</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8722,7 +8722,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8765,7 +8765,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 28319-2025</t>
+          <t>A 43398-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8779,10 +8779,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45818</v>
+        <v>45911</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8838,7 +8838,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 28870-2025</t>
+          <t>A 44020-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8852,10 +8852,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45820</v>
+        <v>45915</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>7.9</v>
+        <v>3.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8911,7 +8911,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 10356-2025</t>
+          <t>A 44600-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8925,10 +8925,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45720</v>
+        <v>45917</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.5</v>
+        <v>7.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8984,7 +8984,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 17685-2024</t>
+          <t>A 25399-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8994,14 +8994,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45418</v>
+        <v>45089</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9014,7 +9014,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9057,7 +9057,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 27908-2025</t>
+          <t>A 44573-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9071,10 +9071,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45817</v>
+        <v>45917</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.1</v>
+        <v>5.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9130,7 +9130,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 42723-2025</t>
+          <t>A 44608-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9144,10 +9144,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45908</v>
+        <v>45917</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9160,7 +9160,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9203,7 +9203,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 43398-2025</t>
+          <t>A 50441-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9217,10 +9217,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45911</v>
+        <v>45216</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9276,7 +9276,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 32842-2025</t>
+          <t>A 32304-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9290,10 +9290,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45839</v>
+        <v>45512</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9306,7 +9306,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>6.1</v>
+        <v>2.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9349,7 +9349,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 35605-2024</t>
+          <t>A 493-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9363,10 +9363,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45531</v>
+        <v>45664</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9379,7 +9379,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.4</v>
+        <v>3.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9422,7 +9422,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 44020-2025</t>
+          <t>A 45991-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9436,10 +9436,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45915</v>
+        <v>45924</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9452,7 +9452,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9495,7 +9495,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 16656-2022</t>
+          <t>A 49449-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9509,10 +9509,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44672</v>
+        <v>45938</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9568,7 +9568,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 44600-2025</t>
+          <t>A 20573-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9582,10 +9582,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45917</v>
+        <v>46140</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9597,8 +9597,13 @@
           <t>MELLERUD</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>7.2</v>
+        <v>1.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9641,7 +9646,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 44608-2025</t>
+          <t>A 24312-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9655,10 +9660,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45917</v>
+        <v>45797</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9671,7 +9676,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9714,7 +9719,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 44573-2025</t>
+          <t>A 45935-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9728,10 +9733,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45917</v>
+        <v>45923</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9744,7 +9749,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>5.5</v>
+        <v>1.2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9804,7 +9809,7 @@
         <v>45923</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9860,7 +9865,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 23450-2025</t>
+          <t>A 4416-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9874,10 +9879,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45792</v>
+        <v>45686</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9890,7 +9895,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9933,7 +9938,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 45935-2025</t>
+          <t>A 15971-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9947,10 +9952,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45923</v>
+        <v>45022</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9963,7 +9968,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10006,7 +10011,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 45991-2025</t>
+          <t>A 53565-2022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10020,10 +10025,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45924</v>
+        <v>44879</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10036,7 +10041,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>4.4</v>
+        <v>1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10079,7 +10084,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 3178-2026</t>
+          <t>A 53254-2022</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10093,10 +10098,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46041</v>
+        <v>44876</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10109,7 +10114,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10152,7 +10157,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 46872-2025</t>
+          <t>A 28865-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10166,10 +10171,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45929</v>
+        <v>45820</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10182,7 +10187,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10225,7 +10230,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 46668-2025</t>
+          <t>A 36146-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10239,10 +10244,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45926</v>
+        <v>45866</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10255,7 +10260,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10298,7 +10303,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 25109-2022</t>
+          <t>A 59723-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10312,10 +10317,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44729</v>
+        <v>45992</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10328,7 +10333,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.8</v>
+        <v>12.3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10371,7 +10376,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 11442-2024</t>
+          <t>A 46668-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10385,10 +10390,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45372</v>
+        <v>45926</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10401,7 +10406,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10444,7 +10449,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 3250-2026</t>
+          <t>A 35603-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10458,10 +10463,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46041</v>
+        <v>45531</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10474,7 +10479,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10517,7 +10522,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 15227-2025</t>
+          <t>A 73351-2021</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10531,10 +10536,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45744</v>
+        <v>44551</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10547,7 +10552,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.7</v>
+        <v>6.1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10590,7 +10595,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 26639-2025</t>
+          <t>A 51916-2022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10600,14 +10605,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45810</v>
+        <v>44868</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10620,7 +10625,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10663,7 +10668,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 36141-2025</t>
+          <t>A 46872-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10677,10 +10682,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45866</v>
+        <v>45929</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10693,7 +10698,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10736,7 +10741,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 36048-2025</t>
+          <t>A 35605-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10750,10 +10755,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45866</v>
+        <v>45531</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10766,7 +10771,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10809,7 +10814,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 53307-2024</t>
+          <t>A 61811-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10823,10 +10828,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45614</v>
+        <v>45264</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10838,8 +10843,13 @@
           <t>MELLERUD</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>2</v>
+        <v>7.9</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10882,7 +10892,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 39728-2023</t>
+          <t>A 21432-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10896,10 +10906,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45167</v>
+        <v>46148</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10912,7 +10922,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.6</v>
+        <v>4.3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10955,7 +10965,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 17543-2023</t>
+          <t>A 34415-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10969,10 +10979,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45036</v>
+        <v>45525</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10985,7 +10995,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.8</v>
+        <v>4.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11028,7 +11038,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 49718-2025</t>
+          <t>A 22364-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11042,10 +11052,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45939</v>
+        <v>46154</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11058,7 +11068,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11101,7 +11111,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 3201-2026</t>
+          <t>A 21977-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11115,10 +11125,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46041</v>
+        <v>46153</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11131,7 +11141,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11174,7 +11184,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 36963-2025</t>
+          <t>A 22337-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11188,10 +11198,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45874</v>
+        <v>46154</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11247,7 +11257,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 52471-2023</t>
+          <t>A 33092-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11261,10 +11271,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45225</v>
+        <v>45126</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11277,7 +11287,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11320,7 +11330,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 53254-2022</t>
+          <t>A 40065-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11334,10 +11344,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44876</v>
+        <v>45168</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11350,7 +11360,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11393,7 +11403,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 38040-2025</t>
+          <t>A 1369-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11407,10 +11417,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45882</v>
+        <v>45667</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11423,7 +11433,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11466,7 +11476,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 43406-2025</t>
+          <t>A 16746-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11480,10 +11490,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45911</v>
+        <v>45030</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11496,7 +11506,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11539,7 +11549,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 38663-2025</t>
+          <t>A 51436-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11553,10 +11563,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45884</v>
+        <v>45950</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11569,7 +11579,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11612,7 +11622,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 5324-2026</t>
+          <t>A 59865-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11626,10 +11636,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46050</v>
+        <v>45639</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11642,7 +11652,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.5</v>
+        <v>5.9</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11685,7 +11695,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 1921-2025</t>
+          <t>A 3989-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11699,10 +11709,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45671</v>
+        <v>44952</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11715,7 +11725,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11758,7 +11768,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 60996-2022</t>
+          <t>A 51783-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11772,10 +11782,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44914</v>
+        <v>45222</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11788,7 +11798,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11831,7 +11841,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 7047-2026</t>
+          <t>A 49718-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11845,10 +11855,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46057</v>
+        <v>45939</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11861,7 +11871,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11904,7 +11914,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 7125-2026</t>
+          <t>A 32832-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11918,10 +11928,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46058</v>
+        <v>45516</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11934,7 +11944,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11977,7 +11987,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 50478-2025</t>
+          <t>A 28863-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11991,10 +12001,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45945</v>
+        <v>45820</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12007,7 +12017,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12050,7 +12060,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 50482-2025</t>
+          <t>A 32498-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12064,10 +12074,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45945</v>
+        <v>45513</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12080,7 +12090,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>8.800000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12123,7 +12133,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 53232-2025</t>
+          <t>A 27510-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12137,10 +12147,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45958</v>
+        <v>45097</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12153,7 +12163,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12196,7 +12206,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 7120-2026</t>
+          <t>A 59269-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12210,10 +12220,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46058</v>
+        <v>45988</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12226,7 +12236,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.8</v>
+        <v>3.5</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12269,7 +12279,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 7117-2026</t>
+          <t>A 22313-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12283,10 +12293,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46058</v>
+        <v>45070</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12299,7 +12309,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12342,7 +12352,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 15323-2024</t>
+          <t>A 25036-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12356,10 +12366,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45400</v>
+        <v>46174</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12372,7 +12382,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>10.6</v>
+        <v>5.9</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12415,7 +12425,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 10398-2024</t>
+          <t>A 43406-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12429,10 +12439,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45365</v>
+        <v>45911</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12445,7 +12455,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12488,7 +12498,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 8160-2026</t>
+          <t>A 36138-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12502,10 +12512,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46064</v>
+        <v>45866</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12518,7 +12528,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12561,7 +12571,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 56026-2025</t>
+          <t>A 25458-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12575,10 +12585,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45973</v>
+        <v>46177</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12591,7 +12601,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12634,7 +12644,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 56349-2025</t>
+          <t>A 14568-2022</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12648,10 +12658,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45974</v>
+        <v>44655</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12707,7 +12717,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 58861-2022</t>
+          <t>A 25954-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12721,10 +12731,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44903</v>
+        <v>46181</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12737,7 +12747,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>4.8</v>
+        <v>1.5</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12780,7 +12790,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 11256-2025</t>
+          <t>A 26527-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12794,10 +12804,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45726</v>
+        <v>46183</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12809,8 +12819,13 @@
           <t>MELLERUD</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I155" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12853,7 +12868,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 9573-2026</t>
+          <t>A 32384-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12867,10 +12882,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46071</v>
+        <v>45120</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12883,7 +12898,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>5.2</v>
+        <v>1.1</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12926,7 +12941,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 8923-2024</t>
+          <t>A 26536-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12940,10 +12955,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45356</v>
+        <v>46183</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12955,8 +12970,13 @@
           <t>MELLERUD</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I157" t="n">
-        <v>3.2</v>
+        <v>0.6</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12999,7 +13019,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 39942-2023</t>
+          <t>A 53232-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13013,10 +13033,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45167</v>
+        <v>45958</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13029,7 +13049,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13072,7 +13092,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 3998-2025</t>
+          <t>A 50478-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13086,10 +13106,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45684</v>
+        <v>45945</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13102,7 +13122,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>8.199999999999999</v>
+        <v>1</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13145,7 +13165,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 11249-2026</t>
+          <t>A 50482-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13159,10 +13179,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46080</v>
+        <v>45945</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13175,7 +13195,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13218,7 +13238,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 59804-2025</t>
+          <t>A 39942-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13232,10 +13252,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45992</v>
+        <v>45167</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13248,7 +13268,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13291,7 +13311,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 59802-2025</t>
+          <t>A 12713-2022</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13305,10 +13325,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45992</v>
+        <v>44641</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13321,7 +13341,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13364,7 +13384,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 11121-2026</t>
+          <t>A 18854-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13374,14 +13394,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46079</v>
+        <v>45042</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13394,7 +13414,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13437,7 +13457,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 59808-2025</t>
+          <t>A 51785-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13451,10 +13471,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45992</v>
+        <v>45222</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13467,7 +13487,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13510,7 +13530,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 11323-2026</t>
+          <t>A 3998-2025</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13520,14 +13540,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46080</v>
+        <v>45684</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13540,7 +13560,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>7.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13583,7 +13603,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 59806-2025</t>
+          <t>A 19872-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13597,10 +13617,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45992</v>
+        <v>45054</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13613,7 +13633,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.5</v>
+        <v>8.4</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13656,7 +13676,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 60203-2025</t>
+          <t>A 56349-2025</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13670,10 +13690,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45994</v>
+        <v>45974</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13686,7 +13706,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13729,7 +13749,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 32384-2023</t>
+          <t>A 56026-2025</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13743,10 +13763,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45120</v>
+        <v>45973</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13759,7 +13779,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13802,7 +13822,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 61177-2025</t>
+          <t>A 8492-2022</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13812,14 +13832,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46000</v>
+        <v>44613</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13832,7 +13852,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13875,7 +13895,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 61180-2025</t>
+          <t>A 29936-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13889,10 +13909,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46000</v>
+        <v>46205</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13905,7 +13925,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13948,7 +13968,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 63249-2025</t>
+          <t>A 33450-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13962,10 +13982,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46010</v>
+        <v>46246</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13978,7 +13998,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14021,7 +14041,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 6283-2023</t>
+          <t>A 29939-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14035,10 +14055,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44965</v>
+        <v>46205</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14051,7 +14071,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14094,7 +14114,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 40064-2023</t>
+          <t>A 10428-2022</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14108,10 +14128,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45168</v>
+        <v>44623</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14124,7 +14144,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14167,7 +14187,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 34415-2024</t>
+          <t>A 21618-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14181,10 +14201,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45525</v>
+        <v>45442</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14197,7 +14217,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>4.3</v>
+        <v>1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14240,7 +14260,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 32304-2024</t>
+          <t>A 21620-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14254,10 +14274,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45512</v>
+        <v>45442</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14270,7 +14290,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14313,7 +14333,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 13594-2026</t>
+          <t>A 33388-2022</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14323,14 +14343,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46096</v>
+        <v>44788</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14343,7 +14363,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14403,7 +14423,7 @@
         <v>45198</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14459,7 +14479,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 21077-2023</t>
+          <t>A 20578-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14473,10 +14493,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45057</v>
+        <v>46140</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14488,8 +14508,13 @@
           <t>MELLERUD</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I178" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14532,7 +14557,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 22313-2023</t>
+          <t>A 16656-2022</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14546,10 +14571,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45070</v>
+        <v>44672</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14562,7 +14587,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14605,7 +14630,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 52128-2021</t>
+          <t>A 34065-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14619,10 +14644,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44463</v>
+        <v>46252</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14635,7 +14660,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14678,7 +14703,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 17160-2024</t>
+          <t>A 51463-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14692,10 +14717,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45412</v>
+        <v>45221</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14708,7 +14733,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14751,7 +14776,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 48256-2022</t>
+          <t>A 59808-2025</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14765,10 +14790,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44858</v>
+        <v>45992</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14781,7 +14806,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14824,7 +14849,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 8152-2023</t>
+          <t>A 59806-2025</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14838,10 +14863,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44974</v>
+        <v>45992</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14854,7 +14879,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14897,7 +14922,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 40065-2023</t>
+          <t>A 59804-2025</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14911,10 +14936,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45168</v>
+        <v>45992</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14927,7 +14952,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14970,7 +14995,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 18055-2026</t>
+          <t>A 34116-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14980,14 +15005,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46125</v>
+        <v>45126</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15000,7 +15025,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15043,7 +15068,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 45834-2023</t>
+          <t>A 59802-2025</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15057,10 +15082,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45195</v>
+        <v>45992</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15073,7 +15098,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15116,7 +15141,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 51463-2023</t>
+          <t>A 56025-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15130,10 +15155,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45221</v>
+        <v>45624</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15146,7 +15171,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15189,7 +15214,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 8492-2022</t>
+          <t>A 11256-2025</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15203,10 +15228,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44613</v>
+        <v>45726</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15219,7 +15244,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15262,7 +15287,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 48879-2024</t>
+          <t>A 60203-2025</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15276,10 +15301,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45594</v>
+        <v>45994</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15292,7 +15317,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15335,7 +15360,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 5647-2023</t>
+          <t>A 8155-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15349,10 +15374,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>44960</v>
+        <v>44974</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15365,7 +15390,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15408,7 +15433,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 24312-2025</t>
+          <t>A 61177-2025</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15418,14 +15443,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45797</v>
+        <v>46000</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15438,7 +15463,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15481,7 +15506,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 493-2025</t>
+          <t>A 61180-2025</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15495,10 +15520,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45664</v>
+        <v>46000</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15511,7 +15536,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15554,7 +15579,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 35603-2024</t>
+          <t>A 53573-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15568,10 +15593,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45531</v>
+        <v>45230</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15584,7 +15609,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15627,7 +15652,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 36146-2025</t>
+          <t>A 61060-2022</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15641,10 +15666,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45866</v>
+        <v>44915</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15657,7 +15682,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1</v>
+        <v>8.4</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15700,7 +15725,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 12334-2024</t>
+          <t>A 61061-2022</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15714,10 +15739,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45378</v>
+        <v>44915</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15730,7 +15755,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15773,7 +15798,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 49449-2025</t>
+          <t>A 55391-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15787,10 +15812,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45938</v>
+        <v>45238</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15803,7 +15828,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15846,7 +15871,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 12713-2022</t>
+          <t>A 54796-2022</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15860,10 +15885,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44641</v>
+        <v>44883</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15876,7 +15901,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15919,7 +15944,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 11219-2024</t>
+          <t>A 13800-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15933,10 +15958,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45371</v>
+        <v>45007</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15949,7 +15974,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>6</v>
+        <v>1.1</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15992,7 +16017,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 18205-2024</t>
+          <t>A 48879-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16006,10 +16031,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45420</v>
+        <v>45594</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16022,7 +16047,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16065,7 +16090,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 53565-2022</t>
+          <t>A 45834-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16079,10 +16104,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44879</v>
+        <v>45195</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16138,7 +16163,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 59723-2025</t>
+          <t>A 31836-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16152,10 +16177,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45992</v>
+        <v>46230</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16168,7 +16193,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>12.3</v>
+        <v>0.7</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16211,7 +16236,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 20573-2026</t>
+          <t>A 63249-2025</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16225,10 +16250,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46140</v>
+        <v>46010</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16240,13 +16265,8 @@
           <t>MELLERUD</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I202" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16289,7 +16309,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 10428-2022</t>
+          <t>A 36960-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16303,10 +16323,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>44623</v>
+        <v>46273</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16319,7 +16339,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.9</v>
+        <v>8.1</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16362,7 +16382,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 28865-2025</t>
+          <t>A 52269-2022</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16376,10 +16396,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45820</v>
+        <v>44873</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16392,7 +16412,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16435,7 +16455,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 54796-2022</t>
+          <t>A 31889-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16449,10 +16469,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>44883</v>
+        <v>46231</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16465,7 +16485,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16508,7 +16528,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 21432-2026</t>
+          <t>A 15323-2024</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16522,10 +16542,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46148</v>
+        <v>45400</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16538,7 +16558,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>4.3</v>
+        <v>10.6</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16581,7 +16601,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 53573-2023</t>
+          <t>A 17160-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16595,10 +16615,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45230</v>
+        <v>45412</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16611,7 +16631,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16654,7 +16674,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 21977-2026</t>
+          <t>A 19545-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16668,10 +16688,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46153</v>
+        <v>45429</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16684,7 +16704,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16727,7 +16747,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 22364-2026</t>
+          <t>A 52128-2021</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16741,10 +16761,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46154</v>
+        <v>44463</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16757,7 +16777,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16800,7 +16820,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 34116-2023</t>
+          <t>A 46917-2022</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16810,14 +16830,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45126</v>
+        <v>44851</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16830,7 +16850,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>4.3</v>
+        <v>0.8</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16873,7 +16893,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 22337-2026</t>
+          <t>A 38251-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16887,10 +16907,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46154</v>
+        <v>46281</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16903,7 +16923,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16946,7 +16966,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 1883-2023</t>
+          <t>A 60996-2022</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16960,10 +16980,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>44939</v>
+        <v>44914</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16976,7 +16996,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17019,7 +17039,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 1886-2023</t>
+          <t>A 12157-2022</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17029,14 +17049,14 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>44939</v>
+        <v>44636</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17049,7 +17069,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17092,7 +17112,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 16746-2023</t>
+          <t>A 32691-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17106,10 +17126,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45030</v>
+        <v>46240</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17122,7 +17142,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17165,7 +17185,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 1369-2025</t>
+          <t>A 9456-2024</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17179,10 +17199,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45667</v>
+        <v>45359</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17195,7 +17215,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17238,7 +17258,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 32832-2024</t>
+          <t>A 32520-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17252,10 +17272,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45516</v>
+        <v>46239</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17268,7 +17288,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17311,7 +17331,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 59865-2024</t>
+          <t>A 1830-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17325,10 +17345,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45639</v>
+        <v>46035</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17341,7 +17361,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>5.9</v>
+        <v>1</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17384,7 +17404,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 51436-2025</t>
+          <t>A 1827-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17398,10 +17418,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45950</v>
+        <v>46035</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17414,7 +17434,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17457,7 +17477,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 28863-2025</t>
+          <t>A 53270-2024</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17471,10 +17491,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45820</v>
+        <v>45614</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17487,7 +17507,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17530,7 +17550,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 27510-2023</t>
+          <t>A 5647-2023</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17544,10 +17564,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45097</v>
+        <v>44960</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17560,7 +17580,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17603,7 +17623,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 334-2023</t>
+          <t>A 7443-2023</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17617,10 +17637,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>44929</v>
+        <v>44971</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17633,7 +17653,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17676,7 +17696,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 32299-2024</t>
+          <t>A 3250-2026</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17690,10 +17710,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45512</v>
+        <v>46041</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17706,7 +17726,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17749,7 +17769,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 59269-2025</t>
+          <t>A 1886-2023</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17763,10 +17783,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45988</v>
+        <v>44939</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17779,7 +17799,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17822,7 +17842,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 25036-2026</t>
+          <t>A 3178-2026</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17836,10 +17856,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46174</v>
+        <v>46041</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17852,7 +17872,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>5.9</v>
+        <v>0.8</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17895,7 +17915,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 32498-2024</t>
+          <t>A 3201-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17909,10 +17929,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45513</v>
+        <v>46041</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17925,7 +17945,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17968,7 +17988,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 43353-2024</t>
+          <t>A 5324-2026</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17982,10 +18002,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45568</v>
+        <v>46050</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17998,7 +18018,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18041,7 +18061,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 36138-2025</t>
+          <t>A 9374-2023</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18055,10 +18075,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45866</v>
+        <v>44981</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18071,7 +18091,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18114,7 +18134,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 25458-2026</t>
+          <t>A 48256-2022</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18128,10 +18148,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>46177</v>
+        <v>44858</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18144,7 +18164,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18187,7 +18207,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 51916-2022</t>
+          <t>A 23238-2024</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18197,14 +18217,14 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>44868</v>
+        <v>45453</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18217,7 +18237,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>4.5</v>
+        <v>1.7</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18260,7 +18280,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 33666-2023</t>
+          <t>A 7154-2024</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18270,14 +18290,14 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45132</v>
+        <v>45344</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18290,7 +18310,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18333,7 +18353,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 25954-2026</t>
+          <t>A 24978-2022</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18347,10 +18367,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>46181</v>
+        <v>44728</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18363,7 +18383,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18406,7 +18426,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 26536-2026</t>
+          <t>A 18205-2024</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18420,10 +18440,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>46183</v>
+        <v>45420</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18435,13 +18455,8 @@
           <t>MELLERUD</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I232" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18484,7 +18499,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 51785-2023</t>
+          <t>A 17543-2023</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18498,10 +18513,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45222</v>
+        <v>45036</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18514,7 +18529,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18557,7 +18572,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 26527-2026</t>
+          <t>A 7117-2026</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18571,10 +18586,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>46183</v>
+        <v>46058</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18586,13 +18601,8 @@
           <t>MELLERUD</t>
         </is>
       </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I234" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18635,7 +18645,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 33092-2023</t>
+          <t>A 7125-2026</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18649,10 +18659,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45126</v>
+        <v>46058</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18665,7 +18675,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18708,7 +18718,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 55391-2023</t>
+          <t>A 7047-2026</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18722,10 +18732,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45238</v>
+        <v>46057</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18738,7 +18748,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18781,7 +18791,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 15971-2023</t>
+          <t>A 7120-2026</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18795,10 +18805,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45022</v>
+        <v>46058</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18811,7 +18821,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18854,7 +18864,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 53317-2024</t>
+          <t>A 17538-2023</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18868,10 +18878,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45614</v>
+        <v>45036</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18884,7 +18894,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>0.3</v>
+        <v>2.3</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18927,7 +18937,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 32691-2026</t>
+          <t>A 11219-2024</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18941,10 +18951,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>46240</v>
+        <v>45371</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18957,7 +18967,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -19000,7 +19010,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 33450-2026</t>
+          <t>A 58861-2022</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -19014,10 +19024,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>46246</v>
+        <v>44903</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19030,7 +19040,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -19073,7 +19083,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 73351-2021</t>
+          <t>A 39728-2023</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -19087,10 +19097,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>44551</v>
+        <v>45167</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19103,7 +19113,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>6.1</v>
+        <v>0.6</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -19146,7 +19156,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 26428-2022</t>
+          <t>A 51173-2023</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19160,10 +19170,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>44736</v>
+        <v>45212</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19176,7 +19186,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19219,7 +19229,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 20578-2026</t>
+          <t>A 4054-2025</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19233,10 +19243,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>46140</v>
+        <v>45684</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19248,13 +19258,8 @@
           <t>MELLERUD</t>
         </is>
       </c>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I243" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19297,7 +19302,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 29936-2026</t>
+          <t>A 14596-2022</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19311,10 +19316,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>46205</v>
+        <v>44655</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19327,7 +19332,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19370,7 +19375,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 29939-2026</t>
+          <t>A 39535-2024</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19384,10 +19389,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>46205</v>
+        <v>45551</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19400,7 +19405,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19443,7 +19448,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 34065-2026</t>
+          <t>A 32549-2024</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19457,10 +19462,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>46252</v>
+        <v>45513</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19473,7 +19478,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19516,7 +19521,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 21618-2024</t>
+          <t>A 21077-2023</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19530,10 +19535,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45442</v>
+        <v>45057</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19546,7 +19551,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19589,7 +19594,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 21620-2024</t>
+          <t>A 9152-2024</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19603,10 +19608,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45442</v>
+        <v>45357</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19619,7 +19624,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19662,7 +19667,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 26530-2023</t>
+          <t>A 8152-2023</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19676,10 +19681,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45092</v>
+        <v>44974</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19692,7 +19697,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19735,7 +19740,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 18854-2023</t>
+          <t>A 21698-2025</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19749,10 +19754,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45042</v>
+        <v>45783</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19765,7 +19770,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19808,7 +19813,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 14568-2022</t>
+          <t>A 21678-2025</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19822,10 +19827,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>44655</v>
+        <v>45783</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19838,7 +19843,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -19881,7 +19886,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 61811-2023</t>
+          <t>A 21689-2025</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19895,10 +19900,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45264</v>
+        <v>45783</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19910,13 +19915,8 @@
           <t>MELLERUD</t>
         </is>
       </c>
-      <c r="H252" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I252" t="n">
-        <v>7.9</v>
+        <v>1.5</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19959,7 +19959,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 25399-2023</t>
+          <t>A 27342-2024</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19969,14 +19969,14 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45089</v>
+        <v>45473</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19989,7 +19989,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -20032,7 +20032,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 23238-2024</t>
+          <t>A 13313-2024</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -20046,10 +20046,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45453</v>
+        <v>45386</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20062,7 +20062,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -20105,7 +20105,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 53270-2024</t>
+          <t>A 8667-2025</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20119,10 +20119,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45614</v>
+        <v>45712</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20135,7 +20135,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20178,7 +20178,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 17538-2023</t>
+          <t>A 60993-2022</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20192,10 +20192,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45036</v>
+        <v>44914</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20208,7 +20208,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20251,7 +20251,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 19545-2024</t>
+          <t>A 10100-2025</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>45429</v>
+        <v>45719</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20281,7 +20281,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20324,7 +20324,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 31836-2026</t>
+          <t>A 10097-2025</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20338,10 +20338,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>46230</v>
+        <v>45719</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20397,7 +20397,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 36960-2026</t>
+          <t>A 10357-2025</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20411,10 +20411,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>46273</v>
+        <v>45720</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20427,7 +20427,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>8.1</v>
+        <v>0.9</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20470,7 +20470,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 50441-2023</t>
+          <t>A 10358-2025</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -20484,10 +20484,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45216</v>
+        <v>45720</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20500,7 +20500,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -20543,7 +20543,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 10401-2024</t>
+          <t>A 11213-2025</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -20557,10 +20557,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>45365</v>
+        <v>45726</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20573,7 +20573,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>7.6</v>
+        <v>4.8</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -20616,7 +20616,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 31889-2026</t>
+          <t>A 24527-2025</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -20630,10 +20630,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>46231</v>
+        <v>45798</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20646,7 +20646,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -20689,7 +20689,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 21689-2025</t>
+          <t>A 24533-2025</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -20703,10 +20703,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>45783</v>
+        <v>45798</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20719,7 +20719,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>1.5</v>
+        <v>5.8</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -20762,7 +20762,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 21678-2025</t>
+          <t>A 43017-2024</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -20776,10 +20776,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>45783</v>
+        <v>45567</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20792,7 +20792,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -20835,7 +20835,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 21698-2025</t>
+          <t>A 25652-2025</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -20849,10 +20849,10 @@
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>45783</v>
+        <v>45803</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20865,7 +20865,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -20908,7 +20908,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>A 38251-2026</t>
+          <t>A 25635-2025</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -20922,10 +20922,10 @@
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>46281</v>
+        <v>45803</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20938,7 +20938,7 @@
         </is>
       </c>
       <c r="I266" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -20981,7 +20981,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>A 32520-2026</t>
+          <t>A 25623-2025</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -20995,10 +20995,10 @@
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>46239</v>
+        <v>45803</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21011,7 +21011,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -21054,7 +21054,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>A 13313-2024</t>
+          <t>A 60395-2024</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -21064,14 +21064,14 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>45386</v>
+        <v>45643</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21127,7 +21127,7 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>A 27342-2024</t>
+          <t>A 8165-2023</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -21141,10 +21141,10 @@
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>45473</v>
+        <v>44974</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         </is>
       </c>
       <c r="I269" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -21200,7 +21200,7 @@
     <row r="270" ht="15" customHeight="1">
       <c r="A270" t="inlineStr">
         <is>
-          <t>A 10100-2025</t>
+          <t>A 17528-2024</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -21214,10 +21214,10 @@
         </is>
       </c>
       <c r="D270" s="1" t="n">
-        <v>45719</v>
+        <v>45415</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21230,7 +21230,7 @@
         </is>
       </c>
       <c r="I270" t="n">
-        <v>1.2</v>
+        <v>3.6</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -21273,7 +21273,7 @@
     <row r="271" ht="15" customHeight="1">
       <c r="A271" t="inlineStr">
         <is>
-          <t>A 8667-2025</t>
+          <t>A 52922-2024</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -21287,10 +21287,10 @@
         </is>
       </c>
       <c r="D271" s="1" t="n">
-        <v>45712</v>
+        <v>45610</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         </is>
       </c>
       <c r="I271" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J271" t="n">
         <v>0</v>
@@ -21346,7 +21346,7 @@
     <row r="272" ht="15" customHeight="1">
       <c r="A272" t="inlineStr">
         <is>
-          <t>A 10357-2025</t>
+          <t>A 11848-2025</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -21360,10 +21360,10 @@
         </is>
       </c>
       <c r="D272" s="1" t="n">
-        <v>45720</v>
+        <v>45728</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21376,7 +21376,7 @@
         </is>
       </c>
       <c r="I272" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J272" t="n">
         <v>0</v>
@@ -21419,7 +21419,7 @@
     <row r="273" ht="15" customHeight="1">
       <c r="A273" t="inlineStr">
         <is>
-          <t>A 10358-2025</t>
+          <t>A 12501-2025</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -21433,10 +21433,10 @@
         </is>
       </c>
       <c r="D273" s="1" t="n">
-        <v>45720</v>
+        <v>45730</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21449,7 +21449,7 @@
         </is>
       </c>
       <c r="I273" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J273" t="n">
         <v>0</v>
@@ -21492,7 +21492,7 @@
     <row r="274" ht="15" customHeight="1">
       <c r="A274" t="inlineStr">
         <is>
-          <t>A 60993-2022</t>
+          <t>A 17693-2023</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -21506,10 +21506,10 @@
         </is>
       </c>
       <c r="D274" s="1" t="n">
-        <v>44914</v>
+        <v>45037</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21522,7 +21522,7 @@
         </is>
       </c>
       <c r="I274" t="n">
-        <v>0.6</v>
+        <v>11.3</v>
       </c>
       <c r="J274" t="n">
         <v>0</v>
@@ -21565,7 +21565,7 @@
     <row r="275" ht="15" customHeight="1">
       <c r="A275" t="inlineStr">
         <is>
-          <t>A 10097-2025</t>
+          <t>A 7228-2025</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -21579,10 +21579,10 @@
         </is>
       </c>
       <c r="D275" s="1" t="n">
-        <v>45719</v>
+        <v>45702</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21595,7 +21595,7 @@
         </is>
       </c>
       <c r="I275" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J275" t="n">
         <v>0</v>
@@ -21638,24 +21638,24 @@
     <row r="276" ht="15" customHeight="1">
       <c r="A276" t="inlineStr">
         <is>
-          <t>A 11213-2025</t>
+          <t>S 10351-2021</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D276" s="1" t="n">
-        <v>45726</v>
+        <v>44551</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21668,7 +21668,7 @@
         </is>
       </c>
       <c r="I276" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="J276" t="n">
         <v>0</v>
@@ -21711,7 +21711,7 @@
     <row r="277" ht="15" customHeight="1">
       <c r="A277" t="inlineStr">
         <is>
-          <t>S 10351-2021</t>
+          <t>S 587-2024</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -21721,14 +21721,14 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D277" s="1" t="n">
-        <v>44551</v>
+        <v>45351</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21741,7 +21741,7 @@
         </is>
       </c>
       <c r="I277" t="n">
-        <v>5.8</v>
+        <v>19</v>
       </c>
       <c r="J277" t="n">
         <v>0</v>
@@ -21784,7 +21784,7 @@
     <row r="278" ht="15" customHeight="1">
       <c r="A278" t="inlineStr">
         <is>
-          <t>S 587-2024</t>
+          <t>S 1695-2026</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -21794,87 +21794,87 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D278" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="E278" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="I278" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J278" t="n">
+        <v>0</v>
+      </c>
+      <c r="K278" t="n">
+        <v>0</v>
+      </c>
+      <c r="L278" t="n">
+        <v>0</v>
+      </c>
+      <c r="M278" t="n">
+        <v>0</v>
+      </c>
+      <c r="N278" t="n">
+        <v>0</v>
+      </c>
+      <c r="O278" t="n">
+        <v>0</v>
+      </c>
+      <c r="P278" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q278" t="n">
+        <v>0</v>
+      </c>
+      <c r="R278" t="n">
+        <v>0</v>
+      </c>
+      <c r="S278" t="n">
+        <v>0</v>
+      </c>
+      <c r="T278" t="n">
+        <v>0</v>
+      </c>
+      <c r="U278" t="n">
+        <v>0</v>
+      </c>
+      <c r="V278" s="2" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>S 1717-2026</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D278" s="1" t="n">
-        <v>45351</v>
-      </c>
-      <c r="E278" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F278" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="I278" t="n">
-        <v>19</v>
-      </c>
-      <c r="J278" t="n">
-        <v>0</v>
-      </c>
-      <c r="K278" t="n">
-        <v>0</v>
-      </c>
-      <c r="L278" t="n">
-        <v>0</v>
-      </c>
-      <c r="M278" t="n">
-        <v>0</v>
-      </c>
-      <c r="N278" t="n">
-        <v>0</v>
-      </c>
-      <c r="O278" t="n">
-        <v>0</v>
-      </c>
-      <c r="P278" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q278" t="n">
-        <v>0</v>
-      </c>
-      <c r="R278" t="n">
-        <v>0</v>
-      </c>
-      <c r="S278" t="n">
-        <v>0</v>
-      </c>
-      <c r="T278" t="n">
-        <v>0</v>
-      </c>
-      <c r="U278" t="n">
-        <v>0</v>
-      </c>
-      <c r="V278" s="2" t="inlineStr"/>
-    </row>
-    <row r="279" ht="15" customHeight="1">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>S 1695-2026</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
       <c r="D279" s="1" t="n">
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21887,7 +21887,7 @@
         </is>
       </c>
       <c r="I279" t="n">
-        <v>1.6</v>
+        <v>30.4</v>
       </c>
       <c r="J279" t="n">
         <v>0</v>
@@ -21926,79 +21926,6 @@
         <v>0</v>
       </c>
       <c r="V279" s="2" t="inlineStr"/>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>S 1717-2026</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D280" s="1" t="n">
-        <v>46188</v>
-      </c>
-      <c r="E280" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F280" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="I280" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="J280" t="n">
-        <v>0</v>
-      </c>
-      <c r="K280" t="n">
-        <v>0</v>
-      </c>
-      <c r="L280" t="n">
-        <v>0</v>
-      </c>
-      <c r="M280" t="n">
-        <v>0</v>
-      </c>
-      <c r="N280" t="n">
-        <v>0</v>
-      </c>
-      <c r="O280" t="n">
-        <v>0</v>
-      </c>
-      <c r="P280" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q280" t="n">
-        <v>0</v>
-      </c>
-      <c r="R280" t="n">
-        <v>0</v>
-      </c>
-      <c r="S280" t="n">
-        <v>0</v>
-      </c>
-      <c r="T280" t="n">
-        <v>0</v>
-      </c>
-      <c r="U280" t="n">
-        <v>0</v>
-      </c>
-      <c r="V280" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt MELLERUD.xlsx
+++ b/Översikt MELLERUD.xlsx
@@ -601,7 +601,7 @@
         <v>46184</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -617,10 +617,10 @@
         <v>5.8</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L2" t="n">
         <v>4</v>
@@ -644,13 +644,13 @@
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="T2" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="U2" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
@@ -675,9 +675,11 @@
 Svart trolldruva
 Thomsons trägnagare
 Traslav
+Vätteros
 Vågbandad barkbock
 Blåsippa
-Skogsbingel</t>
+Skogsbingel
+Gullviva</t>
         </is>
       </c>
       <c r="W2">
@@ -729,7 +731,7 @@
         <v>46112</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -745,13 +747,13 @@
         <v>13.2</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
         <v>13</v>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -766,24 +768,25 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="T3" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="U3" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Svart askbastborre
 Sårläka
+Tjockfotad fingersvamp
 Vedtrappmossa
 Blek stjärnmossa
 Brandticka
@@ -800,7 +803,8 @@
 Vågbandad barkbock
 Blåsippa
 Spillkråka
-Vitsippa</t>
+Vitsippa
+Gullviva</t>
         </is>
       </c>
       <c r="W3">
@@ -856,7 +860,7 @@
         <v>45614</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -872,13 +876,13 @@
         <v>3.5</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
         <v>9</v>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -893,24 +897,25 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="T4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="U4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Svart askbastborre
 Sårläka
+Tjockfotad fingersvamp
 Blek stjärnmossa
 Brandticka
 Fällmossa
@@ -922,7 +927,8 @@
 Trädporella
 Blåsippa
 Spillkråka
-Vitsippa</t>
+Vitsippa
+Gullviva</t>
         </is>
       </c>
       <c r="W4">
@@ -961,7 +967,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 44523-2022</t>
+          <t>A 53463-2024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -975,10 +981,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44840</v>
+        <v>45614</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -991,19 +997,19 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L5" t="n">
         <v>3</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -1015,21 +1021,135 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
       </c>
       <c r="T5" t="n">
+        <v>19</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Grålila vaxing
+Uddbräken
+Lädervaxing
+Scharlakansvaxing
+Sårläka
+Blodvaxing
+Honungsvaxing
+Igelkottsröksvamp
+Luktvaxing
+Ängsvaxing agg.</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 53463-2024 artfynd.xlsx", "A 53463-2024")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 53463-2024 karta.png", "A 53463-2024")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 53463-2024 georefererad karta.tif", "A 53463-2024")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 53463-2024 FSC-klagomål.docx", "A 53463-2024")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 53463-2024 FSC-klagomål mail.docx", "A 53463-2024")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 53463-2024 tillsynsbegäran.docx", "A 53463-2024")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 53463-2024 tillsynsbegäran mail.docx", "A 53463-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 44523-2022</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>44840</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>6</v>
+      </c>
+      <c r="R6" t="n">
+        <v>3</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="n">
         <v>15</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>4</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Aspfjädermossa
 Skirmossa
@@ -1043,149 +1163,35 @@
 Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 44523-2022 artfynd.xlsx", "A 44523-2022")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 44523-2022 karta.png", "A 44523-2022")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 44523-2022 georefererad karta.tif", "A 44523-2022")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 44523-2022 FSC-klagomål.docx", "A 44523-2022")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 44523-2022 FSC-klagomål mail.docx", "A 44523-2022")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 44523-2022 tillsynsbegäran.docx", "A 44523-2022")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 44523-2022 tillsynsbegäran mail.docx", "A 44523-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 53463-2024</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45614</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>5</v>
-      </c>
-      <c r="L6" t="n">
-        <v>3</v>
-      </c>
-      <c r="M6" t="n">
-        <v>2</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>5</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="n">
-        <v>19</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Grålila vaxing
-Uddbräken
-Lädervaxing
-Scharlakansvaxing
-Sårläka
-Blodvaxing
-Honungsvaxing
-Igelkottsröksvamp
-Luktvaxing
-Ängsvaxing agg.</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 53463-2024 artfynd.xlsx", "A 53463-2024")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 53463-2024 karta.png", "A 53463-2024")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 53463-2024 georefererad karta.tif", "A 53463-2024")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 53463-2024 FSC-klagomål.docx", "A 53463-2024")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 53463-2024 FSC-klagomål mail.docx", "A 53463-2024")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 53463-2024 tillsynsbegäran.docx", "A 53463-2024")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 53463-2024 tillsynsbegäran mail.docx", "A 53463-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
@@ -1206,7 +1212,7 @@
         <v>45734</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1319,7 +1325,7 @@
         <v>46020</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1431,7 +1437,7 @@
         <v>45670</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1543,7 +1549,7 @@
         <v>45253</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1653,7 +1659,7 @@
         <v>44963</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1762,7 +1768,7 @@
         <v>45006</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1854,7 +1860,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 28216-2026</t>
+          <t>A 63857-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1868,10 +1874,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46196</v>
+        <v>46020</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1883,28 +1889,23 @@
           <t>MELLERUD</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1913,21 +1914,134 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
       </c>
       <c r="T13" t="n">
+        <v>6</v>
+      </c>
+      <c r="U13" t="n">
+        <v>6</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Björksplintborre
+Rävticka
+Trådticka
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 63857-2025 artfynd.xlsx", "A 63857-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 63857-2025 karta.png", "A 63857-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 63857-2025 georefererad karta.tif", "A 63857-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 63857-2025 FSC-klagomål.docx", "A 63857-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 63857-2025 FSC-klagomål mail.docx", "A 63857-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 63857-2025 tillsynsbegäran.docx", "A 63857-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 63857-2025 tillsynsbegäran mail.docx", "A 63857-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 28216-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>46196</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2</v>
+      </c>
+      <c r="S14" t="n">
         <v>4</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Gulvit blekspik
@@ -1935,112 +2049,112 @@
 Gröngöling</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 28216-2026 artfynd.xlsx", "A 28216-2026")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 28216-2026 karta.png", "A 28216-2026")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 28216-2026 georefererad karta.tif", "A 28216-2026")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 28216-2026 FSC-klagomål.docx", "A 28216-2026")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 28216-2026 FSC-klagomål mail.docx", "A 28216-2026")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 28216-2026 tillsynsbegäran.docx", "A 28216-2026")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 28216-2026 tillsynsbegäran mail.docx", "A 28216-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>A 33141-2026</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
         <v>46244</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
+      <c r="E15" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t>Övriga Aktiebolag</t>
         </is>
       </c>
-      <c r="I14" t="n">
+      <c r="I15" t="n">
         <v>5.9</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J15" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K15" t="n">
         <v>3</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
         <v>1</v>
       </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>4</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T15" t="n">
         <v>7</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U15" t="n">
         <v>7</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Kattfotslav
 Grön sköldmossa
@@ -2048,107 +2162,107 @@
 Mandelriska</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 33141-2026 artfynd.xlsx", "A 33141-2026")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 33141-2026 karta.png", "A 33141-2026")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 33141-2026 georefererad karta.tif", "A 33141-2026")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 33141-2026 FSC-klagomål.docx", "A 33141-2026")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 33141-2026 FSC-klagomål mail.docx", "A 33141-2026")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 33141-2026 tillsynsbegäran.docx", "A 33141-2026")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 33141-2026 tillsynsbegäran mail.docx", "A 33141-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>A 25764-2025</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
         <v>45804</v>
       </c>
-      <c r="E15" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
+      <c r="E16" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
         <v>2.5</v>
       </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>3</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
         <v>1</v>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
         <v>1</v>
       </c>
-      <c r="R15" t="n">
+      <c r="R16" t="n">
         <v>1</v>
       </c>
-      <c r="S15" t="n">
+      <c r="S16" t="n">
         <v>4</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T16" t="n">
         <v>5</v>
       </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Ask
 Guldlockmossa
@@ -2156,142 +2270,35 @@
 Rostfläck</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 25764-2025 artfynd.xlsx", "A 25764-2025")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 25764-2025 karta.png", "A 25764-2025")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 25764-2025 georefererad karta.tif", "A 25764-2025")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 25764-2025 FSC-klagomål.docx", "A 25764-2025")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 25764-2025 FSC-klagomål mail.docx", "A 25764-2025")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 25764-2025 tillsynsbegäran.docx", "A 25764-2025")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 25764-2025 tillsynsbegäran mail.docx", "A 25764-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 63857-2025</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46020</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>2</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>3</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Björksplintborre
-Trådticka
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 63857-2025 artfynd.xlsx", "A 63857-2025")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 63857-2025 karta.png", "A 63857-2025")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 63857-2025 georefererad karta.tif", "A 63857-2025")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 63857-2025 FSC-klagomål.docx", "A 63857-2025")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 63857-2025 FSC-klagomål mail.docx", "A 63857-2025")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 63857-2025 tillsynsbegäran.docx", "A 63857-2025")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 63857-2025 tillsynsbegäran mail.docx", "A 63857-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
@@ -2312,7 +2319,7 @@
         <v>45390</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2424,7 +2431,7 @@
         <v>44896</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2530,7 +2537,7 @@
         <v>44804</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2639,7 +2646,7 @@
         <v>44750</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2727,7 +2734,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 43349-2024</t>
+          <t>A 10814-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2741,10 +2748,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45568</v>
+        <v>45369</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2756,8 +2763,13 @@
           <t>MELLERUD</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>4.1</v>
+        <v>6.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2766,10 +2778,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2784,7 +2796,7 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2793,687 +2805,682 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Brunfläckig pärlemorfjäril</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 10814-2024 artfynd.xlsx", "A 10814-2024")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 10814-2024 karta.png", "A 10814-2024")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 10814-2024 georefererad karta.tif", "A 10814-2024")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 10814-2024 FSC-klagomål.docx", "A 10814-2024")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 10814-2024 FSC-klagomål mail.docx", "A 10814-2024")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 10814-2024 tillsynsbegäran.docx", "A 10814-2024")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 10814-2024 tillsynsbegäran mail.docx", "A 10814-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 23546-2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
         <v>1</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 23546-2026 artfynd.xlsx", "A 23546-2026")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 23546-2026 karta.png", "A 23546-2026")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 23546-2026 georefererad karta.tif", "A 23546-2026")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 23546-2026 FSC-klagomål.docx", "A 23546-2026")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 23546-2026 FSC-klagomål mail.docx", "A 23546-2026")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 23546-2026 tillsynsbegäran.docx", "A 23546-2026")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 23546-2026 tillsynsbegäran mail.docx", "A 23546-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 43531-2025</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>45911</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>8</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 43531-2025 artfynd.xlsx", "A 43531-2025")</f>
+        <v/>
+      </c>
+      <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 43531-2025 karta.png", "A 43531-2025")</f>
+        <v/>
+      </c>
+      <c r="Y23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 43531-2025 georefererad karta.tif", "A 43531-2025")</f>
+        <v/>
+      </c>
+      <c r="AA23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 43531-2025 FSC-klagomål.docx", "A 43531-2025")</f>
+        <v/>
+      </c>
+      <c r="AB23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 43531-2025 FSC-klagomål mail.docx", "A 43531-2025")</f>
+        <v/>
+      </c>
+      <c r="AC23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 43531-2025 tillsynsbegäran.docx", "A 43531-2025")</f>
+        <v/>
+      </c>
+      <c r="AD23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 43531-2025 tillsynsbegäran mail.docx", "A 43531-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 8169-2023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>44974</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>Älg</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 8169-2023 artfynd.xlsx", "A 8169-2023")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 8169-2023 karta.png", "A 8169-2023")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 8169-2023 georefererad karta.tif", "A 8169-2023")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 8169-2023 FSC-klagomål.docx", "A 8169-2023")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 8169-2023 FSC-klagomål mail.docx", "A 8169-2023")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 8169-2023 tillsynsbegäran.docx", "A 8169-2023")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 8169-2023 tillsynsbegäran mail.docx", "A 8169-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 43349-2024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>45568</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 43349-2024 artfynd.xlsx", "A 43349-2024")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 43349-2024 karta.png", "A 43349-2024")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 43349-2024 georefererad karta.tif", "A 43349-2024")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 43349-2024 FSC-klagomål.docx", "A 43349-2024")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 43349-2024 FSC-klagomål mail.docx", "A 43349-2024")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 43349-2024 tillsynsbegäran.docx", "A 43349-2024")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 43349-2024 tillsynsbegäran mail.docx", "A 43349-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 8169-2023</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>44974</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A 26518-2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
         <v>1</v>
       </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
         <v>1</v>
       </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
+      <c r="R26" t="n">
         <v>1</v>
       </c>
-      <c r="T22" t="n">
+      <c r="S26" t="n">
         <v>1</v>
       </c>
-      <c r="U22" t="n">
+      <c r="T26" t="n">
         <v>1</v>
       </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Älg</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 8169-2023 artfynd.xlsx", "A 8169-2023")</f>
+      <c r="U26" t="n">
+        <v>1</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Rotfingersvamp</t>
+        </is>
+      </c>
+      <c r="W26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 26518-2026 artfynd.xlsx", "A 26518-2026")</f>
         <v/>
       </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 8169-2023 karta.png", "A 8169-2023")</f>
+      <c r="X26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 26518-2026 karta.png", "A 26518-2026")</f>
         <v/>
       </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 8169-2023 georefererad karta.tif", "A 8169-2023")</f>
+      <c r="Y26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 26518-2026 georefererad karta.tif", "A 26518-2026")</f>
         <v/>
       </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 8169-2023 FSC-klagomål.docx", "A 8169-2023")</f>
+      <c r="AA26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 26518-2026 FSC-klagomål.docx", "A 26518-2026")</f>
         <v/>
       </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 8169-2023 FSC-klagomål mail.docx", "A 8169-2023")</f>
+      <c r="AB26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 26518-2026 FSC-klagomål mail.docx", "A 26518-2026")</f>
         <v/>
       </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 8169-2023 tillsynsbegäran.docx", "A 8169-2023")</f>
+      <c r="AC26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 26518-2026 tillsynsbegäran.docx", "A 26518-2026")</f>
         <v/>
       </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 8169-2023 tillsynsbegäran mail.docx", "A 8169-2023")</f>
+      <c r="AD26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 26518-2026 tillsynsbegäran mail.docx", "A 26518-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 10814-2024</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>45369</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 3992-2023</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>44952</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J27" t="n">
         <v>1</v>
       </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
         <v>1</v>
       </c>
-      <c r="R23" t="n">
+      <c r="T27" t="n">
         <v>1</v>
       </c>
-      <c r="S23" t="n">
-        <v>1</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Brunfläckig pärlemorfjäril</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 10814-2024 artfynd.xlsx", "A 10814-2024")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 10814-2024 karta.png", "A 10814-2024")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 10814-2024 georefererad karta.tif", "A 10814-2024")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 10814-2024 FSC-klagomål.docx", "A 10814-2024")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 10814-2024 FSC-klagomål mail.docx", "A 10814-2024")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 10814-2024 tillsynsbegäran.docx", "A 10814-2024")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 10814-2024 tillsynsbegäran mail.docx", "A 10814-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 3992-2023</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>44952</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Fläcknycklar</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 3992-2023 artfynd.xlsx", "A 3992-2023")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 3992-2023 karta.png", "A 3992-2023")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 3992-2023 georefererad karta.tif", "A 3992-2023")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 3992-2023 FSC-klagomål.docx", "A 3992-2023")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 3992-2023 FSC-klagomål mail.docx", "A 3992-2023")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 3992-2023 tillsynsbegäran.docx", "A 3992-2023")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 3992-2023 tillsynsbegäran mail.docx", "A 3992-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 23546-2026</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>46163</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 23546-2026 artfynd.xlsx", "A 23546-2026")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 23546-2026 karta.png", "A 23546-2026")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 23546-2026 georefererad karta.tif", "A 23546-2026")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 23546-2026 FSC-klagomål.docx", "A 23546-2026")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 23546-2026 FSC-klagomål mail.docx", "A 23546-2026")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 23546-2026 tillsynsbegäran.docx", "A 23546-2026")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 23546-2026 tillsynsbegäran mail.docx", "A 23546-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 43531-2025</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>45911</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>8</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>1</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 43531-2025 artfynd.xlsx", "A 43531-2025")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 43531-2025 karta.png", "A 43531-2025")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 43531-2025 georefererad karta.tif", "A 43531-2025")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 43531-2025 FSC-klagomål.docx", "A 43531-2025")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 43531-2025 FSC-klagomål mail.docx", "A 43531-2025")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 43531-2025 tillsynsbegäran.docx", "A 43531-2025")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 43531-2025 tillsynsbegäran mail.docx", "A 43531-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 26518-2026</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>46183</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1</v>
-      </c>
-      <c r="S27" t="n">
-        <v>1</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Rotfingersvamp</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 26518-2026 artfynd.xlsx", "A 26518-2026")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 26518-2026 karta.png", "A 26518-2026")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 26518-2026 georefererad karta.tif", "A 26518-2026")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 26518-2026 FSC-klagomål.docx", "A 26518-2026")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 26518-2026 FSC-klagomål mail.docx", "A 26518-2026")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 26518-2026 tillsynsbegäran.docx", "A 26518-2026")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 26518-2026 tillsynsbegäran mail.docx", "A 26518-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
@@ -3494,7 +3501,7 @@
         <v>46281</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3599,7 +3606,7 @@
         <v>44754</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3672,7 +3679,7 @@
         <v>44732</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3728,7 +3735,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 32627-2022</t>
+          <t>A 9008-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3742,10 +3749,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44783</v>
+        <v>44615</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3758,7 +3765,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3801,7 +3808,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 9008-2022</t>
+          <t>A 32627-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3815,10 +3822,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44615</v>
+        <v>44783</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3831,7 +3838,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.1</v>
+        <v>1.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3891,7 +3898,7 @@
         <v>44754</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3964,7 +3971,7 @@
         <v>44461</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4037,7 +4044,7 @@
         <v>44546</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4093,7 +4100,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 29336-2022</t>
+          <t>A 57805-2021</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4107,10 +4114,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44752</v>
+        <v>44484</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4123,7 +4130,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.7</v>
+        <v>11.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4166,7 +4173,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 57805-2021</t>
+          <t>A 29336-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4180,10 +4187,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44484</v>
+        <v>44752</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4196,7 +4203,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>11.3</v>
+        <v>1.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4256,7 +4263,7 @@
         <v>44873</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4329,7 +4336,7 @@
         <v>44469</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4402,7 +4409,7 @@
         <v>44752</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4475,7 +4482,7 @@
         <v>44564</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4548,7 +4555,7 @@
         <v>44460</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4621,7 +4628,7 @@
         <v>44578</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4694,7 +4701,7 @@
         <v>44657</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4767,7 +4774,7 @@
         <v>44840</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4840,7 +4847,7 @@
         <v>44620</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4913,7 +4920,7 @@
         <v>44677</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4986,7 +4993,7 @@
         <v>44720</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5059,7 +5066,7 @@
         <v>44676</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5132,7 +5139,7 @@
         <v>44817</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5205,7 +5212,7 @@
         <v>44539</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5278,7 +5285,7 @@
         <v>44704</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5351,7 +5358,7 @@
         <v>44508</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5424,7 +5431,7 @@
         <v>44484</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5480,7 +5487,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 32642-2022</t>
+          <t>A 52269-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5494,10 +5501,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44783</v>
+        <v>44873</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5510,7 +5517,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5553,7 +5560,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 26530-2023</t>
+          <t>A 32642-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5567,10 +5574,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45092</v>
+        <v>44783</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5583,7 +5590,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5626,7 +5633,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 12334-2024</t>
+          <t>A 61060-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5640,10 +5647,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45378</v>
+        <v>44915</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5656,7 +5663,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2</v>
+        <v>8.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5699,7 +5706,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 10401-2024</t>
+          <t>A 61061-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5713,10 +5720,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45365</v>
+        <v>44915</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5729,7 +5736,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>7.6</v>
+        <v>8.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5772,7 +5779,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 32299-2024</t>
+          <t>A 3989-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5786,10 +5793,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45512</v>
+        <v>44952</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5802,7 +5809,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5845,7 +5852,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 37267-2024</t>
+          <t>A 9374-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5859,10 +5866,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45540</v>
+        <v>44981</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5875,7 +5882,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.2</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5918,7 +5925,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 10398-2024</t>
+          <t>A 4054-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5932,10 +5939,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45365</v>
+        <v>45684</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5948,7 +5955,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5991,7 +5998,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 17685-2024</t>
+          <t>A 19872-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6005,10 +6012,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45418</v>
+        <v>45054</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6021,7 +6028,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.9</v>
+        <v>8.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6064,7 +6071,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 1921-2025</t>
+          <t>A 9152-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6078,10 +6085,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45671</v>
+        <v>45357</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6094,7 +6101,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6137,7 +6144,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 33666-2023</t>
+          <t>A 56025-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6151,10 +6158,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45132</v>
+        <v>45624</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6167,7 +6174,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6210,7 +6217,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 6283-2023</t>
+          <t>A 51173-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6224,10 +6231,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44965</v>
+        <v>45212</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6240,7 +6247,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6283,7 +6290,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 28319-2025</t>
+          <t>A 32549-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6297,10 +6304,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45818</v>
+        <v>45513</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6313,7 +6320,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6356,7 +6363,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 1883-2023</t>
+          <t>A 9456-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6370,10 +6377,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44939</v>
+        <v>45359</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6386,7 +6393,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6429,7 +6436,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 8160-2026</t>
+          <t>A 7154-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6439,14 +6446,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46064</v>
+        <v>45344</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6459,7 +6466,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6502,7 +6509,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 28870-2025</t>
+          <t>A 4416-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6516,10 +6523,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45820</v>
+        <v>45686</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6532,7 +6539,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>7.9</v>
+        <v>0.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6575,7 +6582,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 52471-2023</t>
+          <t>A 33388-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6589,10 +6596,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45225</v>
+        <v>44788</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6605,7 +6612,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6648,7 +6655,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 9573-2026</t>
+          <t>A 24978-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6662,10 +6669,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46071</v>
+        <v>44728</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6678,7 +6685,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>5.2</v>
+        <v>2.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6721,7 +6728,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 38888-2025</t>
+          <t>A 46917-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6735,10 +6742,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45887</v>
+        <v>44851</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6751,7 +6758,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6794,7 +6801,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 53317-2024</t>
+          <t>A 8155-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6808,10 +6815,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45614</v>
+        <v>44974</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6824,7 +6831,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.3</v>
+        <v>2.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6867,7 +6874,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 43353-2024</t>
+          <t>A 37267-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6881,10 +6888,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45568</v>
+        <v>45540</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6897,7 +6904,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.2</v>
+        <v>4.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6940,7 +6947,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 10356-2025</t>
+          <t>A 14596-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6954,10 +6961,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45720</v>
+        <v>44655</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6970,7 +6977,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7013,7 +7020,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 11121-2026</t>
+          <t>A 13800-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7023,14 +7030,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46079</v>
+        <v>45007</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7043,7 +7050,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7086,7 +7093,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 11323-2026</t>
+          <t>A 12157-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7100,10 +7107,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46080</v>
+        <v>44636</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7116,7 +7123,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>7.3</v>
+        <v>2.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7159,7 +7166,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 11249-2026</t>
+          <t>A 39535-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7173,10 +7180,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46080</v>
+        <v>45551</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7189,7 +7196,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7232,7 +7239,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 32842-2025</t>
+          <t>A 51783-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7246,10 +7253,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45839</v>
+        <v>45222</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7262,7 +7269,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>6.1</v>
+        <v>1.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7305,7 +7312,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 13594-2026</t>
+          <t>A 7443-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7315,14 +7322,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46096</v>
+        <v>44971</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7335,7 +7342,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7378,7 +7385,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 23450-2025</t>
+          <t>A 17685-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7392,10 +7399,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45792</v>
+        <v>45418</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7408,7 +7415,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7451,7 +7458,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 334-2023</t>
+          <t>A 10356-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7465,10 +7472,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44929</v>
+        <v>45720</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7481,7 +7488,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7524,7 +7531,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 11442-2024</t>
+          <t>A 35605-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7538,10 +7545,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45372</v>
+        <v>45531</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7554,7 +7561,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7597,7 +7604,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 53307-2024</t>
+          <t>A 16656-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7611,10 +7618,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45614</v>
+        <v>44672</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7627,7 +7634,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7670,7 +7677,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 36141-2025</t>
+          <t>A 25109-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7684,10 +7691,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45866</v>
+        <v>44729</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7700,7 +7707,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7743,7 +7750,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 26639-2025</t>
+          <t>A 39728-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7757,10 +7764,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45810</v>
+        <v>45167</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7773,7 +7780,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>5.4</v>
+        <v>0.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7816,7 +7823,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 15227-2025</t>
+          <t>A 17543-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7830,10 +7837,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45744</v>
+        <v>45036</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7846,7 +7853,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7889,7 +7896,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 36048-2025</t>
+          <t>A 53307-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7903,10 +7910,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45866</v>
+        <v>45614</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7919,7 +7926,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7962,7 +7969,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 36963-2025</t>
+          <t>A 53254-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7976,10 +7983,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45874</v>
+        <v>44876</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7992,7 +7999,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8035,7 +8042,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 18055-2026</t>
+          <t>A 60996-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8049,10 +8056,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46125</v>
+        <v>44914</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8065,7 +8072,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>5.2</v>
+        <v>0.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8108,7 +8115,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 40064-2023</t>
+          <t>A 1921-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8122,10 +8129,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45168</v>
+        <v>45671</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8138,7 +8145,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8181,7 +8188,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 38040-2025</t>
+          <t>A 15323-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8195,10 +8202,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45882</v>
+        <v>45400</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8211,7 +8218,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2</v>
+        <v>10.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8254,7 +8261,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 26428-2022</t>
+          <t>A 10398-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8268,10 +8275,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44736</v>
+        <v>45365</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8284,7 +8291,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8327,7 +8334,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 8923-2024</t>
+          <t>A 38663-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8341,10 +8348,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45356</v>
+        <v>45884</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8357,7 +8364,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8400,7 +8407,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 38653-2025</t>
+          <t>A 36146-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8414,10 +8421,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45884</v>
+        <v>45866</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8430,7 +8437,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>5.3</v>
+        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8473,7 +8480,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 38663-2025</t>
+          <t>A 49449-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8487,10 +8494,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45884</v>
+        <v>45938</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8503,7 +8510,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8546,7 +8553,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 27908-2025</t>
+          <t>A 58861-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8560,10 +8567,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45817</v>
+        <v>44903</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8576,7 +8583,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8619,7 +8626,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 25109-2022</t>
+          <t>A 38653-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8633,10 +8640,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44729</v>
+        <v>45884</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8649,7 +8656,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.8</v>
+        <v>5.3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8692,7 +8699,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 42723-2025</t>
+          <t>A 11256-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8706,10 +8713,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45908</v>
+        <v>45726</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8722,7 +8729,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8765,7 +8772,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 43398-2025</t>
+          <t>A 8923-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8779,10 +8786,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45911</v>
+        <v>45356</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8795,7 +8802,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8838,7 +8845,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 44020-2025</t>
+          <t>A 38888-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8852,10 +8859,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45915</v>
+        <v>45887</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8868,7 +8875,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8911,7 +8918,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 44600-2025</t>
+          <t>A 39942-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8925,10 +8932,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45917</v>
+        <v>45167</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8941,7 +8948,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>7.2</v>
+        <v>1.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8984,7 +8991,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 25399-2023</t>
+          <t>A 3998-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8994,14 +9001,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45089</v>
+        <v>45684</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9014,7 +9021,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9057,7 +9064,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 44573-2025</t>
+          <t>A 32384-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9071,10 +9078,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45917</v>
+        <v>45120</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9087,7 +9094,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>5.5</v>
+        <v>1.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9130,7 +9137,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 44608-2025</t>
+          <t>A 27908-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9144,10 +9151,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45917</v>
+        <v>45817</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9160,7 +9167,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9203,7 +9210,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 50441-2023</t>
+          <t>A 53565-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9217,10 +9224,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45216</v>
+        <v>44879</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9233,7 +9240,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9276,7 +9283,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 32304-2024</t>
+          <t>A 59723-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9290,10 +9297,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45512</v>
+        <v>45992</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9306,7 +9313,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.2</v>
+        <v>12.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9349,7 +9356,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 493-2025</t>
+          <t>A 42723-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9363,10 +9370,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45664</v>
+        <v>45908</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9379,7 +9386,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9422,7 +9429,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 45991-2025</t>
+          <t>A 43398-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9436,10 +9443,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45924</v>
+        <v>45911</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9452,7 +9459,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>4.4</v>
+        <v>1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9495,7 +9502,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 49449-2025</t>
+          <t>A 20573-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9509,10 +9516,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45938</v>
+        <v>46140</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9524,8 +9531,13 @@
           <t>MELLERUD</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9568,7 +9580,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 20573-2026</t>
+          <t>A 44020-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9582,10 +9594,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46140</v>
+        <v>45915</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9597,13 +9609,8 @@
           <t>MELLERUD</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9646,7 +9653,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 24312-2025</t>
+          <t>A 44600-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9660,10 +9667,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45797</v>
+        <v>45917</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9676,7 +9683,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1</v>
+        <v>7.2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9719,7 +9726,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 45935-2025</t>
+          <t>A 44608-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9733,10 +9740,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45923</v>
+        <v>45917</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9792,7 +9799,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 45861-2025</t>
+          <t>A 44573-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9806,10 +9813,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45923</v>
+        <v>45917</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9822,7 +9829,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>10.2</v>
+        <v>5.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9865,7 +9872,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 4416-2025</t>
+          <t>A 6283-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9879,10 +9886,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45686</v>
+        <v>44965</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9895,7 +9902,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9938,7 +9945,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 15971-2023</t>
+          <t>A 40064-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9952,10 +9959,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45022</v>
+        <v>45168</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9968,7 +9975,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10011,7 +10018,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 53565-2022</t>
+          <t>A 34415-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10025,10 +10032,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44879</v>
+        <v>45525</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10041,7 +10048,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1</v>
+        <v>4.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10084,7 +10091,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 53254-2022</t>
+          <t>A 45861-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10098,10 +10105,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44876</v>
+        <v>45923</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10114,7 +10121,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.8</v>
+        <v>10.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10157,7 +10164,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 28865-2025</t>
+          <t>A 45935-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10171,10 +10178,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45820</v>
+        <v>45923</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10187,7 +10194,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10230,7 +10237,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 36146-2025</t>
+          <t>A 32304-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10244,10 +10251,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45866</v>
+        <v>45512</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10260,7 +10267,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10303,7 +10310,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 59723-2025</t>
+          <t>A 46761-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10317,10 +10324,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45992</v>
+        <v>45198</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10333,7 +10340,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>12.3</v>
+        <v>1.3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10376,7 +10383,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 46668-2025</t>
+          <t>A 45991-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10390,10 +10397,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45926</v>
+        <v>45924</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10406,7 +10413,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10449,7 +10456,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 35603-2024</t>
+          <t>A 28865-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10463,10 +10470,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45531</v>
+        <v>45820</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10479,7 +10486,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10522,7 +10529,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 73351-2021</t>
+          <t>A 21077-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10536,10 +10543,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44551</v>
+        <v>45057</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10552,7 +10559,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>6.1</v>
+        <v>1.3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10595,7 +10602,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 51916-2022</t>
+          <t>A 46872-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10605,14 +10612,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44868</v>
+        <v>45929</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10625,7 +10632,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>4.5</v>
+        <v>0.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10668,7 +10675,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 46872-2025</t>
+          <t>A 22313-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10682,10 +10689,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45929</v>
+        <v>45070</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10698,7 +10705,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10741,7 +10748,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 35605-2024</t>
+          <t>A 46668-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10755,10 +10762,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45531</v>
+        <v>45926</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10771,7 +10778,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10814,7 +10821,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 61811-2023</t>
+          <t>A 52128-2021</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10828,10 +10835,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45264</v>
+        <v>44463</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10843,13 +10850,8 @@
           <t>MELLERUD</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>7.9</v>
+        <v>1.9</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10892,7 +10894,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 21432-2026</t>
+          <t>A 17160-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10906,10 +10908,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46148</v>
+        <v>45412</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10922,7 +10924,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10965,7 +10967,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 34415-2024</t>
+          <t>A 48256-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10979,10 +10981,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45525</v>
+        <v>44858</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10995,7 +10997,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>4.3</v>
+        <v>1.9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11038,7 +11040,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 22364-2026</t>
+          <t>A 8152-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11052,10 +11054,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46154</v>
+        <v>44974</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11068,7 +11070,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11111,7 +11113,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 21977-2026</t>
+          <t>A 49718-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11125,10 +11127,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46153</v>
+        <v>45939</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11141,7 +11143,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11184,7 +11186,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 22337-2026</t>
+          <t>A 40065-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11198,10 +11200,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46154</v>
+        <v>45168</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11214,7 +11216,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11257,7 +11259,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 33092-2023</t>
+          <t>A 21432-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11271,10 +11273,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45126</v>
+        <v>46148</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11287,7 +11289,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11330,7 +11332,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 40065-2023</t>
+          <t>A 43406-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11344,10 +11346,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45168</v>
+        <v>45911</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11360,7 +11362,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11403,7 +11405,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 1369-2025</t>
+          <t>A 45834-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11417,10 +11419,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45667</v>
+        <v>45195</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11433,7 +11435,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11476,7 +11478,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 16746-2023</t>
+          <t>A 51463-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11490,10 +11492,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45030</v>
+        <v>45221</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11506,7 +11508,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11549,7 +11551,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 51436-2025</t>
+          <t>A 21977-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11563,10 +11565,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45950</v>
+        <v>46153</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11579,7 +11581,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11622,7 +11624,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 59865-2024</t>
+          <t>A 8492-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11636,10 +11638,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45639</v>
+        <v>44613</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11652,7 +11654,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>5.9</v>
+        <v>1.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11695,7 +11697,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 3989-2023</t>
+          <t>A 50478-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11709,10 +11711,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44952</v>
+        <v>45945</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11725,7 +11727,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11768,7 +11770,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 51783-2023</t>
+          <t>A 50482-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11782,10 +11784,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45222</v>
+        <v>45945</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11798,7 +11800,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11841,7 +11843,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 49718-2025</t>
+          <t>A 53232-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11855,10 +11857,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45939</v>
+        <v>45958</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11871,7 +11873,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11914,7 +11916,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 32832-2024</t>
+          <t>A 48879-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11928,10 +11930,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45516</v>
+        <v>45594</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11944,7 +11946,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11987,7 +11989,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 28863-2025</t>
+          <t>A 5647-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12001,10 +12003,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45820</v>
+        <v>44960</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12017,7 +12019,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12060,7 +12062,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 32498-2024</t>
+          <t>A 22364-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12074,10 +12076,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45513</v>
+        <v>46154</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12090,7 +12092,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12133,7 +12135,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 27510-2023</t>
+          <t>A 12334-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12147,10 +12149,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45097</v>
+        <v>45378</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12163,7 +12165,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12206,7 +12208,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 59269-2025</t>
+          <t>A 56026-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12220,10 +12222,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45988</v>
+        <v>45973</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12236,7 +12238,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12279,7 +12281,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 22313-2023</t>
+          <t>A 12713-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12293,10 +12295,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45070</v>
+        <v>44641</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12309,7 +12311,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12352,7 +12354,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 25036-2026</t>
+          <t>A 56349-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12366,10 +12368,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46174</v>
+        <v>45974</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12382,7 +12384,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>5.9</v>
+        <v>1.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12425,7 +12427,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 43406-2025</t>
+          <t>A 22337-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12439,10 +12441,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45911</v>
+        <v>46154</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12455,7 +12457,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12498,7 +12500,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 36138-2025</t>
+          <t>A 11219-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12512,10 +12514,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45866</v>
+        <v>45371</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12528,7 +12530,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.6</v>
+        <v>6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12571,7 +12573,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 25458-2026</t>
+          <t>A 18205-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12585,10 +12587,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46177</v>
+        <v>45420</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12601,7 +12603,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12644,7 +12646,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 14568-2022</t>
+          <t>A 16746-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12658,10 +12660,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44655</v>
+        <v>45030</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12674,7 +12676,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12717,7 +12719,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 25954-2026</t>
+          <t>A 1369-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12731,10 +12733,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46181</v>
+        <v>45667</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12747,7 +12749,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12790,7 +12792,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 26527-2026</t>
+          <t>A 32832-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12804,10 +12806,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46183</v>
+        <v>45516</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12819,13 +12821,8 @@
           <t>MELLERUD</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I155" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12868,7 +12865,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 32384-2023</t>
+          <t>A 59804-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12882,10 +12879,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45120</v>
+        <v>45992</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12898,7 +12895,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12941,7 +12938,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 26536-2026</t>
+          <t>A 59802-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12955,10 +12952,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46183</v>
+        <v>45992</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12970,13 +12967,8 @@
           <t>MELLERUD</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I157" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13019,7 +13011,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 53232-2025</t>
+          <t>A 59808-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13033,10 +13025,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45958</v>
+        <v>45992</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13049,7 +13041,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13092,7 +13084,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 50478-2025</t>
+          <t>A 59865-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13106,10 +13098,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45945</v>
+        <v>45639</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13122,7 +13114,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1</v>
+        <v>5.9</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13165,7 +13157,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 50482-2025</t>
+          <t>A 51436-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13179,10 +13171,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45945</v>
+        <v>45950</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13195,7 +13187,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>8.800000000000001</v>
+        <v>2</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13238,7 +13230,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 39942-2023</t>
+          <t>A 28863-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13252,10 +13244,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45167</v>
+        <v>45820</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13268,7 +13260,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13311,7 +13303,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 12713-2022</t>
+          <t>A 59806-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13325,10 +13317,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44641</v>
+        <v>45992</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13341,7 +13333,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13384,7 +13376,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 18854-2023</t>
+          <t>A 10428-2022</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13398,10 +13390,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45042</v>
+        <v>44623</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13414,7 +13406,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13457,7 +13449,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 51785-2023</t>
+          <t>A 60203-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13471,10 +13463,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45222</v>
+        <v>45994</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13487,7 +13479,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13530,7 +13522,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 3998-2025</t>
+          <t>A 61177-2025</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13540,14 +13532,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45684</v>
+        <v>46000</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13560,7 +13552,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>8.199999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13603,7 +13595,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 19872-2023</t>
+          <t>A 61180-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13617,10 +13609,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45054</v>
+        <v>46000</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13633,7 +13625,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>8.4</v>
+        <v>1</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13676,7 +13668,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 56349-2025</t>
+          <t>A 54796-2022</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13690,10 +13682,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45974</v>
+        <v>44883</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13749,7 +13741,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 56026-2025</t>
+          <t>A 53573-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13763,10 +13755,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45973</v>
+        <v>45230</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13779,7 +13771,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13822,7 +13814,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 8492-2022</t>
+          <t>A 63249-2025</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13836,10 +13828,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44613</v>
+        <v>46010</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13852,7 +13844,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13895,7 +13887,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 29936-2026</t>
+          <t>A 34116-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13905,14 +13897,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46205</v>
+        <v>45126</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13925,7 +13917,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.6</v>
+        <v>4.3</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13968,7 +13960,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 33450-2026</t>
+          <t>A 1883-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13982,10 +13974,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46246</v>
+        <v>44939</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13998,7 +13990,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14041,7 +14033,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 29939-2026</t>
+          <t>A 1886-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14055,10 +14047,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46205</v>
+        <v>44939</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14071,7 +14063,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14114,7 +14106,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 10428-2022</t>
+          <t>A 1830-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14128,10 +14120,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44623</v>
+        <v>46035</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14144,7 +14136,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14187,7 +14179,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 21618-2024</t>
+          <t>A 1827-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14201,10 +14193,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45442</v>
+        <v>46035</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14217,7 +14209,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14260,7 +14252,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 21620-2024</t>
+          <t>A 59269-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14274,10 +14266,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45442</v>
+        <v>45988</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14290,7 +14282,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14333,7 +14325,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 33388-2022</t>
+          <t>A 3178-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14347,10 +14339,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44788</v>
+        <v>46041</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14363,7 +14355,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>8.699999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14406,7 +14398,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 46761-2023</t>
+          <t>A 27510-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14420,10 +14412,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45198</v>
+        <v>45097</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14436,7 +14428,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14479,7 +14471,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 20578-2026</t>
+          <t>A 334-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14493,10 +14485,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46140</v>
+        <v>44929</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14508,13 +14500,8 @@
           <t>MELLERUD</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I178" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14557,7 +14544,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 16656-2022</t>
+          <t>A 3250-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14571,10 +14558,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44672</v>
+        <v>46041</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14630,7 +14617,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 34065-2026</t>
+          <t>A 32299-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14644,10 +14631,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46252</v>
+        <v>45512</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14660,7 +14647,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14703,7 +14690,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 51463-2023</t>
+          <t>A 3201-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14717,10 +14704,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45221</v>
+        <v>46041</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14733,7 +14720,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14776,7 +14763,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 59808-2025</t>
+          <t>A 25036-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14790,10 +14777,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45992</v>
+        <v>46174</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14806,7 +14793,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>0.5</v>
+        <v>5.9</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14849,7 +14836,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 59806-2025</t>
+          <t>A 5324-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14863,10 +14850,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45992</v>
+        <v>46050</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14922,7 +14909,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 59804-2025</t>
+          <t>A 7047-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14936,10 +14923,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45992</v>
+        <v>46057</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14952,7 +14939,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14995,7 +14982,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 34116-2023</t>
+          <t>A 7125-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15005,14 +14992,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45126</v>
+        <v>46058</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15025,7 +15012,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>4.3</v>
+        <v>0.9</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15068,7 +15055,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 59802-2025</t>
+          <t>A 7120-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15082,10 +15069,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45992</v>
+        <v>46058</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15141,7 +15128,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 56025-2024</t>
+          <t>A 7117-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15155,10 +15142,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45624</v>
+        <v>46058</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15171,7 +15158,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15214,7 +15201,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 11256-2025</t>
+          <t>A 36138-2025</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15228,10 +15215,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45726</v>
+        <v>45866</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15244,7 +15231,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15287,7 +15274,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 60203-2025</t>
+          <t>A 25458-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15301,10 +15288,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45994</v>
+        <v>46177</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15317,7 +15304,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15360,7 +15347,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 8155-2023</t>
+          <t>A 8160-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15374,10 +15361,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>44974</v>
+        <v>46064</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15433,7 +15420,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 61177-2025</t>
+          <t>A 9573-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15443,14 +15430,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46000</v>
+        <v>46071</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15463,7 +15450,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.9</v>
+        <v>5.2</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15506,7 +15493,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 61180-2025</t>
+          <t>A 32498-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15520,10 +15507,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46000</v>
+        <v>45513</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15536,7 +15523,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15579,7 +15566,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 53573-2023</t>
+          <t>A 43353-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15593,10 +15580,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45230</v>
+        <v>45568</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15609,7 +15596,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15652,7 +15639,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 61060-2022</t>
+          <t>A 25954-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15666,10 +15653,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44915</v>
+        <v>46181</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15682,7 +15669,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>8.4</v>
+        <v>1.5</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15725,7 +15712,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 61061-2022</t>
+          <t>A 26536-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15739,10 +15726,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44915</v>
+        <v>46183</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15754,8 +15741,13 @@
           <t>MELLERUD</t>
         </is>
       </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I195" t="n">
-        <v>8.5</v>
+        <v>0.6</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15798,7 +15790,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 55391-2023</t>
+          <t>A 51916-2022</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15808,14 +15800,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45238</v>
+        <v>44868</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15828,7 +15820,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15871,7 +15863,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 54796-2022</t>
+          <t>A 26527-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15885,10 +15877,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44883</v>
+        <v>46183</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15900,8 +15892,13 @@
           <t>MELLERUD</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I197" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15944,7 +15941,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 13800-2023</t>
+          <t>A 33666-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15958,10 +15955,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45007</v>
+        <v>45132</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15974,7 +15971,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16017,7 +16014,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 48879-2024</t>
+          <t>A 11249-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16031,10 +16028,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45594</v>
+        <v>46080</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16047,7 +16044,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16090,7 +16087,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 45834-2023</t>
+          <t>A 11121-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16100,14 +16097,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45195</v>
+        <v>46079</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16163,7 +16160,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 31836-2026</t>
+          <t>A 11323-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16173,14 +16170,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46230</v>
+        <v>46080</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16193,7 +16190,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.7</v>
+        <v>7.3</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16236,7 +16233,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 63249-2025</t>
+          <t>A 51785-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16250,10 +16247,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46010</v>
+        <v>45222</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16266,7 +16263,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16309,7 +16306,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 36960-2026</t>
+          <t>A 13594-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16319,14 +16316,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46273</v>
+        <v>46096</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16339,7 +16336,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>8.1</v>
+        <v>0.9</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16382,7 +16379,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 52269-2022</t>
+          <t>A 33092-2023</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16396,10 +16393,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>44873</v>
+        <v>45126</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16412,7 +16409,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>4.6</v>
+        <v>2.9</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16455,7 +16452,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 31889-2026</t>
+          <t>A 55391-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16469,10 +16466,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46231</v>
+        <v>45238</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16485,7 +16482,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16528,7 +16525,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 15323-2024</t>
+          <t>A 15971-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16542,10 +16539,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45400</v>
+        <v>45022</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16558,7 +16555,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>10.6</v>
+        <v>1.5</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16601,7 +16598,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 17160-2024</t>
+          <t>A 53317-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16615,10 +16612,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45412</v>
+        <v>45614</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16631,7 +16628,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>3.5</v>
+        <v>0.3</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16674,7 +16671,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 19545-2024</t>
+          <t>A 73351-2021</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16688,10 +16685,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45429</v>
+        <v>44551</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16704,7 +16701,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.7</v>
+        <v>6.1</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16747,7 +16744,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 52128-2021</t>
+          <t>A 18055-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16761,10 +16758,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>44463</v>
+        <v>46125</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16777,7 +16774,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.9</v>
+        <v>5.2</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16820,7 +16817,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 46917-2022</t>
+          <t>A 26428-2022</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16834,10 +16831,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>44851</v>
+        <v>44736</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16850,7 +16847,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16893,7 +16890,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 38251-2026</t>
+          <t>A 33450-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16907,10 +16904,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46281</v>
+        <v>46246</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16923,7 +16920,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16966,7 +16963,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 60996-2022</t>
+          <t>A 21618-2024</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16980,10 +16977,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>44914</v>
+        <v>45442</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16996,7 +16993,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17039,7 +17036,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 12157-2022</t>
+          <t>A 21620-2024</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17049,14 +17046,14 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>44636</v>
+        <v>45442</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17069,7 +17066,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17112,7 +17109,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 32691-2026</t>
+          <t>A 26530-2023</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17126,10 +17123,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46240</v>
+        <v>45092</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17142,7 +17139,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17185,7 +17182,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 9456-2024</t>
+          <t>A 24312-2025</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17199,10 +17196,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45359</v>
+        <v>45797</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17215,7 +17212,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17258,7 +17255,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 32520-2026</t>
+          <t>A 493-2025</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17272,10 +17269,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46239</v>
+        <v>45664</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17288,7 +17285,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17331,7 +17328,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 1830-2026</t>
+          <t>A 35603-2024</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17345,10 +17342,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46035</v>
+        <v>45531</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17361,7 +17358,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17404,7 +17401,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 1827-2026</t>
+          <t>A 18854-2023</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17418,10 +17415,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46035</v>
+        <v>45042</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17434,7 +17431,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17477,7 +17474,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 53270-2024</t>
+          <t>A 14568-2022</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17491,10 +17488,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45614</v>
+        <v>44655</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17507,7 +17504,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17550,7 +17547,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 5647-2023</t>
+          <t>A 61811-2023</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17564,10 +17561,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>44960</v>
+        <v>45264</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17579,8 +17576,13 @@
           <t>MELLERUD</t>
         </is>
       </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I220" t="n">
-        <v>0.7</v>
+        <v>7.9</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17623,7 +17625,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 7443-2023</t>
+          <t>A 20578-2026</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17637,10 +17639,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>44971</v>
+        <v>46140</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17652,8 +17654,13 @@
           <t>MELLERUD</t>
         </is>
       </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I221" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17696,7 +17703,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 3250-2026</t>
+          <t>A 29936-2026</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17710,10 +17717,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>46041</v>
+        <v>46205</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17726,7 +17733,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17769,7 +17776,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 1886-2023</t>
+          <t>A 29939-2026</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17783,10 +17790,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>44939</v>
+        <v>46205</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17799,7 +17806,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17842,7 +17849,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 3178-2026</t>
+          <t>A 34065-2026</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17856,10 +17863,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46041</v>
+        <v>46252</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17872,7 +17879,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17915,7 +17922,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 3201-2026</t>
+          <t>A 25399-2023</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17925,14 +17932,14 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46041</v>
+        <v>45089</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17945,7 +17952,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17988,7 +17995,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 5324-2026</t>
+          <t>A 23238-2024</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18002,10 +18009,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>46050</v>
+        <v>45453</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18018,7 +18025,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18061,7 +18068,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 9374-2023</t>
+          <t>A 53270-2024</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18075,10 +18082,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>44981</v>
+        <v>45614</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18091,7 +18098,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18134,7 +18141,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 48256-2022</t>
+          <t>A 17538-2023</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18148,10 +18155,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>44858</v>
+        <v>45036</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18164,7 +18171,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18207,7 +18214,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 23238-2024</t>
+          <t>A 19545-2024</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18221,10 +18228,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45453</v>
+        <v>45429</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18237,7 +18244,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18280,7 +18287,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 7154-2024</t>
+          <t>A 50441-2023</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18290,14 +18297,14 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45344</v>
+        <v>45216</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18310,7 +18317,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18353,7 +18360,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 24978-2022</t>
+          <t>A 10401-2024</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18367,10 +18374,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>44728</v>
+        <v>45365</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18383,7 +18390,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>2.4</v>
+        <v>7.6</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18426,7 +18433,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 18205-2024</t>
+          <t>A 21689-2025</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18440,10 +18447,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45420</v>
+        <v>45783</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18456,7 +18463,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18499,7 +18506,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 17543-2023</t>
+          <t>A 21678-2025</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18513,10 +18520,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45036</v>
+        <v>45783</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18529,7 +18536,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18572,7 +18579,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 7117-2026</t>
+          <t>A 21698-2025</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18586,10 +18593,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>46058</v>
+        <v>45783</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18602,7 +18609,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18645,7 +18652,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 7125-2026</t>
+          <t>A 31836-2026</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18659,10 +18666,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>46058</v>
+        <v>46230</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18675,7 +18682,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18718,7 +18725,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 7047-2026</t>
+          <t>A 36960-2026</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18732,10 +18739,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>46057</v>
+        <v>46273</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18748,7 +18755,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>1.7</v>
+        <v>8.1</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18791,7 +18798,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 7120-2026</t>
+          <t>A 13313-2024</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18805,10 +18812,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>46058</v>
+        <v>45386</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18821,7 +18828,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18864,7 +18871,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 17538-2023</t>
+          <t>A 31889-2026</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18878,10 +18885,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45036</v>
+        <v>46231</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18894,7 +18901,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18937,7 +18944,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 11219-2024</t>
+          <t>A 27342-2024</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18951,10 +18958,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45371</v>
+        <v>45473</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18967,7 +18974,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -19010,7 +19017,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 58861-2022</t>
+          <t>A 10100-2025</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -19024,10 +19031,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>44903</v>
+        <v>45719</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19040,7 +19047,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>4.8</v>
+        <v>1.2</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -19083,7 +19090,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 39728-2023</t>
+          <t>A 8667-2025</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -19097,10 +19104,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45167</v>
+        <v>45712</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19113,7 +19120,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -19156,7 +19163,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 51173-2023</t>
+          <t>A 10357-2025</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19170,10 +19177,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45212</v>
+        <v>45720</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19186,7 +19193,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19229,7 +19236,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 4054-2025</t>
+          <t>A 10358-2025</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19243,10 +19250,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45684</v>
+        <v>45720</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19259,7 +19266,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19302,7 +19309,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 14596-2022</t>
+          <t>A 60993-2022</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19316,10 +19323,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>44655</v>
+        <v>44914</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19332,7 +19339,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19375,7 +19382,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 39535-2024</t>
+          <t>A 38251-2026</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19389,10 +19396,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45551</v>
+        <v>46281</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19405,7 +19412,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>4.7</v>
+        <v>0.8</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19448,7 +19455,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 32549-2024</t>
+          <t>A 10097-2025</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19462,10 +19469,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45513</v>
+        <v>45719</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19478,7 +19485,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19521,7 +19528,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 21077-2023</t>
+          <t>A 11213-2025</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19535,10 +19542,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45057</v>
+        <v>45726</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19551,7 +19558,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>1.3</v>
+        <v>4.8</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19594,7 +19601,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 9152-2024</t>
+          <t>A 32520-2026</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19608,10 +19615,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45357</v>
+        <v>46239</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19624,7 +19631,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19667,7 +19674,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 8152-2023</t>
+          <t>A 32691-2026</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19681,10 +19688,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>44974</v>
+        <v>46240</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19697,7 +19704,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19740,7 +19747,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 21698-2025</t>
+          <t>A 24533-2025</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19754,10 +19761,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45783</v>
+        <v>45798</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19770,7 +19777,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>0.5</v>
+        <v>5.8</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19813,7 +19820,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 21678-2025</t>
+          <t>A 24527-2025</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19827,10 +19834,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>45783</v>
+        <v>45798</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19843,7 +19850,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -19886,7 +19893,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 21689-2025</t>
+          <t>A 43017-2024</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19900,10 +19907,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45783</v>
+        <v>45567</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19916,7 +19923,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19959,7 +19966,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 27342-2024</t>
+          <t>A 25623-2025</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19973,10 +19980,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45473</v>
+        <v>45803</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19989,7 +19996,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -20032,7 +20039,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 13313-2024</t>
+          <t>A 25652-2025</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -20046,10 +20053,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45386</v>
+        <v>45803</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20062,7 +20069,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -20105,7 +20112,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 8667-2025</t>
+          <t>A 25635-2025</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20119,10 +20126,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45712</v>
+        <v>45803</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20135,7 +20142,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>3.1</v>
+        <v>0.4</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20178,7 +20185,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 60993-2022</t>
+          <t>A 60395-2024</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20188,14 +20195,14 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>44914</v>
+        <v>45643</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20208,7 +20215,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20251,7 +20258,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 10100-2025</t>
+          <t>A 17693-2023</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -20265,10 +20272,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>45719</v>
+        <v>45037</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20281,7 +20288,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>1.2</v>
+        <v>11.3</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20324,7 +20331,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 10097-2025</t>
+          <t>A 12501-2025</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20338,10 +20345,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45719</v>
+        <v>45730</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20354,7 +20361,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20397,7 +20404,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 10357-2025</t>
+          <t>A 11848-2025</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20411,10 +20418,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>45720</v>
+        <v>45728</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20427,7 +20434,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20470,7 +20477,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 10358-2025</t>
+          <t>A 8165-2023</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -20484,10 +20491,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45720</v>
+        <v>44974</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20500,7 +20507,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -20543,7 +20550,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 11213-2025</t>
+          <t>A 17528-2024</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -20557,10 +20564,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>45726</v>
+        <v>45415</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20573,7 +20580,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -20616,7 +20623,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 24527-2025</t>
+          <t>A 52922-2024</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -20630,10 +20637,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>45798</v>
+        <v>45610</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20646,7 +20653,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>3.6</v>
+        <v>1.2</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -20689,7 +20696,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 24533-2025</t>
+          <t>A 7228-2025</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -20703,10 +20710,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>45798</v>
+        <v>45702</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20719,7 +20726,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>5.8</v>
+        <v>1.4</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -20762,7 +20769,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 43017-2024</t>
+          <t>A 28319-2025</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -20776,10 +20783,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>45567</v>
+        <v>45818</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20792,7 +20799,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -20835,7 +20842,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 25652-2025</t>
+          <t>A 28870-2025</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -20849,10 +20856,10 @@
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>45803</v>
+        <v>45820</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20865,7 +20872,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>0.6</v>
+        <v>7.9</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -20908,7 +20915,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>A 25635-2025</t>
+          <t>A 32842-2025</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -20922,10 +20929,10 @@
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>45803</v>
+        <v>45839</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20938,7 +20945,7 @@
         </is>
       </c>
       <c r="I266" t="n">
-        <v>0.4</v>
+        <v>6.1</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -20981,7 +20988,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>A 25623-2025</t>
+          <t>A 23450-2025</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -20995,10 +21002,10 @@
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>45803</v>
+        <v>45792</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21011,7 +21018,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -21054,7 +21061,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>A 60395-2024</t>
+          <t>A 11442-2024</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -21064,14 +21071,14 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>45643</v>
+        <v>45372</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21084,7 +21091,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -21127,7 +21134,7 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>A 8165-2023</t>
+          <t>A 15227-2025</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -21141,10 +21148,10 @@
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>44974</v>
+        <v>45744</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21157,7 +21164,7 @@
         </is>
       </c>
       <c r="I269" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -21200,7 +21207,7 @@
     <row r="270" ht="15" customHeight="1">
       <c r="A270" t="inlineStr">
         <is>
-          <t>A 17528-2024</t>
+          <t>A 26639-2025</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -21214,10 +21221,10 @@
         </is>
       </c>
       <c r="D270" s="1" t="n">
-        <v>45415</v>
+        <v>45810</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21230,7 +21237,7 @@
         </is>
       </c>
       <c r="I270" t="n">
-        <v>3.6</v>
+        <v>5.4</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -21273,7 +21280,7 @@
     <row r="271" ht="15" customHeight="1">
       <c r="A271" t="inlineStr">
         <is>
-          <t>A 52922-2024</t>
+          <t>A 36141-2025</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -21287,10 +21294,10 @@
         </is>
       </c>
       <c r="D271" s="1" t="n">
-        <v>45610</v>
+        <v>45866</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21303,7 +21310,7 @@
         </is>
       </c>
       <c r="I271" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J271" t="n">
         <v>0</v>
@@ -21346,7 +21353,7 @@
     <row r="272" ht="15" customHeight="1">
       <c r="A272" t="inlineStr">
         <is>
-          <t>A 11848-2025</t>
+          <t>A 36048-2025</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -21360,10 +21367,10 @@
         </is>
       </c>
       <c r="D272" s="1" t="n">
-        <v>45728</v>
+        <v>45866</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21376,7 +21383,7 @@
         </is>
       </c>
       <c r="I272" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J272" t="n">
         <v>0</v>
@@ -21419,7 +21426,7 @@
     <row r="273" ht="15" customHeight="1">
       <c r="A273" t="inlineStr">
         <is>
-          <t>A 12501-2025</t>
+          <t>A 36963-2025</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -21433,10 +21440,10 @@
         </is>
       </c>
       <c r="D273" s="1" t="n">
-        <v>45730</v>
+        <v>45874</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21449,7 +21456,7 @@
         </is>
       </c>
       <c r="I273" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J273" t="n">
         <v>0</v>
@@ -21492,7 +21499,7 @@
     <row r="274" ht="15" customHeight="1">
       <c r="A274" t="inlineStr">
         <is>
-          <t>A 17693-2023</t>
+          <t>A 52471-2023</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -21506,10 +21513,10 @@
         </is>
       </c>
       <c r="D274" s="1" t="n">
-        <v>45037</v>
+        <v>45225</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21522,7 +21529,7 @@
         </is>
       </c>
       <c r="I274" t="n">
-        <v>11.3</v>
+        <v>2.5</v>
       </c>
       <c r="J274" t="n">
         <v>0</v>
@@ -21565,7 +21572,7 @@
     <row r="275" ht="15" customHeight="1">
       <c r="A275" t="inlineStr">
         <is>
-          <t>A 7228-2025</t>
+          <t>A 38040-2025</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -21579,10 +21586,10 @@
         </is>
       </c>
       <c r="D275" s="1" t="n">
-        <v>45702</v>
+        <v>45882</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21595,7 +21602,7 @@
         </is>
       </c>
       <c r="I275" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J275" t="n">
         <v>0</v>
@@ -21655,7 +21662,7 @@
         <v>44551</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21728,7 +21735,7 @@
         <v>45351</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21801,7 +21808,7 @@
         <v>46184</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21874,7 +21881,7 @@
         <v>46188</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>

--- a/Översikt MELLERUD.xlsx
+++ b/Översikt MELLERUD.xlsx
@@ -601,7 +601,7 @@
         <v>46184</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>46112</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>45614</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>45614</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44840</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>45734</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>46020</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>45670</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>45253</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>44963</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>45006</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>46020</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>46196</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>46244</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>45804</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>45390</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>44896</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>44804</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>44750</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>45369</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>46163</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>45911</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>44974</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>45568</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>46183</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>44952</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         <v>46281</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>44754</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>44732</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>44615</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         <v>44783</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>44754</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>44461</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>44546</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>44484</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>44752</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>44873</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4336,7 +4336,7 @@
         <v>44469</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>44752</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>44564</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>44460</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>44578</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         <v>44657</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>44840</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>44620</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
         <v>44677</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>44720</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>44676</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5139,7 +5139,7 @@
         <v>44817</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>44539</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         <v>44704</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>44508</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         <v>44484</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>44873</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>44783</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>44915</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>44915</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>44952</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>44981</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         <v>45684</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>45054</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>45357</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>45624</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>45212</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>45513</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
         <v>45359</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>45344</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>45686</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
         <v>44788</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>44728</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>44851</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         <v>44974</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         <v>45540</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>44655</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>45007</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>44636</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>45551</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>45222</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7329,7 +7329,7 @@
         <v>44971</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>45418</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>45720</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7548,7 +7548,7 @@
         <v>45531</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>44672</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>44729</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         <v>45167</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>45036</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7913,7 +7913,7 @@
         <v>45614</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7986,7 +7986,7 @@
         <v>44876</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>44914</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8132,7 +8132,7 @@
         <v>45671</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         <v>45400</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>45365</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>45884</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>45866</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         <v>45938</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>44903</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>45884</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8716,7 +8716,7 @@
         <v>45726</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8789,7 +8789,7 @@
         <v>45356</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8862,7 +8862,7 @@
         <v>45887</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         <v>45167</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>45684</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>45120</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9154,7 +9154,7 @@
         <v>45817</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>44879</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>45992</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9373,7 +9373,7 @@
         <v>45908</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         <v>45911</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9519,7 +9519,7 @@
         <v>46140</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         <v>45915</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>45917</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9743,7 +9743,7 @@
         <v>45917</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>45917</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9889,7 +9889,7 @@
         <v>44965</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
         <v>45168</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10035,7 +10035,7 @@
         <v>45525</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>45923</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10181,7 +10181,7 @@
         <v>45923</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10254,7 +10254,7 @@
         <v>45512</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10327,7 +10327,7 @@
         <v>45198</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10400,7 +10400,7 @@
         <v>45924</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>45820</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10546,7 +10546,7 @@
         <v>45057</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10619,7 +10619,7 @@
         <v>45929</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>45070</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>45926</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>44463</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>45412</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>44858</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>44974</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11130,7 +11130,7 @@
         <v>45939</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11203,7 +11203,7 @@
         <v>45168</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11276,7 +11276,7 @@
         <v>46148</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11349,7 +11349,7 @@
         <v>45911</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>45195</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11495,7 +11495,7 @@
         <v>45221</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11568,7 +11568,7 @@
         <v>46153</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11641,7 +11641,7 @@
         <v>44613</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11714,7 +11714,7 @@
         <v>45945</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11787,7 +11787,7 @@
         <v>45945</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11860,7 +11860,7 @@
         <v>45958</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         <v>45594</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>44960</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12079,7 +12079,7 @@
         <v>46154</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         <v>45378</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12225,7 +12225,7 @@
         <v>45973</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12298,7 +12298,7 @@
         <v>44641</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12371,7 +12371,7 @@
         <v>45974</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12444,7 +12444,7 @@
         <v>46154</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>45371</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12590,7 +12590,7 @@
         <v>45420</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12663,7 +12663,7 @@
         <v>45030</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12736,7 +12736,7 @@
         <v>45667</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         <v>45516</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12882,7 +12882,7 @@
         <v>45992</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12955,7 +12955,7 @@
         <v>45992</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13028,7 +13028,7 @@
         <v>45992</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13101,7 +13101,7 @@
         <v>45639</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13174,7 +13174,7 @@
         <v>45950</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13247,7 +13247,7 @@
         <v>45820</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13320,7 +13320,7 @@
         <v>45992</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13393,7 +13393,7 @@
         <v>44623</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13466,7 +13466,7 @@
         <v>45994</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13539,7 +13539,7 @@
         <v>46000</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13612,7 +13612,7 @@
         <v>46000</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13685,7 +13685,7 @@
         <v>44883</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13758,7 +13758,7 @@
         <v>45230</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
         <v>46010</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         <v>45126</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>44939</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>44939</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>46035</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14196,7 +14196,7 @@
         <v>46035</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>45988</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14342,7 +14342,7 @@
         <v>46041</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14415,7 +14415,7 @@
         <v>45097</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14488,7 +14488,7 @@
         <v>44929</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14561,7 +14561,7 @@
         <v>46041</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14634,7 +14634,7 @@
         <v>45512</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14707,7 +14707,7 @@
         <v>46041</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14780,7 +14780,7 @@
         <v>46174</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14853,7 +14853,7 @@
         <v>46050</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14926,7 +14926,7 @@
         <v>46057</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14999,7 +14999,7 @@
         <v>46058</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
         <v>46058</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15145,7 +15145,7 @@
         <v>46058</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         <v>45866</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15291,7 +15291,7 @@
         <v>46177</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15364,7 +15364,7 @@
         <v>46064</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15437,7 +15437,7 @@
         <v>46071</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15510,7 +15510,7 @@
         <v>45513</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15583,7 +15583,7 @@
         <v>45568</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15656,7 +15656,7 @@
         <v>46181</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15729,7 +15729,7 @@
         <v>46183</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15807,7 +15807,7 @@
         <v>44868</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15880,7 +15880,7 @@
         <v>46183</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15958,7 +15958,7 @@
         <v>45132</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>46080</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16104,7 +16104,7 @@
         <v>46079</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16177,7 +16177,7 @@
         <v>46080</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16250,7 +16250,7 @@
         <v>45222</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16323,7 +16323,7 @@
         <v>46096</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16396,7 +16396,7 @@
         <v>45126</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16469,7 +16469,7 @@
         <v>45238</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16542,7 +16542,7 @@
         <v>45022</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16615,7 +16615,7 @@
         <v>45614</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16688,7 +16688,7 @@
         <v>44551</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16761,7 +16761,7 @@
         <v>46125</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16834,7 +16834,7 @@
         <v>44736</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         <v>46246</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16980,7 +16980,7 @@
         <v>45442</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17053,7 +17053,7 @@
         <v>45442</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17126,7 +17126,7 @@
         <v>45092</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17199,7 +17199,7 @@
         <v>45797</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17272,7 +17272,7 @@
         <v>45664</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>45531</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17418,7 +17418,7 @@
         <v>45042</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         <v>44655</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>45264</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17642,7 +17642,7 @@
         <v>46140</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17720,7 +17720,7 @@
         <v>46205</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17793,7 +17793,7 @@
         <v>46205</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17866,7 +17866,7 @@
         <v>46252</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17939,7 +17939,7 @@
         <v>45089</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18012,7 +18012,7 @@
         <v>45453</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18085,7 +18085,7 @@
         <v>45614</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18158,7 +18158,7 @@
         <v>45036</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18231,7 +18231,7 @@
         <v>45429</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         <v>45216</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18377,7 +18377,7 @@
         <v>45365</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18450,7 +18450,7 @@
         <v>45783</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18523,7 +18523,7 @@
         <v>45783</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18596,7 +18596,7 @@
         <v>45783</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>46230</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18742,7 +18742,7 @@
         <v>46273</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18815,7 +18815,7 @@
         <v>45386</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
         <v>46231</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
         <v>45473</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         <v>45719</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         <v>45712</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>45720</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19253,7 +19253,7 @@
         <v>45720</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19326,7 +19326,7 @@
         <v>44914</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19399,7 +19399,7 @@
         <v>46281</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>45719</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19545,7 +19545,7 @@
         <v>45726</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>46239</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19691,7 +19691,7 @@
         <v>46240</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19764,7 +19764,7 @@
         <v>45798</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19837,7 +19837,7 @@
         <v>45798</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19910,7 +19910,7 @@
         <v>45567</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19983,7 +19983,7 @@
         <v>45803</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20056,7 +20056,7 @@
         <v>45803</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20129,7 +20129,7 @@
         <v>45803</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
         <v>45643</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>45037</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20348,7 +20348,7 @@
         <v>45730</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20421,7 +20421,7 @@
         <v>45728</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20494,7 +20494,7 @@
         <v>44974</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20567,7 +20567,7 @@
         <v>45415</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20640,7 +20640,7 @@
         <v>45610</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20713,7 +20713,7 @@
         <v>45702</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20786,7 +20786,7 @@
         <v>45818</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20859,7 +20859,7 @@
         <v>45820</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20932,7 +20932,7 @@
         <v>45839</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>45792</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21078,7 +21078,7 @@
         <v>45372</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21151,7 +21151,7 @@
         <v>45744</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21224,7 +21224,7 @@
         <v>45810</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21297,7 +21297,7 @@
         <v>45866</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21370,7 +21370,7 @@
         <v>45866</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21443,7 +21443,7 @@
         <v>45874</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>45225</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>45882</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21662,7 +21662,7 @@
         <v>44551</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>45351</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         <v>46184</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21881,7 +21881,7 @@
         <v>46188</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>

--- a/Översikt MELLERUD.xlsx
+++ b/Översikt MELLERUD.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE279"/>
+  <dimension ref="A1:AE276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>46184</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>46112</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>45614</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>45614</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44840</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>45734</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>46020</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>45670</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>45253</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>44963</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>45006</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>46020</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>46196</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>46244</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>45804</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>45390</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>44896</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>44804</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>44750</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>45369</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>46163</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>45911</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 8169-2023</t>
+          <t>A 26518-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44974</v>
+        <v>46183</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3088,8 +3088,13 @@
           <t>MELLERUD</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3098,10 +3103,10 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>1</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3116,7 +3121,7 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3129,253 +3134,248 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
+          <t>Rotfingersvamp</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 26518-2026 artfynd.xlsx", "A 26518-2026")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 26518-2026 karta.png", "A 26518-2026")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 26518-2026 georefererad karta.tif", "A 26518-2026")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 26518-2026 FSC-klagomål.docx", "A 26518-2026")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 26518-2026 FSC-klagomål mail.docx", "A 26518-2026")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 26518-2026 tillsynsbegäran.docx", "A 26518-2026")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 26518-2026 tillsynsbegäran mail.docx", "A 26518-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 8169-2023</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>44974</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>Älg</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 8169-2023 artfynd.xlsx", "A 8169-2023")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 8169-2023 karta.png", "A 8169-2023")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 8169-2023 georefererad karta.tif", "A 8169-2023")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 8169-2023 FSC-klagomål.docx", "A 8169-2023")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 8169-2023 FSC-klagomål mail.docx", "A 8169-2023")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 8169-2023 tillsynsbegäran.docx", "A 8169-2023")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 8169-2023 tillsynsbegäran mail.docx", "A 8169-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>A 43349-2024</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
         <v>45568</v>
       </c>
-      <c r="E25" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
+      <c r="E26" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
         <v>4.1</v>
       </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
         <v>1</v>
       </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
         <v>1</v>
       </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
         <v>1</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T26" t="n">
         <v>1</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U26" t="n">
         <v>1</v>
       </c>
-      <c r="V25" s="2" t="inlineStr">
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Älg</t>
         </is>
       </c>
-      <c r="W25">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 43349-2024 artfynd.xlsx", "A 43349-2024")</f>
         <v/>
       </c>
-      <c r="X25">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 43349-2024 karta.png", "A 43349-2024")</f>
         <v/>
       </c>
-      <c r="Y25">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 43349-2024 georefererad karta.tif", "A 43349-2024")</f>
         <v/>
       </c>
-      <c r="AA25">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 43349-2024 FSC-klagomål.docx", "A 43349-2024")</f>
         <v/>
       </c>
-      <c r="AB25">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 43349-2024 FSC-klagomål mail.docx", "A 43349-2024")</f>
         <v/>
       </c>
-      <c r="AC25">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 43349-2024 tillsynsbegäran.docx", "A 43349-2024")</f>
         <v/>
       </c>
-      <c r="AD25">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 43349-2024 tillsynsbegäran mail.docx", "A 43349-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 26518-2026</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>46183</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1</v>
-      </c>
-      <c r="S26" t="n">
-        <v>1</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Rotfingersvamp</t>
-        </is>
-      </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 26518-2026 artfynd.xlsx", "A 26518-2026")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 26518-2026 karta.png", "A 26518-2026")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 26518-2026 georefererad karta.tif", "A 26518-2026")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 26518-2026 FSC-klagomål.docx", "A 26518-2026")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 26518-2026 FSC-klagomål mail.docx", "A 26518-2026")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 26518-2026 tillsynsbegäran.docx", "A 26518-2026")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 26518-2026 tillsynsbegäran mail.docx", "A 26518-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>44952</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         <v>46281</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>44754</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>44732</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>44615</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         <v>44783</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>44754</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 51547-2021</t>
+          <t>A 72617-2021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3968,10 +3968,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44461</v>
+        <v>44546</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4027,7 +4027,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 72617-2021</t>
+          <t>A 29336-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4041,10 +4041,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44546</v>
+        <v>44752</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4117,7 +4117,7 @@
         <v>44484</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 29336-2022</t>
+          <t>A 52243-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4187,10 +4187,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44752</v>
+        <v>44873</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4246,7 +4246,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 52243-2022</t>
+          <t>A 53672-2021</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4260,10 +4260,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44873</v>
+        <v>44469</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4276,7 +4276,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4319,7 +4319,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 53672-2021</t>
+          <t>A 29341-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4333,10 +4333,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44469</v>
+        <v>44752</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.7</v>
+        <v>3.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4392,7 +4392,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 29341-2022</t>
+          <t>A 73-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4406,10 +4406,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44752</v>
+        <v>44564</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4465,7 +4465,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 73-2022</t>
+          <t>A 2355-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4479,10 +4479,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44564</v>
+        <v>44578</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.8</v>
+        <v>0.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4538,7 +4538,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 50694-2021</t>
+          <t>A 15025-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4548,14 +4548,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44460</v>
+        <v>44657</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4611,7 +4611,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 2355-2022</t>
+          <t>A 9796-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4625,10 +4625,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44578</v>
+        <v>44620</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4684,7 +4684,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 15025-2022</t>
+          <t>A 44530-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4698,10 +4698,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44657</v>
+        <v>44840</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4757,7 +4757,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 44530-2022</t>
+          <t>A 17109-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4767,14 +4767,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44840</v>
+        <v>44677</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 9796-2022</t>
+          <t>A 23350-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4844,10 +4844,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44620</v>
+        <v>44720</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4903,7 +4903,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 17109-2022</t>
+          <t>A 17019-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4913,14 +4913,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44677</v>
+        <v>44676</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 23350-2022</t>
+          <t>A 39171-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44720</v>
+        <v>44817</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5049,7 +5049,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 17019-2022</t>
+          <t>A 71252-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5063,10 +5063,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44676</v>
+        <v>44539</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5122,7 +5122,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 39171-2022</t>
+          <t>A 21097-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5136,10 +5136,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44817</v>
+        <v>44704</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5195,7 +5195,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 71252-2021</t>
+          <t>A 63539-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5209,10 +5209,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44539</v>
+        <v>44508</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5268,7 +5268,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 21097-2022</t>
+          <t>A 57801-2021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5282,10 +5282,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44704</v>
+        <v>44484</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5341,7 +5341,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 63539-2021</t>
+          <t>A 32642-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5355,10 +5355,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44508</v>
+        <v>44783</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.1</v>
+        <v>4.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5414,7 +5414,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 57801-2021</t>
+          <t>A 61060-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5428,10 +5428,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44484</v>
+        <v>44915</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3</v>
+        <v>8.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5487,7 +5487,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 52269-2022</t>
+          <t>A 61061-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5501,10 +5501,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44873</v>
+        <v>44915</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.6</v>
+        <v>8.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5560,7 +5560,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 32642-2022</t>
+          <t>A 3989-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5574,10 +5574,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44783</v>
+        <v>44952</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5633,7 +5633,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 61060-2022</t>
+          <t>A 9374-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5647,10 +5647,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44915</v>
+        <v>44981</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>8.4</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5706,7 +5706,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 61061-2022</t>
+          <t>A 4054-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5720,10 +5720,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44915</v>
+        <v>45684</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>8.5</v>
+        <v>1.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5779,7 +5779,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 3989-2023</t>
+          <t>A 9152-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5793,10 +5793,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44952</v>
+        <v>45357</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5852,7 +5852,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 9374-2023</t>
+          <t>A 19872-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5866,10 +5866,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44981</v>
+        <v>45054</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>8.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5925,7 +5925,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 4054-2025</t>
+          <t>A 56025-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5939,10 +5939,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45684</v>
+        <v>45624</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5998,7 +5998,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 19872-2023</t>
+          <t>A 52269-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6012,10 +6012,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45054</v>
+        <v>44873</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>8.4</v>
+        <v>4.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6071,7 +6071,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 9152-2024</t>
+          <t>A 32549-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6085,10 +6085,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45357</v>
+        <v>45513</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6144,7 +6144,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 56025-2024</t>
+          <t>A 51173-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45624</v>
+        <v>45212</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6217,7 +6217,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 51173-2023</t>
+          <t>A 9456-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6231,10 +6231,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45212</v>
+        <v>45359</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6290,7 +6290,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 32549-2024</t>
+          <t>A 7154-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6300,14 +6300,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45513</v>
+        <v>45344</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6363,7 +6363,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 9456-2024</t>
+          <t>A 4416-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6377,10 +6377,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45359</v>
+        <v>45686</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6436,7 +6436,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 7154-2024</t>
+          <t>A 33388-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6446,14 +6446,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45344</v>
+        <v>44788</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 4416-2025</t>
+          <t>A 24978-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6523,10 +6523,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45686</v>
+        <v>44728</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6582,7 +6582,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 33388-2022</t>
+          <t>A 46917-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6596,10 +6596,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44788</v>
+        <v>44851</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>8.699999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6655,7 +6655,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 24978-2022</t>
+          <t>A 37267-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6669,10 +6669,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44728</v>
+        <v>45540</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6728,7 +6728,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 46917-2022</t>
+          <t>A 8155-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6742,10 +6742,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44851</v>
+        <v>44974</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6801,7 +6801,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 8155-2023</t>
+          <t>A 14596-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6815,10 +6815,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44974</v>
+        <v>44655</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6874,7 +6874,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 37267-2024</t>
+          <t>A 13800-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6888,10 +6888,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45540</v>
+        <v>45007</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6947,7 +6947,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 14596-2022</t>
+          <t>A 51783-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6961,10 +6961,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44655</v>
+        <v>45222</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7020,7 +7020,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 13800-2023</t>
+          <t>A 12157-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7030,14 +7030,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45007</v>
+        <v>44636</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7093,7 +7093,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 12157-2022</t>
+          <t>A 39535-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7103,14 +7103,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44636</v>
+        <v>45551</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.7</v>
+        <v>4.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7166,7 +7166,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 39535-2024</t>
+          <t>A 7443-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7180,10 +7180,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45551</v>
+        <v>44971</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4.7</v>
+        <v>0.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7239,7 +7239,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 51783-2023</t>
+          <t>A 17685-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7253,10 +7253,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45222</v>
+        <v>45418</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7312,7 +7312,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 7443-2023</t>
+          <t>A 10356-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7326,10 +7326,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44971</v>
+        <v>45720</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7385,7 +7385,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 17685-2024</t>
+          <t>A 35605-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7399,10 +7399,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45418</v>
+        <v>45531</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7458,7 +7458,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 10356-2025</t>
+          <t>A 16656-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7472,10 +7472,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45720</v>
+        <v>44672</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7531,7 +7531,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 35605-2024</t>
+          <t>A 25109-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7545,10 +7545,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45531</v>
+        <v>44729</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7604,7 +7604,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 16656-2022</t>
+          <t>A 39728-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7618,10 +7618,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44672</v>
+        <v>45167</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7677,7 +7677,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 25109-2022</t>
+          <t>A 17543-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7691,10 +7691,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44729</v>
+        <v>45036</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7750,7 +7750,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 39728-2023</t>
+          <t>A 53307-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7764,10 +7764,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45167</v>
+        <v>45614</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7823,7 +7823,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 17543-2023</t>
+          <t>A 53254-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7837,10 +7837,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45036</v>
+        <v>44876</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 53307-2024</t>
+          <t>A 36963-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7910,10 +7910,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45614</v>
+        <v>45874</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7969,7 +7969,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 53254-2022</t>
+          <t>A 38653-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7983,10 +7983,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44876</v>
+        <v>45884</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.8</v>
+        <v>5.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 60996-2022</t>
+          <t>A 1921-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8056,10 +8056,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44914</v>
+        <v>45671</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 1921-2025</t>
+          <t>A 60996-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8129,10 +8129,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45671</v>
+        <v>44914</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8188,7 +8188,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 15323-2024</t>
+          <t>A 38888-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8202,10 +8202,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45400</v>
+        <v>45887</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>10.6</v>
+        <v>1.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8261,7 +8261,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 10398-2024</t>
+          <t>A 52471-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8275,10 +8275,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45365</v>
+        <v>45225</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8334,7 +8334,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 38663-2025</t>
+          <t>A 24312-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8348,10 +8348,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45884</v>
+        <v>45797</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>4.2</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8407,7 +8407,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 36146-2025</t>
+          <t>A 493-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8421,10 +8421,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45866</v>
+        <v>45664</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8480,7 +8480,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 49449-2025</t>
+          <t>A 38663-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8494,10 +8494,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45938</v>
+        <v>45884</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8553,7 +8553,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 58861-2022</t>
+          <t>A 35603-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8567,10 +8567,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44903</v>
+        <v>45531</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4.8</v>
+        <v>1.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8626,7 +8626,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 38653-2025</t>
+          <t>A 36146-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8640,10 +8640,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45884</v>
+        <v>45866</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8656,7 +8656,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>5.3</v>
+        <v>1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8699,7 +8699,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 11256-2025</t>
+          <t>A 15323-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8713,10 +8713,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45726</v>
+        <v>45400</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.5</v>
+        <v>10.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8772,7 +8772,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 8923-2024</t>
+          <t>A 10398-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8786,10 +8786,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45356</v>
+        <v>45365</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8845,7 +8845,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 38888-2025</t>
+          <t>A 49449-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8859,10 +8859,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45887</v>
+        <v>45938</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8918,7 +8918,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 39942-2023</t>
+          <t>A 27908-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8932,10 +8932,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45167</v>
+        <v>45817</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8991,7 +8991,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 3998-2025</t>
+          <t>A 58861-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9005,10 +9005,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45684</v>
+        <v>44903</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>8.199999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9064,7 +9064,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 32384-2023</t>
+          <t>A 42723-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9078,10 +9078,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45120</v>
+        <v>45908</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9137,7 +9137,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 27908-2025</t>
+          <t>A 11256-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9151,10 +9151,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45817</v>
+        <v>45726</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9210,7 +9210,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 53565-2022</t>
+          <t>A 43398-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9224,10 +9224,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44879</v>
+        <v>45911</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 59723-2025</t>
+          <t>A 8923-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9297,10 +9297,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45992</v>
+        <v>45356</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>12.3</v>
+        <v>3.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9356,7 +9356,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 42723-2025</t>
+          <t>A 44020-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9370,10 +9370,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45908</v>
+        <v>45915</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 43398-2025</t>
+          <t>A 44600-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9443,10 +9443,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45911</v>
+        <v>45917</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1</v>
+        <v>7.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9502,7 +9502,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 20573-2026</t>
+          <t>A 44608-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9516,10 +9516,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46140</v>
+        <v>45917</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9531,13 +9531,8 @@
           <t>MELLERUD</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9580,7 +9575,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 44020-2025</t>
+          <t>A 44573-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9594,10 +9589,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45915</v>
+        <v>45917</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9610,7 +9605,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>3.1</v>
+        <v>5.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9653,7 +9648,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 44600-2025</t>
+          <t>A 39942-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9667,10 +9662,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45917</v>
+        <v>45167</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9683,7 +9678,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>7.2</v>
+        <v>1.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9726,7 +9721,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 44608-2025</t>
+          <t>A 53565-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9740,10 +9735,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45917</v>
+        <v>44879</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9756,7 +9751,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9799,7 +9794,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 44573-2025</t>
+          <t>A 3998-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9813,10 +9808,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45917</v>
+        <v>45684</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9829,7 +9824,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>5.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9872,7 +9867,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 6283-2023</t>
+          <t>A 45861-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9886,10 +9881,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44965</v>
+        <v>45923</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9902,7 +9897,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1</v>
+        <v>10.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9945,7 +9940,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 40064-2023</t>
+          <t>A 45935-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9959,10 +9954,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45168</v>
+        <v>45923</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9975,7 +9970,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10018,7 +10013,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 34415-2024</t>
+          <t>A 45991-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10032,10 +10027,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45525</v>
+        <v>45924</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10048,7 +10043,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10091,7 +10086,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 45861-2025</t>
+          <t>A 46872-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10105,10 +10100,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45923</v>
+        <v>45929</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10121,7 +10116,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>10.2</v>
+        <v>0.4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10164,7 +10159,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 45935-2025</t>
+          <t>A 46668-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10178,10 +10173,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45923</v>
+        <v>45926</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10194,7 +10189,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10237,7 +10232,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 32304-2024</t>
+          <t>A 59723-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10251,10 +10246,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45512</v>
+        <v>45992</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10267,7 +10262,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.2</v>
+        <v>12.3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10310,7 +10305,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 46761-2023</t>
+          <t>A 32384-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10324,10 +10319,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45198</v>
+        <v>45120</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10340,7 +10335,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10383,7 +10378,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 45991-2025</t>
+          <t>A 20573-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10397,10 +10392,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45924</v>
+        <v>46140</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10412,8 +10407,13 @@
           <t>MELLERUD</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>4.4</v>
+        <v>1.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10473,7 +10473,7 @@
         <v>45820</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 21077-2023</t>
+          <t>A 21432-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10543,10 +10543,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45057</v>
+        <v>46148</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10559,7 +10559,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10602,7 +10602,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 46872-2025</t>
+          <t>A 21977-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10616,10 +10616,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45929</v>
+        <v>46153</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10632,7 +10632,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10675,7 +10675,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 22313-2023</t>
+          <t>A 22364-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10689,10 +10689,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45070</v>
+        <v>46154</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10705,7 +10705,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10748,7 +10748,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 46668-2025</t>
+          <t>A 49718-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10762,10 +10762,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45926</v>
+        <v>45939</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10821,7 +10821,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 52128-2021</t>
+          <t>A 22337-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10835,10 +10835,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44463</v>
+        <v>46154</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10851,7 +10851,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10894,7 +10894,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 17160-2024</t>
+          <t>A 6283-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10908,10 +10908,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45412</v>
+        <v>44965</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10967,7 +10967,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 48256-2022</t>
+          <t>A 43406-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10981,10 +10981,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44858</v>
+        <v>45911</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10997,7 +10997,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11040,7 +11040,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 8152-2023</t>
+          <t>A 40064-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11054,10 +11054,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44974</v>
+        <v>45168</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11113,7 +11113,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 49718-2025</t>
+          <t>A 34415-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11127,10 +11127,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45939</v>
+        <v>45525</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11186,7 +11186,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 40065-2023</t>
+          <t>A 16746-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11200,10 +11200,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45168</v>
+        <v>45030</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11216,7 +11216,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11259,7 +11259,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 21432-2026</t>
+          <t>A 1369-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11273,10 +11273,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46148</v>
+        <v>45667</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>4.3</v>
+        <v>1.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11332,7 +11332,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 43406-2025</t>
+          <t>A 32304-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11346,10 +11346,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45911</v>
+        <v>45512</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11362,7 +11362,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11405,7 +11405,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 45834-2023</t>
+          <t>A 46761-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11419,10 +11419,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45195</v>
+        <v>45198</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11435,7 +11435,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11478,7 +11478,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 51463-2023</t>
+          <t>A 32832-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11492,10 +11492,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45221</v>
+        <v>45516</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11508,7 +11508,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11551,7 +11551,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 21977-2026</t>
+          <t>A 50478-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11565,10 +11565,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46153</v>
+        <v>45945</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11581,7 +11581,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11624,7 +11624,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 8492-2022</t>
+          <t>A 50482-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11638,10 +11638,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44613</v>
+        <v>45945</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11654,7 +11654,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11697,7 +11697,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 50478-2025</t>
+          <t>A 53232-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11711,10 +11711,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45945</v>
+        <v>45958</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11727,7 +11727,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11770,7 +11770,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 50482-2025</t>
+          <t>A 21077-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11784,10 +11784,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45945</v>
+        <v>45057</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11800,7 +11800,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>8.800000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11843,7 +11843,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 53232-2025</t>
+          <t>A 59865-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11857,10 +11857,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45958</v>
+        <v>45639</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11873,7 +11873,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.8</v>
+        <v>5.9</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11916,7 +11916,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 48879-2024</t>
+          <t>A 22313-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11930,10 +11930,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45594</v>
+        <v>45070</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 5647-2023</t>
+          <t>A 51436-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12003,10 +12003,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44960</v>
+        <v>45950</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12019,7 +12019,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12062,7 +12062,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 22364-2026</t>
+          <t>A 52128-2021</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12076,10 +12076,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46154</v>
+        <v>44463</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12092,7 +12092,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12135,7 +12135,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 12334-2024</t>
+          <t>A 17160-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12149,10 +12149,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45378</v>
+        <v>45412</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12165,7 +12165,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12208,7 +12208,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 56026-2025</t>
+          <t>A 48256-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12222,10 +12222,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45973</v>
+        <v>44858</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12238,7 +12238,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12281,7 +12281,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 12713-2022</t>
+          <t>A 28863-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12295,10 +12295,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44641</v>
+        <v>45820</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12311,7 +12311,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12354,7 +12354,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 56349-2025</t>
+          <t>A 56026-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12368,10 +12368,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45974</v>
+        <v>45973</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12384,7 +12384,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12427,7 +12427,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 22337-2026</t>
+          <t>A 56349-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46154</v>
+        <v>45974</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12500,7 +12500,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 11219-2024</t>
+          <t>A 8152-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12514,10 +12514,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45371</v>
+        <v>44974</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12530,7 +12530,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>6</v>
+        <v>1.4</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 18205-2024</t>
+          <t>A 40065-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12587,10 +12587,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45420</v>
+        <v>45168</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12603,7 +12603,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12646,7 +12646,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 16746-2023</t>
+          <t>A 45834-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12660,10 +12660,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45030</v>
+        <v>45195</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12676,7 +12676,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12719,7 +12719,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 1369-2025</t>
+          <t>A 51463-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12733,10 +12733,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45667</v>
+        <v>45221</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12749,7 +12749,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12792,7 +12792,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 32832-2024</t>
+          <t>A 59804-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12806,10 +12806,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45516</v>
+        <v>45992</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12822,7 +12822,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12865,7 +12865,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 59804-2025</t>
+          <t>A 59802-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12882,7 +12882,7 @@
         <v>45992</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12895,7 +12895,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12938,7 +12938,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 59802-2025</t>
+          <t>A 59808-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12955,7 +12955,7 @@
         <v>45992</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12968,7 +12968,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13011,7 +13011,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 59808-2025</t>
+          <t>A 59269-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13025,10 +13025,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45992</v>
+        <v>45988</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13041,7 +13041,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13084,7 +13084,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 59865-2024</t>
+          <t>A 59806-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13098,10 +13098,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45639</v>
+        <v>45992</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13114,7 +13114,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>5.9</v>
+        <v>0.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13157,7 +13157,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 51436-2025</t>
+          <t>A 8492-2022</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13171,10 +13171,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45950</v>
+        <v>44613</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13187,7 +13187,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13230,7 +13230,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 28863-2025</t>
+          <t>A 60203-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13244,10 +13244,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45820</v>
+        <v>45994</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13260,7 +13260,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13303,7 +13303,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 59806-2025</t>
+          <t>A 48879-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13317,10 +13317,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45992</v>
+        <v>45594</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13333,7 +13333,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13376,7 +13376,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 10428-2022</t>
+          <t>A 61177-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13386,14 +13386,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44623</v>
+        <v>46000</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13406,7 +13406,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13449,7 +13449,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 60203-2025</t>
+          <t>A 61180-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13463,10 +13463,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45994</v>
+        <v>46000</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13479,7 +13479,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13522,7 +13522,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 61177-2025</t>
+          <t>A 25036-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13532,14 +13532,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46000</v>
+        <v>46174</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13552,7 +13552,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.9</v>
+        <v>5.9</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13595,7 +13595,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 61180-2025</t>
+          <t>A 5647-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13609,10 +13609,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46000</v>
+        <v>44960</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13625,7 +13625,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13668,7 +13668,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 54796-2022</t>
+          <t>A 12334-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13682,10 +13682,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44883</v>
+        <v>45378</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13698,7 +13698,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13741,7 +13741,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 53573-2023</t>
+          <t>A 12713-2022</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13755,10 +13755,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45230</v>
+        <v>44641</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13831,7 +13831,7 @@
         <v>46010</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13887,7 +13887,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 34116-2023</t>
+          <t>A 36138-2025</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13897,14 +13897,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45126</v>
+        <v>45866</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>4.3</v>
+        <v>1.6</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13960,7 +13960,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 1883-2023</t>
+          <t>A 11219-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13974,10 +13974,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44939</v>
+        <v>45371</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.4</v>
+        <v>6</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14033,7 +14033,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 1886-2023</t>
+          <t>A 25458-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14047,10 +14047,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44939</v>
+        <v>46177</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14063,7 +14063,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14106,7 +14106,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 1830-2026</t>
+          <t>A 18205-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14120,10 +14120,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46035</v>
+        <v>45420</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14136,7 +14136,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14179,7 +14179,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 1827-2026</t>
+          <t>A 25954-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14193,10 +14193,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46035</v>
+        <v>46181</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14252,7 +14252,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 59269-2025</t>
+          <t>A 26536-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14266,10 +14266,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45988</v>
+        <v>46183</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14281,8 +14281,13 @@
           <t>MELLERUD</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I175" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14325,7 +14330,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 3178-2026</t>
+          <t>A 1830-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14339,10 +14344,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46041</v>
+        <v>46035</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14355,7 +14360,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14398,7 +14403,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 27510-2023</t>
+          <t>A 26527-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14412,10 +14417,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45097</v>
+        <v>46183</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14427,8 +14432,13 @@
           <t>MELLERUD</t>
         </is>
       </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I177" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14471,7 +14481,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 334-2023</t>
+          <t>A 1827-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14485,10 +14495,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44929</v>
+        <v>46035</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14501,7 +14511,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14544,7 +14554,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 3250-2026</t>
+          <t>A 3178-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14561,7 +14571,7 @@
         <v>46041</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14574,7 +14584,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14617,7 +14627,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 32299-2024</t>
+          <t>A 3250-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14631,10 +14641,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45512</v>
+        <v>46041</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14647,7 +14657,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14707,7 +14717,7 @@
         <v>46041</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14763,7 +14773,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 25036-2026</t>
+          <t>A 5324-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14777,10 +14787,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46174</v>
+        <v>46050</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14793,7 +14803,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>5.9</v>
+        <v>0.5</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14836,7 +14846,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 5324-2026</t>
+          <t>A 10428-2022</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14850,10 +14860,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46050</v>
+        <v>44623</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14866,7 +14876,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14926,7 +14936,7 @@
         <v>46057</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14999,7 +15009,7 @@
         <v>46058</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15072,7 +15082,7 @@
         <v>46058</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15145,7 +15155,7 @@
         <v>46058</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15201,7 +15211,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 36138-2025</t>
+          <t>A 54796-2022</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15215,10 +15225,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45866</v>
+        <v>44883</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15231,7 +15241,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15274,7 +15284,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 25458-2026</t>
+          <t>A 53573-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15288,10 +15298,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46177</v>
+        <v>45230</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15304,7 +15314,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15347,7 +15357,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 8160-2026</t>
+          <t>A 9573-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15361,10 +15371,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46064</v>
+        <v>46071</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15377,7 +15387,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>2.7</v>
+        <v>5.2</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15420,7 +15430,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 9573-2026</t>
+          <t>A 11249-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15434,10 +15444,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46071</v>
+        <v>46080</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15450,7 +15460,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15493,7 +15503,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 32498-2024</t>
+          <t>A 11121-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15503,14 +15513,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45513</v>
+        <v>46079</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15523,7 +15533,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15566,7 +15576,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 43353-2024</t>
+          <t>A 11323-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15576,14 +15586,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45568</v>
+        <v>46080</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15596,7 +15606,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.2</v>
+        <v>7.3</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15639,7 +15649,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 25954-2026</t>
+          <t>A 34116-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15649,14 +15659,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46181</v>
+        <v>45126</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15669,7 +15679,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.5</v>
+        <v>4.3</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15712,7 +15722,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 26536-2026</t>
+          <t>A 1883-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15726,10 +15736,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46183</v>
+        <v>44939</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15741,13 +15751,8 @@
           <t>MELLERUD</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I195" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15790,7 +15795,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 51916-2022</t>
+          <t>A 1886-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15800,14 +15805,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44868</v>
+        <v>44939</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15820,7 +15825,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15863,7 +15868,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 26527-2026</t>
+          <t>A 33450-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15877,10 +15882,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46183</v>
+        <v>46246</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15892,13 +15897,8 @@
           <t>MELLERUD</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I197" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15941,7 +15941,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 33666-2023</t>
+          <t>A 13594-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15951,14 +15951,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45132</v>
+        <v>46096</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15971,7 +15971,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16014,7 +16014,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 11249-2026</t>
+          <t>A 27510-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16028,10 +16028,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46080</v>
+        <v>45097</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16044,7 +16044,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16087,7 +16087,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 11121-2026</t>
+          <t>A 334-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16097,14 +16097,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46079</v>
+        <v>44929</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16160,7 +16160,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 11323-2026</t>
+          <t>A 32299-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16170,14 +16170,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46080</v>
+        <v>45512</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16190,7 +16190,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>7.3</v>
+        <v>3.1</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16233,7 +16233,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 51785-2023</t>
+          <t>A 20578-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16247,10 +16247,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45222</v>
+        <v>46140</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16262,8 +16262,13 @@
           <t>MELLERUD</t>
         </is>
       </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I202" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16306,7 +16311,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 13594-2026</t>
+          <t>A 18055-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16316,14 +16321,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46096</v>
+        <v>46125</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16336,7 +16341,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>0.9</v>
+        <v>5.2</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16379,7 +16384,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 33092-2023</t>
+          <t>A 32498-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16393,10 +16398,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45126</v>
+        <v>45513</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16409,7 +16414,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16452,7 +16457,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 55391-2023</t>
+          <t>A 43353-2024</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16466,10 +16471,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45238</v>
+        <v>45568</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16482,7 +16487,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16525,7 +16530,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 15971-2023</t>
+          <t>A 29936-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16539,10 +16544,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45022</v>
+        <v>46205</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16555,7 +16560,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16598,7 +16603,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 53317-2024</t>
+          <t>A 51916-2022</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16608,14 +16613,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45614</v>
+        <v>44868</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16628,7 +16633,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>0.3</v>
+        <v>4.5</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16671,7 +16676,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 73351-2021</t>
+          <t>A 33666-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16685,10 +16690,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>44551</v>
+        <v>45132</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16701,7 +16706,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>6.1</v>
+        <v>0.4</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16744,7 +16749,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 18055-2026</t>
+          <t>A 29939-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16758,10 +16763,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46125</v>
+        <v>46205</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16774,7 +16779,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>5.2</v>
+        <v>3</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16817,7 +16822,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 26428-2022</t>
+          <t>A 51785-2023</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16831,10 +16836,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>44736</v>
+        <v>45222</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16847,7 +16852,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>0.4</v>
+        <v>3.1</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16890,7 +16895,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 33450-2026</t>
+          <t>A 34065-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16904,10 +16909,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46246</v>
+        <v>46252</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16920,7 +16925,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16963,7 +16968,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 21618-2024</t>
+          <t>A 33092-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16977,10 +16982,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45442</v>
+        <v>45126</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16993,7 +16998,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17036,7 +17041,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 21620-2024</t>
+          <t>A 55391-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17050,10 +17055,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45442</v>
+        <v>45238</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17066,7 +17071,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17109,7 +17114,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 26530-2023</t>
+          <t>A 15971-2023</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17123,10 +17128,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45092</v>
+        <v>45022</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17139,7 +17144,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17182,7 +17187,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 24312-2025</t>
+          <t>A 53317-2024</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17196,10 +17201,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45797</v>
+        <v>45614</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17212,7 +17217,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17255,7 +17260,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 493-2025</t>
+          <t>A 73351-2021</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17269,10 +17274,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45664</v>
+        <v>44551</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17285,7 +17290,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>3.9</v>
+        <v>6.1</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17328,7 +17333,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 35603-2024</t>
+          <t>A 26428-2022</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17342,10 +17347,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45531</v>
+        <v>44736</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17358,7 +17363,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17401,7 +17406,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 18854-2023</t>
+          <t>A 21618-2024</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17415,10 +17420,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45042</v>
+        <v>45442</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17431,7 +17436,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17474,7 +17479,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 14568-2022</t>
+          <t>A 21620-2024</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17488,10 +17493,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>44655</v>
+        <v>45442</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17504,7 +17509,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17547,7 +17552,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 61811-2023</t>
+          <t>A 26530-2023</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17561,10 +17566,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45264</v>
+        <v>45092</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17576,13 +17581,8 @@
           <t>MELLERUD</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I220" t="n">
-        <v>7.9</v>
+        <v>2.5</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17625,7 +17625,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 20578-2026</t>
+          <t>A 31836-2026</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17639,10 +17639,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>46140</v>
+        <v>46230</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17654,13 +17654,8 @@
           <t>MELLERUD</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I221" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17703,7 +17698,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 29936-2026</t>
+          <t>A 36960-2026</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17717,10 +17712,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>46205</v>
+        <v>46273</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17733,7 +17728,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>1.6</v>
+        <v>8.1</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17776,7 +17771,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 29939-2026</t>
+          <t>A 18854-2023</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17790,10 +17785,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>46205</v>
+        <v>45042</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17806,7 +17801,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17849,7 +17844,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 34065-2026</t>
+          <t>A 14568-2022</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17863,10 +17858,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46252</v>
+        <v>44655</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17879,7 +17874,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17922,7 +17917,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 25399-2023</t>
+          <t>A 61811-2023</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17932,14 +17927,14 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45089</v>
+        <v>45264</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17951,8 +17946,13 @@
           <t>MELLERUD</t>
         </is>
       </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I225" t="n">
-        <v>1.9</v>
+        <v>7.9</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17995,7 +17995,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 23238-2024</t>
+          <t>A 31889-2026</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18009,10 +18009,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45453</v>
+        <v>46231</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18025,7 +18025,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18068,7 +18068,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 53270-2024</t>
+          <t>A 25399-2023</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18078,14 +18078,14 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45614</v>
+        <v>45089</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18098,7 +18098,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18141,7 +18141,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 17538-2023</t>
+          <t>A 23238-2024</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18155,10 +18155,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45036</v>
+        <v>45453</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18171,7 +18171,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18214,7 +18214,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 19545-2024</t>
+          <t>A 38251-2026</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18228,10 +18228,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45429</v>
+        <v>46281</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18287,7 +18287,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 50441-2023</t>
+          <t>A 53270-2024</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18301,10 +18301,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45216</v>
+        <v>45614</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18317,7 +18317,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18360,7 +18360,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 10401-2024</t>
+          <t>A 17538-2023</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18374,10 +18374,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45365</v>
+        <v>45036</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18390,7 +18390,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>7.6</v>
+        <v>2.3</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18433,7 +18433,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 21689-2025</t>
+          <t>A 32520-2026</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18447,10 +18447,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45783</v>
+        <v>46239</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18463,7 +18463,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18506,7 +18506,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 21678-2025</t>
+          <t>A 32691-2026</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18520,10 +18520,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45783</v>
+        <v>46240</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18536,7 +18536,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18579,7 +18579,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 21698-2025</t>
+          <t>A 38040-2025</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18593,10 +18593,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45783</v>
+        <v>45882</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18609,7 +18609,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18652,7 +18652,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 31836-2026</t>
+          <t>A 19545-2024</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18666,10 +18666,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>46230</v>
+        <v>45429</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18725,7 +18725,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 36960-2026</t>
+          <t>A 50441-2023</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18739,10 +18739,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>46273</v>
+        <v>45216</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>8.1</v>
+        <v>2.7</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18798,7 +18798,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 13313-2024</t>
+          <t>A 10401-2024</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18812,10 +18812,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45386</v>
+        <v>45365</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18828,7 +18828,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>2.1</v>
+        <v>7.6</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18871,7 +18871,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 31889-2026</t>
+          <t>A 21689-2025</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18885,10 +18885,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>46231</v>
+        <v>45783</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18901,7 +18901,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18944,7 +18944,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 27342-2024</t>
+          <t>A 21678-2025</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18958,10 +18958,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45473</v>
+        <v>45783</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18974,7 +18974,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -19017,7 +19017,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 10100-2025</t>
+          <t>A 21698-2025</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -19031,10 +19031,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45719</v>
+        <v>45783</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19047,7 +19047,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -19090,7 +19090,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 8667-2025</t>
+          <t>A 13313-2024</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -19104,10 +19104,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45712</v>
+        <v>45386</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19120,7 +19120,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -19163,7 +19163,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 10357-2025</t>
+          <t>A 27342-2024</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19177,10 +19177,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45720</v>
+        <v>45473</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19236,7 +19236,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 10358-2025</t>
+          <t>A 10100-2025</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19250,10 +19250,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45720</v>
+        <v>45719</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19309,7 +19309,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 60993-2022</t>
+          <t>A 8667-2025</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19323,10 +19323,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>44914</v>
+        <v>45712</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19382,7 +19382,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 38251-2026</t>
+          <t>A 10357-2025</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19396,10 +19396,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>46281</v>
+        <v>45720</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19412,7 +19412,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19455,7 +19455,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 10097-2025</t>
+          <t>A 10358-2025</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19469,10 +19469,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45719</v>
+        <v>45720</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19528,7 +19528,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 11213-2025</t>
+          <t>A 60993-2022</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19542,10 +19542,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45726</v>
+        <v>44914</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19558,7 +19558,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19601,7 +19601,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 32520-2026</t>
+          <t>A 10097-2025</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19615,10 +19615,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>46239</v>
+        <v>45719</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19631,7 +19631,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19674,7 +19674,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 32691-2026</t>
+          <t>A 11213-2025</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19688,10 +19688,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>46240</v>
+        <v>45726</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19704,7 +19704,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>1</v>
+        <v>4.8</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19764,7 +19764,7 @@
         <v>45798</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19837,7 +19837,7 @@
         <v>45798</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19910,7 +19910,7 @@
         <v>45567</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19983,7 +19983,7 @@
         <v>45803</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20056,7 +20056,7 @@
         <v>45803</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20129,7 +20129,7 @@
         <v>45803</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
         <v>45643</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>45037</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20348,7 +20348,7 @@
         <v>45730</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20421,7 +20421,7 @@
         <v>45728</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20494,7 +20494,7 @@
         <v>44974</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20567,7 +20567,7 @@
         <v>45415</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20640,7 +20640,7 @@
         <v>45610</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20713,7 +20713,7 @@
         <v>45702</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20786,7 +20786,7 @@
         <v>45818</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20859,7 +20859,7 @@
         <v>45820</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20932,7 +20932,7 @@
         <v>45839</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>45792</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21078,7 +21078,7 @@
         <v>45372</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21151,7 +21151,7 @@
         <v>45744</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21224,7 +21224,7 @@
         <v>45810</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21297,7 +21297,7 @@
         <v>45866</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21370,7 +21370,7 @@
         <v>45866</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21426,24 +21426,24 @@
     <row r="273" ht="15" customHeight="1">
       <c r="A273" t="inlineStr">
         <is>
-          <t>A 36963-2025</t>
+          <t>S 10351-2021</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D273" s="1" t="n">
-        <v>45874</v>
+        <v>44551</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21456,7 +21456,7 @@
         </is>
       </c>
       <c r="I273" t="n">
-        <v>0.7</v>
+        <v>5.8</v>
       </c>
       <c r="J273" t="n">
         <v>0</v>
@@ -21499,24 +21499,24 @@
     <row r="274" ht="15" customHeight="1">
       <c r="A274" t="inlineStr">
         <is>
-          <t>A 52471-2023</t>
+          <t>S 587-2024</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D274" s="1" t="n">
-        <v>45225</v>
+        <v>45351</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21529,7 +21529,7 @@
         </is>
       </c>
       <c r="I274" t="n">
-        <v>2.5</v>
+        <v>19</v>
       </c>
       <c r="J274" t="n">
         <v>0</v>
@@ -21572,24 +21572,24 @@
     <row r="275" ht="15" customHeight="1">
       <c r="A275" t="inlineStr">
         <is>
-          <t>A 38040-2025</t>
+          <t>S 1695-2026</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D275" s="1" t="n">
-        <v>45882</v>
+        <v>46184</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21602,7 +21602,7 @@
         </is>
       </c>
       <c r="I275" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J275" t="n">
         <v>0</v>
@@ -21642,10 +21642,10 @@
       </c>
       <c r="V275" s="2" t="inlineStr"/>
     </row>
-    <row r="276" ht="15" customHeight="1">
+    <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>S 10351-2021</t>
+          <t>S 1717-2026</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -21655,14 +21655,14 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D276" s="1" t="n">
-        <v>44551</v>
+        <v>46188</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21675,7 +21675,7 @@
         </is>
       </c>
       <c r="I276" t="n">
-        <v>5.8</v>
+        <v>30.4</v>
       </c>
       <c r="J276" t="n">
         <v>0</v>
@@ -21714,225 +21714,6 @@
         <v>0</v>
       </c>
       <c r="V276" s="2" t="inlineStr"/>
-    </row>
-    <row r="277" ht="15" customHeight="1">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>S 587-2024</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D277" s="1" t="n">
-        <v>45351</v>
-      </c>
-      <c r="E277" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F277" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="I277" t="n">
-        <v>19</v>
-      </c>
-      <c r="J277" t="n">
-        <v>0</v>
-      </c>
-      <c r="K277" t="n">
-        <v>0</v>
-      </c>
-      <c r="L277" t="n">
-        <v>0</v>
-      </c>
-      <c r="M277" t="n">
-        <v>0</v>
-      </c>
-      <c r="N277" t="n">
-        <v>0</v>
-      </c>
-      <c r="O277" t="n">
-        <v>0</v>
-      </c>
-      <c r="P277" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q277" t="n">
-        <v>0</v>
-      </c>
-      <c r="R277" t="n">
-        <v>0</v>
-      </c>
-      <c r="S277" t="n">
-        <v>0</v>
-      </c>
-      <c r="T277" t="n">
-        <v>0</v>
-      </c>
-      <c r="U277" t="n">
-        <v>0</v>
-      </c>
-      <c r="V277" s="2" t="inlineStr"/>
-    </row>
-    <row r="278" ht="15" customHeight="1">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>S 1695-2026</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D278" s="1" t="n">
-        <v>46184</v>
-      </c>
-      <c r="E278" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F278" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="I278" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J278" t="n">
-        <v>0</v>
-      </c>
-      <c r="K278" t="n">
-        <v>0</v>
-      </c>
-      <c r="L278" t="n">
-        <v>0</v>
-      </c>
-      <c r="M278" t="n">
-        <v>0</v>
-      </c>
-      <c r="N278" t="n">
-        <v>0</v>
-      </c>
-      <c r="O278" t="n">
-        <v>0</v>
-      </c>
-      <c r="P278" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q278" t="n">
-        <v>0</v>
-      </c>
-      <c r="R278" t="n">
-        <v>0</v>
-      </c>
-      <c r="S278" t="n">
-        <v>0</v>
-      </c>
-      <c r="T278" t="n">
-        <v>0</v>
-      </c>
-      <c r="U278" t="n">
-        <v>0</v>
-      </c>
-      <c r="V278" s="2" t="inlineStr"/>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>S 1717-2026</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D279" s="1" t="n">
-        <v>46188</v>
-      </c>
-      <c r="E279" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F279" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="I279" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="J279" t="n">
-        <v>0</v>
-      </c>
-      <c r="K279" t="n">
-        <v>0</v>
-      </c>
-      <c r="L279" t="n">
-        <v>0</v>
-      </c>
-      <c r="M279" t="n">
-        <v>0</v>
-      </c>
-      <c r="N279" t="n">
-        <v>0</v>
-      </c>
-      <c r="O279" t="n">
-        <v>0</v>
-      </c>
-      <c r="P279" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q279" t="n">
-        <v>0</v>
-      </c>
-      <c r="R279" t="n">
-        <v>0</v>
-      </c>
-      <c r="S279" t="n">
-        <v>0</v>
-      </c>
-      <c r="T279" t="n">
-        <v>0</v>
-      </c>
-      <c r="U279" t="n">
-        <v>0</v>
-      </c>
-      <c r="V279" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt MELLERUD.xlsx
+++ b/Översikt MELLERUD.xlsx
@@ -601,7 +601,7 @@
         <v>46184</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>46112</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>45614</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>45614</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44840</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>45734</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 63859-2025</t>
+          <t>A 1491-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46020</v>
+        <v>45670</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1338,45 +1338,157 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="J8" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="n">
-        <v>6</v>
-      </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
         <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>8</v>
       </c>
       <c r="T8" t="n">
+        <v>15</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Uddbräken
+Jungfrulin
+Sårläka
+Nästrot
+Skogsknipprot
+Svart trolldruva
+Taggbräken
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 1491-2025 artfynd.xlsx", "A 1491-2025")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 1491-2025 karta.png", "A 1491-2025")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 1491-2025 georefererad karta.tif", "A 1491-2025")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 1491-2025 FSC-klagomål.docx", "A 1491-2025")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 1491-2025 FSC-klagomål mail.docx", "A 1491-2025")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 1491-2025 tillsynsbegäran.docx", "A 1491-2025")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 1491-2025 tillsynsbegäran mail.docx", "A 1491-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 63859-2025</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>46020</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>6</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>8</v>
+      </c>
+      <c r="T9" t="n">
         <v>14</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U9" t="n">
         <v>14</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Svart askbastborre
 Björksplintborre
@@ -1388,147 +1500,35 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 63859-2025 artfynd.xlsx", "A 63859-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 63859-2025 karta.png", "A 63859-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 63859-2025 georefererad karta.tif", "A 63859-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 63859-2025 FSC-klagomål.docx", "A 63859-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 63859-2025 FSC-klagomål mail.docx", "A 63859-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 63859-2025 tillsynsbegäran.docx", "A 63859-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 63859-2025 tillsynsbegäran mail.docx", "A 63859-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 1491-2025</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45670</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>8</v>
-      </c>
-      <c r="T9" t="n">
-        <v>15</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Uddbräken
-Jungfrulin
-Sårläka
-Nästrot
-Skogsknipprot
-Svart trolldruva
-Taggbräken
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 1491-2025 artfynd.xlsx", "A 1491-2025")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 1491-2025 karta.png", "A 1491-2025")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 1491-2025 georefererad karta.tif", "A 1491-2025")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 1491-2025 FSC-klagomål.docx", "A 1491-2025")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 1491-2025 FSC-klagomål mail.docx", "A 1491-2025")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 1491-2025 tillsynsbegäran.docx", "A 1491-2025")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 1491-2025 tillsynsbegäran mail.docx", "A 1491-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>45253</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>44963</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>45006</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 63857-2025</t>
+          <t>A 25764-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46020</v>
+        <v>45804</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>3</v>
@@ -1905,7 +1905,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1914,21 +1914,129 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
       </c>
       <c r="T13" t="n">
+        <v>5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Guldlockmossa
+Lönnlav
+Rostfläck</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 25764-2025 artfynd.xlsx", "A 25764-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 25764-2025 karta.png", "A 25764-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 25764-2025 georefererad karta.tif", "A 25764-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 25764-2025 FSC-klagomål.docx", "A 25764-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 25764-2025 FSC-klagomål mail.docx", "A 25764-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 25764-2025 tillsynsbegäran.docx", "A 25764-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 25764-2025 tillsynsbegäran mail.docx", "A 25764-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 63857-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>46020</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
+      <c r="T14" t="n">
         <v>6</v>
       </c>
-      <c r="U13" t="n">
+      <c r="U14" t="n">
         <v>6</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Björksplintborre
 Rävticka
@@ -1936,112 +2044,225 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 63857-2025 artfynd.xlsx", "A 63857-2025")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 63857-2025 karta.png", "A 63857-2025")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 63857-2025 georefererad karta.tif", "A 63857-2025")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 63857-2025 FSC-klagomål.docx", "A 63857-2025")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 63857-2025 FSC-klagomål mail.docx", "A 63857-2025")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 63857-2025 tillsynsbegäran.docx", "A 63857-2025")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 63857-2025 tillsynsbegäran mail.docx", "A 63857-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 33141-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4</v>
+      </c>
+      <c r="T15" t="n">
+        <v>7</v>
+      </c>
+      <c r="U15" t="n">
+        <v>7</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Kattfotslav
+Grön sköldmossa
+Kornknutmossa
+Mandelriska</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 33141-2026 artfynd.xlsx", "A 33141-2026")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 33141-2026 karta.png", "A 33141-2026")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 33141-2026 georefererad karta.tif", "A 33141-2026")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 33141-2026 FSC-klagomål.docx", "A 33141-2026")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 33141-2026 FSC-klagomål mail.docx", "A 33141-2026")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 33141-2026 tillsynsbegäran.docx", "A 33141-2026")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 33141-2026 tillsynsbegäran mail.docx", "A 33141-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>A 28216-2026</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
         <v>46196</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
+      <c r="E16" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
         <is>
           <t>Kommuner</t>
         </is>
       </c>
-      <c r="I14" t="n">
+      <c r="I16" t="n">
         <v>2.5</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J16" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K16" t="n">
         <v>1</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>1</v>
       </c>
-      <c r="N14" t="n">
+      <c r="N16" t="n">
         <v>1</v>
       </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
         <v>2</v>
       </c>
-      <c r="R14" t="n">
+      <c r="R16" t="n">
         <v>2</v>
       </c>
-      <c r="S14" t="n">
+      <c r="S16" t="n">
         <v>4</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T16" t="n">
         <v>4</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Gulvit blekspik
@@ -2049,256 +2270,35 @@
 Gröngöling</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 28216-2026 artfynd.xlsx", "A 28216-2026")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 28216-2026 karta.png", "A 28216-2026")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 28216-2026 georefererad karta.tif", "A 28216-2026")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 28216-2026 FSC-klagomål.docx", "A 28216-2026")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 28216-2026 FSC-klagomål mail.docx", "A 28216-2026")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 28216-2026 tillsynsbegäran.docx", "A 28216-2026")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 28216-2026 tillsynsbegäran mail.docx", "A 28216-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 33141-2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46244</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>4</v>
-      </c>
-      <c r="T15" t="n">
-        <v>7</v>
-      </c>
-      <c r="U15" t="n">
-        <v>7</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Kattfotslav
-Grön sköldmossa
-Kornknutmossa
-Mandelriska</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 33141-2026 artfynd.xlsx", "A 33141-2026")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 33141-2026 karta.png", "A 33141-2026")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 33141-2026 georefererad karta.tif", "A 33141-2026")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 33141-2026 FSC-klagomål.docx", "A 33141-2026")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 33141-2026 FSC-klagomål mail.docx", "A 33141-2026")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 33141-2026 tillsynsbegäran.docx", "A 33141-2026")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 33141-2026 tillsynsbegäran mail.docx", "A 33141-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 25764-2025</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45804</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>3</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" t="n">
-        <v>4</v>
-      </c>
-      <c r="T16" t="n">
-        <v>5</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Guldlockmossa
-Lönnlav
-Rostfläck</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 25764-2025 artfynd.xlsx", "A 25764-2025")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 25764-2025 karta.png", "A 25764-2025")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 25764-2025 georefererad karta.tif", "A 25764-2025")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 25764-2025 FSC-klagomål.docx", "A 25764-2025")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 25764-2025 FSC-klagomål mail.docx", "A 25764-2025")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 25764-2025 tillsynsbegäran.docx", "A 25764-2025")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 25764-2025 tillsynsbegäran mail.docx", "A 25764-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>45390</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>44896</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>44804</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>44750</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 10814-2024</t>
+          <t>A 43349-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2748,10 +2748,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45369</v>
+        <v>45568</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2763,13 +2763,8 @@
           <t>MELLERUD</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>6.6</v>
+        <v>4.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2778,10 +2773,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2796,7 +2791,7 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2805,682 +2800,687 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 43349-2024 artfynd.xlsx", "A 43349-2024")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 43349-2024 karta.png", "A 43349-2024")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 43349-2024 georefererad karta.tif", "A 43349-2024")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 43349-2024 FSC-klagomål.docx", "A 43349-2024")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 43349-2024 FSC-klagomål mail.docx", "A 43349-2024")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 43349-2024 tillsynsbegäran.docx", "A 43349-2024")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 43349-2024 tillsynsbegäran mail.docx", "A 43349-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 8169-2023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>44974</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 8169-2023 artfynd.xlsx", "A 8169-2023")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 8169-2023 karta.png", "A 8169-2023")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 8169-2023 georefererad karta.tif", "A 8169-2023")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 8169-2023 FSC-klagomål.docx", "A 8169-2023")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 8169-2023 FSC-klagomål mail.docx", "A 8169-2023")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 8169-2023 tillsynsbegäran.docx", "A 8169-2023")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 8169-2023 tillsynsbegäran mail.docx", "A 8169-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 10814-2024</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>45369</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 10814-2024 artfynd.xlsx", "A 10814-2024")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 10814-2024 karta.png", "A 10814-2024")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 10814-2024 georefererad karta.tif", "A 10814-2024")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 10814-2024 FSC-klagomål.docx", "A 10814-2024")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 10814-2024 FSC-klagomål mail.docx", "A 10814-2024")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 10814-2024 tillsynsbegäran.docx", "A 10814-2024")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 10814-2024 tillsynsbegäran mail.docx", "A 10814-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 3992-2023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>44952</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 3992-2023 artfynd.xlsx", "A 3992-2023")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 3992-2023 karta.png", "A 3992-2023")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 3992-2023 georefererad karta.tif", "A 3992-2023")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 3992-2023 FSC-klagomål.docx", "A 3992-2023")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 3992-2023 FSC-klagomål mail.docx", "A 3992-2023")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 3992-2023 tillsynsbegäran.docx", "A 3992-2023")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 3992-2023 tillsynsbegäran mail.docx", "A 3992-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>A 23546-2026</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
         <v>46163</v>
       </c>
-      <c r="E22" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
+      <c r="E25" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
         <v>3.6</v>
       </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
         <v>1</v>
       </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
         <v>1</v>
       </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
         <v>1</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T25" t="n">
         <v>3</v>
       </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Lunglav</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 23546-2026 artfynd.xlsx", "A 23546-2026")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 23546-2026 karta.png", "A 23546-2026")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 23546-2026 georefererad karta.tif", "A 23546-2026")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 23546-2026 FSC-klagomål.docx", "A 23546-2026")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 23546-2026 FSC-klagomål mail.docx", "A 23546-2026")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 23546-2026 tillsynsbegäran.docx", "A 23546-2026")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 23546-2026 tillsynsbegäran mail.docx", "A 23546-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>A 43531-2025</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
         <v>45911</v>
       </c>
-      <c r="E23" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
+      <c r="E26" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
         <is>
           <t>Övriga Aktiebolag</t>
         </is>
       </c>
-      <c r="I23" t="n">
+      <c r="I26" t="n">
         <v>8</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J26" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
         <v>1</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T26" t="n">
         <v>1</v>
       </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Kungsfågel</t>
         </is>
       </c>
-      <c r="W23">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 43531-2025 artfynd.xlsx", "A 43531-2025")</f>
         <v/>
       </c>
-      <c r="X23">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 43531-2025 karta.png", "A 43531-2025")</f>
         <v/>
       </c>
-      <c r="Y23">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 43531-2025 georefererad karta.tif", "A 43531-2025")</f>
         <v/>
       </c>
-      <c r="AA23">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 43531-2025 FSC-klagomål.docx", "A 43531-2025")</f>
         <v/>
       </c>
-      <c r="AB23">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 43531-2025 FSC-klagomål mail.docx", "A 43531-2025")</f>
         <v/>
       </c>
-      <c r="AC23">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 43531-2025 tillsynsbegäran.docx", "A 43531-2025")</f>
         <v/>
       </c>
-      <c r="AD23">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 43531-2025 tillsynsbegäran mail.docx", "A 43531-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>A 26518-2026</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
         <v>46183</v>
       </c>
-      <c r="E24" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
+      <c r="E27" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
         <is>
           <t>Kommuner</t>
         </is>
       </c>
-      <c r="I24" t="n">
+      <c r="I27" t="n">
         <v>0.4</v>
       </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
         <v>1</v>
       </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
         <v>1</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R27" t="n">
         <v>1</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S27" t="n">
         <v>1</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T27" t="n">
         <v>1</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U27" t="n">
         <v>1</v>
       </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Rotfingersvamp</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 26518-2026 artfynd.xlsx", "A 26518-2026")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 26518-2026 karta.png", "A 26518-2026")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 26518-2026 georefererad karta.tif", "A 26518-2026")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 26518-2026 FSC-klagomål.docx", "A 26518-2026")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 26518-2026 FSC-klagomål mail.docx", "A 26518-2026")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 26518-2026 tillsynsbegäran.docx", "A 26518-2026")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 26518-2026 tillsynsbegäran mail.docx", "A 26518-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 8169-2023</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>44974</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Älg</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 8169-2023 artfynd.xlsx", "A 8169-2023")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 8169-2023 karta.png", "A 8169-2023")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 8169-2023 georefererad karta.tif", "A 8169-2023")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 8169-2023 FSC-klagomål.docx", "A 8169-2023")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 8169-2023 FSC-klagomål mail.docx", "A 8169-2023")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 8169-2023 tillsynsbegäran.docx", "A 8169-2023")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 8169-2023 tillsynsbegäran mail.docx", "A 8169-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 43349-2024</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>45568</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>1</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Älg</t>
-        </is>
-      </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 43349-2024 artfynd.xlsx", "A 43349-2024")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 43349-2024 karta.png", "A 43349-2024")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 43349-2024 georefererad karta.tif", "A 43349-2024")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 43349-2024 FSC-klagomål.docx", "A 43349-2024")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 43349-2024 FSC-klagomål mail.docx", "A 43349-2024")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 43349-2024 tillsynsbegäran.docx", "A 43349-2024")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 43349-2024 tillsynsbegäran mail.docx", "A 43349-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 3992-2023</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>44952</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>1</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 3992-2023 artfynd.xlsx", "A 3992-2023")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 3992-2023 karta.png", "A 3992-2023")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 3992-2023 georefererad karta.tif", "A 3992-2023")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 3992-2023 FSC-klagomål.docx", "A 3992-2023")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 3992-2023 FSC-klagomål mail.docx", "A 3992-2023")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 3992-2023 tillsynsbegäran.docx", "A 3992-2023")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 3992-2023 tillsynsbegäran mail.docx", "A 3992-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         <v>46281</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>44754</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>44732</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>44615</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         <v>44783</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>44754</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>44546</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>44752</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>44484</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>44873</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>44469</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4336,7 +4336,7 @@
         <v>44752</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>44564</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>44578</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>44657</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>44620</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         <v>44840</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>44677</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 23350-2022</t>
+          <t>A 8923-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4844,10 +4844,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44720</v>
+        <v>45356</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.4</v>
+        <v>3.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4903,7 +4903,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 17019-2022</t>
+          <t>A 27342-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4917,10 +4917,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44676</v>
+        <v>45473</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4993,7 +4993,7 @@
         <v>44817</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>44539</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 21097-2022</t>
+          <t>A 25109-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5136,10 +5136,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44704</v>
+        <v>44729</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5195,7 +5195,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 63539-2021</t>
+          <t>A 13313-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5209,10 +5209,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44508</v>
+        <v>45386</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5268,7 +5268,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 57801-2021</t>
+          <t>A 21097-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5282,10 +5282,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44484</v>
+        <v>44704</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5341,7 +5341,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 32642-2022</t>
+          <t>A 63539-2021</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5355,10 +5355,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44783</v>
+        <v>44508</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5414,7 +5414,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 61060-2022</t>
+          <t>A 57801-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5428,10 +5428,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44915</v>
+        <v>44484</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>8.4</v>
+        <v>3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5487,7 +5487,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 61061-2022</t>
+          <t>A 25399-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5497,14 +5497,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44915</v>
+        <v>45089</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>8.5</v>
+        <v>1.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5560,7 +5560,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 3989-2023</t>
+          <t>A 23350-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5574,10 +5574,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44952</v>
+        <v>44720</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5633,7 +5633,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 9374-2023</t>
+          <t>A 17019-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5647,10 +5647,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44981</v>
+        <v>44676</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5706,7 +5706,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 4054-2025</t>
+          <t>A 50441-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5720,10 +5720,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45684</v>
+        <v>45216</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5779,7 +5779,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 9152-2024</t>
+          <t>A 32304-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5793,10 +5793,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45357</v>
+        <v>45512</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5852,7 +5852,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 19872-2023</t>
+          <t>A 32642-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5866,10 +5866,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45054</v>
+        <v>44783</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>8.4</v>
+        <v>4.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5925,7 +5925,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 56025-2024</t>
+          <t>A 8667-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5939,10 +5939,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45624</v>
+        <v>45712</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5998,7 +5998,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 52269-2022</t>
+          <t>A 60993-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6012,10 +6012,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44873</v>
+        <v>44914</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.6</v>
+        <v>0.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6071,7 +6071,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 32549-2024</t>
+          <t>A 4416-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6085,10 +6085,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45513</v>
+        <v>45686</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6144,7 +6144,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 51173-2023</t>
+          <t>A 15971-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45212</v>
+        <v>45022</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6217,7 +6217,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 9456-2024</t>
+          <t>A 10401-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6231,10 +6231,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45359</v>
+        <v>45365</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.8</v>
+        <v>7.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6290,7 +6290,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 7154-2024</t>
+          <t>A 10100-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6300,14 +6300,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45344</v>
+        <v>45719</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6363,7 +6363,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 4416-2025</t>
+          <t>A 10097-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6377,10 +6377,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45686</v>
+        <v>45719</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6436,7 +6436,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 33388-2022</t>
+          <t>A 53254-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6450,10 +6450,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44788</v>
+        <v>44876</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>8.699999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 24978-2022</t>
+          <t>A 10357-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6523,10 +6523,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44728</v>
+        <v>45720</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6582,7 +6582,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 46917-2022</t>
+          <t>A 10358-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6596,10 +6596,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44851</v>
+        <v>45720</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6655,7 +6655,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 37267-2024</t>
+          <t>A 11213-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6669,10 +6669,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45540</v>
+        <v>45726</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6728,7 +6728,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 8155-2023</t>
+          <t>A 26530-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6742,10 +6742,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44974</v>
+        <v>45092</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6801,7 +6801,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 14596-2022</t>
+          <t>A 73351-2021</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6815,10 +6815,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44655</v>
+        <v>44551</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.9</v>
+        <v>6.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6874,7 +6874,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 13800-2023</t>
+          <t>A 51916-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6884,14 +6884,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45007</v>
+        <v>44868</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6947,7 +6947,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 51783-2023</t>
+          <t>A 12334-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6961,10 +6961,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45222</v>
+        <v>45378</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7020,7 +7020,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 12157-2022</t>
+          <t>A 52471-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7030,14 +7030,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44636</v>
+        <v>45225</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7093,7 +7093,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 39535-2024</t>
+          <t>A 35605-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7107,10 +7107,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45551</v>
+        <v>45531</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.7</v>
+        <v>1.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7166,7 +7166,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 7443-2023</t>
+          <t>A 61811-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7180,10 +7180,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44971</v>
+        <v>45264</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7195,8 +7195,13 @@
           <t>MELLERUD</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>0.6</v>
+        <v>7.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7239,7 +7244,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 17685-2024</t>
+          <t>A 38888-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7253,10 +7258,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45418</v>
+        <v>45887</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7269,7 +7274,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7312,7 +7317,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 10356-2025</t>
+          <t>A 24527-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7326,10 +7331,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45720</v>
+        <v>45798</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7342,7 +7347,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7385,7 +7390,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 35605-2024</t>
+          <t>A 24533-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7399,10 +7404,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45531</v>
+        <v>45798</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7415,7 +7420,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.4</v>
+        <v>5.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7458,7 +7463,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 16656-2022</t>
+          <t>A 43017-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7472,10 +7477,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44672</v>
+        <v>45567</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7488,7 +7493,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7531,7 +7536,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 25109-2022</t>
+          <t>A 34415-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7545,10 +7550,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44729</v>
+        <v>45525</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7561,7 +7566,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.8</v>
+        <v>4.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7604,7 +7609,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 39728-2023</t>
+          <t>A 33092-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7618,10 +7623,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45167</v>
+        <v>45126</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7634,7 +7639,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7677,7 +7682,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 17543-2023</t>
+          <t>A 40065-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7691,10 +7696,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45036</v>
+        <v>45168</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7707,7 +7712,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7750,7 +7755,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 53307-2024</t>
+          <t>A 3989-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7764,10 +7769,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45614</v>
+        <v>44952</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7780,7 +7785,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7823,7 +7828,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 53254-2022</t>
+          <t>A 51783-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7837,10 +7842,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44876</v>
+        <v>45222</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7896,7 +7901,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 36963-2025</t>
+          <t>A 27908-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7910,10 +7915,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45874</v>
+        <v>45817</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7926,7 +7931,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7969,7 +7974,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 38653-2025</t>
+          <t>A 42723-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7983,10 +7988,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45884</v>
+        <v>45908</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7999,7 +8004,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>5.3</v>
+        <v>2.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8042,7 +8047,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 1921-2025</t>
+          <t>A 43398-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8056,10 +8061,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45671</v>
+        <v>45911</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8072,7 +8077,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8115,7 +8120,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 60996-2022</t>
+          <t>A 32498-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8129,10 +8134,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44914</v>
+        <v>45513</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8145,7 +8150,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8188,7 +8193,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 38888-2025</t>
+          <t>A 32299-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8202,10 +8207,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45887</v>
+        <v>45512</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8218,7 +8223,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8261,7 +8266,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 52471-2023</t>
+          <t>A 44020-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8275,10 +8280,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45225</v>
+        <v>45915</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8291,7 +8296,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8334,7 +8339,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 24312-2025</t>
+          <t>A 27510-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8348,10 +8353,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45797</v>
+        <v>45097</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8364,7 +8369,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8407,7 +8412,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 493-2025</t>
+          <t>A 44600-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8421,10 +8426,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45664</v>
+        <v>45917</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8437,7 +8442,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3.9</v>
+        <v>7.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8480,7 +8485,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 38663-2025</t>
+          <t>A 25652-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8494,10 +8499,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45884</v>
+        <v>45803</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8510,7 +8515,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8553,7 +8558,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 35603-2024</t>
+          <t>A 44573-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8567,10 +8572,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45531</v>
+        <v>45917</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8583,7 +8588,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.7</v>
+        <v>5.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8626,7 +8631,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 36146-2025</t>
+          <t>A 44608-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8640,10 +8645,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45866</v>
+        <v>45917</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8656,7 +8661,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8699,7 +8704,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 15323-2024</t>
+          <t>A 25635-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8713,10 +8718,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45400</v>
+        <v>45803</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8729,7 +8734,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>10.6</v>
+        <v>0.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8772,7 +8777,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 10398-2024</t>
+          <t>A 25623-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8786,10 +8791,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45365</v>
+        <v>45803</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8802,7 +8807,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8845,7 +8850,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 49449-2025</t>
+          <t>A 45991-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8859,10 +8864,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45938</v>
+        <v>45924</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8875,7 +8880,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2</v>
+        <v>4.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8918,7 +8923,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 27908-2025</t>
+          <t>A 37267-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8932,10 +8937,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45817</v>
+        <v>45540</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8948,7 +8953,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8991,7 +8996,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 58861-2022</t>
+          <t>A 45935-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9005,10 +9010,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44903</v>
+        <v>45923</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9021,7 +9026,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>4.8</v>
+        <v>1.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9064,7 +9069,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 42723-2025</t>
+          <t>A 45861-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9078,10 +9083,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45908</v>
+        <v>45923</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9094,7 +9099,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.4</v>
+        <v>10.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9137,7 +9142,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 11256-2025</t>
+          <t>A 22313-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9151,10 +9156,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45726</v>
+        <v>45070</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9167,7 +9172,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9210,7 +9215,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 43398-2025</t>
+          <t>A 46668-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9224,10 +9229,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45911</v>
+        <v>45926</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9240,7 +9245,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9283,7 +9288,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 8923-2024</t>
+          <t>A 60395-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9293,14 +9298,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45356</v>
+        <v>45643</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9313,7 +9318,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9356,7 +9361,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 44020-2025</t>
+          <t>A 46872-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9370,10 +9375,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45915</v>
+        <v>45929</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9386,7 +9391,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3.1</v>
+        <v>0.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9429,7 +9434,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 44600-2025</t>
+          <t>A 10398-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9443,10 +9448,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45917</v>
+        <v>45365</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9459,7 +9464,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>7.2</v>
+        <v>1.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9502,7 +9507,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 44608-2025</t>
+          <t>A 14568-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9516,10 +9521,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45917</v>
+        <v>44655</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9532,7 +9537,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9575,7 +9580,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 44573-2025</t>
+          <t>A 8165-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9589,10 +9594,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45917</v>
+        <v>44974</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9605,7 +9610,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>5.5</v>
+        <v>1.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9648,7 +9653,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 39942-2023</t>
+          <t>A 17528-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9662,10 +9667,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45167</v>
+        <v>45415</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9678,7 +9683,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9721,7 +9726,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 53565-2022</t>
+          <t>A 52922-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9735,10 +9740,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44879</v>
+        <v>45610</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9751,7 +9756,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9794,7 +9799,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 3998-2025</t>
+          <t>A 11848-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9808,10 +9813,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45684</v>
+        <v>45728</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9824,7 +9829,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>8.199999999999999</v>
+        <v>2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9867,7 +9872,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 45861-2025</t>
+          <t>A 17685-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9881,10 +9886,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45923</v>
+        <v>45418</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9897,7 +9902,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>10.2</v>
+        <v>0.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9940,7 +9945,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 45935-2025</t>
+          <t>A 12501-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9954,10 +9959,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45923</v>
+        <v>45730</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9970,7 +9975,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10013,7 +10018,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 45991-2025</t>
+          <t>A 32384-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10027,10 +10032,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45924</v>
+        <v>45120</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10043,7 +10048,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10086,7 +10091,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 46872-2025</t>
+          <t>A 17693-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10100,10 +10105,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45929</v>
+        <v>45037</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10116,7 +10121,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.4</v>
+        <v>11.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10159,7 +10164,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 46668-2025</t>
+          <t>A 33666-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10173,10 +10178,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45926</v>
+        <v>45132</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10189,7 +10194,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10232,7 +10237,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 59723-2025</t>
+          <t>A 49718-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10246,10 +10251,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45992</v>
+        <v>45939</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10262,7 +10267,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>12.3</v>
+        <v>1.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10305,7 +10310,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 32384-2023</t>
+          <t>A 1921-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10319,10 +10324,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45120</v>
+        <v>45671</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10335,7 +10340,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10378,7 +10383,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 20573-2026</t>
+          <t>A 6283-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10392,10 +10397,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46140</v>
+        <v>44965</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10407,13 +10412,8 @@
           <t>MELLERUD</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10456,7 +10456,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 28865-2025</t>
+          <t>A 1883-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10470,10 +10470,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45820</v>
+        <v>44939</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10529,7 +10529,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 21432-2026</t>
+          <t>A 39942-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10543,10 +10543,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46148</v>
+        <v>45167</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10559,7 +10559,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>4.3</v>
+        <v>1.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10602,7 +10602,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 21977-2026</t>
+          <t>A 43406-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10616,10 +10616,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46153</v>
+        <v>45911</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 22364-2026</t>
+          <t>A 53317-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10689,10 +10689,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46154</v>
+        <v>45614</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10705,7 +10705,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.8</v>
+        <v>0.3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10748,7 +10748,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 49718-2025</t>
+          <t>A 12713-2022</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10762,10 +10762,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45939</v>
+        <v>44641</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10821,7 +10821,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 22337-2026</t>
+          <t>A 18854-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10835,10 +10835,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46154</v>
+        <v>45042</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10851,7 +10851,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10894,7 +10894,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 6283-2023</t>
+          <t>A 43353-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10908,10 +10908,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44965</v>
+        <v>45568</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10967,7 +10967,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 43406-2025</t>
+          <t>A 10356-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10981,10 +10981,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45911</v>
+        <v>45720</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10997,7 +10997,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11040,7 +11040,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 40064-2023</t>
+          <t>A 7228-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11054,10 +11054,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45168</v>
+        <v>45702</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11113,7 +11113,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 34415-2024</t>
+          <t>A 28319-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11127,10 +11127,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45525</v>
+        <v>45818</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>4.3</v>
+        <v>1.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11186,7 +11186,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 16746-2023</t>
+          <t>A 51785-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11200,10 +11200,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45030</v>
+        <v>45222</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11216,7 +11216,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11259,7 +11259,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 1369-2025</t>
+          <t>A 3998-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11273,10 +11273,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45667</v>
+        <v>45684</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11332,7 +11332,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 32304-2024</t>
+          <t>A 53232-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11346,10 +11346,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45512</v>
+        <v>45958</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11362,7 +11362,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11405,7 +11405,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 46761-2023</t>
+          <t>A 50478-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11419,10 +11419,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45198</v>
+        <v>45945</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11435,7 +11435,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11478,7 +11478,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 32832-2024</t>
+          <t>A 50482-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11492,10 +11492,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45516</v>
+        <v>45945</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11508,7 +11508,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11551,7 +11551,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 50478-2025</t>
+          <t>A 19872-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11565,10 +11565,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45945</v>
+        <v>45054</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11581,7 +11581,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1</v>
+        <v>8.4</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11624,7 +11624,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 50482-2025</t>
+          <t>A 8492-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11638,10 +11638,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45945</v>
+        <v>44613</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11654,7 +11654,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>8.800000000000001</v>
+        <v>1.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11697,7 +11697,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 53232-2025</t>
+          <t>A 28870-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11711,10 +11711,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45958</v>
+        <v>45820</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11727,7 +11727,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.8</v>
+        <v>7.9</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11770,7 +11770,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 21077-2023</t>
+          <t>A 334-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11784,10 +11784,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45057</v>
+        <v>44929</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11800,7 +11800,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11843,7 +11843,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 59865-2024</t>
+          <t>A 56349-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11857,10 +11857,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45639</v>
+        <v>45974</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11873,7 +11873,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>5.9</v>
+        <v>1.5</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11916,7 +11916,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 22313-2023</t>
+          <t>A 53307-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11930,10 +11930,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45070</v>
+        <v>45614</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11946,7 +11946,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11989,7 +11989,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 51436-2025</t>
+          <t>A 56026-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12003,10 +12003,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45950</v>
+        <v>45973</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12019,7 +12019,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12062,7 +12062,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 52128-2021</t>
+          <t>A 10428-2022</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12076,10 +12076,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44463</v>
+        <v>44623</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 17160-2024</t>
+          <t>A 21618-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12149,10 +12149,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45412</v>
+        <v>45442</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12165,7 +12165,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12208,7 +12208,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 48256-2022</t>
+          <t>A 21620-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12222,10 +12222,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44858</v>
+        <v>45442</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12238,7 +12238,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12281,7 +12281,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 28863-2025</t>
+          <t>A 33388-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12295,10 +12295,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45820</v>
+        <v>44788</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12311,7 +12311,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12354,7 +12354,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 56026-2025</t>
+          <t>A 46761-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12368,10 +12368,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45973</v>
+        <v>45198</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12384,7 +12384,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12427,7 +12427,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 56349-2025</t>
+          <t>A 16656-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45974</v>
+        <v>44672</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12500,7 +12500,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 8152-2023</t>
+          <t>A 51463-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12514,10 +12514,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44974</v>
+        <v>45221</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12530,7 +12530,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 40065-2023</t>
+          <t>A 59808-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12587,10 +12587,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45168</v>
+        <v>45992</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12603,7 +12603,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12646,7 +12646,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 45834-2023</t>
+          <t>A 59806-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12660,10 +12660,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45195</v>
+        <v>45992</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12676,7 +12676,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12719,7 +12719,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 51463-2023</t>
+          <t>A 40064-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12733,10 +12733,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45221</v>
+        <v>45168</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12749,7 +12749,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12809,7 +12809,7 @@
         <v>45992</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12865,7 +12865,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 59802-2025</t>
+          <t>A 26428-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12879,10 +12879,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45992</v>
+        <v>44736</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12895,7 +12895,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12938,7 +12938,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 59808-2025</t>
+          <t>A 59802-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12955,7 +12955,7 @@
         <v>45992</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12968,7 +12968,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13011,7 +13011,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 59269-2025</t>
+          <t>A 60203-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13025,10 +13025,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45988</v>
+        <v>45994</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13041,7 +13041,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13084,7 +13084,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 59806-2025</t>
+          <t>A 34116-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13094,14 +13094,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45992</v>
+        <v>45126</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13114,7 +13114,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.5</v>
+        <v>4.3</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13157,7 +13157,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 8492-2022</t>
+          <t>A 61177-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13167,14 +13167,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44613</v>
+        <v>46000</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13187,7 +13187,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13230,7 +13230,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 60203-2025</t>
+          <t>A 61180-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13244,10 +13244,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45994</v>
+        <v>46000</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13260,7 +13260,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13303,7 +13303,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 48879-2024</t>
+          <t>A 56025-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13317,10 +13317,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45594</v>
+        <v>45624</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13333,7 +13333,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13376,7 +13376,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 61177-2025</t>
+          <t>A 11256-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13386,14 +13386,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46000</v>
+        <v>45726</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13406,7 +13406,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13449,7 +13449,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 61180-2025</t>
+          <t>A 1830-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13463,10 +13463,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46000</v>
+        <v>46035</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 25036-2026</t>
+          <t>A 8155-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13536,10 +13536,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46174</v>
+        <v>44974</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13552,7 +13552,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>5.9</v>
+        <v>2.7</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13595,7 +13595,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 5647-2023</t>
+          <t>A 1827-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13609,10 +13609,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44960</v>
+        <v>46035</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13625,7 +13625,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13668,7 +13668,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 12334-2024</t>
+          <t>A 3250-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13682,10 +13682,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45378</v>
+        <v>46041</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13698,7 +13698,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13741,7 +13741,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 12713-2022</t>
+          <t>A 53573-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13755,10 +13755,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44641</v>
+        <v>45230</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13814,7 +13814,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 63249-2025</t>
+          <t>A 32842-2025</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13828,10 +13828,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46010</v>
+        <v>45839</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13844,7 +13844,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.6</v>
+        <v>6.1</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13887,7 +13887,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 36138-2025</t>
+          <t>A 61060-2022</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13901,10 +13901,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45866</v>
+        <v>44915</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.6</v>
+        <v>8.4</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13960,7 +13960,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 11219-2024</t>
+          <t>A 61061-2022</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13974,10 +13974,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45371</v>
+        <v>44915</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14033,7 +14033,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 25458-2026</t>
+          <t>A 3178-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14047,10 +14047,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46177</v>
+        <v>46041</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14063,7 +14063,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14106,7 +14106,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 18205-2024</t>
+          <t>A 3201-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14120,10 +14120,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45420</v>
+        <v>46041</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14136,7 +14136,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14179,7 +14179,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 25954-2026</t>
+          <t>A 55391-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14193,10 +14193,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46181</v>
+        <v>45238</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14252,7 +14252,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 26536-2026</t>
+          <t>A 63249-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14266,10 +14266,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46183</v>
+        <v>46010</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14279,11 +14279,6 @@
       <c r="G175" t="inlineStr">
         <is>
           <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I175" t="n">
@@ -14330,7 +14325,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 1830-2026</t>
+          <t>A 5324-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14344,10 +14339,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46035</v>
+        <v>46050</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14360,7 +14355,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14403,7 +14398,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 26527-2026</t>
+          <t>A 54796-2022</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14417,10 +14412,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46183</v>
+        <v>44883</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14432,13 +14427,8 @@
           <t>MELLERUD</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I177" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14481,7 +14471,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 1827-2026</t>
+          <t>A 13800-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14495,10 +14485,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46035</v>
+        <v>45007</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14511,7 +14501,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14554,7 +14544,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 3178-2026</t>
+          <t>A 32520-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14568,10 +14558,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46041</v>
+        <v>46239</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14584,7 +14574,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.8</v>
+        <v>3.6</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14627,7 +14617,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 3250-2026</t>
+          <t>A 48879-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14641,10 +14631,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46041</v>
+        <v>45594</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14657,7 +14647,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14700,7 +14690,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 3201-2026</t>
+          <t>A 45834-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14714,10 +14704,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46041</v>
+        <v>45195</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14730,7 +14720,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14773,7 +14763,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 5324-2026</t>
+          <t>A 32691-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14787,10 +14777,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46050</v>
+        <v>46240</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14803,7 +14793,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14846,7 +14836,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 10428-2022</t>
+          <t>A 7117-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14860,10 +14850,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44623</v>
+        <v>46058</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14876,7 +14866,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14919,7 +14909,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 7047-2026</t>
+          <t>A 7125-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14933,10 +14923,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14949,7 +14939,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14992,7 +14982,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 7125-2026</t>
+          <t>A 7047-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15006,10 +14996,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15022,7 +15012,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15082,7 +15072,7 @@
         <v>46058</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15138,7 +15128,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 7117-2026</t>
+          <t>A 38040-2025</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15152,10 +15142,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46058</v>
+        <v>45882</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15168,7 +15158,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15211,7 +15201,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 54796-2022</t>
+          <t>A 52269-2022</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15225,10 +15215,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44883</v>
+        <v>44873</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15241,7 +15231,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.5</v>
+        <v>4.6</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15284,7 +15274,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 53573-2023</t>
+          <t>A 9573-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15298,10 +15288,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45230</v>
+        <v>46071</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15314,7 +15304,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15357,7 +15347,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 9573-2026</t>
+          <t>A 15323-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15371,10 +15361,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46071</v>
+        <v>45400</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15387,7 +15377,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>5.2</v>
+        <v>10.6</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15430,7 +15420,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 11249-2026</t>
+          <t>A 11121-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15440,14 +15430,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46080</v>
+        <v>46079</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15460,7 +15450,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15503,7 +15493,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 11121-2026</t>
+          <t>A 17160-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15513,14 +15503,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46079</v>
+        <v>45412</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15533,7 +15523,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15576,7 +15566,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 11323-2026</t>
+          <t>A 33450-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15586,14 +15576,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46080</v>
+        <v>46246</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15606,7 +15596,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>7.3</v>
+        <v>2.2</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15649,7 +15639,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 34116-2023</t>
+          <t>A 11323-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15663,10 +15653,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45126</v>
+        <v>46080</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15679,7 +15669,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>4.3</v>
+        <v>7.3</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15722,7 +15712,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 1883-2023</t>
+          <t>A 19545-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15736,10 +15726,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44939</v>
+        <v>45429</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15752,7 +15742,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15795,7 +15785,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 1886-2023</t>
+          <t>A 11249-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15809,10 +15799,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44939</v>
+        <v>46080</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15825,7 +15815,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1</v>
+        <v>4.8</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15868,7 +15858,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 33450-2026</t>
+          <t>A 52128-2021</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15882,10 +15872,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46246</v>
+        <v>44463</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15898,7 +15888,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15941,7 +15931,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 13594-2026</t>
+          <t>A 46917-2022</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15951,14 +15941,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46096</v>
+        <v>44851</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15971,7 +15961,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16014,7 +16004,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 27510-2023</t>
+          <t>A 60996-2022</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16028,10 +16018,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45097</v>
+        <v>44914</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16044,7 +16034,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16087,7 +16077,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 334-2023</t>
+          <t>A 23450-2025</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16101,10 +16091,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44929</v>
+        <v>45792</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16117,7 +16107,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16160,7 +16150,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 32299-2024</t>
+          <t>A 12157-2022</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16170,14 +16160,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45512</v>
+        <v>44636</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16190,7 +16180,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16233,7 +16223,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 20578-2026</t>
+          <t>A 13594-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16243,14 +16233,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46140</v>
+        <v>46096</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16262,13 +16252,8 @@
           <t>MELLERUD</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I202" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16311,7 +16296,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 18055-2026</t>
+          <t>A 9456-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16325,10 +16310,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46125</v>
+        <v>45359</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16341,7 +16326,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>5.2</v>
+        <v>1.8</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16384,7 +16369,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 32498-2024</t>
+          <t>A 11442-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16398,10 +16383,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45513</v>
+        <v>45372</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16414,7 +16399,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16457,7 +16442,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 43353-2024</t>
+          <t>A 53270-2024</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16471,10 +16456,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45568</v>
+        <v>45614</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16487,7 +16472,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16530,7 +16515,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 29936-2026</t>
+          <t>A 5647-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16544,10 +16529,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46205</v>
+        <v>44960</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16560,7 +16545,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16603,7 +16588,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 51916-2022</t>
+          <t>A 7443-2023</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16613,14 +16598,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>44868</v>
+        <v>44971</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16633,7 +16618,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>4.5</v>
+        <v>0.6</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16676,7 +16661,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 33666-2023</t>
+          <t>A 1886-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16690,10 +16675,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45132</v>
+        <v>44939</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16706,7 +16691,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16749,7 +16734,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 29939-2026</t>
+          <t>A 36141-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16763,10 +16748,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46205</v>
+        <v>45866</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16779,7 +16764,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16822,7 +16807,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 51785-2023</t>
+          <t>A 26639-2025</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16836,10 +16821,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45222</v>
+        <v>45810</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16852,7 +16837,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>3.1</v>
+        <v>5.4</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16895,7 +16880,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 34065-2026</t>
+          <t>A 15227-2025</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16909,10 +16894,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46252</v>
+        <v>45744</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16925,7 +16910,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16968,7 +16953,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 33092-2023</t>
+          <t>A 36048-2025</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16982,10 +16967,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45126</v>
+        <v>45866</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16998,7 +16983,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17041,7 +17026,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 55391-2023</t>
+          <t>A 9374-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17055,10 +17040,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45238</v>
+        <v>44981</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17071,7 +17056,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17114,7 +17099,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 15971-2023</t>
+          <t>A 48256-2022</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17128,10 +17113,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45022</v>
+        <v>44858</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17144,7 +17129,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17187,7 +17172,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 53317-2024</t>
+          <t>A 23238-2024</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17201,10 +17186,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45614</v>
+        <v>45453</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17217,7 +17202,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>0.3</v>
+        <v>1.7</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17260,7 +17245,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 73351-2021</t>
+          <t>A 18055-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17274,10 +17259,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>44551</v>
+        <v>46125</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17290,7 +17275,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>6.1</v>
+        <v>5.2</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17333,7 +17318,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 26428-2022</t>
+          <t>A 7154-2024</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17343,14 +17328,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>44736</v>
+        <v>45344</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17363,7 +17348,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17406,7 +17391,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 21618-2024</t>
+          <t>A 24978-2022</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17420,10 +17405,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45442</v>
+        <v>44728</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17436,7 +17421,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17479,7 +17464,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 21620-2024</t>
+          <t>A 36963-2025</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17493,10 +17478,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45442</v>
+        <v>45874</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17509,7 +17494,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17552,7 +17537,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 26530-2023</t>
+          <t>A 18205-2024</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17566,10 +17551,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45092</v>
+        <v>45420</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17582,7 +17567,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17625,7 +17610,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 31836-2026</t>
+          <t>A 17543-2023</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17639,10 +17624,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>46230</v>
+        <v>45036</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17655,7 +17640,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17698,7 +17683,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 36960-2026</t>
+          <t>A 17538-2023</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17712,10 +17697,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>46273</v>
+        <v>45036</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17728,7 +17713,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>8.1</v>
+        <v>2.3</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17771,7 +17756,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 18854-2023</t>
+          <t>A 11219-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17785,10 +17770,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45042</v>
+        <v>45371</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17801,7 +17786,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>3.3</v>
+        <v>6</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17844,7 +17829,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 14568-2022</t>
+          <t>A 38653-2025</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17858,10 +17843,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>44655</v>
+        <v>45884</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17874,7 +17859,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17917,7 +17902,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 61811-2023</t>
+          <t>A 38663-2025</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17931,10 +17916,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45264</v>
+        <v>45884</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17946,13 +17931,8 @@
           <t>MELLERUD</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I225" t="n">
-        <v>7.9</v>
+        <v>4.2</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17995,7 +17975,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 31889-2026</t>
+          <t>A 493-2025</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18009,10 +17989,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>46231</v>
+        <v>45664</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18025,7 +18005,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>2.7</v>
+        <v>3.9</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18068,7 +18048,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 25399-2023</t>
+          <t>A 49449-2025</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18078,14 +18058,14 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45089</v>
+        <v>45938</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18098,7 +18078,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18141,7 +18121,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 23238-2024</t>
+          <t>A 20573-2026</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18155,10 +18135,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45453</v>
+        <v>46140</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18170,8 +18150,13 @@
           <t>MELLERUD</t>
         </is>
       </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I228" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18214,7 +18199,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 38251-2026</t>
+          <t>A 24312-2025</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18228,10 +18213,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>46281</v>
+        <v>45797</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18244,7 +18229,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18287,7 +18272,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 53270-2024</t>
+          <t>A 53565-2022</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18301,10 +18286,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45614</v>
+        <v>44879</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18317,7 +18302,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18360,7 +18345,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 17538-2023</t>
+          <t>A 58861-2022</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18374,10 +18359,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45036</v>
+        <v>44903</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18390,7 +18375,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>2.3</v>
+        <v>4.8</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18433,7 +18418,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 32520-2026</t>
+          <t>A 28865-2025</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18447,10 +18432,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>46239</v>
+        <v>45820</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18463,7 +18448,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18506,7 +18491,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 32691-2026</t>
+          <t>A 39728-2023</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18520,10 +18505,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>46240</v>
+        <v>45167</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18536,7 +18521,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18579,7 +18564,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 38040-2025</t>
+          <t>A 36146-2025</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18593,10 +18578,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45882</v>
+        <v>45866</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18609,7 +18594,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18652,7 +18637,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 19545-2024</t>
+          <t>A 51173-2023</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18666,10 +18651,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45429</v>
+        <v>45212</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18682,7 +18667,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18725,7 +18710,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 50441-2023</t>
+          <t>A 59723-2025</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18739,10 +18724,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45216</v>
+        <v>45992</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18755,7 +18740,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>2.7</v>
+        <v>12.3</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18798,7 +18783,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 10401-2024</t>
+          <t>A 4054-2025</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18812,10 +18797,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45365</v>
+        <v>45684</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18828,7 +18813,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>7.6</v>
+        <v>1.9</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18871,7 +18856,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 21689-2025</t>
+          <t>A 14596-2022</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18885,10 +18870,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45783</v>
+        <v>44655</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18901,7 +18886,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18944,7 +18929,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 21678-2025</t>
+          <t>A 35603-2024</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18958,10 +18943,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45783</v>
+        <v>45531</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18974,7 +18959,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -19017,7 +19002,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 21698-2025</t>
+          <t>A 39535-2024</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -19031,10 +19016,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45783</v>
+        <v>45551</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19047,7 +19032,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -19090,7 +19075,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 13313-2024</t>
+          <t>A 32549-2024</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -19104,10 +19089,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45386</v>
+        <v>45513</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19120,7 +19105,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -19163,7 +19148,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 27342-2024</t>
+          <t>A 21077-2023</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19177,10 +19162,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45473</v>
+        <v>45057</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19193,7 +19178,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19236,7 +19221,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 10100-2025</t>
+          <t>A 9152-2024</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19250,10 +19235,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45719</v>
+        <v>45357</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19266,7 +19251,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19309,7 +19294,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 8667-2025</t>
+          <t>A 8152-2023</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19323,10 +19308,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45712</v>
+        <v>44974</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19339,7 +19324,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19382,7 +19367,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 10357-2025</t>
+          <t>A 21432-2026</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19396,10 +19381,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45720</v>
+        <v>46148</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19412,7 +19397,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>0.9</v>
+        <v>4.3</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19455,7 +19440,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 10358-2025</t>
+          <t>A 22364-2026</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19469,10 +19454,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45720</v>
+        <v>46154</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19485,7 +19470,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19528,7 +19513,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 60993-2022</t>
+          <t>A 21698-2025</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19542,10 +19527,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>44914</v>
+        <v>45783</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19558,7 +19543,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19601,7 +19586,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 10097-2025</t>
+          <t>A 21678-2025</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19615,10 +19600,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45719</v>
+        <v>45783</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19631,7 +19616,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19674,7 +19659,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 11213-2025</t>
+          <t>A 21689-2025</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19688,10 +19673,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45726</v>
+        <v>45783</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19704,7 +19689,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>4.8</v>
+        <v>1.5</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19747,7 +19732,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 24533-2025</t>
+          <t>A 21977-2026</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19761,10 +19746,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45798</v>
+        <v>46153</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19777,7 +19762,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>5.8</v>
+        <v>1.5</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19820,7 +19805,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 24527-2025</t>
+          <t>A 22337-2026</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19834,10 +19819,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>45798</v>
+        <v>46154</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19850,7 +19835,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>3.6</v>
+        <v>0.7</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -19893,7 +19878,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 43017-2024</t>
+          <t>A 1369-2025</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19907,10 +19892,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45567</v>
+        <v>45667</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19923,7 +19908,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19966,7 +19951,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 25623-2025</t>
+          <t>A 16746-2023</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19980,10 +19965,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45803</v>
+        <v>45030</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19996,7 +19981,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -20039,7 +20024,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 25652-2025</t>
+          <t>A 51436-2025</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -20053,10 +20038,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45803</v>
+        <v>45950</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20069,7 +20054,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -20112,7 +20097,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 25635-2025</t>
+          <t>A 59865-2024</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20126,10 +20111,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45803</v>
+        <v>45639</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20142,7 +20127,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>0.4</v>
+        <v>5.9</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20185,7 +20170,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 60395-2024</t>
+          <t>A 32832-2024</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20195,14 +20180,14 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45643</v>
+        <v>45516</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20215,7 +20200,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20258,7 +20243,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 17693-2023</t>
+          <t>A 28863-2025</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -20272,10 +20257,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>45037</v>
+        <v>45820</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20288,7 +20273,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>11.3</v>
+        <v>1.9</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20331,7 +20316,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 12501-2025</t>
+          <t>A 59269-2025</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20345,10 +20330,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45730</v>
+        <v>45988</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20361,7 +20346,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20404,7 +20389,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 11848-2025</t>
+          <t>A 25036-2026</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20418,10 +20403,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>45728</v>
+        <v>46174</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20434,7 +20419,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>2</v>
+        <v>5.9</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20477,7 +20462,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 8165-2023</t>
+          <t>A 36138-2025</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -20491,10 +20476,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>44974</v>
+        <v>45866</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20507,7 +20492,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -20550,7 +20535,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 17528-2024</t>
+          <t>A 25458-2026</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -20564,10 +20549,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>45415</v>
+        <v>46177</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20580,7 +20565,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -20623,7 +20608,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 52922-2024</t>
+          <t>A 25954-2026</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -20637,10 +20622,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>45610</v>
+        <v>46181</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20653,7 +20638,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -20696,7 +20681,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 7228-2025</t>
+          <t>A 26527-2026</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -20710,10 +20695,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>45702</v>
+        <v>46183</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20725,8 +20710,13 @@
           <t>MELLERUD</t>
         </is>
       </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I263" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -20769,7 +20759,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 28319-2025</t>
+          <t>A 26536-2026</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -20783,10 +20773,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>45818</v>
+        <v>46183</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20798,8 +20788,13 @@
           <t>MELLERUD</t>
         </is>
       </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I264" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -20842,7 +20837,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 28870-2025</t>
+          <t>A 29936-2026</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -20856,10 +20851,10 @@
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>45820</v>
+        <v>46205</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20872,7 +20867,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>7.9</v>
+        <v>1.6</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -20915,7 +20910,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>A 32842-2025</t>
+          <t>A 29939-2026</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -20929,10 +20924,10 @@
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>45839</v>
+        <v>46205</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20945,7 +20940,7 @@
         </is>
       </c>
       <c r="I266" t="n">
-        <v>6.1</v>
+        <v>3</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -20988,7 +20983,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>A 23450-2025</t>
+          <t>A 20578-2026</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -21002,10 +20997,10 @@
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>45792</v>
+        <v>46140</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21017,8 +21012,13 @@
           <t>MELLERUD</t>
         </is>
       </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I267" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -21061,7 +21061,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>A 11442-2024</t>
+          <t>A 34065-2026</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -21075,10 +21075,10 @@
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>45372</v>
+        <v>46252</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21091,7 +21091,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -21134,7 +21134,7 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>A 15227-2025</t>
+          <t>A 31836-2026</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -21148,10 +21148,10 @@
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>45744</v>
+        <v>46230</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21207,7 +21207,7 @@
     <row r="270" ht="15" customHeight="1">
       <c r="A270" t="inlineStr">
         <is>
-          <t>A 26639-2025</t>
+          <t>A 36960-2026</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -21221,10 +21221,10 @@
         </is>
       </c>
       <c r="D270" s="1" t="n">
-        <v>45810</v>
+        <v>46273</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21237,7 +21237,7 @@
         </is>
       </c>
       <c r="I270" t="n">
-        <v>5.4</v>
+        <v>8.1</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -21280,7 +21280,7 @@
     <row r="271" ht="15" customHeight="1">
       <c r="A271" t="inlineStr">
         <is>
-          <t>A 36141-2025</t>
+          <t>A 31889-2026</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -21294,10 +21294,10 @@
         </is>
       </c>
       <c r="D271" s="1" t="n">
-        <v>45866</v>
+        <v>46231</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21310,7 +21310,7 @@
         </is>
       </c>
       <c r="I271" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J271" t="n">
         <v>0</v>
@@ -21353,7 +21353,7 @@
     <row r="272" ht="15" customHeight="1">
       <c r="A272" t="inlineStr">
         <is>
-          <t>A 36048-2025</t>
+          <t>A 38251-2026</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -21367,10 +21367,10 @@
         </is>
       </c>
       <c r="D272" s="1" t="n">
-        <v>45866</v>
+        <v>46281</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21383,7 +21383,7 @@
         </is>
       </c>
       <c r="I272" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J272" t="n">
         <v>0</v>
@@ -21443,7 +21443,7 @@
         <v>44551</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>45351</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>46184</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21662,7 +21662,7 @@
         <v>46188</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>

--- a/Översikt MELLERUD.xlsx
+++ b/Översikt MELLERUD.xlsx
@@ -601,7 +601,7 @@
         <v>46184</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>46112</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>45614</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>45614</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44840</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>45734</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>46020</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>45670</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>45253</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>44963</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>45006</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>46020</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 28216-2026</t>
+          <t>A 25764-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1982,10 +1982,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46196</v>
+        <v>45804</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1995,27 +1995,22 @@
       <c r="G14" t="inlineStr">
         <is>
           <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I14" t="n">
         <v>2.5</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
@@ -2027,21 +2022,134 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
       </c>
       <c r="T14" t="n">
+        <v>5</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Guldlockmossa
+Lönnlav
+Rostfläck</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 25764-2025 artfynd.xlsx", "A 25764-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 25764-2025 karta.png", "A 25764-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 25764-2025 georefererad karta.tif", "A 25764-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 25764-2025 FSC-klagomål.docx", "A 25764-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 25764-2025 FSC-klagomål mail.docx", "A 25764-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 25764-2025 tillsynsbegäran.docx", "A 25764-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 25764-2025 tillsynsbegäran mail.docx", "A 25764-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 28216-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46196</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2</v>
+      </c>
+      <c r="S15" t="n">
         <v>4</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Gulvit blekspik
@@ -2049,112 +2157,112 @@
 Gröngöling</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 28216-2026 artfynd.xlsx", "A 28216-2026")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 28216-2026 karta.png", "A 28216-2026")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 28216-2026 georefererad karta.tif", "A 28216-2026")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 28216-2026 FSC-klagomål.docx", "A 28216-2026")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 28216-2026 FSC-klagomål mail.docx", "A 28216-2026")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 28216-2026 tillsynsbegäran.docx", "A 28216-2026")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 28216-2026 tillsynsbegäran mail.docx", "A 28216-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>A 33141-2026</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
         <v>46244</v>
       </c>
-      <c r="E15" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
+      <c r="E16" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
         <is>
           <t>Övriga Aktiebolag</t>
         </is>
       </c>
-      <c r="I15" t="n">
+      <c r="I16" t="n">
         <v>5.9</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J16" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K16" t="n">
         <v>3</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
         <v>1</v>
       </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>4</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T16" t="n">
         <v>7</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U16" t="n">
         <v>7</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Kattfotslav
 Grön sköldmossa
@@ -2162,143 +2270,35 @@
 Mandelriska</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 33141-2026 artfynd.xlsx", "A 33141-2026")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 33141-2026 karta.png", "A 33141-2026")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 33141-2026 georefererad karta.tif", "A 33141-2026")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 33141-2026 FSC-klagomål.docx", "A 33141-2026")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 33141-2026 FSC-klagomål mail.docx", "A 33141-2026")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 33141-2026 tillsynsbegäran.docx", "A 33141-2026")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 33141-2026 tillsynsbegäran mail.docx", "A 33141-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 25764-2025</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45804</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>3</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" t="n">
-        <v>4</v>
-      </c>
-      <c r="T16" t="n">
-        <v>5</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Guldlockmossa
-Lönnlav
-Rostfläck</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 25764-2025 artfynd.xlsx", "A 25764-2025")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 25764-2025 karta.png", "A 25764-2025")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 25764-2025 georefererad karta.tif", "A 25764-2025")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 25764-2025 FSC-klagomål.docx", "A 25764-2025")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 25764-2025 FSC-klagomål mail.docx", "A 25764-2025")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 25764-2025 tillsynsbegäran.docx", "A 25764-2025")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 25764-2025 tillsynsbegäran mail.docx", "A 25764-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>45390</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>44896</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>44804</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>44750</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 10814-2024</t>
+          <t>A 43349-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2748,10 +2748,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45369</v>
+        <v>45568</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2763,13 +2763,8 @@
           <t>MELLERUD</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>6.6</v>
+        <v>4.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2778,10 +2773,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2796,7 +2791,7 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2805,682 +2800,687 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 43349-2024 artfynd.xlsx", "A 43349-2024")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 43349-2024 karta.png", "A 43349-2024")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 43349-2024 georefererad karta.tif", "A 43349-2024")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 43349-2024 FSC-klagomål.docx", "A 43349-2024")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 43349-2024 FSC-klagomål mail.docx", "A 43349-2024")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 43349-2024 tillsynsbegäran.docx", "A 43349-2024")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 43349-2024 tillsynsbegäran mail.docx", "A 43349-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 8169-2023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>44974</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 8169-2023 artfynd.xlsx", "A 8169-2023")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 8169-2023 karta.png", "A 8169-2023")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 8169-2023 georefererad karta.tif", "A 8169-2023")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 8169-2023 FSC-klagomål.docx", "A 8169-2023")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 8169-2023 FSC-klagomål mail.docx", "A 8169-2023")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 8169-2023 tillsynsbegäran.docx", "A 8169-2023")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 8169-2023 tillsynsbegäran mail.docx", "A 8169-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 10814-2024</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>45369</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 10814-2024 artfynd.xlsx", "A 10814-2024")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 10814-2024 karta.png", "A 10814-2024")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 10814-2024 georefererad karta.tif", "A 10814-2024")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 10814-2024 FSC-klagomål.docx", "A 10814-2024")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 10814-2024 FSC-klagomål mail.docx", "A 10814-2024")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 10814-2024 tillsynsbegäran.docx", "A 10814-2024")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 10814-2024 tillsynsbegäran mail.docx", "A 10814-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 3992-2023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>44952</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 3992-2023 artfynd.xlsx", "A 3992-2023")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 3992-2023 karta.png", "A 3992-2023")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 3992-2023 georefererad karta.tif", "A 3992-2023")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 3992-2023 FSC-klagomål.docx", "A 3992-2023")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 3992-2023 FSC-klagomål mail.docx", "A 3992-2023")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 3992-2023 tillsynsbegäran.docx", "A 3992-2023")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 3992-2023 tillsynsbegäran mail.docx", "A 3992-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>A 23546-2026</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
         <v>46163</v>
       </c>
-      <c r="E22" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
+      <c r="E25" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
         <v>3.6</v>
       </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
         <v>1</v>
       </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
         <v>1</v>
       </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
         <v>1</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T25" t="n">
         <v>3</v>
       </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Lunglav</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 23546-2026 artfynd.xlsx", "A 23546-2026")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 23546-2026 karta.png", "A 23546-2026")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 23546-2026 georefererad karta.tif", "A 23546-2026")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 23546-2026 FSC-klagomål.docx", "A 23546-2026")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 23546-2026 FSC-klagomål mail.docx", "A 23546-2026")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 23546-2026 tillsynsbegäran.docx", "A 23546-2026")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 23546-2026 tillsynsbegäran mail.docx", "A 23546-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>A 43531-2025</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
         <v>45911</v>
       </c>
-      <c r="E23" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
+      <c r="E26" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
         <is>
           <t>Övriga Aktiebolag</t>
         </is>
       </c>
-      <c r="I23" t="n">
+      <c r="I26" t="n">
         <v>8</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J26" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
         <v>1</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T26" t="n">
         <v>1</v>
       </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Kungsfågel</t>
         </is>
       </c>
-      <c r="W23">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 43531-2025 artfynd.xlsx", "A 43531-2025")</f>
         <v/>
       </c>
-      <c r="X23">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 43531-2025 karta.png", "A 43531-2025")</f>
         <v/>
       </c>
-      <c r="Y23">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 43531-2025 georefererad karta.tif", "A 43531-2025")</f>
         <v/>
       </c>
-      <c r="AA23">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 43531-2025 FSC-klagomål.docx", "A 43531-2025")</f>
         <v/>
       </c>
-      <c r="AB23">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 43531-2025 FSC-klagomål mail.docx", "A 43531-2025")</f>
         <v/>
       </c>
-      <c r="AC23">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 43531-2025 tillsynsbegäran.docx", "A 43531-2025")</f>
         <v/>
       </c>
-      <c r="AD23">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 43531-2025 tillsynsbegäran mail.docx", "A 43531-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 8169-2023</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>44974</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 26518-2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
         <v>1</v>
       </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
         <v>1</v>
       </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
+      <c r="R27" t="n">
         <v>1</v>
       </c>
-      <c r="T24" t="n">
+      <c r="S27" t="n">
         <v>1</v>
       </c>
-      <c r="U24" t="n">
+      <c r="T27" t="n">
         <v>1</v>
       </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Älg</t>
-        </is>
-      </c>
-      <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 8169-2023 artfynd.xlsx", "A 8169-2023")</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 8169-2023 karta.png", "A 8169-2023")</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 8169-2023 georefererad karta.tif", "A 8169-2023")</f>
-        <v/>
-      </c>
-      <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 8169-2023 FSC-klagomål.docx", "A 8169-2023")</f>
-        <v/>
-      </c>
-      <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 8169-2023 FSC-klagomål mail.docx", "A 8169-2023")</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 8169-2023 tillsynsbegäran.docx", "A 8169-2023")</f>
-        <v/>
-      </c>
-      <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 8169-2023 tillsynsbegäran mail.docx", "A 8169-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 26518-2026</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>46183</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
+      <c r="U27" t="n">
         <v>1</v>
       </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Rotfingersvamp</t>
         </is>
       </c>
-      <c r="W25">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 26518-2026 artfynd.xlsx", "A 26518-2026")</f>
         <v/>
       </c>
-      <c r="X25">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 26518-2026 karta.png", "A 26518-2026")</f>
         <v/>
       </c>
-      <c r="Y25">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 26518-2026 georefererad karta.tif", "A 26518-2026")</f>
         <v/>
       </c>
-      <c r="AA25">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 26518-2026 FSC-klagomål.docx", "A 26518-2026")</f>
         <v/>
       </c>
-      <c r="AB25">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 26518-2026 FSC-klagomål mail.docx", "A 26518-2026")</f>
         <v/>
       </c>
-      <c r="AC25">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 26518-2026 tillsynsbegäran.docx", "A 26518-2026")</f>
         <v/>
       </c>
-      <c r="AD25">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 26518-2026 tillsynsbegäran mail.docx", "A 26518-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 43349-2024</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>45568</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>1</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Älg</t>
-        </is>
-      </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 43349-2024 artfynd.xlsx", "A 43349-2024")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 43349-2024 karta.png", "A 43349-2024")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 43349-2024 georefererad karta.tif", "A 43349-2024")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 43349-2024 FSC-klagomål.docx", "A 43349-2024")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 43349-2024 FSC-klagomål mail.docx", "A 43349-2024")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 43349-2024 tillsynsbegäran.docx", "A 43349-2024")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 43349-2024 tillsynsbegäran mail.docx", "A 43349-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 3992-2023</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>44952</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>1</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 3992-2023 artfynd.xlsx", "A 3992-2023")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 3992-2023 karta.png", "A 3992-2023")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 3992-2023 georefererad karta.tif", "A 3992-2023")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 3992-2023 FSC-klagomål.docx", "A 3992-2023")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 3992-2023 FSC-klagomål mail.docx", "A 3992-2023")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 3992-2023 tillsynsbegäran.docx", "A 3992-2023")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 3992-2023 tillsynsbegäran mail.docx", "A 3992-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         <v>46281</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>44754</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>44732</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>44615</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         <v>44783</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>44754</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>44546</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>44752</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>44484</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>44873</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>44469</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4336,7 +4336,7 @@
         <v>44752</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>44564</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>44578</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>44657</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 9796-2022</t>
+          <t>A 44530-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4625,10 +4625,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44620</v>
+        <v>44840</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4684,7 +4684,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 44530-2022</t>
+          <t>A 9796-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4698,10 +4698,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44840</v>
+        <v>44620</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4774,7 +4774,7 @@
         <v>44677</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>44720</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
         <v>44676</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>44817</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>44539</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 63539-2021</t>
+          <t>A 21097-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5136,10 +5136,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44508</v>
+        <v>44704</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5212,7 +5212,7 @@
         <v>44484</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 21097-2022</t>
+          <t>A 63539-2021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5282,10 +5282,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44704</v>
+        <v>44508</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5341,7 +5341,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 52269-2022</t>
+          <t>A 32642-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5355,10 +5355,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44873</v>
+        <v>44783</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5414,7 +5414,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 32642-2022</t>
+          <t>A 10401-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5428,10 +5428,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44783</v>
+        <v>45365</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>4.2</v>
+        <v>7.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5487,7 +5487,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 61060-2022</t>
+          <t>A 26530-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5501,10 +5501,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44915</v>
+        <v>45092</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>8.4</v>
+        <v>2.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5560,7 +5560,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 61061-2022</t>
+          <t>A 12334-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5574,10 +5574,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44915</v>
+        <v>45378</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5633,7 +5633,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 3989-2023</t>
+          <t>A 24527-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5647,10 +5647,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44952</v>
+        <v>45798</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5706,7 +5706,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 9374-2023</t>
+          <t>A 24533-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5720,10 +5720,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44981</v>
+        <v>45798</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>5.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5779,7 +5779,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 4054-2025</t>
+          <t>A 43017-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5793,10 +5793,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45684</v>
+        <v>45567</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5852,7 +5852,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 19872-2023</t>
+          <t>A 52471-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5866,10 +5866,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45054</v>
+        <v>45225</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>8.4</v>
+        <v>2.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5925,7 +5925,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 9152-2024</t>
+          <t>A 38888-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5939,10 +5939,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45357</v>
+        <v>45887</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5998,7 +5998,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 56025-2024</t>
+          <t>A 1830-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6012,10 +6012,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45624</v>
+        <v>46035</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6071,7 +6071,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 51173-2023</t>
+          <t>A 1827-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6085,10 +6085,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45212</v>
+        <v>46035</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6144,7 +6144,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 32549-2024</t>
+          <t>A 32299-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45513</v>
+        <v>45512</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6217,7 +6217,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 7154-2024</t>
+          <t>A 3250-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6227,14 +6227,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45344</v>
+        <v>46041</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6290,7 +6290,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 4416-2025</t>
+          <t>A 3178-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45686</v>
+        <v>46041</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6363,7 +6363,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 33388-2022</t>
+          <t>A 3201-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6377,10 +6377,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44788</v>
+        <v>46041</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>8.699999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6436,7 +6436,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 24978-2022</t>
+          <t>A 37267-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6450,10 +6450,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44728</v>
+        <v>45540</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 46917-2022</t>
+          <t>A 27908-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6523,10 +6523,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44851</v>
+        <v>45817</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6582,7 +6582,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 8155-2023</t>
+          <t>A 5324-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6596,10 +6596,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44974</v>
+        <v>46050</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6655,7 +6655,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 37267-2024</t>
+          <t>A 42723-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6669,10 +6669,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45540</v>
+        <v>45908</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6728,7 +6728,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 14596-2022</t>
+          <t>A 10398-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6742,10 +6742,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44655</v>
+        <v>45365</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6801,7 +6801,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 13800-2023</t>
+          <t>A 43398-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6815,10 +6815,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45007</v>
+        <v>45911</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6874,7 +6874,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 12157-2022</t>
+          <t>A 25652-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6884,14 +6884,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44636</v>
+        <v>45803</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6947,7 +6947,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 51783-2023</t>
+          <t>A 7117-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6961,10 +6961,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45222</v>
+        <v>46058</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7020,7 +7020,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 39535-2024</t>
+          <t>A 7125-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7034,10 +7034,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45551</v>
+        <v>46058</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.7</v>
+        <v>0.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7093,7 +7093,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 7443-2023</t>
+          <t>A 7047-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7107,10 +7107,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44971</v>
+        <v>46057</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7166,7 +7166,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 10356-2025</t>
+          <t>A 7120-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7180,10 +7180,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45720</v>
+        <v>46058</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7239,7 +7239,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 17685-2024</t>
+          <t>A 44020-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7253,10 +7253,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45418</v>
+        <v>45915</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7312,7 +7312,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 9456-2024</t>
+          <t>A 44600-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7326,10 +7326,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45359</v>
+        <v>45917</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.8</v>
+        <v>7.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7385,7 +7385,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 35605-2024</t>
+          <t>A 44573-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7399,10 +7399,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45531</v>
+        <v>45917</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.4</v>
+        <v>5.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7458,7 +7458,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 16656-2022</t>
+          <t>A 25635-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7472,10 +7472,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44672</v>
+        <v>45803</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7531,7 +7531,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 25109-2022</t>
+          <t>A 44608-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7545,10 +7545,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44729</v>
+        <v>45917</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7604,7 +7604,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 39728-2023</t>
+          <t>A 17685-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7618,10 +7618,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45167</v>
+        <v>45418</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7677,7 +7677,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 17543-2023</t>
+          <t>A 25623-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7691,10 +7691,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45036</v>
+        <v>45803</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7750,7 +7750,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 53307-2024</t>
+          <t>A 45991-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7764,10 +7764,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45614</v>
+        <v>45924</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2</v>
+        <v>4.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7823,7 +7823,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 53254-2022</t>
+          <t>A 33666-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7837,10 +7837,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44876</v>
+        <v>45132</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7896,7 +7896,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 38653-2025</t>
+          <t>A 1921-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7910,10 +7910,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45884</v>
+        <v>45671</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>5.3</v>
+        <v>0.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7969,7 +7969,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 36963-2025</t>
+          <t>A 45935-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7983,10 +7983,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45874</v>
+        <v>45923</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 1921-2025</t>
+          <t>A 45861-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8056,10 +8056,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45671</v>
+        <v>45923</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.4</v>
+        <v>10.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 38888-2025</t>
+          <t>A 9573-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8129,10 +8129,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45887</v>
+        <v>46071</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.2</v>
+        <v>5.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8188,7 +8188,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 24312-2025</t>
+          <t>A 6283-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8202,10 +8202,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45797</v>
+        <v>44965</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8261,7 +8261,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 60996-2022</t>
+          <t>A 1883-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8275,10 +8275,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44914</v>
+        <v>44939</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8334,7 +8334,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 493-2025</t>
+          <t>A 46668-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8348,10 +8348,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45664</v>
+        <v>45926</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.9</v>
+        <v>0.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8407,7 +8407,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 52471-2023</t>
+          <t>A 46872-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8421,10 +8421,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45225</v>
+        <v>45929</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8480,7 +8480,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 35603-2024</t>
+          <t>A 11121-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8490,14 +8490,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45531</v>
+        <v>46079</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8553,7 +8553,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 38663-2025</t>
+          <t>A 11323-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8563,14 +8563,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45884</v>
+        <v>46080</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4.2</v>
+        <v>7.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8626,7 +8626,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 15323-2024</t>
+          <t>A 11249-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8640,10 +8640,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45400</v>
+        <v>46080</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8656,7 +8656,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>10.6</v>
+        <v>4.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8699,7 +8699,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 10398-2024</t>
+          <t>A 60395-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8709,14 +8709,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45365</v>
+        <v>45643</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8772,7 +8772,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 36146-2025</t>
+          <t>A 53317-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8786,10 +8786,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45866</v>
+        <v>45614</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8845,7 +8845,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 27908-2025</t>
+          <t>A 43353-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8859,10 +8859,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45817</v>
+        <v>45568</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8918,7 +8918,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 49449-2025</t>
+          <t>A 10356-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8932,10 +8932,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45938</v>
+        <v>45720</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8991,7 +8991,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 58861-2022</t>
+          <t>A 49718-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9005,10 +9005,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44903</v>
+        <v>45939</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>4.8</v>
+        <v>1.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9064,7 +9064,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 42723-2025</t>
+          <t>A 13594-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9074,14 +9074,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45908</v>
+        <v>46096</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9137,7 +9137,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 11256-2025</t>
+          <t>A 8165-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9151,10 +9151,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45726</v>
+        <v>44974</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9210,7 +9210,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 8923-2024</t>
+          <t>A 43406-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9224,10 +9224,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45356</v>
+        <v>45911</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9283,7 +9283,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 43398-2025</t>
+          <t>A 17528-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9297,10 +9297,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45911</v>
+        <v>45415</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9356,7 +9356,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 39942-2023</t>
+          <t>A 52922-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9370,10 +9370,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45167</v>
+        <v>45610</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 44020-2025</t>
+          <t>A 334-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9443,10 +9443,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45915</v>
+        <v>44929</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9502,7 +9502,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 44600-2025</t>
+          <t>A 53232-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9516,10 +9516,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45917</v>
+        <v>45958</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>7.2</v>
+        <v>0.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9575,7 +9575,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 3998-2025</t>
+          <t>A 50478-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9589,10 +9589,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45684</v>
+        <v>45945</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>8.199999999999999</v>
+        <v>1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9648,7 +9648,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 44608-2025</t>
+          <t>A 50482-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9662,10 +9662,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45917</v>
+        <v>45945</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9721,7 +9721,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 44573-2025</t>
+          <t>A 53307-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9735,10 +9735,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45917</v>
+        <v>45614</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>5.5</v>
+        <v>2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9794,7 +9794,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 45861-2025</t>
+          <t>A 18055-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9808,10 +9808,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45923</v>
+        <v>46125</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>10.2</v>
+        <v>5.2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9867,7 +9867,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 45935-2025</t>
+          <t>A 11848-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9881,10 +9881,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45923</v>
+        <v>45728</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9940,7 +9940,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 45991-2025</t>
+          <t>A 12501-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9954,10 +9954,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45924</v>
+        <v>45730</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>4.4</v>
+        <v>2.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10013,7 +10013,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 46872-2025</t>
+          <t>A 17693-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10027,10 +10027,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45929</v>
+        <v>45037</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.4</v>
+        <v>11.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10086,7 +10086,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 32384-2023</t>
+          <t>A 56026-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10100,10 +10100,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45120</v>
+        <v>45973</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10159,7 +10159,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 46668-2025</t>
+          <t>A 40064-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10173,10 +10173,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45926</v>
+        <v>45168</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10189,7 +10189,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10232,7 +10232,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 49718-2025</t>
+          <t>A 26428-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10246,10 +10246,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45939</v>
+        <v>44736</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10262,7 +10262,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10305,7 +10305,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 6283-2023</t>
+          <t>A 8923-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10319,10 +10319,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44965</v>
+        <v>45356</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10378,7 +10378,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 40064-2023</t>
+          <t>A 59808-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10392,10 +10392,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45168</v>
+        <v>45992</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10451,7 +10451,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 34415-2024</t>
+          <t>A 59806-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10465,10 +10465,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45525</v>
+        <v>45992</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>4.3</v>
+        <v>0.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10524,7 +10524,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 43406-2025</t>
+          <t>A 25109-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10538,10 +10538,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45911</v>
+        <v>44729</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10554,7 +10554,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10597,7 +10597,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 32304-2024</t>
+          <t>A 59804-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10611,10 +10611,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45512</v>
+        <v>45992</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10670,7 +10670,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 46761-2023</t>
+          <t>A 7228-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10684,10 +10684,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45198</v>
+        <v>45702</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10700,7 +10700,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10743,7 +10743,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 21077-2023</t>
+          <t>A 59802-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10757,10 +10757,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45057</v>
+        <v>45992</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10816,7 +10816,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 22313-2023</t>
+          <t>A 60203-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10830,10 +10830,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45070</v>
+        <v>45994</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10846,7 +10846,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10889,7 +10889,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 53565-2022</t>
+          <t>A 61177-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10899,14 +10899,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44879</v>
+        <v>46000</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10919,7 +10919,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10962,7 +10962,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 17160-2024</t>
+          <t>A 61180-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10976,10 +10976,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45412</v>
+        <v>46000</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10992,7 +10992,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11035,7 +11035,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 48256-2022</t>
+          <t>A 493-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11049,10 +11049,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44858</v>
+        <v>45664</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.9</v>
+        <v>3.9</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11108,7 +11108,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 59723-2025</t>
+          <t>A 49449-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11122,10 +11122,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45992</v>
+        <v>45938</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11138,7 +11138,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>12.3</v>
+        <v>2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11181,7 +11181,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 50478-2025</t>
+          <t>A 28319-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11195,10 +11195,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45945</v>
+        <v>45818</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11211,7 +11211,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11254,7 +11254,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 50482-2025</t>
+          <t>A 20573-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11268,10 +11268,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45945</v>
+        <v>46140</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11283,8 +11283,13 @@
           <t>MELLERUD</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>8.800000000000001</v>
+        <v>1.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11327,7 +11332,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 53232-2025</t>
+          <t>A 25399-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11337,14 +11342,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45958</v>
+        <v>45089</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11357,7 +11362,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11400,7 +11405,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 20573-2026</t>
+          <t>A 24312-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11414,10 +11419,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46140</v>
+        <v>45797</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11429,13 +11434,8 @@
           <t>MELLERUD</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11478,7 +11478,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 8152-2023</t>
+          <t>A 50441-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11492,10 +11492,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44974</v>
+        <v>45216</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11508,7 +11508,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11551,7 +11551,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 56026-2025</t>
+          <t>A 53565-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11565,10 +11565,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45973</v>
+        <v>44879</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11581,7 +11581,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11624,7 +11624,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 40065-2023</t>
+          <t>A 32304-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11638,10 +11638,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45168</v>
+        <v>45512</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11654,7 +11654,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11697,7 +11697,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 56349-2025</t>
+          <t>A 63249-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11711,10 +11711,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45974</v>
+        <v>46010</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11727,7 +11727,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11770,7 +11770,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 45834-2023</t>
+          <t>A 28870-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11784,10 +11784,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45195</v>
+        <v>45820</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11800,7 +11800,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1</v>
+        <v>7.9</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11843,7 +11843,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 51463-2023</t>
+          <t>A 28865-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11857,10 +11857,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45221</v>
+        <v>45820</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11873,7 +11873,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11916,7 +11916,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 28865-2025</t>
+          <t>A 36146-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11930,10 +11930,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45820</v>
+        <v>45866</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11946,7 +11946,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11989,7 +11989,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 8492-2022</t>
+          <t>A 59723-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12003,10 +12003,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44613</v>
+        <v>45992</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12019,7 +12019,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.6</v>
+        <v>12.3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12062,7 +12062,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 48879-2024</t>
+          <t>A 4416-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12076,10 +12076,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45594</v>
+        <v>45686</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12092,7 +12092,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12135,7 +12135,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 59804-2025</t>
+          <t>A 15971-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12149,10 +12149,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45992</v>
+        <v>45022</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12165,7 +12165,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12208,7 +12208,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 59802-2025</t>
+          <t>A 35603-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12222,10 +12222,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45992</v>
+        <v>45531</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12238,7 +12238,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12281,7 +12281,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 21432-2026</t>
+          <t>A 53254-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12295,10 +12295,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46148</v>
+        <v>44876</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12311,7 +12311,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>4.3</v>
+        <v>1.8</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12354,7 +12354,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 59808-2025</t>
+          <t>A 73351-2021</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12368,10 +12368,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45992</v>
+        <v>44551</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12384,7 +12384,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.5</v>
+        <v>6.1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12427,7 +12427,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 5647-2023</t>
+          <t>A 21432-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44960</v>
+        <v>46148</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.7</v>
+        <v>4.3</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12500,7 +12500,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 59806-2025</t>
+          <t>A 51916-2022</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12510,14 +12510,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45992</v>
+        <v>44868</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12530,7 +12530,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 21977-2026</t>
+          <t>A 22364-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12587,10 +12587,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12603,7 +12603,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12646,7 +12646,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 60203-2025</t>
+          <t>A 35605-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12660,10 +12660,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45994</v>
+        <v>45531</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 22364-2026</t>
+          <t>A 61811-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12733,10 +12733,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46154</v>
+        <v>45264</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12748,8 +12748,13 @@
           <t>MELLERUD</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I154" t="n">
-        <v>2.8</v>
+        <v>7.9</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12792,7 +12797,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 61177-2025</t>
+          <t>A 21977-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12802,14 +12807,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46000</v>
+        <v>46153</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12822,7 +12827,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12865,7 +12870,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 61180-2025</t>
+          <t>A 22337-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12879,10 +12884,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46000</v>
+        <v>46154</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12895,7 +12900,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12938,7 +12943,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 22337-2026</t>
+          <t>A 1369-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12952,10 +12957,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46154</v>
+        <v>45667</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12968,7 +12973,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13011,7 +13016,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 12334-2024</t>
+          <t>A 34415-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13025,10 +13030,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45378</v>
+        <v>45525</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13041,7 +13046,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>2</v>
+        <v>4.3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13084,7 +13089,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 12713-2022</t>
+          <t>A 16746-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13098,10 +13103,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44641</v>
+        <v>45030</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13114,7 +13119,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13157,7 +13162,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 16746-2023</t>
+          <t>A 51436-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13171,10 +13176,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45030</v>
+        <v>45950</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13187,7 +13192,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13230,7 +13235,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 11219-2024</t>
+          <t>A 59865-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13244,10 +13249,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45371</v>
+        <v>45639</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13260,7 +13265,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13303,7 +13308,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 1369-2025</t>
+          <t>A 32842-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13317,10 +13322,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45667</v>
+        <v>45839</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13333,7 +13338,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.9</v>
+        <v>6.1</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13393,7 +13398,7 @@
         <v>45516</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13449,7 +13454,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 63249-2025</t>
+          <t>A 33092-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13463,10 +13468,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46010</v>
+        <v>45126</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13479,7 +13484,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13522,7 +13527,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 18205-2024</t>
+          <t>A 40065-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13536,10 +13541,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45420</v>
+        <v>45168</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13552,7 +13557,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13595,7 +13600,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 59865-2024</t>
+          <t>A 28863-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13609,10 +13614,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45639</v>
+        <v>45820</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13625,7 +13630,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>5.9</v>
+        <v>1.9</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13668,7 +13673,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 51436-2025</t>
+          <t>A 23450-2025</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13682,10 +13687,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45950</v>
+        <v>45792</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13698,7 +13703,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13741,7 +13746,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 1830-2026</t>
+          <t>A 3989-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13755,10 +13760,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46035</v>
+        <v>44952</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13771,7 +13776,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13814,7 +13819,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 28863-2025</t>
+          <t>A 51783-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13828,10 +13833,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45820</v>
+        <v>45222</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13844,7 +13849,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13887,7 +13892,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 1827-2026</t>
+          <t>A 11442-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13901,10 +13906,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46035</v>
+        <v>45372</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13917,7 +13922,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13960,7 +13965,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 3178-2026</t>
+          <t>A 59269-2025</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13974,10 +13979,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46041</v>
+        <v>45988</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13990,7 +13995,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.8</v>
+        <v>3.5</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14033,7 +14038,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 3250-2026</t>
+          <t>A 36141-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14047,10 +14052,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46041</v>
+        <v>45866</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14063,7 +14068,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14106,7 +14111,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 10428-2022</t>
+          <t>A 26639-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14120,10 +14125,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44623</v>
+        <v>45810</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14136,7 +14141,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.9</v>
+        <v>5.4</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14179,7 +14184,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 3201-2026</t>
+          <t>A 15227-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14193,10 +14198,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46041</v>
+        <v>45744</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14209,7 +14214,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>3.2</v>
+        <v>0.7</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14252,7 +14257,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 5324-2026</t>
+          <t>A 32498-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14266,10 +14271,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46050</v>
+        <v>45513</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14282,7 +14287,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14325,7 +14330,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 54796-2022</t>
+          <t>A 36048-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14339,10 +14344,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44883</v>
+        <v>45866</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14355,7 +14360,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14398,7 +14403,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 53573-2023</t>
+          <t>A 27510-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14412,10 +14417,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45230</v>
+        <v>45097</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14428,7 +14433,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14471,7 +14476,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 7047-2026</t>
+          <t>A 25036-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14485,10 +14490,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46057</v>
+        <v>46174</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14501,7 +14506,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.7</v>
+        <v>5.9</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14544,7 +14549,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 7125-2026</t>
+          <t>A 36138-2025</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14558,10 +14563,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46058</v>
+        <v>45866</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14574,7 +14579,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14617,7 +14622,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 7120-2026</t>
+          <t>A 25458-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14631,10 +14636,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46058</v>
+        <v>46177</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14647,7 +14652,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14690,7 +14695,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 7117-2026</t>
+          <t>A 25954-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14704,10 +14709,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46058</v>
+        <v>46181</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14720,7 +14725,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14763,7 +14768,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 34116-2023</t>
+          <t>A 22313-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14773,14 +14778,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45126</v>
+        <v>45070</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14793,7 +14798,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>4.3</v>
+        <v>1.1</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14836,7 +14841,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 1883-2023</t>
+          <t>A 26527-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14850,10 +14855,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44939</v>
+        <v>46183</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14865,8 +14870,13 @@
           <t>MELLERUD</t>
         </is>
       </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I183" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14909,7 +14919,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 1886-2023</t>
+          <t>A 26536-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14923,10 +14933,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44939</v>
+        <v>46183</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14938,8 +14948,13 @@
           <t>MELLERUD</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I184" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14982,7 +14997,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 9573-2026</t>
+          <t>A 36963-2025</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14996,10 +15011,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46071</v>
+        <v>45874</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15012,7 +15027,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>5.2</v>
+        <v>0.7</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15055,7 +15070,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 59269-2025</t>
+          <t>A 14568-2022</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15069,10 +15084,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45988</v>
+        <v>44655</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15085,7 +15100,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15128,7 +15143,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 11249-2026</t>
+          <t>A 32384-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15142,10 +15157,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46080</v>
+        <v>45120</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15158,7 +15173,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>4.8</v>
+        <v>1.1</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15201,7 +15216,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 11121-2026</t>
+          <t>A 39942-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15211,14 +15226,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46079</v>
+        <v>45167</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15231,7 +15246,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15274,7 +15289,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 11323-2026</t>
+          <t>A 12713-2022</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15284,14 +15299,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46080</v>
+        <v>44641</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15304,7 +15319,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>7.3</v>
+        <v>2.9</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15347,7 +15362,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 25036-2026</t>
+          <t>A 18854-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15361,10 +15376,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46174</v>
+        <v>45042</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15377,7 +15392,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>5.9</v>
+        <v>3.3</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15420,7 +15435,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 27510-2023</t>
+          <t>A 38653-2025</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15434,10 +15449,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45097</v>
+        <v>45884</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15450,7 +15465,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.5</v>
+        <v>5.3</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15493,7 +15508,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 334-2023</t>
+          <t>A 38663-2025</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15507,10 +15522,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>44929</v>
+        <v>45884</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15523,7 +15538,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15566,7 +15581,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 32299-2024</t>
+          <t>A 29936-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15580,10 +15595,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45512</v>
+        <v>46205</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15596,7 +15611,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15639,7 +15654,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 13594-2026</t>
+          <t>A 29939-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15649,14 +15664,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46096</v>
+        <v>46205</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15669,7 +15684,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15712,7 +15727,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 36138-2025</t>
+          <t>A 51785-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15726,10 +15741,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45866</v>
+        <v>45222</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15742,7 +15757,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15785,7 +15800,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 25458-2026</t>
+          <t>A 3998-2025</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15799,10 +15814,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46177</v>
+        <v>45684</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15815,7 +15830,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>2.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15858,7 +15873,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 25954-2026</t>
+          <t>A 19872-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15872,10 +15887,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46181</v>
+        <v>45054</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15888,7 +15903,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1.5</v>
+        <v>8.4</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15931,7 +15946,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 26536-2026</t>
+          <t>A 20578-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15945,10 +15960,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46183</v>
+        <v>46140</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15966,7 +15981,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16009,7 +16024,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 26527-2026</t>
+          <t>A 8492-2022</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16023,10 +16038,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46183</v>
+        <v>44613</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16038,13 +16053,8 @@
           <t>MELLERUD</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I199" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16087,7 +16097,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 18055-2026</t>
+          <t>A 34065-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16101,10 +16111,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46125</v>
+        <v>46252</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16117,7 +16127,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>5.2</v>
+        <v>0.6</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16160,7 +16170,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 32498-2024</t>
+          <t>A 10428-2022</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16174,10 +16184,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45513</v>
+        <v>44623</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16190,7 +16200,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16233,7 +16243,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 43353-2024</t>
+          <t>A 21618-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16247,10 +16257,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45568</v>
+        <v>45442</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16263,7 +16273,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16306,7 +16316,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 51916-2022</t>
+          <t>A 21620-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16316,14 +16326,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>44868</v>
+        <v>45442</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16336,7 +16346,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16379,7 +16389,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 33666-2023</t>
+          <t>A 33388-2022</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16393,10 +16403,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45132</v>
+        <v>44788</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16409,7 +16419,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16452,7 +16462,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 51785-2023</t>
+          <t>A 46761-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16466,10 +16476,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45222</v>
+        <v>45198</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16482,7 +16492,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16525,7 +16535,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 33092-2023</t>
+          <t>A 16656-2022</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16539,10 +16549,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45126</v>
+        <v>44672</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16555,7 +16565,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16598,7 +16608,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 55391-2023</t>
+          <t>A 51463-2023</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16612,10 +16622,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45238</v>
+        <v>45221</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16628,7 +16638,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16671,7 +16681,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 20578-2026</t>
+          <t>A 34116-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16681,14 +16691,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46140</v>
+        <v>45126</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16700,13 +16710,8 @@
           <t>MELLERUD</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I208" t="n">
-        <v>1</v>
+        <v>4.3</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16749,7 +16754,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 15971-2023</t>
+          <t>A 56025-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16763,10 +16768,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45022</v>
+        <v>45624</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16779,7 +16784,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16822,7 +16827,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 53317-2024</t>
+          <t>A 11256-2025</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16836,10 +16841,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45614</v>
+        <v>45726</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16852,7 +16857,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16895,7 +16900,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 29936-2026</t>
+          <t>A 8155-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16909,10 +16914,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46205</v>
+        <v>44974</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16925,7 +16930,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16968,7 +16973,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 29939-2026</t>
+          <t>A 31836-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16982,10 +16987,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46205</v>
+        <v>46230</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16998,7 +17003,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17041,7 +17046,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 73351-2021</t>
+          <t>A 53573-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17055,10 +17060,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>44551</v>
+        <v>45230</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17071,7 +17076,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>6.1</v>
+        <v>3.8</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17114,7 +17119,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 34065-2026</t>
+          <t>A 61060-2022</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17128,10 +17133,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46252</v>
+        <v>44915</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17144,7 +17149,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>0.6</v>
+        <v>8.4</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17187,7 +17192,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 26428-2022</t>
+          <t>A 61061-2022</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17201,10 +17206,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>44736</v>
+        <v>44915</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17217,7 +17222,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>0.4</v>
+        <v>8.5</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17260,7 +17265,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 21618-2024</t>
+          <t>A 55391-2023</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17274,10 +17279,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45442</v>
+        <v>45238</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17290,7 +17295,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17333,7 +17338,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 21620-2024</t>
+          <t>A 54796-2022</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17347,10 +17352,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45442</v>
+        <v>44883</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17363,7 +17368,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17406,7 +17411,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 26530-2023</t>
+          <t>A 36960-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17420,10 +17425,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45092</v>
+        <v>46273</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17436,7 +17441,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>2.5</v>
+        <v>8.1</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17479,7 +17484,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 18854-2023</t>
+          <t>A 31889-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17493,10 +17498,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45042</v>
+        <v>46231</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17509,7 +17514,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17552,7 +17557,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 14568-2022</t>
+          <t>A 13800-2023</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17566,10 +17571,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>44655</v>
+        <v>45007</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17582,7 +17587,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17625,7 +17630,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 61811-2023</t>
+          <t>A 48879-2024</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17639,10 +17644,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45264</v>
+        <v>45594</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17654,13 +17659,8 @@
           <t>MELLERUD</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I221" t="n">
-        <v>7.9</v>
+        <v>1.1</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17703,7 +17703,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 25399-2023</t>
+          <t>A 45834-2023</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17713,14 +17713,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45089</v>
+        <v>45195</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17733,7 +17733,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17776,7 +17776,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 23238-2024</t>
+          <t>A 38251-2026</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17790,10 +17790,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45453</v>
+        <v>46281</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17806,7 +17806,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17849,7 +17849,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 53270-2024</t>
+          <t>A 32520-2026</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17863,10 +17863,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45614</v>
+        <v>46239</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17879,7 +17879,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>0.9</v>
+        <v>3.6</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17922,7 +17922,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 17538-2023</t>
+          <t>A 32691-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17936,10 +17936,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45036</v>
+        <v>46240</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17995,7 +17995,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 31836-2026</t>
+          <t>A 52269-2022</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18009,10 +18009,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>46230</v>
+        <v>44873</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18025,7 +18025,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>0.7</v>
+        <v>4.6</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18068,7 +18068,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 36960-2026</t>
+          <t>A 15323-2024</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18082,10 +18082,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>46273</v>
+        <v>45400</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18098,7 +18098,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>8.1</v>
+        <v>10.6</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18141,7 +18141,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 19545-2024</t>
+          <t>A 38040-2025</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18155,10 +18155,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45429</v>
+        <v>45882</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18171,7 +18171,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18214,7 +18214,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 31889-2026</t>
+          <t>A 17160-2024</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18228,10 +18228,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>46231</v>
+        <v>45412</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18287,7 +18287,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 50441-2023</t>
+          <t>A 19545-2024</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18301,10 +18301,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45216</v>
+        <v>45429</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18317,7 +18317,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18360,7 +18360,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 10401-2024</t>
+          <t>A 46917-2022</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18374,10 +18374,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45365</v>
+        <v>44851</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18390,7 +18390,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>7.6</v>
+        <v>0.8</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18433,7 +18433,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 38251-2026</t>
+          <t>A 33450-2026</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18447,10 +18447,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>46281</v>
+        <v>46246</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18463,7 +18463,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18506,7 +18506,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 32520-2026</t>
+          <t>A 60996-2022</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18520,10 +18520,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>46239</v>
+        <v>44914</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18536,7 +18536,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>3.6</v>
+        <v>0.7</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18579,7 +18579,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 32691-2026</t>
+          <t>A 12157-2022</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18589,14 +18589,14 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>46240</v>
+        <v>44636</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18609,7 +18609,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18652,7 +18652,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 21689-2025</t>
+          <t>A 56349-2025</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18666,10 +18666,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45783</v>
+        <v>45974</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18725,7 +18725,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 21678-2025</t>
+          <t>A 9456-2024</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18739,10 +18739,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45783</v>
+        <v>45359</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18798,7 +18798,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 38040-2025</t>
+          <t>A 53270-2024</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18812,10 +18812,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45882</v>
+        <v>45614</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18828,7 +18828,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18871,7 +18871,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 21698-2025</t>
+          <t>A 5647-2023</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18885,10 +18885,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45783</v>
+        <v>44960</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18901,7 +18901,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18944,7 +18944,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 13313-2024</t>
+          <t>A 7443-2023</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18958,10 +18958,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45386</v>
+        <v>44971</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18974,7 +18974,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -19017,7 +19017,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 27342-2024</t>
+          <t>A 1886-2023</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -19031,10 +19031,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45473</v>
+        <v>44939</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19047,7 +19047,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -19090,7 +19090,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 10100-2025</t>
+          <t>A 9374-2023</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -19104,10 +19104,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45719</v>
+        <v>44981</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19120,7 +19120,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -19163,7 +19163,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 8667-2025</t>
+          <t>A 48256-2022</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19177,10 +19177,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45712</v>
+        <v>44858</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19236,7 +19236,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 10357-2025</t>
+          <t>A 23238-2024</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19250,10 +19250,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45720</v>
+        <v>45453</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19309,7 +19309,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 10358-2025</t>
+          <t>A 7154-2024</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19319,14 +19319,14 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45720</v>
+        <v>45344</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19382,7 +19382,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 60993-2022</t>
+          <t>A 24978-2022</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19396,10 +19396,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>44914</v>
+        <v>44728</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19412,7 +19412,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19455,7 +19455,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 10097-2025</t>
+          <t>A 18205-2024</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19469,10 +19469,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45719</v>
+        <v>45420</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19528,7 +19528,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 11213-2025</t>
+          <t>A 17543-2023</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19542,10 +19542,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45726</v>
+        <v>45036</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19558,7 +19558,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19601,7 +19601,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 24533-2025</t>
+          <t>A 17538-2023</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19615,10 +19615,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45798</v>
+        <v>45036</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19631,7 +19631,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>5.8</v>
+        <v>2.3</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19674,7 +19674,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 24527-2025</t>
+          <t>A 11219-2024</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19688,10 +19688,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45798</v>
+        <v>45371</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19704,7 +19704,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19747,7 +19747,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 43017-2024</t>
+          <t>A 58861-2022</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19761,10 +19761,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45567</v>
+        <v>44903</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19820,7 +19820,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 33450-2026</t>
+          <t>A 39728-2023</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19834,10 +19834,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>46246</v>
+        <v>45167</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -19893,7 +19893,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 25623-2025</t>
+          <t>A 51173-2023</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19907,10 +19907,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45803</v>
+        <v>45212</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19923,7 +19923,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19966,7 +19966,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 25652-2025</t>
+          <t>A 4054-2025</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19980,10 +19980,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45803</v>
+        <v>45684</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19996,7 +19996,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -20039,7 +20039,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 25635-2025</t>
+          <t>A 14596-2022</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -20053,10 +20053,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45803</v>
+        <v>44655</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20069,7 +20069,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -20112,7 +20112,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 60395-2024</t>
+          <t>A 39535-2024</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20122,14 +20122,14 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45643</v>
+        <v>45551</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20142,7 +20142,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>2.1</v>
+        <v>4.7</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20185,7 +20185,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 17693-2023</t>
+          <t>A 32549-2024</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20199,10 +20199,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45037</v>
+        <v>45513</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20215,7 +20215,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>11.3</v>
+        <v>1</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20258,7 +20258,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 12501-2025</t>
+          <t>A 21077-2023</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -20272,10 +20272,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>45730</v>
+        <v>45057</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20288,7 +20288,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20331,7 +20331,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 11848-2025</t>
+          <t>A 9152-2024</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20345,10 +20345,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45728</v>
+        <v>45357</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20361,7 +20361,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20404,7 +20404,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 8165-2023</t>
+          <t>A 8152-2023</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20421,7 +20421,7 @@
         <v>44974</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20434,7 +20434,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20477,7 +20477,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 17528-2024</t>
+          <t>A 21698-2025</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -20491,10 +20491,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45415</v>
+        <v>45783</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20507,7 +20507,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>3.6</v>
+        <v>0.5</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -20550,7 +20550,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 52922-2024</t>
+          <t>A 21678-2025</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -20564,10 +20564,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>45610</v>
+        <v>45783</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20580,7 +20580,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -20623,7 +20623,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 7228-2025</t>
+          <t>A 21689-2025</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -20637,10 +20637,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>45702</v>
+        <v>45783</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -20696,7 +20696,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 28319-2025</t>
+          <t>A 27342-2024</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -20710,10 +20710,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>45818</v>
+        <v>45473</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20726,7 +20726,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -20769,7 +20769,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 28870-2025</t>
+          <t>A 13313-2024</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -20783,10 +20783,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>45820</v>
+        <v>45386</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20799,7 +20799,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>7.9</v>
+        <v>2.1</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -20842,7 +20842,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 32842-2025</t>
+          <t>A 8667-2025</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -20856,10 +20856,10 @@
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>45839</v>
+        <v>45712</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20872,7 +20872,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>6.1</v>
+        <v>3.1</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -20915,7 +20915,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>A 23450-2025</t>
+          <t>A 60993-2022</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -20929,10 +20929,10 @@
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>45792</v>
+        <v>44914</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20945,7 +20945,7 @@
         </is>
       </c>
       <c r="I266" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -20988,7 +20988,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>A 11442-2024</t>
+          <t>A 10100-2025</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -21002,10 +21002,10 @@
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>45372</v>
+        <v>45719</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21018,7 +21018,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -21061,7 +21061,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>A 15227-2025</t>
+          <t>A 10097-2025</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -21075,10 +21075,10 @@
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>45744</v>
+        <v>45719</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21091,7 +21091,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -21134,7 +21134,7 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>A 26639-2025</t>
+          <t>A 10357-2025</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -21148,10 +21148,10 @@
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>45810</v>
+        <v>45720</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21164,7 +21164,7 @@
         </is>
       </c>
       <c r="I269" t="n">
-        <v>5.4</v>
+        <v>0.9</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -21207,7 +21207,7 @@
     <row r="270" ht="15" customHeight="1">
       <c r="A270" t="inlineStr">
         <is>
-          <t>A 36141-2025</t>
+          <t>A 10358-2025</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -21221,10 +21221,10 @@
         </is>
       </c>
       <c r="D270" s="1" t="n">
-        <v>45866</v>
+        <v>45720</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21237,7 +21237,7 @@
         </is>
       </c>
       <c r="I270" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -21280,7 +21280,7 @@
     <row r="271" ht="15" customHeight="1">
       <c r="A271" t="inlineStr">
         <is>
-          <t>A 36048-2025</t>
+          <t>A 11213-2025</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -21294,10 +21294,10 @@
         </is>
       </c>
       <c r="D271" s="1" t="n">
-        <v>45866</v>
+        <v>45726</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21310,7 +21310,7 @@
         </is>
       </c>
       <c r="I271" t="n">
-        <v>1.2</v>
+        <v>4.8</v>
       </c>
       <c r="J271" t="n">
         <v>0</v>
@@ -21370,7 +21370,7 @@
         <v>44551</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21443,7 +21443,7 @@
         <v>45351</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>46184</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>46188</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>

--- a/Översikt MELLERUD.xlsx
+++ b/Översikt MELLERUD.xlsx
@@ -601,7 +601,7 @@
         <v>46184</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>46112</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>45614</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>45614</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44840</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>45734</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>46020</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>45670</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>45253</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>44963</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>45006</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>46020</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>45804</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>46196</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>46244</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>45390</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>44896</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>44804</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>44750</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>45568</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>44974</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>45369</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>44952</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>46163</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>45911</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>46183</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         <v>46281</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>44754</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>44732</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>44615</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         <v>44783</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>44754</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>44546</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>44752</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>44484</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>44873</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>44469</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4336,7 +4336,7 @@
         <v>44752</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>44564</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>44578</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>44657</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>44840</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         <v>44620</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>44677</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>44720</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
         <v>44676</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>44817</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>44539</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5139,7 +5139,7 @@
         <v>44704</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>44484</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         <v>44508</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>44783</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         <v>45365</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>45092</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>45378</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>45798</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>45798</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>45567</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>45225</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         <v>45887</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>46035</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>46035</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>45512</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>46041</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>46041</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
         <v>46041</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>45540</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>45817</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
         <v>46050</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>45908</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>45365</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         <v>45911</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         <v>45803</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>46058</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>46058</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>46057</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>46058</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>45915</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7329,7 +7329,7 @@
         <v>45917</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>45917</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>45803</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7548,7 +7548,7 @@
         <v>45917</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>45418</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>45803</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         <v>45924</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>45132</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7913,7 +7913,7 @@
         <v>45671</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7986,7 +7986,7 @@
         <v>45923</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>45923</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8132,7 +8132,7 @@
         <v>46071</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         <v>44965</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>44939</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>45926</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>45929</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         <v>46079</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>46080</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>46080</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8716,7 +8716,7 @@
         <v>45643</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8789,7 +8789,7 @@
         <v>45614</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8862,7 +8862,7 @@
         <v>45568</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         <v>45720</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>45939</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>46096</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9154,7 +9154,7 @@
         <v>44974</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>45911</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>45415</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9373,7 +9373,7 @@
         <v>45610</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         <v>44929</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9519,7 +9519,7 @@
         <v>45958</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>45945</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>45945</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9738,7 +9738,7 @@
         <v>45614</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         <v>46125</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>45728</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         <v>45730</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>45037</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10103,7 +10103,7 @@
         <v>45973</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
         <v>45168</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>44736</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         <v>45356</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10395,7 +10395,7 @@
         <v>45992</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         <v>45992</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         <v>44729</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>45992</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
         <v>45702</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10760,7 +10760,7 @@
         <v>45992</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>45994</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>46000</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10979,7 +10979,7 @@
         <v>46000</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         <v>45664</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
         <v>45938</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>45818</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11271,7 +11271,7 @@
         <v>46140</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11349,7 +11349,7 @@
         <v>45089</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>45797</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11495,7 +11495,7 @@
         <v>45216</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11568,7 +11568,7 @@
         <v>44879</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11641,7 +11641,7 @@
         <v>45512</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11714,7 +11714,7 @@
         <v>46010</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11787,7 +11787,7 @@
         <v>45820</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11860,7 +11860,7 @@
         <v>45820</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         <v>45866</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>45992</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12079,7 +12079,7 @@
         <v>45686</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         <v>45022</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12225,7 +12225,7 @@
         <v>45531</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12298,7 +12298,7 @@
         <v>44876</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12371,7 +12371,7 @@
         <v>44551</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12444,7 +12444,7 @@
         <v>46148</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>44868</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12590,7 +12590,7 @@
         <v>46154</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12663,7 +12663,7 @@
         <v>45531</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12736,7 +12736,7 @@
         <v>45264</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12814,7 +12814,7 @@
         <v>46153</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12887,7 +12887,7 @@
         <v>46154</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12960,7 +12960,7 @@
         <v>45667</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>45525</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         <v>45030</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13179,7 +13179,7 @@
         <v>45950</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13252,7 +13252,7 @@
         <v>45639</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13325,7 +13325,7 @@
         <v>45839</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13398,7 +13398,7 @@
         <v>45516</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>45126</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13544,7 +13544,7 @@
         <v>45168</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13617,7 +13617,7 @@
         <v>45820</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13690,7 +13690,7 @@
         <v>45792</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13763,7 +13763,7 @@
         <v>44952</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13836,7 +13836,7 @@
         <v>45222</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13909,7 +13909,7 @@
         <v>45372</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>45988</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14055,7 +14055,7 @@
         <v>45866</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14128,7 +14128,7 @@
         <v>45810</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14201,7 +14201,7 @@
         <v>45744</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14274,7 +14274,7 @@
         <v>45513</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         <v>45866</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14420,7 +14420,7 @@
         <v>45097</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14493,7 +14493,7 @@
         <v>46174</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>45866</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>46177</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14712,7 +14712,7 @@
         <v>46181</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14785,7 +14785,7 @@
         <v>45070</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14858,7 +14858,7 @@
         <v>46183</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14936,7 +14936,7 @@
         <v>46183</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
         <v>45874</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15087,7 +15087,7 @@
         <v>44655</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>45120</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15233,7 +15233,7 @@
         <v>45167</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15306,7 +15306,7 @@
         <v>44641</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15379,7 +15379,7 @@
         <v>45042</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15452,7 +15452,7 @@
         <v>45884</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15525,7 +15525,7 @@
         <v>45884</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15598,7 +15598,7 @@
         <v>46205</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>46205</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15744,7 +15744,7 @@
         <v>45222</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15817,7 +15817,7 @@
         <v>45684</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15890,7 +15890,7 @@
         <v>45054</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15963,7 +15963,7 @@
         <v>46140</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16041,7 +16041,7 @@
         <v>44613</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16114,7 +16114,7 @@
         <v>46252</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16187,7 +16187,7 @@
         <v>44623</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16260,7 +16260,7 @@
         <v>45442</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16333,7 +16333,7 @@
         <v>45442</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16406,7 +16406,7 @@
         <v>44788</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16479,7 +16479,7 @@
         <v>45198</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16552,7 +16552,7 @@
         <v>44672</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16625,7 +16625,7 @@
         <v>45221</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16698,7 +16698,7 @@
         <v>45126</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16771,7 +16771,7 @@
         <v>45624</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16844,7 +16844,7 @@
         <v>45726</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16917,7 +16917,7 @@
         <v>44974</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16990,7 +16990,7 @@
         <v>46230</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17063,7 +17063,7 @@
         <v>45230</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17136,7 +17136,7 @@
         <v>44915</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>44915</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17282,7 +17282,7 @@
         <v>45238</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17355,7 +17355,7 @@
         <v>44883</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17428,7 +17428,7 @@
         <v>46273</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17501,7 +17501,7 @@
         <v>46231</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17574,7 +17574,7 @@
         <v>45007</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17647,7 +17647,7 @@
         <v>45594</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17720,7 +17720,7 @@
         <v>45195</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17793,7 +17793,7 @@
         <v>46281</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17866,7 +17866,7 @@
         <v>46239</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17939,7 +17939,7 @@
         <v>46240</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18012,7 +18012,7 @@
         <v>44873</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18085,7 +18085,7 @@
         <v>45400</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18158,7 +18158,7 @@
         <v>45882</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18231,7 +18231,7 @@
         <v>45412</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         <v>45429</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18377,7 +18377,7 @@
         <v>44851</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18450,7 +18450,7 @@
         <v>46246</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18523,7 +18523,7 @@
         <v>44914</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18596,7 +18596,7 @@
         <v>44636</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>45974</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18742,7 +18742,7 @@
         <v>45359</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18815,7 +18815,7 @@
         <v>45614</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
         <v>44960</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
         <v>44971</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         <v>44939</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         <v>44981</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>44858</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19253,7 +19253,7 @@
         <v>45453</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19326,7 +19326,7 @@
         <v>45344</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19399,7 +19399,7 @@
         <v>44728</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>45420</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19545,7 +19545,7 @@
         <v>45036</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>45036</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19691,7 +19691,7 @@
         <v>45371</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19764,7 +19764,7 @@
         <v>44903</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19837,7 +19837,7 @@
         <v>45167</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19910,7 +19910,7 @@
         <v>45212</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19983,7 +19983,7 @@
         <v>45684</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20056,7 +20056,7 @@
         <v>44655</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20129,7 +20129,7 @@
         <v>45551</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
         <v>45513</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>45057</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20348,7 +20348,7 @@
         <v>45357</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20421,7 +20421,7 @@
         <v>44974</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20494,7 +20494,7 @@
         <v>45783</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20567,7 +20567,7 @@
         <v>45783</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20640,7 +20640,7 @@
         <v>45783</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20713,7 +20713,7 @@
         <v>45473</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20786,7 +20786,7 @@
         <v>45386</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20859,7 +20859,7 @@
         <v>45712</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20932,7 +20932,7 @@
         <v>44914</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>45719</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21078,7 +21078,7 @@
         <v>45719</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21151,7 +21151,7 @@
         <v>45720</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21224,7 +21224,7 @@
         <v>45720</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21297,7 +21297,7 @@
         <v>45726</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21370,7 +21370,7 @@
         <v>44551</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21443,7 +21443,7 @@
         <v>45351</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>46184</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>46188</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>

--- a/Översikt MELLERUD.xlsx
+++ b/Översikt MELLERUD.xlsx
@@ -601,7 +601,7 @@
         <v>46184</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>46112</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>45614</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>45614</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44840</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>45734</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>46020</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>45670</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>45253</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>44963</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>45006</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>46020</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>45804</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>46196</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>46244</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>45390</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>44896</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>44804</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>44750</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>45568</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>44974</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>45369</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>44952</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>46163</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>45911</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>46183</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         <v>46281</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>44754</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>44732</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>44615</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         <v>44783</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>44754</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>44546</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>44752</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>44484</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>44873</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>44469</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4336,7 +4336,7 @@
         <v>44752</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>44564</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>44578</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>44657</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>44840</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         <v>44620</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>44677</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>44720</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
         <v>44676</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>44817</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>44539</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5139,7 +5139,7 @@
         <v>44704</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>44484</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         <v>44508</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>44783</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         <v>45365</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>45092</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>45378</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>45798</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>45798</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>45567</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>45225</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         <v>45887</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>46035</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>46035</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>45512</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>46041</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>46041</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
         <v>46041</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>45540</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>45817</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
         <v>46050</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>45908</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>45365</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         <v>45911</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         <v>45803</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>46058</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>46058</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>46057</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>46058</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>45915</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7329,7 +7329,7 @@
         <v>45917</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>45917</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>45803</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7548,7 +7548,7 @@
         <v>45917</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>45418</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>45803</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         <v>45924</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>45132</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7913,7 +7913,7 @@
         <v>45671</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7986,7 +7986,7 @@
         <v>45923</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>45923</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8132,7 +8132,7 @@
         <v>46071</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         <v>44965</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>44939</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>45926</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>45929</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         <v>46079</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>46080</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>46080</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8716,7 +8716,7 @@
         <v>45643</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8789,7 +8789,7 @@
         <v>45614</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8862,7 +8862,7 @@
         <v>45568</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         <v>45720</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>45939</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>46096</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9154,7 +9154,7 @@
         <v>44974</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>45911</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>45415</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9373,7 +9373,7 @@
         <v>45610</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         <v>44929</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9519,7 +9519,7 @@
         <v>45958</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>45945</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>45945</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9738,7 +9738,7 @@
         <v>45614</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         <v>46125</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>45728</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         <v>45730</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>45037</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10103,7 +10103,7 @@
         <v>45973</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
         <v>45168</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>44736</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         <v>45356</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10395,7 +10395,7 @@
         <v>45992</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         <v>45992</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         <v>44729</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>45992</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
         <v>45702</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10760,7 +10760,7 @@
         <v>45992</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>45994</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>46000</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10979,7 +10979,7 @@
         <v>46000</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         <v>45664</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
         <v>45938</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>45818</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11271,7 +11271,7 @@
         <v>46140</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11349,7 +11349,7 @@
         <v>45089</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>45797</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11495,7 +11495,7 @@
         <v>45216</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11568,7 +11568,7 @@
         <v>44879</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11641,7 +11641,7 @@
         <v>45512</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11714,7 +11714,7 @@
         <v>46010</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11787,7 +11787,7 @@
         <v>45820</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11860,7 +11860,7 @@
         <v>45820</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         <v>45866</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>45992</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12079,7 +12079,7 @@
         <v>45686</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         <v>45022</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12225,7 +12225,7 @@
         <v>45531</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12298,7 +12298,7 @@
         <v>44876</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12371,7 +12371,7 @@
         <v>44551</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12444,7 +12444,7 @@
         <v>46148</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>44868</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12590,7 +12590,7 @@
         <v>46154</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12663,7 +12663,7 @@
         <v>45531</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12736,7 +12736,7 @@
         <v>45264</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12814,7 +12814,7 @@
         <v>46153</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12887,7 +12887,7 @@
         <v>46154</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12960,7 +12960,7 @@
         <v>45667</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>45525</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         <v>45030</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13179,7 +13179,7 @@
         <v>45950</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13252,7 +13252,7 @@
         <v>45639</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13325,7 +13325,7 @@
         <v>45839</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13398,7 +13398,7 @@
         <v>45516</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>45126</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13544,7 +13544,7 @@
         <v>45168</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13617,7 +13617,7 @@
         <v>45820</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13690,7 +13690,7 @@
         <v>45792</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13763,7 +13763,7 @@
         <v>44952</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13836,7 +13836,7 @@
         <v>45222</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13909,7 +13909,7 @@
         <v>45372</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>45988</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14055,7 +14055,7 @@
         <v>45866</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14128,7 +14128,7 @@
         <v>45810</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14201,7 +14201,7 @@
         <v>45744</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14274,7 +14274,7 @@
         <v>45513</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         <v>45866</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14420,7 +14420,7 @@
         <v>45097</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14493,7 +14493,7 @@
         <v>46174</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>45866</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>46177</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14712,7 +14712,7 @@
         <v>46181</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14785,7 +14785,7 @@
         <v>45070</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14858,7 +14858,7 @@
         <v>46183</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14936,7 +14936,7 @@
         <v>46183</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
         <v>45874</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15087,7 +15087,7 @@
         <v>44655</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>45120</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15233,7 +15233,7 @@
         <v>45167</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15306,7 +15306,7 @@
         <v>44641</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15379,7 +15379,7 @@
         <v>45042</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15452,7 +15452,7 @@
         <v>45884</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15525,7 +15525,7 @@
         <v>45884</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15598,7 +15598,7 @@
         <v>46205</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>46205</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15744,7 +15744,7 @@
         <v>45222</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15817,7 +15817,7 @@
         <v>45684</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15890,7 +15890,7 @@
         <v>45054</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15963,7 +15963,7 @@
         <v>46140</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16041,7 +16041,7 @@
         <v>44613</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16114,7 +16114,7 @@
         <v>46252</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16187,7 +16187,7 @@
         <v>44623</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16260,7 +16260,7 @@
         <v>45442</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16333,7 +16333,7 @@
         <v>45442</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16406,7 +16406,7 @@
         <v>44788</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16479,7 +16479,7 @@
         <v>45198</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16552,7 +16552,7 @@
         <v>44672</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16625,7 +16625,7 @@
         <v>45221</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16698,7 +16698,7 @@
         <v>45126</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16771,7 +16771,7 @@
         <v>45624</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16844,7 +16844,7 @@
         <v>45726</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16917,7 +16917,7 @@
         <v>44974</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16990,7 +16990,7 @@
         <v>46230</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17063,7 +17063,7 @@
         <v>45230</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17136,7 +17136,7 @@
         <v>44915</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>44915</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17282,7 +17282,7 @@
         <v>45238</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17355,7 +17355,7 @@
         <v>44883</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17428,7 +17428,7 @@
         <v>46273</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17501,7 +17501,7 @@
         <v>46231</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17574,7 +17574,7 @@
         <v>45007</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17647,7 +17647,7 @@
         <v>45594</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17720,7 +17720,7 @@
         <v>45195</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17793,7 +17793,7 @@
         <v>46281</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17866,7 +17866,7 @@
         <v>46239</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17939,7 +17939,7 @@
         <v>46240</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18012,7 +18012,7 @@
         <v>44873</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18085,7 +18085,7 @@
         <v>45400</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18158,7 +18158,7 @@
         <v>45882</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18231,7 +18231,7 @@
         <v>45412</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         <v>45429</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18377,7 +18377,7 @@
         <v>44851</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18450,7 +18450,7 @@
         <v>46246</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18523,7 +18523,7 @@
         <v>44914</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18596,7 +18596,7 @@
         <v>44636</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>45974</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18742,7 +18742,7 @@
         <v>45359</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18815,7 +18815,7 @@
         <v>45614</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
         <v>44960</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
         <v>44971</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         <v>44939</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         <v>44981</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>44858</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19253,7 +19253,7 @@
         <v>45453</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19326,7 +19326,7 @@
         <v>45344</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19399,7 +19399,7 @@
         <v>44728</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>45420</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19545,7 +19545,7 @@
         <v>45036</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>45036</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19691,7 +19691,7 @@
         <v>45371</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19764,7 +19764,7 @@
         <v>44903</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19837,7 +19837,7 @@
         <v>45167</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19910,7 +19910,7 @@
         <v>45212</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19983,7 +19983,7 @@
         <v>45684</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20056,7 +20056,7 @@
         <v>44655</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20129,7 +20129,7 @@
         <v>45551</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
         <v>45513</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>45057</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20348,7 +20348,7 @@
         <v>45357</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20421,7 +20421,7 @@
         <v>44974</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20494,7 +20494,7 @@
         <v>45783</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20567,7 +20567,7 @@
         <v>45783</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20640,7 +20640,7 @@
         <v>45783</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20713,7 +20713,7 @@
         <v>45473</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20786,7 +20786,7 @@
         <v>45386</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20859,7 +20859,7 @@
         <v>45712</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20932,7 +20932,7 @@
         <v>44914</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>45719</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21078,7 +21078,7 @@
         <v>45719</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21151,7 +21151,7 @@
         <v>45720</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21224,7 +21224,7 @@
         <v>45720</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21297,7 +21297,7 @@
         <v>45726</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21370,7 +21370,7 @@
         <v>44551</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21443,7 +21443,7 @@
         <v>45351</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>46184</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>46188</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>

--- a/Översikt MELLERUD.xlsx
+++ b/Översikt MELLERUD.xlsx
@@ -601,7 +601,7 @@
         <v>46184</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>46112</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>45614</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 53463-2024</t>
+          <t>A 44523-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45614</v>
+        <v>44840</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -997,19 +997,19 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
         <v>3</v>
       </c>
       <c r="M5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -1021,21 +1021,135 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
       </c>
       <c r="T5" t="n">
+        <v>15</v>
+      </c>
+      <c r="U5" t="n">
+        <v>4</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Aspfjädermossa
+Skirmossa
+Stor skogsbäckmossa
+Blå säckmossa
+Dunmossa
+Sårläka
+Skogshakmossa
+Trind spretmossa
+Blåsippa
+Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 44523-2022 artfynd.xlsx", "A 44523-2022")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 44523-2022 karta.png", "A 44523-2022")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 44523-2022 georefererad karta.tif", "A 44523-2022")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 44523-2022 FSC-klagomål.docx", "A 44523-2022")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 44523-2022 FSC-klagomål mail.docx", "A 44523-2022")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 44523-2022 tillsynsbegäran.docx", "A 44523-2022")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 44523-2022 tillsynsbegäran mail.docx", "A 44523-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 53463-2024</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45614</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="n">
         <v>19</v>
       </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Grålila vaxing
 Uddbräken
@@ -1049,149 +1163,35 @@
 Ängsvaxing agg.</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 53463-2024 artfynd.xlsx", "A 53463-2024")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 53463-2024 karta.png", "A 53463-2024")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 53463-2024 georefererad karta.tif", "A 53463-2024")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 53463-2024 FSC-klagomål.docx", "A 53463-2024")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 53463-2024 FSC-klagomål mail.docx", "A 53463-2024")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 53463-2024 tillsynsbegäran.docx", "A 53463-2024")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 53463-2024 tillsynsbegäran mail.docx", "A 53463-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 44523-2022</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>44840</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" t="n">
-        <v>3</v>
-      </c>
-      <c r="M6" t="n">
-        <v>3</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>6</v>
-      </c>
-      <c r="R6" t="n">
-        <v>3</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="n">
-        <v>15</v>
-      </c>
-      <c r="U6" t="n">
-        <v>4</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Aspfjädermossa
-Skirmossa
-Stor skogsbäckmossa
-Blå säckmossa
-Dunmossa
-Sårläka
-Skogshakmossa
-Trind spretmossa
-Blåsippa
-Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 44523-2022 artfynd.xlsx", "A 44523-2022")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 44523-2022 karta.png", "A 44523-2022")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 44523-2022 georefererad karta.tif", "A 44523-2022")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 44523-2022 FSC-klagomål.docx", "A 44523-2022")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 44523-2022 FSC-klagomål mail.docx", "A 44523-2022")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 44523-2022 tillsynsbegäran.docx", "A 44523-2022")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 44523-2022 tillsynsbegäran mail.docx", "A 44523-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>45734</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 63859-2025</t>
+          <t>A 1491-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46020</v>
+        <v>45670</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1338,45 +1338,157 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="J8" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="n">
-        <v>6</v>
-      </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
         <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>8</v>
       </c>
       <c r="T8" t="n">
+        <v>15</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Uddbräken
+Jungfrulin
+Sårläka
+Nästrot
+Skogsknipprot
+Svart trolldruva
+Taggbräken
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 1491-2025 artfynd.xlsx", "A 1491-2025")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 1491-2025 karta.png", "A 1491-2025")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 1491-2025 georefererad karta.tif", "A 1491-2025")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 1491-2025 FSC-klagomål.docx", "A 1491-2025")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 1491-2025 FSC-klagomål mail.docx", "A 1491-2025")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 1491-2025 tillsynsbegäran.docx", "A 1491-2025")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 1491-2025 tillsynsbegäran mail.docx", "A 1491-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 63859-2025</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>46020</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>6</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>8</v>
+      </c>
+      <c r="T9" t="n">
         <v>14</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U9" t="n">
         <v>14</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Svart askbastborre
 Björksplintborre
@@ -1388,147 +1500,35 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 63859-2025 artfynd.xlsx", "A 63859-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 63859-2025 karta.png", "A 63859-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 63859-2025 georefererad karta.tif", "A 63859-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 63859-2025 FSC-klagomål.docx", "A 63859-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 63859-2025 FSC-klagomål mail.docx", "A 63859-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 63859-2025 tillsynsbegäran.docx", "A 63859-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 63859-2025 tillsynsbegäran mail.docx", "A 63859-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 1491-2025</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45670</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>8</v>
-      </c>
-      <c r="T9" t="n">
-        <v>15</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Uddbräken
-Jungfrulin
-Sårläka
-Nästrot
-Skogsknipprot
-Svart trolldruva
-Taggbräken
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 1491-2025 artfynd.xlsx", "A 1491-2025")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 1491-2025 karta.png", "A 1491-2025")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 1491-2025 georefererad karta.tif", "A 1491-2025")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 1491-2025 FSC-klagomål.docx", "A 1491-2025")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 1491-2025 FSC-klagomål mail.docx", "A 1491-2025")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 1491-2025 tillsynsbegäran.docx", "A 1491-2025")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 1491-2025 tillsynsbegäran mail.docx", "A 1491-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>45253</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>44963</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>45006</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 63857-2025</t>
+          <t>A 25764-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46020</v>
+        <v>45804</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>3</v>
@@ -1905,7 +1905,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1914,21 +1914,129 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
       </c>
       <c r="T13" t="n">
+        <v>5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Guldlockmossa
+Lönnlav
+Rostfläck</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 25764-2025 artfynd.xlsx", "A 25764-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 25764-2025 karta.png", "A 25764-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 25764-2025 georefererad karta.tif", "A 25764-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 25764-2025 FSC-klagomål.docx", "A 25764-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 25764-2025 FSC-klagomål mail.docx", "A 25764-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 25764-2025 tillsynsbegäran.docx", "A 25764-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 25764-2025 tillsynsbegäran mail.docx", "A 25764-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 63857-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>46020</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
+      <c r="T14" t="n">
         <v>6</v>
       </c>
-      <c r="U13" t="n">
+      <c r="U14" t="n">
         <v>6</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Björksplintborre
 Rävticka
@@ -1936,143 +2044,35 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 63857-2025 artfynd.xlsx", "A 63857-2025")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 63857-2025 karta.png", "A 63857-2025")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 63857-2025 georefererad karta.tif", "A 63857-2025")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 63857-2025 FSC-klagomål.docx", "A 63857-2025")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 63857-2025 FSC-klagomål mail.docx", "A 63857-2025")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 63857-2025 tillsynsbegäran.docx", "A 63857-2025")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 63857-2025 tillsynsbegäran mail.docx", "A 63857-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 25764-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45804</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>4</v>
-      </c>
-      <c r="T14" t="n">
-        <v>5</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Guldlockmossa
-Lönnlav
-Rostfläck</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 25764-2025 artfynd.xlsx", "A 25764-2025")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 25764-2025 karta.png", "A 25764-2025")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 25764-2025 georefererad karta.tif", "A 25764-2025")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 25764-2025 FSC-klagomål.docx", "A 25764-2025")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 25764-2025 FSC-klagomål mail.docx", "A 25764-2025")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 25764-2025 tillsynsbegäran.docx", "A 25764-2025")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 25764-2025 tillsynsbegäran mail.docx", "A 25764-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>46196</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>46244</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>45390</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>44896</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>44804</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>44750</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 43349-2024</t>
+          <t>A 10814-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2748,10 +2748,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45568</v>
+        <v>45369</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2763,8 +2763,13 @@
           <t>MELLERUD</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>4.1</v>
+        <v>6.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2773,10 +2778,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2791,7 +2796,7 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2800,687 +2805,682 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Brunfläckig pärlemorfjäril</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 10814-2024 artfynd.xlsx", "A 10814-2024")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 10814-2024 karta.png", "A 10814-2024")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 10814-2024 georefererad karta.tif", "A 10814-2024")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 10814-2024 FSC-klagomål.docx", "A 10814-2024")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 10814-2024 FSC-klagomål mail.docx", "A 10814-2024")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 10814-2024 tillsynsbegäran.docx", "A 10814-2024")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 10814-2024 tillsynsbegäran mail.docx", "A 10814-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 23546-2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
         <v>1</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 23546-2026 artfynd.xlsx", "A 23546-2026")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 23546-2026 karta.png", "A 23546-2026")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 23546-2026 georefererad karta.tif", "A 23546-2026")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 23546-2026 FSC-klagomål.docx", "A 23546-2026")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 23546-2026 FSC-klagomål mail.docx", "A 23546-2026")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 23546-2026 tillsynsbegäran.docx", "A 23546-2026")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 23546-2026 tillsynsbegäran mail.docx", "A 23546-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 8169-2023</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>44974</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Älg</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 8169-2023 artfynd.xlsx", "A 8169-2023")</f>
+        <v/>
+      </c>
+      <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 8169-2023 karta.png", "A 8169-2023")</f>
+        <v/>
+      </c>
+      <c r="Y23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 8169-2023 georefererad karta.tif", "A 8169-2023")</f>
+        <v/>
+      </c>
+      <c r="AA23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 8169-2023 FSC-klagomål.docx", "A 8169-2023")</f>
+        <v/>
+      </c>
+      <c r="AB23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 8169-2023 FSC-klagomål mail.docx", "A 8169-2023")</f>
+        <v/>
+      </c>
+      <c r="AC23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 8169-2023 tillsynsbegäran.docx", "A 8169-2023")</f>
+        <v/>
+      </c>
+      <c r="AD23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 8169-2023 tillsynsbegäran mail.docx", "A 8169-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 43531-2025</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>45911</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>8</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 43531-2025 artfynd.xlsx", "A 43531-2025")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 43531-2025 karta.png", "A 43531-2025")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 43531-2025 georefererad karta.tif", "A 43531-2025")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 43531-2025 FSC-klagomål.docx", "A 43531-2025")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 43531-2025 FSC-klagomål mail.docx", "A 43531-2025")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 43531-2025 tillsynsbegäran.docx", "A 43531-2025")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 43531-2025 tillsynsbegäran mail.docx", "A 43531-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 43349-2024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>45568</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 43349-2024 artfynd.xlsx", "A 43349-2024")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 43349-2024 karta.png", "A 43349-2024")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 43349-2024 georefererad karta.tif", "A 43349-2024")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 43349-2024 FSC-klagomål.docx", "A 43349-2024")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 43349-2024 FSC-klagomål mail.docx", "A 43349-2024")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 43349-2024 tillsynsbegäran.docx", "A 43349-2024")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 43349-2024 tillsynsbegäran mail.docx", "A 43349-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 8169-2023</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>44974</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A 26518-2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
         <v>1</v>
       </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
         <v>1</v>
       </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
+      <c r="R26" t="n">
         <v>1</v>
       </c>
-      <c r="T22" t="n">
+      <c r="S26" t="n">
         <v>1</v>
       </c>
-      <c r="U22" t="n">
+      <c r="T26" t="n">
         <v>1</v>
       </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Älg</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 8169-2023 artfynd.xlsx", "A 8169-2023")</f>
+      <c r="U26" t="n">
+        <v>1</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Rotfingersvamp</t>
+        </is>
+      </c>
+      <c r="W26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 26518-2026 artfynd.xlsx", "A 26518-2026")</f>
         <v/>
       </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 8169-2023 karta.png", "A 8169-2023")</f>
+      <c r="X26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 26518-2026 karta.png", "A 26518-2026")</f>
         <v/>
       </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 8169-2023 georefererad karta.tif", "A 8169-2023")</f>
+      <c r="Y26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 26518-2026 georefererad karta.tif", "A 26518-2026")</f>
         <v/>
       </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 8169-2023 FSC-klagomål.docx", "A 8169-2023")</f>
+      <c r="AA26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 26518-2026 FSC-klagomål.docx", "A 26518-2026")</f>
         <v/>
       </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 8169-2023 FSC-klagomål mail.docx", "A 8169-2023")</f>
+      <c r="AB26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 26518-2026 FSC-klagomål mail.docx", "A 26518-2026")</f>
         <v/>
       </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 8169-2023 tillsynsbegäran.docx", "A 8169-2023")</f>
+      <c r="AC26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 26518-2026 tillsynsbegäran.docx", "A 26518-2026")</f>
         <v/>
       </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 8169-2023 tillsynsbegäran mail.docx", "A 8169-2023")</f>
+      <c r="AD26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 26518-2026 tillsynsbegäran mail.docx", "A 26518-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 10814-2024</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>45369</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 3992-2023</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>44952</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J27" t="n">
         <v>1</v>
       </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
         <v>1</v>
       </c>
-      <c r="R23" t="n">
+      <c r="T27" t="n">
         <v>1</v>
       </c>
-      <c r="S23" t="n">
-        <v>1</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Brunfläckig pärlemorfjäril</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 10814-2024 artfynd.xlsx", "A 10814-2024")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 10814-2024 karta.png", "A 10814-2024")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 10814-2024 georefererad karta.tif", "A 10814-2024")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 10814-2024 FSC-klagomål.docx", "A 10814-2024")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 10814-2024 FSC-klagomål mail.docx", "A 10814-2024")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 10814-2024 tillsynsbegäran.docx", "A 10814-2024")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 10814-2024 tillsynsbegäran mail.docx", "A 10814-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 3992-2023</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>44952</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Fläcknycklar</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 3992-2023 artfynd.xlsx", "A 3992-2023")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 3992-2023 karta.png", "A 3992-2023")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 3992-2023 georefererad karta.tif", "A 3992-2023")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 3992-2023 FSC-klagomål.docx", "A 3992-2023")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 3992-2023 FSC-klagomål mail.docx", "A 3992-2023")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 3992-2023 tillsynsbegäran.docx", "A 3992-2023")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 3992-2023 tillsynsbegäran mail.docx", "A 3992-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 23546-2026</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>46163</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 23546-2026 artfynd.xlsx", "A 23546-2026")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 23546-2026 karta.png", "A 23546-2026")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 23546-2026 georefererad karta.tif", "A 23546-2026")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 23546-2026 FSC-klagomål.docx", "A 23546-2026")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 23546-2026 FSC-klagomål mail.docx", "A 23546-2026")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 23546-2026 tillsynsbegäran.docx", "A 23546-2026")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 23546-2026 tillsynsbegäran mail.docx", "A 23546-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 43531-2025</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>45911</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>8</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>1</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 43531-2025 artfynd.xlsx", "A 43531-2025")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 43531-2025 karta.png", "A 43531-2025")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 43531-2025 georefererad karta.tif", "A 43531-2025")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 43531-2025 FSC-klagomål.docx", "A 43531-2025")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 43531-2025 FSC-klagomål mail.docx", "A 43531-2025")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 43531-2025 tillsynsbegäran.docx", "A 43531-2025")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 43531-2025 tillsynsbegäran mail.docx", "A 43531-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 26518-2026</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>46183</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1</v>
-      </c>
-      <c r="S27" t="n">
-        <v>1</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Rotfingersvamp</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 26518-2026 artfynd.xlsx", "A 26518-2026")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 26518-2026 karta.png", "A 26518-2026")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 26518-2026 georefererad karta.tif", "A 26518-2026")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 26518-2026 FSC-klagomål.docx", "A 26518-2026")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 26518-2026 FSC-klagomål mail.docx", "A 26518-2026")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 26518-2026 tillsynsbegäran.docx", "A 26518-2026")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 26518-2026 tillsynsbegäran mail.docx", "A 26518-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         <v>46281</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>44754</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>44732</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 9008-2022</t>
+          <t>A 32627-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3749,10 +3749,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44615</v>
+        <v>44783</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.1</v>
+        <v>1.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3808,7 +3808,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 32627-2022</t>
+          <t>A 9008-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3822,10 +3822,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44783</v>
+        <v>44615</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3898,7 +3898,7 @@
         <v>44754</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>44546</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 29336-2022</t>
+          <t>A 57805-2021</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4041,10 +4041,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44752</v>
+        <v>44484</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.7</v>
+        <v>11.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4100,7 +4100,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 57805-2021</t>
+          <t>A 29336-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4114,10 +4114,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44484</v>
+        <v>44752</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>11.3</v>
+        <v>1.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4190,7 +4190,7 @@
         <v>44873</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>44469</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4336,7 +4336,7 @@
         <v>44752</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>44564</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>44578</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>44657</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 44530-2022</t>
+          <t>A 9796-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4625,10 +4625,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44840</v>
+        <v>44620</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4684,7 +4684,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 9796-2022</t>
+          <t>A 44530-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4698,10 +4698,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44620</v>
+        <v>44840</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4774,7 +4774,7 @@
         <v>44677</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>44720</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
         <v>44676</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>44817</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>44539</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 21097-2022</t>
+          <t>A 63539-2021</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5136,10 +5136,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44704</v>
+        <v>44508</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5212,7 +5212,7 @@
         <v>44484</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 63539-2021</t>
+          <t>A 21097-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5282,10 +5282,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44508</v>
+        <v>44704</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5341,7 +5341,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 32642-2022</t>
+          <t>A 52269-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5355,10 +5355,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44783</v>
+        <v>44873</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5414,7 +5414,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 10401-2024</t>
+          <t>A 32642-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5428,10 +5428,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45365</v>
+        <v>44783</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>7.6</v>
+        <v>4.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5487,7 +5487,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 26530-2023</t>
+          <t>A 61060-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5501,10 +5501,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45092</v>
+        <v>44915</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.5</v>
+        <v>8.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5560,7 +5560,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 12334-2024</t>
+          <t>A 61061-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5574,10 +5574,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45378</v>
+        <v>44915</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5633,7 +5633,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 24527-2025</t>
+          <t>A 3989-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5647,10 +5647,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45798</v>
+        <v>44952</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5706,7 +5706,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 24533-2025</t>
+          <t>A 9374-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5720,10 +5720,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45798</v>
+        <v>44981</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>5.8</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5779,7 +5779,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 43017-2024</t>
+          <t>A 4054-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5793,10 +5793,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45567</v>
+        <v>45684</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5852,7 +5852,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 52471-2023</t>
+          <t>A 9152-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5866,10 +5866,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45225</v>
+        <v>45357</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5925,7 +5925,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 38888-2025</t>
+          <t>A 19872-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5939,10 +5939,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45887</v>
+        <v>45054</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.2</v>
+        <v>8.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5998,7 +5998,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 1830-2026</t>
+          <t>A 56025-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6012,10 +6012,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46035</v>
+        <v>45624</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6071,7 +6071,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 1827-2026</t>
+          <t>A 51173-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6085,10 +6085,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46035</v>
+        <v>45212</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6144,7 +6144,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 32299-2024</t>
+          <t>A 10100-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45512</v>
+        <v>45719</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6217,7 +6217,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 3250-2026</t>
+          <t>A 8667-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6231,10 +6231,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46041</v>
+        <v>45712</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6290,7 +6290,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 3178-2026</t>
+          <t>A 10357-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46041</v>
+        <v>45720</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6363,7 +6363,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 3201-2026</t>
+          <t>A 10358-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6377,10 +6377,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46041</v>
+        <v>45720</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.2</v>
+        <v>0.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6436,7 +6436,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 37267-2024</t>
+          <t>A 60993-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6450,10 +6450,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45540</v>
+        <v>44914</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 27908-2025</t>
+          <t>A 10097-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6523,10 +6523,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45817</v>
+        <v>45719</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6582,7 +6582,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 5324-2026</t>
+          <t>A 11213-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6596,10 +6596,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46050</v>
+        <v>45726</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6655,7 +6655,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 42723-2025</t>
+          <t>A 9456-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6669,10 +6669,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45908</v>
+        <v>45359</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6728,7 +6728,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 10398-2024</t>
+          <t>A 32549-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6742,10 +6742,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45365</v>
+        <v>45513</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6801,7 +6801,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 43398-2025</t>
+          <t>A 38653-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6815,10 +6815,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45911</v>
+        <v>45884</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>5.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6874,7 +6874,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 25652-2025</t>
+          <t>A 38888-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6888,10 +6888,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45803</v>
+        <v>45887</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6947,7 +6947,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 7117-2026</t>
+          <t>A 24533-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6961,10 +6961,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46058</v>
+        <v>45798</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.8</v>
+        <v>5.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7020,7 +7020,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 7125-2026</t>
+          <t>A 7154-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7030,14 +7030,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46058</v>
+        <v>45344</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 7047-2026</t>
+          <t>A 24527-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7107,10 +7107,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46057</v>
+        <v>45798</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.7</v>
+        <v>3.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7166,7 +7166,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 7120-2026</t>
+          <t>A 43017-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7180,10 +7180,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46058</v>
+        <v>45567</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7239,7 +7239,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 44020-2025</t>
+          <t>A 4416-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7253,10 +7253,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45915</v>
+        <v>45686</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7312,7 +7312,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 44600-2025</t>
+          <t>A 25623-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7326,10 +7326,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45917</v>
+        <v>45803</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>7.2</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7385,7 +7385,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 44573-2025</t>
+          <t>A 25652-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7399,10 +7399,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45917</v>
+        <v>45803</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>5.5</v>
+        <v>0.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7475,7 +7475,7 @@
         <v>45803</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7531,7 +7531,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 44608-2025</t>
+          <t>A 33388-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7545,10 +7545,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45917</v>
+        <v>44788</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7604,7 +7604,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 17685-2024</t>
+          <t>A 24978-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7618,10 +7618,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45418</v>
+        <v>44728</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7677,7 +7677,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 25623-2025</t>
+          <t>A 27908-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7691,10 +7691,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45803</v>
+        <v>45817</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7750,7 +7750,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 45991-2025</t>
+          <t>A 46917-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7764,10 +7764,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45924</v>
+        <v>44851</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>4.4</v>
+        <v>0.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7823,7 +7823,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 33666-2023</t>
+          <t>A 37267-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7837,10 +7837,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45132</v>
+        <v>45540</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.4</v>
+        <v>4.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7896,7 +7896,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 1921-2025</t>
+          <t>A 60395-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7906,14 +7906,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45671</v>
+        <v>45643</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7969,7 +7969,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 45935-2025</t>
+          <t>A 42723-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7983,10 +7983,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45923</v>
+        <v>45908</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 45861-2025</t>
+          <t>A 14596-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8056,10 +8056,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45923</v>
+        <v>44655</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>10.2</v>
+        <v>0.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 9573-2026</t>
+          <t>A 13800-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8129,10 +8129,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46071</v>
+        <v>45007</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>5.2</v>
+        <v>1.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8188,7 +8188,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 6283-2023</t>
+          <t>A 8155-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8202,10 +8202,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44965</v>
+        <v>44974</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8261,7 +8261,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 1883-2023</t>
+          <t>A 17693-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8275,10 +8275,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44939</v>
+        <v>45037</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.4</v>
+        <v>11.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8334,7 +8334,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 46668-2025</t>
+          <t>A 12501-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8348,10 +8348,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45926</v>
+        <v>45730</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8407,7 +8407,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 46872-2025</t>
+          <t>A 11848-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8421,10 +8421,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45929</v>
+        <v>45728</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8480,7 +8480,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 11121-2026</t>
+          <t>A 8165-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8490,14 +8490,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46079</v>
+        <v>44974</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8553,7 +8553,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 11323-2026</t>
+          <t>A 12157-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8567,10 +8567,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46080</v>
+        <v>44636</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>7.3</v>
+        <v>2.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8626,7 +8626,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 11249-2026</t>
+          <t>A 43398-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8640,10 +8640,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46080</v>
+        <v>45911</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8656,7 +8656,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8699,7 +8699,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 60395-2024</t>
+          <t>A 17528-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8709,14 +8709,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45643</v>
+        <v>45415</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8772,7 +8772,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 53317-2024</t>
+          <t>A 52922-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8786,10 +8786,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45614</v>
+        <v>45610</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8845,7 +8845,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 43353-2024</t>
+          <t>A 7228-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8859,10 +8859,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45568</v>
+        <v>45702</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8918,7 +8918,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 10356-2025</t>
+          <t>A 44020-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8932,10 +8932,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45720</v>
+        <v>45915</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8991,7 +8991,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 49718-2025</t>
+          <t>A 44600-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9005,10 +9005,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45939</v>
+        <v>45917</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.1</v>
+        <v>7.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9064,7 +9064,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 13594-2026</t>
+          <t>A 28319-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9074,14 +9074,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46096</v>
+        <v>45818</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9137,7 +9137,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 8165-2023</t>
+          <t>A 44608-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9151,10 +9151,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44974</v>
+        <v>45917</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9210,7 +9210,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 43406-2025</t>
+          <t>A 44573-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9224,10 +9224,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45911</v>
+        <v>45917</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9283,7 +9283,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 17528-2024</t>
+          <t>A 63249-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9297,10 +9297,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45415</v>
+        <v>46010</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9356,7 +9356,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 52922-2024</t>
+          <t>A 51783-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9370,10 +9370,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45610</v>
+        <v>45222</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 334-2023</t>
+          <t>A 28870-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9443,10 +9443,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44929</v>
+        <v>45820</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.8</v>
+        <v>7.9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9502,7 +9502,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 53232-2025</t>
+          <t>A 45861-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9516,10 +9516,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45958</v>
+        <v>45923</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.8</v>
+        <v>10.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9575,7 +9575,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 50478-2025</t>
+          <t>A 45935-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9589,10 +9589,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45945</v>
+        <v>45923</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9648,7 +9648,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 50482-2025</t>
+          <t>A 45991-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9662,10 +9662,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45945</v>
+        <v>45924</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>8.800000000000001</v>
+        <v>4.4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9721,7 +9721,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 53307-2024</t>
+          <t>A 39535-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9735,10 +9735,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45614</v>
+        <v>45551</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2</v>
+        <v>4.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9794,7 +9794,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 18055-2026</t>
+          <t>A 46872-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9808,10 +9808,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46125</v>
+        <v>45929</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>5.2</v>
+        <v>0.4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9867,7 +9867,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 11848-2025</t>
+          <t>A 7443-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9881,10 +9881,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45728</v>
+        <v>44971</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9940,7 +9940,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 12501-2025</t>
+          <t>A 46668-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9954,10 +9954,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45730</v>
+        <v>45926</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10013,7 +10013,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 17693-2023</t>
+          <t>A 10356-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10027,10 +10027,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45037</v>
+        <v>45720</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>11.3</v>
+        <v>0.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10086,7 +10086,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 56026-2025</t>
+          <t>A 32842-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10100,10 +10100,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45973</v>
+        <v>45839</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.2</v>
+        <v>6.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10159,7 +10159,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 40064-2023</t>
+          <t>A 17685-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10173,10 +10173,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45168</v>
+        <v>45418</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10189,7 +10189,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10232,7 +10232,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 26428-2022</t>
+          <t>A 49718-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10246,10 +10246,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44736</v>
+        <v>45939</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10262,7 +10262,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10305,7 +10305,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 8923-2024</t>
+          <t>A 23450-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10319,10 +10319,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45356</v>
+        <v>45792</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10378,7 +10378,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 59808-2025</t>
+          <t>A 35605-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10392,10 +10392,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45992</v>
+        <v>45531</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10451,7 +10451,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 59806-2025</t>
+          <t>A 43406-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10465,10 +10465,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45992</v>
+        <v>45911</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10524,7 +10524,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 25109-2022</t>
+          <t>A 16656-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10538,10 +10538,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44729</v>
+        <v>44672</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10554,7 +10554,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10597,7 +10597,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 59804-2025</t>
+          <t>A 11442-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10611,10 +10611,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45992</v>
+        <v>45372</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10670,7 +10670,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 7228-2025</t>
+          <t>A 15227-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10684,10 +10684,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45702</v>
+        <v>45744</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10700,7 +10700,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10743,7 +10743,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 59802-2025</t>
+          <t>A 26639-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10757,10 +10757,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45992</v>
+        <v>45810</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.8</v>
+        <v>5.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10816,7 +10816,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 60203-2025</t>
+          <t>A 36141-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10830,10 +10830,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45994</v>
+        <v>45866</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10846,7 +10846,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10889,7 +10889,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 61177-2025</t>
+          <t>A 36048-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10899,14 +10899,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46000</v>
+        <v>45866</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10919,7 +10919,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10962,7 +10962,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 61180-2025</t>
+          <t>A 50478-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10976,10 +10976,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46000</v>
+        <v>45945</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 493-2025</t>
+          <t>A 50482-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11049,10 +11049,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45664</v>
+        <v>45945</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11108,7 +11108,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 49449-2025</t>
+          <t>A 53232-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11122,10 +11122,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45938</v>
+        <v>45958</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11138,7 +11138,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11181,7 +11181,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 28319-2025</t>
+          <t>A 1830-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11195,10 +11195,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45818</v>
+        <v>46035</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11211,7 +11211,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11254,7 +11254,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 20573-2026</t>
+          <t>A 36963-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11268,10 +11268,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46140</v>
+        <v>45874</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11283,13 +11283,8 @@
           <t>MELLERUD</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11332,7 +11327,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 25399-2023</t>
+          <t>A 25109-2022</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11342,14 +11337,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45089</v>
+        <v>44729</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11362,7 +11357,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11405,7 +11400,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 24312-2025</t>
+          <t>A 1827-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11419,10 +11414,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45797</v>
+        <v>46035</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11435,7 +11430,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11478,7 +11473,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 50441-2023</t>
+          <t>A 52471-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11492,10 +11487,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45216</v>
+        <v>45225</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11508,7 +11503,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11551,7 +11546,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 53565-2022</t>
+          <t>A 53307-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11565,10 +11560,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44879</v>
+        <v>45614</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11581,7 +11576,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11624,7 +11619,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 32304-2024</t>
+          <t>A 39728-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11638,10 +11633,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45512</v>
+        <v>45167</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11654,7 +11649,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11697,7 +11692,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 63249-2025</t>
+          <t>A 38663-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11711,10 +11706,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46010</v>
+        <v>45884</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11727,7 +11722,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11770,7 +11765,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 28870-2025</t>
+          <t>A 17543-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11784,10 +11779,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45820</v>
+        <v>45036</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11800,7 +11795,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>7.9</v>
+        <v>1.8</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11843,7 +11838,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 28865-2025</t>
+          <t>A 56026-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11857,10 +11852,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45820</v>
+        <v>45973</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11873,7 +11868,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11916,7 +11911,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 36146-2025</t>
+          <t>A 3178-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11930,10 +11925,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45866</v>
+        <v>46041</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11946,7 +11941,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11989,7 +11984,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 59723-2025</t>
+          <t>A 3250-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12003,10 +11998,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45992</v>
+        <v>46041</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12019,7 +12014,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>12.3</v>
+        <v>1.2</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12062,7 +12057,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 4416-2025</t>
+          <t>A 53254-2022</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12076,10 +12071,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45686</v>
+        <v>44876</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12092,7 +12087,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12135,7 +12130,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 15971-2023</t>
+          <t>A 3201-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12149,10 +12144,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45022</v>
+        <v>46041</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12165,7 +12160,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12208,7 +12203,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 35603-2024</t>
+          <t>A 1921-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12222,10 +12217,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45531</v>
+        <v>45671</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12238,7 +12233,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12281,7 +12276,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 53254-2022</t>
+          <t>A 60996-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12295,10 +12290,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44876</v>
+        <v>44914</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12311,7 +12306,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12354,7 +12349,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 73351-2021</t>
+          <t>A 59804-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12368,10 +12363,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44551</v>
+        <v>45992</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12384,7 +12379,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>6.1</v>
+        <v>2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12427,7 +12422,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 21432-2026</t>
+          <t>A 59802-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12441,10 +12436,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46148</v>
+        <v>45992</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12457,7 +12452,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>4.3</v>
+        <v>0.8</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12500,7 +12495,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 51916-2022</t>
+          <t>A 59808-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12510,14 +12505,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44868</v>
+        <v>45992</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12530,7 +12525,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12573,7 +12568,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 22364-2026</t>
+          <t>A 5324-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12587,10 +12582,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46154</v>
+        <v>46050</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12603,7 +12598,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12646,7 +12641,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 35605-2024</t>
+          <t>A 59806-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12660,10 +12655,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45531</v>
+        <v>45992</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12676,7 +12671,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12719,7 +12714,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 61811-2023</t>
+          <t>A 60203-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12733,10 +12728,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45264</v>
+        <v>45994</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12748,13 +12743,8 @@
           <t>MELLERUD</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I154" t="n">
-        <v>7.9</v>
+        <v>1.4</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12797,7 +12787,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 21977-2026</t>
+          <t>A 15323-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12811,10 +12801,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46153</v>
+        <v>45400</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12827,7 +12817,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.5</v>
+        <v>10.6</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12870,7 +12860,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 22337-2026</t>
+          <t>A 10398-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12884,10 +12874,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46154</v>
+        <v>45365</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12900,7 +12890,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12943,7 +12933,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 1369-2025</t>
+          <t>A 61177-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12953,14 +12943,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45667</v>
+        <v>46000</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12973,7 +12963,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13016,7 +13006,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 34415-2024</t>
+          <t>A 61180-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13030,10 +13020,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45525</v>
+        <v>46000</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13046,7 +13036,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>4.3</v>
+        <v>1</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13089,7 +13079,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 16746-2023</t>
+          <t>A 7047-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13103,10 +13093,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45030</v>
+        <v>46057</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13119,7 +13109,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13162,7 +13152,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 51436-2025</t>
+          <t>A 7125-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13176,10 +13166,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45950</v>
+        <v>46058</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13192,7 +13182,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13235,7 +13225,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 59865-2024</t>
+          <t>A 58861-2022</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13249,10 +13239,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45639</v>
+        <v>44903</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13265,7 +13255,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13308,7 +13298,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 32842-2025</t>
+          <t>A 7120-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13322,10 +13312,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45839</v>
+        <v>46058</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13338,7 +13328,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>6.1</v>
+        <v>0.8</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13381,7 +13371,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 32832-2024</t>
+          <t>A 7117-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13395,10 +13385,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45516</v>
+        <v>46058</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13411,7 +13401,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13454,7 +13444,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 33092-2023</t>
+          <t>A 11256-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13468,10 +13458,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45126</v>
+        <v>45726</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13484,7 +13474,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13527,7 +13517,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 40065-2023</t>
+          <t>A 8923-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13541,10 +13531,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45168</v>
+        <v>45356</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13557,7 +13547,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13600,7 +13590,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 28863-2025</t>
+          <t>A 39942-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13614,10 +13604,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45820</v>
+        <v>45167</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13630,7 +13620,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13673,7 +13663,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 23450-2025</t>
+          <t>A 3998-2025</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13687,10 +13677,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45792</v>
+        <v>45684</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13703,7 +13693,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>2.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13746,7 +13736,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 3989-2023</t>
+          <t>A 9573-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13760,10 +13750,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44952</v>
+        <v>46071</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13776,7 +13766,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.5</v>
+        <v>5.2</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13819,7 +13809,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 51783-2023</t>
+          <t>A 11249-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13833,10 +13823,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45222</v>
+        <v>46080</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13849,7 +13839,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13892,7 +13882,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 11442-2024</t>
+          <t>A 11121-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13902,14 +13892,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45372</v>
+        <v>46079</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13922,7 +13912,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13965,7 +13955,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 59269-2025</t>
+          <t>A 32384-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13979,10 +13969,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45988</v>
+        <v>45120</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13995,7 +13985,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14038,7 +14028,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 36141-2025</t>
+          <t>A 11323-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14048,14 +14038,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45866</v>
+        <v>46080</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14068,7 +14058,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.9</v>
+        <v>7.3</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14111,7 +14101,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 26639-2025</t>
+          <t>A 6283-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14125,10 +14115,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45810</v>
+        <v>44965</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14141,7 +14131,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>5.4</v>
+        <v>1</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14184,7 +14174,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 15227-2025</t>
+          <t>A 13594-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14194,14 +14184,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45744</v>
+        <v>46096</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14214,7 +14204,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14257,7 +14247,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 32498-2024</t>
+          <t>A 40064-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14271,10 +14261,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45513</v>
+        <v>45168</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14330,7 +14320,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 36048-2025</t>
+          <t>A 34415-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14344,10 +14334,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45866</v>
+        <v>45525</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14360,7 +14350,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14403,7 +14393,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 27510-2023</t>
+          <t>A 32304-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14417,10 +14407,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45097</v>
+        <v>45512</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14433,7 +14423,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14476,7 +14466,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 25036-2026</t>
+          <t>A 46761-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14490,10 +14480,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46174</v>
+        <v>45198</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14506,7 +14496,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>5.9</v>
+        <v>1.3</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14549,7 +14539,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 36138-2025</t>
+          <t>A 21077-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14563,10 +14553,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45866</v>
+        <v>45057</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14579,7 +14569,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14622,7 +14612,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 25458-2026</t>
+          <t>A 22313-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14636,10 +14626,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46177</v>
+        <v>45070</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14652,7 +14642,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14695,7 +14685,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 25954-2026</t>
+          <t>A 17160-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14709,10 +14699,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46181</v>
+        <v>45412</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14725,7 +14715,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14768,7 +14758,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 22313-2023</t>
+          <t>A 48256-2022</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14782,10 +14772,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45070</v>
+        <v>44858</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14798,7 +14788,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14841,7 +14831,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 26527-2026</t>
+          <t>A 8152-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14855,10 +14845,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46183</v>
+        <v>44974</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14870,13 +14860,8 @@
           <t>MELLERUD</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I183" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14919,7 +14904,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 26536-2026</t>
+          <t>A 18055-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14933,10 +14918,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46183</v>
+        <v>46125</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14948,13 +14933,8 @@
           <t>MELLERUD</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I184" t="n">
-        <v>0.6</v>
+        <v>5.2</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14997,7 +14977,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 36963-2025</t>
+          <t>A 40065-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15011,10 +14991,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45874</v>
+        <v>45168</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15027,7 +15007,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15070,7 +15050,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 14568-2022</t>
+          <t>A 45834-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15084,10 +15064,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44655</v>
+        <v>45195</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15100,7 +15080,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15143,7 +15123,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 32384-2023</t>
+          <t>A 51463-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15157,10 +15137,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45120</v>
+        <v>45221</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15173,7 +15153,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15216,7 +15196,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 39942-2023</t>
+          <t>A 8492-2022</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15230,10 +15210,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45167</v>
+        <v>44613</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15246,7 +15226,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15289,7 +15269,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 12713-2022</t>
+          <t>A 48879-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15303,10 +15283,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>44641</v>
+        <v>45594</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15319,7 +15299,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15362,7 +15342,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 18854-2023</t>
+          <t>A 24312-2025</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15376,10 +15356,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45042</v>
+        <v>45797</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15392,7 +15372,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15435,7 +15415,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 38653-2025</t>
+          <t>A 493-2025</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15449,10 +15429,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45884</v>
+        <v>45664</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15465,7 +15445,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>5.3</v>
+        <v>3.9</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15508,7 +15488,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 38663-2025</t>
+          <t>A 5647-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15522,10 +15502,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45884</v>
+        <v>44960</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15538,7 +15518,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>4.2</v>
+        <v>0.7</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15581,7 +15561,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 29936-2026</t>
+          <t>A 35603-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15595,10 +15575,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46205</v>
+        <v>45531</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15611,7 +15591,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15654,7 +15634,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 29939-2026</t>
+          <t>A 36146-2025</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15668,10 +15648,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46205</v>
+        <v>45866</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15684,7 +15664,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15727,7 +15707,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 51785-2023</t>
+          <t>A 49449-2025</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15741,10 +15721,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45222</v>
+        <v>45938</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15757,7 +15737,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15800,7 +15780,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 3998-2025</t>
+          <t>A 12334-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15814,10 +15794,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45684</v>
+        <v>45378</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15830,7 +15810,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>8.199999999999999</v>
+        <v>2</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15873,7 +15853,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 19872-2023</t>
+          <t>A 12713-2022</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15887,10 +15867,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45054</v>
+        <v>44641</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15903,7 +15883,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>8.4</v>
+        <v>2.9</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15946,7 +15926,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 20578-2026</t>
+          <t>A 11219-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15960,10 +15940,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46140</v>
+        <v>45371</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15975,13 +15955,8 @@
           <t>MELLERUD</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I198" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16024,7 +15999,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 8492-2022</t>
+          <t>A 18205-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16038,10 +16013,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44613</v>
+        <v>45420</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16054,7 +16029,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16097,7 +16072,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 34065-2026</t>
+          <t>A 53565-2022</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16111,10 +16086,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46252</v>
+        <v>44879</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16127,7 +16102,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16170,7 +16145,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 10428-2022</t>
+          <t>A 59723-2025</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16184,10 +16159,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>44623</v>
+        <v>45992</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16200,7 +16175,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.9</v>
+        <v>12.3</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16243,7 +16218,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 21618-2024</t>
+          <t>A 20573-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16257,10 +16232,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45442</v>
+        <v>46140</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16272,8 +16247,13 @@
           <t>MELLERUD</t>
         </is>
       </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I202" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16316,7 +16296,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 21620-2024</t>
+          <t>A 28865-2025</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16330,10 +16310,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45442</v>
+        <v>45820</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16346,7 +16326,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16389,7 +16369,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 33388-2022</t>
+          <t>A 10428-2022</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16403,10 +16383,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>44788</v>
+        <v>44623</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16419,7 +16399,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>8.699999999999999</v>
+        <v>1.9</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16462,7 +16442,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 46761-2023</t>
+          <t>A 21432-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16476,10 +16456,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45198</v>
+        <v>46148</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16492,7 +16472,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16535,7 +16515,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 16656-2022</t>
+          <t>A 54796-2022</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16549,10 +16529,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44672</v>
+        <v>44883</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16565,7 +16545,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16608,7 +16588,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 51463-2023</t>
+          <t>A 21977-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16622,10 +16602,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45221</v>
+        <v>46153</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16638,7 +16618,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16681,7 +16661,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 34116-2023</t>
+          <t>A 53573-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16691,14 +16671,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45126</v>
+        <v>45230</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16711,7 +16691,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16754,7 +16734,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 56025-2024</t>
+          <t>A 22364-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16768,10 +16748,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45624</v>
+        <v>46154</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16784,7 +16764,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16827,7 +16807,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 11256-2025</t>
+          <t>A 22337-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16841,10 +16821,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45726</v>
+        <v>46154</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16857,7 +16837,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16900,7 +16880,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 8155-2023</t>
+          <t>A 34116-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16910,14 +16890,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>44974</v>
+        <v>45126</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16930,7 +16910,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16973,7 +16953,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 31836-2026</t>
+          <t>A 16746-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16987,10 +16967,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46230</v>
+        <v>45030</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17003,7 +16983,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17046,7 +17026,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 53573-2023</t>
+          <t>A 1369-2025</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17060,10 +17040,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45230</v>
+        <v>45667</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17076,7 +17056,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>3.8</v>
+        <v>1.9</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17119,7 +17099,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 61060-2022</t>
+          <t>A 32832-2024</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17133,10 +17113,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>44915</v>
+        <v>45516</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17149,7 +17129,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>8.4</v>
+        <v>1.8</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17192,7 +17172,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 61061-2022</t>
+          <t>A 1883-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17206,10 +17186,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>44915</v>
+        <v>44939</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17222,7 +17202,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>8.5</v>
+        <v>1.4</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17265,7 +17245,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 55391-2023</t>
+          <t>A 1886-2023</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17279,10 +17259,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45238</v>
+        <v>44939</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17295,7 +17275,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17338,7 +17318,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 54796-2022</t>
+          <t>A 59865-2024</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17352,10 +17332,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>44883</v>
+        <v>45639</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17368,7 +17348,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1.5</v>
+        <v>5.9</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17411,7 +17391,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 36960-2026</t>
+          <t>A 51436-2025</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17425,10 +17405,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46273</v>
+        <v>45950</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17441,7 +17421,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>8.1</v>
+        <v>2</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17484,7 +17464,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 31889-2026</t>
+          <t>A 28863-2025</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17498,10 +17478,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46231</v>
+        <v>45820</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17514,7 +17494,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17557,7 +17537,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 13800-2023</t>
+          <t>A 27510-2023</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17571,10 +17551,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45007</v>
+        <v>45097</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17587,7 +17567,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17630,7 +17610,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 48879-2024</t>
+          <t>A 334-2023</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17644,10 +17624,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45594</v>
+        <v>44929</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17660,7 +17640,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17703,7 +17683,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 45834-2023</t>
+          <t>A 32299-2024</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17717,10 +17697,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45195</v>
+        <v>45512</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17733,7 +17713,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17776,7 +17756,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 38251-2026</t>
+          <t>A 59269-2025</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17790,10 +17770,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>46281</v>
+        <v>45988</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17806,7 +17786,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>0.8</v>
+        <v>3.5</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17849,7 +17829,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 32520-2026</t>
+          <t>A 25036-2026</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17863,10 +17843,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46239</v>
+        <v>46174</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17879,7 +17859,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>3.6</v>
+        <v>5.9</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17922,7 +17902,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 32691-2026</t>
+          <t>A 36138-2025</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17936,10 +17916,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46240</v>
+        <v>45866</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17952,7 +17932,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17995,7 +17975,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 52269-2022</t>
+          <t>A 25458-2026</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18009,10 +17989,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>44873</v>
+        <v>46177</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18025,7 +18005,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>4.6</v>
+        <v>2.1</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18068,7 +18048,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 15323-2024</t>
+          <t>A 32498-2024</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18082,10 +18062,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45400</v>
+        <v>45513</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18098,7 +18078,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>10.6</v>
+        <v>1.3</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18141,7 +18121,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 38040-2025</t>
+          <t>A 43353-2024</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18155,10 +18135,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45882</v>
+        <v>45568</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18171,7 +18151,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18214,7 +18194,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 17160-2024</t>
+          <t>A 51916-2022</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18224,14 +18204,14 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45412</v>
+        <v>44868</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18244,7 +18224,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18287,7 +18267,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 19545-2024</t>
+          <t>A 25954-2026</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18301,10 +18281,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45429</v>
+        <v>46181</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18317,7 +18297,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18360,7 +18340,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 46917-2022</t>
+          <t>A 26536-2026</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18374,10 +18354,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>44851</v>
+        <v>46183</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18389,8 +18369,13 @@
           <t>MELLERUD</t>
         </is>
       </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I231" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18433,7 +18418,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 33450-2026</t>
+          <t>A 33666-2023</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18447,10 +18432,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>46246</v>
+        <v>45132</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18463,7 +18448,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18506,7 +18491,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 60996-2022</t>
+          <t>A 26527-2026</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18520,10 +18505,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>44914</v>
+        <v>46183</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18535,8 +18520,13 @@
           <t>MELLERUD</t>
         </is>
       </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I233" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18579,7 +18569,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 12157-2022</t>
+          <t>A 51785-2023</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18589,14 +18579,14 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>44636</v>
+        <v>45222</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18609,7 +18599,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18652,7 +18642,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 56349-2025</t>
+          <t>A 33092-2023</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18666,10 +18656,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45974</v>
+        <v>45126</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18682,7 +18672,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18725,7 +18715,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 9456-2024</t>
+          <t>A 55391-2023</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18739,10 +18729,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45359</v>
+        <v>45238</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18755,7 +18745,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18798,7 +18788,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 53270-2024</t>
+          <t>A 15971-2023</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18812,10 +18802,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45614</v>
+        <v>45022</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18828,7 +18818,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18871,7 +18861,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 5647-2023</t>
+          <t>A 53317-2024</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18885,10 +18875,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>44960</v>
+        <v>45614</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18901,7 +18891,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18944,7 +18934,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 7443-2023</t>
+          <t>A 73351-2021</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18958,10 +18948,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>44971</v>
+        <v>44551</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18974,7 +18964,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>0.6</v>
+        <v>6.1</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -19017,7 +19007,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 1886-2023</t>
+          <t>A 20578-2026</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -19031,10 +19021,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>44939</v>
+        <v>46140</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19044,6 +19034,11 @@
       <c r="G240" t="inlineStr">
         <is>
           <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I240" t="n">
@@ -19090,7 +19085,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 9374-2023</t>
+          <t>A 26428-2022</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -19104,10 +19099,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>44981</v>
+        <v>44736</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19120,7 +19115,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -19163,7 +19158,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 48256-2022</t>
+          <t>A 29936-2026</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19177,10 +19172,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>44858</v>
+        <v>46205</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19193,7 +19188,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19236,7 +19231,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 23238-2024</t>
+          <t>A 29939-2026</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19250,10 +19245,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45453</v>
+        <v>46205</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19266,7 +19261,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19309,7 +19304,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 7154-2024</t>
+          <t>A 34065-2026</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19319,14 +19314,14 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45344</v>
+        <v>46252</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19339,7 +19334,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19382,7 +19377,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 24978-2022</t>
+          <t>A 21618-2024</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19396,10 +19391,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>44728</v>
+        <v>45442</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19412,7 +19407,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19455,7 +19450,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 18205-2024</t>
+          <t>A 21620-2024</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19469,10 +19464,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45420</v>
+        <v>45442</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19485,7 +19480,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19528,7 +19523,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 17543-2023</t>
+          <t>A 26530-2023</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19542,10 +19537,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45036</v>
+        <v>45092</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19558,7 +19553,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19601,7 +19596,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 17538-2023</t>
+          <t>A 18854-2023</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19615,10 +19610,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45036</v>
+        <v>45042</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19631,7 +19626,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19674,7 +19669,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 11219-2024</t>
+          <t>A 14568-2022</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19688,10 +19683,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45371</v>
+        <v>44655</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19704,7 +19699,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19747,7 +19742,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 58861-2022</t>
+          <t>A 61811-2023</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19761,10 +19756,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>44903</v>
+        <v>45264</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19776,8 +19771,13 @@
           <t>MELLERUD</t>
         </is>
       </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I250" t="n">
-        <v>4.8</v>
+        <v>7.9</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19820,7 +19820,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 39728-2023</t>
+          <t>A 25399-2023</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19830,14 +19830,14 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>45167</v>
+        <v>45089</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -19893,7 +19893,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 51173-2023</t>
+          <t>A 23238-2024</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19907,10 +19907,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45212</v>
+        <v>45453</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19923,7 +19923,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19966,7 +19966,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 4054-2025</t>
+          <t>A 53270-2024</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19980,10 +19980,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45684</v>
+        <v>45614</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19996,7 +19996,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -20039,7 +20039,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 14596-2022</t>
+          <t>A 17538-2023</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -20053,10 +20053,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>44655</v>
+        <v>45036</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20069,7 +20069,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -20112,7 +20112,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 39535-2024</t>
+          <t>A 31836-2026</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20126,10 +20126,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45551</v>
+        <v>46230</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20142,7 +20142,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>4.7</v>
+        <v>0.7</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20185,7 +20185,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 32549-2024</t>
+          <t>A 19545-2024</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20199,10 +20199,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45513</v>
+        <v>45429</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20215,7 +20215,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20258,7 +20258,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 21077-2023</t>
+          <t>A 36960-2026</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -20272,10 +20272,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>45057</v>
+        <v>46273</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20288,7 +20288,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>1.3</v>
+        <v>8.1</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20331,7 +20331,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 9152-2024</t>
+          <t>A 50441-2023</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20345,10 +20345,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45357</v>
+        <v>45216</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20361,7 +20361,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20404,7 +20404,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 8152-2023</t>
+          <t>A 10401-2024</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20418,10 +20418,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>44974</v>
+        <v>45365</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20434,7 +20434,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>1.4</v>
+        <v>7.6</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20477,7 +20477,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 21698-2025</t>
+          <t>A 31889-2026</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -20491,10 +20491,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45783</v>
+        <v>46231</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20507,7 +20507,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -20550,7 +20550,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 21678-2025</t>
+          <t>A 38251-2026</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -20564,10 +20564,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>45783</v>
+        <v>46281</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20580,7 +20580,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -20640,7 +20640,7 @@
         <v>45783</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 27342-2024</t>
+          <t>A 21678-2025</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -20710,10 +20710,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>45473</v>
+        <v>45783</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20726,7 +20726,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -20769,7 +20769,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 13313-2024</t>
+          <t>A 21698-2025</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -20783,10 +20783,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>45386</v>
+        <v>45783</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20799,7 +20799,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -20842,7 +20842,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 8667-2025</t>
+          <t>A 13313-2024</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -20856,10 +20856,10 @@
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>45712</v>
+        <v>45386</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20872,7 +20872,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -20915,7 +20915,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>A 60993-2022</t>
+          <t>A 32520-2026</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -20929,10 +20929,10 @@
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>44914</v>
+        <v>46239</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20945,7 +20945,7 @@
         </is>
       </c>
       <c r="I266" t="n">
-        <v>0.6</v>
+        <v>3.6</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -20988,7 +20988,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>A 10100-2025</t>
+          <t>A 32691-2026</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -21002,10 +21002,10 @@
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>45719</v>
+        <v>46240</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21018,7 +21018,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -21061,7 +21061,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>A 10097-2025</t>
+          <t>A 27342-2024</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -21075,10 +21075,10 @@
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>45719</v>
+        <v>45473</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21091,7 +21091,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -21134,7 +21134,7 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>A 10357-2025</t>
+          <t>A 38040-2025</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -21148,10 +21148,10 @@
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>45720</v>
+        <v>45882</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21164,7 +21164,7 @@
         </is>
       </c>
       <c r="I269" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -21207,7 +21207,7 @@
     <row r="270" ht="15" customHeight="1">
       <c r="A270" t="inlineStr">
         <is>
-          <t>A 10358-2025</t>
+          <t>A 33450-2026</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -21221,10 +21221,10 @@
         </is>
       </c>
       <c r="D270" s="1" t="n">
-        <v>45720</v>
+        <v>46246</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21237,7 +21237,7 @@
         </is>
       </c>
       <c r="I270" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -21280,7 +21280,7 @@
     <row r="271" ht="15" customHeight="1">
       <c r="A271" t="inlineStr">
         <is>
-          <t>A 11213-2025</t>
+          <t>A 56349-2025</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -21294,10 +21294,10 @@
         </is>
       </c>
       <c r="D271" s="1" t="n">
-        <v>45726</v>
+        <v>45974</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21310,7 +21310,7 @@
         </is>
       </c>
       <c r="I271" t="n">
-        <v>4.8</v>
+        <v>1.5</v>
       </c>
       <c r="J271" t="n">
         <v>0</v>
@@ -21370,7 +21370,7 @@
         <v>44551</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21443,7 +21443,7 @@
         <v>45351</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>46184</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>46188</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>

--- a/Översikt MELLERUD.xlsx
+++ b/Översikt MELLERUD.xlsx
@@ -601,7 +601,7 @@
         <v>46184</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>46112</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>45614</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>44840</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>45614</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>45734</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 1491-2025</t>
+          <t>A 63859-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45670</v>
+        <v>46020</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1338,45 +1338,157 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>1</v>
       </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3</v>
-      </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>8</v>
       </c>
       <c r="T8" t="n">
+        <v>14</v>
+      </c>
+      <c r="U8" t="n">
+        <v>14</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Svart askbastborre
+Björksplintborre
+Fällmossa
+Guldlockmossa
+Platt fjädermossa
+Slanklav
+Traslav
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 63859-2025 artfynd.xlsx", "A 63859-2025")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 63859-2025 karta.png", "A 63859-2025")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 63859-2025 georefererad karta.tif", "A 63859-2025")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 63859-2025 FSC-klagomål.docx", "A 63859-2025")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 63859-2025 FSC-klagomål mail.docx", "A 63859-2025")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 63859-2025 tillsynsbegäran.docx", "A 63859-2025")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 63859-2025 tillsynsbegäran mail.docx", "A 63859-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 1491-2025</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45670</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>8</v>
+      </c>
+      <c r="T9" t="n">
         <v>15</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U9" t="n">
         <v>2</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Uddbräken
 Jungfrulin
@@ -1388,147 +1500,35 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 1491-2025 artfynd.xlsx", "A 1491-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 1491-2025 karta.png", "A 1491-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 1491-2025 georefererad karta.tif", "A 1491-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 1491-2025 FSC-klagomål.docx", "A 1491-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 1491-2025 FSC-klagomål mail.docx", "A 1491-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 1491-2025 tillsynsbegäran.docx", "A 1491-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 1491-2025 tillsynsbegäran mail.docx", "A 1491-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 63859-2025</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>46020</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>6</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>8</v>
-      </c>
-      <c r="T9" t="n">
-        <v>14</v>
-      </c>
-      <c r="U9" t="n">
-        <v>14</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Svart askbastborre
-Björksplintborre
-Fällmossa
-Guldlockmossa
-Platt fjädermossa
-Slanklav
-Traslav
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 63859-2025 artfynd.xlsx", "A 63859-2025")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 63859-2025 karta.png", "A 63859-2025")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 63859-2025 georefererad karta.tif", "A 63859-2025")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 63859-2025 FSC-klagomål.docx", "A 63859-2025")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 63859-2025 FSC-klagomål mail.docx", "A 63859-2025")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 63859-2025 tillsynsbegäran.docx", "A 63859-2025")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 63859-2025 tillsynsbegäran mail.docx", "A 63859-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>45253</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>44963</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>45006</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 25764-2025</t>
+          <t>A 63857-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45804</v>
+        <v>46020</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>3</v>
@@ -1905,7 +1905,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1914,21 +1914,129 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
       </c>
       <c r="T13" t="n">
+        <v>6</v>
+      </c>
+      <c r="U13" t="n">
+        <v>6</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Björksplintborre
+Rävticka
+Trådticka
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 63857-2025 artfynd.xlsx", "A 63857-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 63857-2025 karta.png", "A 63857-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 63857-2025 georefererad karta.tif", "A 63857-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 63857-2025 FSC-klagomål.docx", "A 63857-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 63857-2025 FSC-klagomål mail.docx", "A 63857-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 63857-2025 tillsynsbegäran.docx", "A 63857-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 63857-2025 tillsynsbegäran mail.docx", "A 63857-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 25764-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45804</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
+      <c r="T14" t="n">
         <v>5</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Ask
 Guldlockmossa
@@ -1936,143 +2044,35 @@
 Rostfläck</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 25764-2025 artfynd.xlsx", "A 25764-2025")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 25764-2025 karta.png", "A 25764-2025")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 25764-2025 georefererad karta.tif", "A 25764-2025")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 25764-2025 FSC-klagomål.docx", "A 25764-2025")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 25764-2025 FSC-klagomål mail.docx", "A 25764-2025")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 25764-2025 tillsynsbegäran.docx", "A 25764-2025")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 25764-2025 tillsynsbegäran mail.docx", "A 25764-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 63857-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>46020</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>4</v>
-      </c>
-      <c r="T14" t="n">
-        <v>6</v>
-      </c>
-      <c r="U14" t="n">
-        <v>6</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Björksplintborre
-Rävticka
-Trådticka
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 63857-2025 artfynd.xlsx", "A 63857-2025")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 63857-2025 karta.png", "A 63857-2025")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 63857-2025 georefererad karta.tif", "A 63857-2025")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 63857-2025 FSC-klagomål.docx", "A 63857-2025")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 63857-2025 FSC-klagomål mail.docx", "A 63857-2025")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 63857-2025 tillsynsbegäran.docx", "A 63857-2025")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 63857-2025 tillsynsbegäran mail.docx", "A 63857-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>46196</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>46244</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>45390</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>44896</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>44804</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>44750</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 10814-2024</t>
+          <t>A 43349-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2748,10 +2748,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45369</v>
+        <v>45568</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2763,13 +2763,8 @@
           <t>MELLERUD</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>6.6</v>
+        <v>4.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2778,10 +2773,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2796,7 +2791,7 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2805,682 +2800,687 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 43349-2024 artfynd.xlsx", "A 43349-2024")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 43349-2024 karta.png", "A 43349-2024")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 43349-2024 georefererad karta.tif", "A 43349-2024")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 43349-2024 FSC-klagomål.docx", "A 43349-2024")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 43349-2024 FSC-klagomål mail.docx", "A 43349-2024")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 43349-2024 tillsynsbegäran.docx", "A 43349-2024")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 43349-2024 tillsynsbegäran mail.docx", "A 43349-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 8169-2023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>44974</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 8169-2023 artfynd.xlsx", "A 8169-2023")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 8169-2023 karta.png", "A 8169-2023")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 8169-2023 georefererad karta.tif", "A 8169-2023")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 8169-2023 FSC-klagomål.docx", "A 8169-2023")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 8169-2023 FSC-klagomål mail.docx", "A 8169-2023")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 8169-2023 tillsynsbegäran.docx", "A 8169-2023")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 8169-2023 tillsynsbegäran mail.docx", "A 8169-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 10814-2024</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>45369</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 10814-2024 artfynd.xlsx", "A 10814-2024")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 10814-2024 karta.png", "A 10814-2024")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 10814-2024 georefererad karta.tif", "A 10814-2024")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 10814-2024 FSC-klagomål.docx", "A 10814-2024")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 10814-2024 FSC-klagomål mail.docx", "A 10814-2024")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 10814-2024 tillsynsbegäran.docx", "A 10814-2024")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 10814-2024 tillsynsbegäran mail.docx", "A 10814-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 3992-2023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>44952</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 3992-2023 artfynd.xlsx", "A 3992-2023")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 3992-2023 karta.png", "A 3992-2023")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 3992-2023 georefererad karta.tif", "A 3992-2023")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 3992-2023 FSC-klagomål.docx", "A 3992-2023")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 3992-2023 FSC-klagomål mail.docx", "A 3992-2023")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 3992-2023 tillsynsbegäran.docx", "A 3992-2023")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 3992-2023 tillsynsbegäran mail.docx", "A 3992-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>A 23546-2026</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
         <v>46163</v>
       </c>
-      <c r="E22" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
+      <c r="E25" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
         <v>3.6</v>
       </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
         <v>1</v>
       </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
         <v>1</v>
       </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
         <v>1</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T25" t="n">
         <v>3</v>
       </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Lunglav</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 23546-2026 artfynd.xlsx", "A 23546-2026")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 23546-2026 karta.png", "A 23546-2026")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 23546-2026 georefererad karta.tif", "A 23546-2026")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 23546-2026 FSC-klagomål.docx", "A 23546-2026")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 23546-2026 FSC-klagomål mail.docx", "A 23546-2026")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 23546-2026 tillsynsbegäran.docx", "A 23546-2026")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 23546-2026 tillsynsbegäran mail.docx", "A 23546-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 8169-2023</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>44974</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A 43531-2025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>45911</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>8</v>
+      </c>
+      <c r="J26" t="n">
         <v>1</v>
       </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
         <v>1</v>
       </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
+      <c r="T26" t="n">
         <v>1</v>
       </c>
-      <c r="T23" t="n">
-        <v>1</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Älg</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 8169-2023 artfynd.xlsx", "A 8169-2023")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 8169-2023 karta.png", "A 8169-2023")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 8169-2023 georefererad karta.tif", "A 8169-2023")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 8169-2023 FSC-klagomål.docx", "A 8169-2023")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 8169-2023 FSC-klagomål mail.docx", "A 8169-2023")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 8169-2023 tillsynsbegäran.docx", "A 8169-2023")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 8169-2023 tillsynsbegäran mail.docx", "A 8169-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 43531-2025</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>45911</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>8</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Kungsfågel</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 43531-2025 artfynd.xlsx", "A 43531-2025")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 43531-2025 karta.png", "A 43531-2025")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 43531-2025 georefererad karta.tif", "A 43531-2025")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 43531-2025 FSC-klagomål.docx", "A 43531-2025")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 43531-2025 FSC-klagomål mail.docx", "A 43531-2025")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 43531-2025 tillsynsbegäran.docx", "A 43531-2025")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 43531-2025 tillsynsbegäran mail.docx", "A 43531-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 43349-2024</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>45568</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 26518-2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>MELLERUD</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
         <v>1</v>
       </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
         <v>1</v>
       </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
+      <c r="R27" t="n">
         <v>1</v>
       </c>
-      <c r="T25" t="n">
+      <c r="S27" t="n">
         <v>1</v>
       </c>
-      <c r="U25" t="n">
+      <c r="T27" t="n">
         <v>1</v>
       </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Älg</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 43349-2024 artfynd.xlsx", "A 43349-2024")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 43349-2024 karta.png", "A 43349-2024")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 43349-2024 georefererad karta.tif", "A 43349-2024")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 43349-2024 FSC-klagomål.docx", "A 43349-2024")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 43349-2024 FSC-klagomål mail.docx", "A 43349-2024")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 43349-2024 tillsynsbegäran.docx", "A 43349-2024")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 43349-2024 tillsynsbegäran mail.docx", "A 43349-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 26518-2026</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>46183</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
+      <c r="U27" t="n">
         <v>1</v>
       </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1</v>
-      </c>
-      <c r="S26" t="n">
-        <v>1</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Rotfingersvamp</t>
         </is>
       </c>
-      <c r="W26">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 26518-2026 artfynd.xlsx", "A 26518-2026")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 26518-2026 karta.png", "A 26518-2026")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 26518-2026 georefererad karta.tif", "A 26518-2026")</f>
         <v/>
       </c>
-      <c r="AA26">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 26518-2026 FSC-klagomål.docx", "A 26518-2026")</f>
         <v/>
       </c>
-      <c r="AB26">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 26518-2026 FSC-klagomål mail.docx", "A 26518-2026")</f>
         <v/>
       </c>
-      <c r="AC26">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 26518-2026 tillsynsbegäran.docx", "A 26518-2026")</f>
         <v/>
       </c>
-      <c r="AD26">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 26518-2026 tillsynsbegäran mail.docx", "A 26518-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 3992-2023</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>44952</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>MELLERUD</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>1</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/artfynd/A 3992-2023 artfynd.xlsx", "A 3992-2023")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor/A 3992-2023 karta.png", "A 3992-2023")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/kartor_geotiff/A 3992-2023 georefererad karta.tif", "A 3992-2023")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomål/A 3992-2023 FSC-klagomål.docx", "A 3992-2023")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/klagomålsmail/A 3992-2023 FSC-klagomål mail.docx", "A 3992-2023")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsyn/A 3992-2023 tillsynsbegäran.docx", "A 3992-2023")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1461/tillsynsmail/A 3992-2023 tillsynsbegäran mail.docx", "A 3992-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         <v>46281</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>44754</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>44732</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 32627-2022</t>
+          <t>A 9008-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3749,10 +3749,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44783</v>
+        <v>44615</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3808,7 +3808,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 9008-2022</t>
+          <t>A 32627-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3822,10 +3822,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44615</v>
+        <v>44783</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.1</v>
+        <v>1.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3898,7 +3898,7 @@
         <v>44754</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>44546</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 57805-2021</t>
+          <t>A 29336-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4041,10 +4041,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44484</v>
+        <v>44752</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>11.3</v>
+        <v>1.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4100,7 +4100,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 29336-2022</t>
+          <t>A 57805-2021</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4114,10 +4114,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44752</v>
+        <v>44484</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.7</v>
+        <v>11.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4190,7 +4190,7 @@
         <v>44873</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>44469</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4336,7 +4336,7 @@
         <v>44752</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>44564</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>44578</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>44657</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>44620</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         <v>44840</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>44677</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>44720</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
         <v>44676</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>44817</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>44539</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 63539-2021</t>
+          <t>A 21097-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5136,10 +5136,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44508</v>
+        <v>44704</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5212,7 +5212,7 @@
         <v>44484</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 21097-2022</t>
+          <t>A 63539-2021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5282,10 +5282,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44704</v>
+        <v>44508</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5341,7 +5341,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 52269-2022</t>
+          <t>A 32642-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5355,10 +5355,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44873</v>
+        <v>44783</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5414,7 +5414,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 32642-2022</t>
+          <t>A 10401-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5428,10 +5428,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44783</v>
+        <v>45365</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>4.2</v>
+        <v>7.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5487,7 +5487,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 61060-2022</t>
+          <t>A 26530-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5501,10 +5501,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44915</v>
+        <v>45092</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>8.4</v>
+        <v>2.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5560,7 +5560,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 61061-2022</t>
+          <t>A 12334-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5574,10 +5574,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44915</v>
+        <v>45378</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5633,7 +5633,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 3989-2023</t>
+          <t>A 8667-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5647,10 +5647,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44952</v>
+        <v>45712</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5706,7 +5706,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 9374-2023</t>
+          <t>A 60993-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5720,10 +5720,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44981</v>
+        <v>44914</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5779,7 +5779,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 4054-2025</t>
+          <t>A 10100-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5793,10 +5793,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45684</v>
+        <v>45719</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5852,7 +5852,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 9152-2024</t>
+          <t>A 10097-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5866,10 +5866,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45357</v>
+        <v>45719</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5925,7 +5925,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 19872-2023</t>
+          <t>A 10357-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5939,10 +5939,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45054</v>
+        <v>45720</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>8.4</v>
+        <v>0.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5998,7 +5998,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 56025-2024</t>
+          <t>A 10358-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6012,10 +6012,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45624</v>
+        <v>45720</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6071,7 +6071,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 51173-2023</t>
+          <t>A 11213-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6085,10 +6085,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45212</v>
+        <v>45726</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6144,7 +6144,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 10100-2025</t>
+          <t>A 52471-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45719</v>
+        <v>45225</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6217,7 +6217,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 8667-2025</t>
+          <t>A 24527-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6231,10 +6231,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45712</v>
+        <v>45798</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6290,7 +6290,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 10357-2025</t>
+          <t>A 24533-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45720</v>
+        <v>45798</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.9</v>
+        <v>5.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6363,7 +6363,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 10358-2025</t>
+          <t>A 43017-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6377,10 +6377,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45720</v>
+        <v>45567</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6436,7 +6436,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 60993-2022</t>
+          <t>A 38888-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6450,10 +6450,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44914</v>
+        <v>45887</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 10097-2025</t>
+          <t>A 32299-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6523,10 +6523,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45719</v>
+        <v>45512</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6582,7 +6582,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 11213-2025</t>
+          <t>A 25652-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6596,10 +6596,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45726</v>
+        <v>45803</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6655,7 +6655,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 9456-2024</t>
+          <t>A 25635-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6669,10 +6669,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45359</v>
+        <v>45803</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6728,7 +6728,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 32549-2024</t>
+          <t>A 25623-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6742,10 +6742,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45513</v>
+        <v>45803</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 38653-2025</t>
+          <t>A 27908-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6815,10 +6815,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45884</v>
+        <v>45817</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>5.3</v>
+        <v>2.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6874,7 +6874,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 38888-2025</t>
+          <t>A 60395-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6884,14 +6884,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45887</v>
+        <v>45643</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6947,7 +6947,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 24533-2025</t>
+          <t>A 42723-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6961,10 +6961,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45798</v>
+        <v>45908</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>5.8</v>
+        <v>2.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7020,7 +7020,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 7154-2024</t>
+          <t>A 37267-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7030,14 +7030,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45344</v>
+        <v>45540</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.9</v>
+        <v>4.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7093,7 +7093,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 24527-2025</t>
+          <t>A 8165-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7107,10 +7107,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45798</v>
+        <v>44974</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.6</v>
+        <v>1.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7166,7 +7166,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 43017-2024</t>
+          <t>A 17528-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7180,10 +7180,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45567</v>
+        <v>45415</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7239,7 +7239,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 4416-2025</t>
+          <t>A 52922-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7253,10 +7253,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45686</v>
+        <v>45610</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7312,7 +7312,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 25623-2025</t>
+          <t>A 11848-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7326,10 +7326,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45803</v>
+        <v>45728</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7385,7 +7385,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 25652-2025</t>
+          <t>A 43398-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7399,10 +7399,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45803</v>
+        <v>45911</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7458,7 +7458,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 25635-2025</t>
+          <t>A 12501-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7472,10 +7472,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45803</v>
+        <v>45730</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7531,7 +7531,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 33388-2022</t>
+          <t>A 17693-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7545,10 +7545,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44788</v>
+        <v>45037</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>8.699999999999999</v>
+        <v>11.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7604,7 +7604,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 24978-2022</t>
+          <t>A 10398-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7618,10 +7618,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44728</v>
+        <v>45365</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7677,7 +7677,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 27908-2025</t>
+          <t>A 1830-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7691,10 +7691,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45817</v>
+        <v>46035</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7750,7 +7750,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 46917-2022</t>
+          <t>A 1827-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7764,10 +7764,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44851</v>
+        <v>46035</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7823,7 +7823,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 37267-2024</t>
+          <t>A 7228-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7837,10 +7837,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45540</v>
+        <v>45702</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7896,7 +7896,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 60395-2024</t>
+          <t>A 28319-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7906,14 +7906,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45643</v>
+        <v>45818</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7969,7 +7969,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 42723-2025</t>
+          <t>A 28870-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7983,10 +7983,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45908</v>
+        <v>45820</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.4</v>
+        <v>7.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 14596-2022</t>
+          <t>A 17685-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8056,10 +8056,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44655</v>
+        <v>45418</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8115,7 +8115,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 13800-2023</t>
+          <t>A 44020-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8129,10 +8129,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45007</v>
+        <v>45915</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8188,7 +8188,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 8155-2023</t>
+          <t>A 3250-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8202,10 +8202,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44974</v>
+        <v>46041</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8261,7 +8261,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 17693-2023</t>
+          <t>A 44600-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8275,10 +8275,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45037</v>
+        <v>45917</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>11.3</v>
+        <v>7.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8334,7 +8334,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 12501-2025</t>
+          <t>A 33666-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8348,10 +8348,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45730</v>
+        <v>45132</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8407,7 +8407,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 11848-2025</t>
+          <t>A 44573-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8421,10 +8421,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45728</v>
+        <v>45917</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8480,7 +8480,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 8165-2023</t>
+          <t>A 1921-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8494,10 +8494,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44974</v>
+        <v>45671</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8553,7 +8553,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 12157-2022</t>
+          <t>A 44608-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8563,14 +8563,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44636</v>
+        <v>45917</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8626,7 +8626,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 43398-2025</t>
+          <t>A 6283-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8640,10 +8640,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45911</v>
+        <v>44965</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 17528-2024</t>
+          <t>A 1883-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8713,10 +8713,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45415</v>
+        <v>44939</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3.6</v>
+        <v>1.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8772,7 +8772,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 52922-2024</t>
+          <t>A 45991-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8786,10 +8786,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45610</v>
+        <v>45924</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.2</v>
+        <v>4.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8845,7 +8845,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 7228-2025</t>
+          <t>A 45935-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8859,10 +8859,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45702</v>
+        <v>45923</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8918,7 +8918,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 44020-2025</t>
+          <t>A 45861-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8932,10 +8932,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45915</v>
+        <v>45923</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>3.1</v>
+        <v>10.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8991,7 +8991,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 44600-2025</t>
+          <t>A 3178-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9005,10 +9005,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45917</v>
+        <v>46041</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>7.2</v>
+        <v>0.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9064,7 +9064,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 28319-2025</t>
+          <t>A 46668-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9078,10 +9078,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45818</v>
+        <v>45926</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9137,7 +9137,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 44608-2025</t>
+          <t>A 46872-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9151,10 +9151,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45917</v>
+        <v>45929</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9210,7 +9210,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 44573-2025</t>
+          <t>A 32842-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9224,10 +9224,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45917</v>
+        <v>45839</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9283,7 +9283,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 63249-2025</t>
+          <t>A 3201-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9297,10 +9297,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46010</v>
+        <v>46041</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.6</v>
+        <v>3.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9356,7 +9356,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 51783-2023</t>
+          <t>A 53317-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9370,10 +9370,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45222</v>
+        <v>45614</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 28870-2025</t>
+          <t>A 43353-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9443,10 +9443,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45820</v>
+        <v>45568</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>7.9</v>
+        <v>1.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9502,7 +9502,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 45861-2025</t>
+          <t>A 10356-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9516,10 +9516,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45923</v>
+        <v>45720</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>10.2</v>
+        <v>0.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9575,7 +9575,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 45935-2025</t>
+          <t>A 23450-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9589,10 +9589,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45923</v>
+        <v>45792</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9648,7 +9648,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 45991-2025</t>
+          <t>A 49718-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9662,10 +9662,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45924</v>
+        <v>45939</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9721,7 +9721,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 39535-2024</t>
+          <t>A 11442-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9735,10 +9735,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45551</v>
+        <v>45372</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9794,7 +9794,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 46872-2025</t>
+          <t>A 36141-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9808,10 +9808,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45929</v>
+        <v>45866</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9867,7 +9867,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 7443-2023</t>
+          <t>A 26639-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9881,10 +9881,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44971</v>
+        <v>45810</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.6</v>
+        <v>5.4</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9940,7 +9940,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 46668-2025</t>
+          <t>A 15227-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9954,10 +9954,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45926</v>
+        <v>45744</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10013,7 +10013,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 10356-2025</t>
+          <t>A 36048-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10027,10 +10027,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45720</v>
+        <v>45866</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10086,7 +10086,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 32842-2025</t>
+          <t>A 5324-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10100,10 +10100,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45839</v>
+        <v>46050</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>6.1</v>
+        <v>0.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10159,7 +10159,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 17685-2024</t>
+          <t>A 43406-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10173,10 +10173,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45418</v>
+        <v>45911</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10189,7 +10189,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10232,7 +10232,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 49718-2025</t>
+          <t>A 36963-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10246,10 +10246,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45939</v>
+        <v>45874</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10262,7 +10262,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10305,7 +10305,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 23450-2025</t>
+          <t>A 334-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10319,10 +10319,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45792</v>
+        <v>44929</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10378,7 +10378,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 35605-2024</t>
+          <t>A 7117-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10392,10 +10392,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45531</v>
+        <v>46058</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10451,7 +10451,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 43406-2025</t>
+          <t>A 53232-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10465,10 +10465,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45911</v>
+        <v>45958</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10524,7 +10524,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 16656-2022</t>
+          <t>A 7125-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10538,10 +10538,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44672</v>
+        <v>46058</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10554,7 +10554,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10597,7 +10597,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 11442-2024</t>
+          <t>A 7047-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10611,10 +10611,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45372</v>
+        <v>46057</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10670,7 +10670,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 15227-2025</t>
+          <t>A 50478-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10684,10 +10684,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45744</v>
+        <v>45945</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10700,7 +10700,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10743,7 +10743,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 26639-2025</t>
+          <t>A 50482-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10757,10 +10757,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45810</v>
+        <v>45945</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>5.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10816,7 +10816,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 36141-2025</t>
+          <t>A 53307-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10830,10 +10830,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45866</v>
+        <v>45614</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10846,7 +10846,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10889,7 +10889,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 36048-2025</t>
+          <t>A 7120-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10903,10 +10903,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45866</v>
+        <v>46058</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10919,7 +10919,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10962,7 +10962,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 50478-2025</t>
+          <t>A 38653-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10976,10 +10976,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45945</v>
+        <v>45884</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10992,7 +10992,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1</v>
+        <v>5.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11035,7 +11035,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 50482-2025</t>
+          <t>A 38663-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11049,10 +11049,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45945</v>
+        <v>45884</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>8.800000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11108,7 +11108,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 53232-2025</t>
+          <t>A 56026-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11122,10 +11122,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45958</v>
+        <v>45973</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11138,7 +11138,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11181,7 +11181,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 1830-2026</t>
+          <t>A 9573-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11195,10 +11195,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46035</v>
+        <v>46071</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11211,7 +11211,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1</v>
+        <v>5.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11254,7 +11254,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 36963-2025</t>
+          <t>A 40064-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11268,10 +11268,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45874</v>
+        <v>45168</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11327,7 +11327,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 25109-2022</t>
+          <t>A 26428-2022</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11341,10 +11341,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44729</v>
+        <v>44736</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11400,7 +11400,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 1827-2026</t>
+          <t>A 8923-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11414,10 +11414,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46035</v>
+        <v>45356</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11430,7 +11430,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11473,7 +11473,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 52471-2023</t>
+          <t>A 59808-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11487,10 +11487,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45225</v>
+        <v>45992</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11503,7 +11503,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11546,7 +11546,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 53307-2024</t>
+          <t>A 25109-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11560,10 +11560,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45614</v>
+        <v>44729</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11576,7 +11576,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11619,7 +11619,7 @@
     <row r="139" ht="15" customHeight=